--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,9 +413,385 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Handle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Variant Command</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Variant SKU</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Variant Barcode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variant Price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Variant Compare At Price</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Variant Cost</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Variant Weight</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Variant Weight Unit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Tracker</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Policy</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Variant Inventory Qty</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Variant Fulfillment Service</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Variant Requires Shipping</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Variant Taxable</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Variant Image</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Google Shopping / MPN</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Google Shopping / Condition</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.sku [single_line_text_field]</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.produktinfo [multi_line_text_field]</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Variant Metafield: custom.variantbilleder [list.single_line_text_field]</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Option1 Name</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Option1 Value</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Option2 Name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Option2 Value</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Option3 Name</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Option3 Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>spisebordssaet-til-haven-5-dele-massivt-teaktrae-2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3385964</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8721288759917</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2619</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3499</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1540</v>
+      </c>
+      <c r="H2" t="n">
+        <v>27900</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>63</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759917_wbg-fr_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3385964</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3385964</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette eksklusive havemøbelset emmer af moderne stil og kombinerer form og funktion, så det forbedrer ethvert udendørs rum. Det er perfekt til dem, der elsker minimalistisk design, og passer ind i enhver have eller terrasse. Den varme brune farve spiller godt sammen med naturen og skaber et hyggeligt sted til samvær eller stille øjeblikke. De smukke mønstre i akacietræ tilføjer et unikt præg, som garanteret vil sætte gang i snakken.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Fuld akaciekonstruktion&lt;/b&gt; Hele sættet er lavet af massivt akacietræ, som er kendt for at være super holdbart og modstandsdygtigt over for vejret. Den tætte åre og solidt byggeri klarer de skiftende årstider, så du får en siddeplads, der holder. Den taktile overflade giver et naturligt look og tilføjer en varm følelse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Elegant design&lt;/b&gt; Bordet og stolene har en smuk bagside, der gør, at de ser godt ud fra alle vinkler. Den slanke silhuet rammer essensen af moderne stil og elegance. Denne opmærksomhed på detaljerne sikrer, at sættet forbliver et stilfuldt indslag i enhver have.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Behagelige armlæn&lt;/b&gt; Stolene har armlæn i massivt akacietræ, som både er komfortable og passer godt ind i designet. De giver støtte til brugerne og gør det nemt at slappe af under måltider og samtaler.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse&lt;/b&gt; Det kræver ikke meget vedligeholdelse for at holde sættet flot. Tør overfladen af med en klud for at undgå støv og bevare dens naturlige skønhed. Denne enkle pleje sikrer, at træets luksuriøse udstråling forbliver intakt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem samling&lt;/b&gt; Sættet er nemt at samle med to personer og en skruetrækker. Den hurtige opsætning gør, at du hurtigt kan nyde dit nye spiseområde uden behov for specielle værktøjer eller færdigheder. Alle nødvendige dele og instruktioner er inkluderet for din bekvemmelighed.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Brun&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Pladser&lt;/li&gt;&lt;li&gt;Maks. vægt: 220 kg&lt;/li&gt;&lt;li&gt;Pladser: 2&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Havestol: 46 x 45 x 89 cm (LxWxH)&lt;/li&gt;&lt;li&gt;1 x Havetabel: 85 x 85 x 76 cm (LxWxH)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759917_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721288759917_wbg-fr_en_px16_2.jpg, https://vdxl.im/8721288759917_wbg-fr_en_px16_3.jpg, https://vdxl.im/8721288759917_wbg-to_en_px16_1.jpg, https://vdxl.im/8721288759917_wbg-siz_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Rund</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Med armlæn</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>spisebordssaet-til-haven-5-dele-massivt-teaktrae-2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3385965</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8721288759924</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2319</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3099</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1362</v>
+      </c>
+      <c r="H3" t="n">
+        <v>28900</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>200</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759924_mo-im_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3385965</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3385965</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette eksklusive havemøbelset emmer af moderne stil og kombinerer form og funktion, så det forbedrer ethvert udendørs rum. Det er perfekt til dem, der elsker minimalistisk design, og passer ind i enhver have eller terrasse. Den varme brune farve spiller godt sammen med naturen og skaber et hyggeligt sted til samvær eller stille øjeblikke. De smukke mønstre i akacietræ tilføjer et unikt præg, som garanteret vil sætte gang i snakken.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Fuld akaciekonstruktion&lt;/b&gt; Hele sættet er lavet af massivt akacietræ, som er kendt for at være super holdbart og modstandsdygtigt over for vejret. Den tætte åre og solidt byggeri klarer de skiftende årstider, så du får en siddeplads, der holder. Den taktile overflade giver et naturligt look og tilføjer en varm følelse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Elegant design&lt;/b&gt; Bordet og stolene har en smuk bagside, der gør, at de ser godt ud fra alle vinkler. Den slanke silhuet rammer essensen af moderne stil og elegance. Denne opmærksomhed på detaljerne sikrer, at sættet forbliver et stilfuldt indslag i enhver have.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Behagelige armlæn&lt;/b&gt; Stolene har armlæn i massivt akacietræ, som både er komfortable og passer godt ind i designet. De giver støtte til brugerne og gør det nemt at slappe af under måltider og samtaler.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse&lt;/b&gt; Det kræver ikke meget vedligeholdelse for at holde sættet flot. Tør overfladen af med en klud for at undgå støv og bevare dens naturlige skønhed. Denne enkle pleje sikrer, at træets luksuriøse udstråling forbliver intakt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem samling&lt;/b&gt; Sættet er nemt at samle med to personer og en skruetrækker. Den hurtige opsætning gør, at du hurtigt kan nyde dit nye spiseområde uden behov for specielle værktøjer eller færdigheder. Alle nødvendige dele og instruktioner er inkluderet for din bekvemmelighed.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Brun&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Pladser&lt;/li&gt;&lt;li&gt;Maks. vægt: 220 kg&lt;/li&gt;&lt;li&gt;Pladser: 2&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Havestol: 46 x 45 x 89 cm (LxWxH)&lt;/li&gt;&lt;li&gt;1 x Havetabel: 85 x 85 x 76 cm (LxWxH)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759924_mo-im_en_px16_1.jpg, https://vdxl.im/8721288759924_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288759924_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288759924_mo-im_en_px16_2.jpg, https://vdxl.im/8721288759924_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288759924_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288759924_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721288759924_wbg-to_en_px16_1.jpg, https://vdxl.im/8721288759924_detail_en_px16_1.jpg, https://vdxl.im/8721288759924_wbg-fu_en_px16_1.jpg, https://vdxl.im/8721288759924_wbg-fu_en_px16_2.jpg, https://vdxl.im/8721288759924_wbg-siz_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ottekantet</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Med armlæn</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8-delt-havemobelsaet-med-puder-gra-poly-rattan-akacia</t>
+          <t>skuffeskab-med-skrivebordsplade-moss-massivt-fyr-gyldenbrun</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3349921</t>
+          <t>42032404</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8721158230355</t>
+          <t>8721364737556</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5679</v>
+        <v>1409</v>
       </c>
       <c r="F2" t="n">
-        <v>7579</v>
+        <v>1879</v>
       </c>
       <c r="G2" t="n">
-        <v>3338</v>
+        <v>828</v>
       </c>
       <c r="H2" t="n">
-        <v>75400</v>
+        <v>22390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158230355_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364737556_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3349921</t>
+          <t>42032404</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3349921</t>
+          <t>42032404</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette elegante Havemøbel Sæt er et fremragende supplement til ethvert udendørs miljø, der legemliggør et sofistikeret design præget af glatte linjer og en minimalistisk tilgang. Dette sæts moderne æstetik integreres problemfrit med forskellige havestile, hvilket giver en funktionel løsning til udendørs spisning eller afslappede sammenkomster. Dets stilfulde og holdbare designelementer sikrer, at det forbliver visuelt tiltalende, mens det tilbyder praktisk funktionalitet til afslapning og underholdning.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Elegant Poly Rattan Design&lt;/b&gt; Den primære konstruktion af sættet består af poly rattan, kendt for sin UV-modstand, hvilket sikrer både holdbarhed og stil gennem forskellige sæsoner. Dette materiale giver et raffineret udseende og kombineres godt med moderne haveæstetik, hvilket skaber en hyggelig og stilfuld atmosfære til udendørs spisning og interaktion.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidigt Akacietræsoverflade&lt;/b&gt; Dette havemøbel sæt inkluderer overflader lavet af solidt akacietræ, hvilket øger det visuelle appeller med en naturlig finish. Træet modstår vejrfaktorer og tilføjer et strejf af rustik charme til det moderne design, så du kan afholde elegante udendørs middage eller afslappede sommerbruncher med lethed og elegance.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pulverlakeret Stål Stabilitet&lt;/b&gt; Støttende strukturen, pulverlakeret stål tilbyder robusthed og stabilitet. Coatingprocessen giver et ekstra lag beskyttelse mod  og slid, hvilket sikrer, at strukturen bevarer sin integritet og udseende over tid, mens den er et pålideligt møbel til daglig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Justerbar Modulær Konfiguration&lt;/b&gt; Med et modulært design kan dette sæt omkonfigureres til at passe til forskellige pladsbegrænsninger eller personlige præferencer. Med justerbare fødder kan du sikre, at komponenterne står helt lige på ujævnt terræn, og fanger den alsidighed, der er nødvendig for forskellige have-omgivelser.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Lav Vedligeholdelse og Holdbarhed&lt;/b&gt; Det er enkelt at passe på dette havemøbel sæt med anbefalede beskyttelsesforanstaltninger. Dæk det til, når det ikke er i brug, for at bevare kvaliteten. Denne proaktive tilgang sikrer langsigtet glæde, og vedligeholder det som et centralt møbel i dit udendørs boligområde.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort og cream&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, stål og massivt akacietræ&lt;/li&gt;&lt;li&gt;Slutte: Mat&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 55 x 73 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 36,7 kg&lt;/li&gt;&lt;li&gt;Modulær&lt;/li&gt;&lt;li&gt;Justerbare fødder&lt;/li&gt;&lt;li&gt;Siddepladser: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædepude aftagelig: Lynlåslukning&lt;/li&gt;&lt;li&gt;Rammemateriale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Med 7 puder&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;4 x Sidesofa med opbevaringsfunktion&lt;/li&gt;&lt;li&gt;3 x Midtersæde med opbevaringsfunktion&lt;/li&gt;&lt;li&gt;1 x Havebord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Få et moderne touch med dette praktiske rulleskab med skrivebord, der er designet til at opfylde mange behov. Det enkle og funktionelle design gør det til den perfekte tilføjelse til ethvert hjem eller kontor. Dette stilfulde møbel bliver en uundgåelig hjælper for dem, der har brug for effektiv organisering og arbejdsplads. Den glatte rektangulære form sammen med den naturlige skønhed af massivt fyrretræ giver en moderne atmosfære, der løfter ethvert hjem eller arbejdsplads.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Moderne enkelhed:&lt;/b&gt; Rulleskabet med skrivebord er designet med fokus på enkelhed og funktionalitet. De rene linjer og manglen på dekor gør det til en attraktiv samt praktisk tilføjelse til ethvert rum. Det moderne look passer perfekt ind i nutidig indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Robust materiale:&lt;/b&gt; Skabet er lavet af massivt fyrretræ, som sikrer lang levetid og stabilitet. Det robuste materiale holder længe, selv med daglig brug, og gør det til en troværdig løsning til hjemmekontorer eller soveværelser.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Integreret design:&lt;/b&gt; Med et sammenfoldeligt skrivebord giver dette 2-i-1 design mulighed for pladsbesparelse, når det ikke er i brug. Uanset om det bruges som skrivebord eller opbevaringsskab, muliggør det funktionalitet og effektivitet for dem, der vil udnytte deres kvadratmeter bedst.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Praktiske funktioner:&lt;/b&gt; Skabet er let at flytte takket være de monterede hjul. Det gør det nemt at ændre indretningen, hvilket forbedrer rummets fleksibilitet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Unik opbevaringsløsning:&lt;/b&gt; Med minimalistiske greb får du nem adgang til opbevaringen uden at gå på kompromis med det ryddelige udseende. Grebene er placeret strategisk for at gøre det nemt at bruge. &lt;ul&gt;&lt;li&gt;Farve: Klar lak&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 105,5 x 39 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 7 skuffer&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 7&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Rulleskab med skrivebord&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158230355_mo-im_en_hd_1.jpg, https://vdxl.im/8721158230355_wbg-an-m_en_hd_4.jpg, https://vdxl.im/8721158230355_mo-im_en_hd_2.jpg, https://vdxl.im/8721158230355_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158230355_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158230355_wbg-an_en_hd_3.jpg, https://vdxl.im/8721158230355_detail_en_hd_1.jpg, https://vdxl.im/8721158230355_detail_en_hd_2.jpg, https://vdxl.im/8721158230355_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158230355_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158230355_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158230355_wbg-siz_en_hd_3.jpg, https://vdxl.im/8721158230355_wbg-siz-si_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364737556_mo-im_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364737556_mo-im_en_px16_2.jpg, https://vdxl.im/8721364737556_wbg-an_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-si_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-ba_en_px16_1.jpg, https://vdxl.im/8721364737556_detail_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-fu_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Sort og cremefarvet</t>
+          <t>Brun</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -667,7 +667,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gamingstol-med-fodstotte-kunstlaeder</t>
+          <t>skuffeskab-moss-massivt-fyrretrae</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -677,25 +677,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3143704</t>
+          <t>42032402</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8720287229131</t>
+          <t>8721364737532</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>979</v>
+        <v>1169</v>
       </c>
       <c r="F3" t="n">
-        <v>1309</v>
+        <v>1559</v>
       </c>
       <c r="G3" t="n">
-        <v>575</v>
+        <v>685</v>
       </c>
       <c r="H3" t="n">
-        <v>16600</v>
+        <v>18040</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -732,12 +732,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720287229131_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364737532_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3143704</t>
+          <t>42032402</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3143704</t>
+          <t>42032402</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd at sidde i denne unikke gamingstol, og opgradér din spiloplevelse med komfort!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Justerbart ryglæn og højde: Den er særligt designet med en lænefunktion, så du kan justere ryglænet og fodstøtten efter behov. Brug håndtaget til at justere sædehøjden.&lt;/li&gt;&lt;li&gt;Praktisk design: Det 360 graders drejelige design giver større bevægelsesfrihed. Derudover er det nemt at bevæge stolen rundt med de rullende hjul.&lt;/li&gt;&lt;li&gt;Robust og stabilt stel: Stellet i metal og krydsfiner sikrer robusthed og stabilitet&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort og hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75 % PVC, 5 % bomuld, 20 % polyester), metal, krydsfiner&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Produktmål: 67 x 58 x (118-128) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Liggemål: 67 x 127 x (103-113) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 37 x 41,5 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra gulvet: 40,5-50 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde fra jorden: 65-74,5 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde: 24,5 cm&lt;/li&gt;&lt;/ul&gt; Vær opmærksom på risikoen for åben ild og andre varmekilder i nærheden af ​​produktet. Maks. 110 kg pr. sæde. Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan medføre skader på produktet og potentiel risiko for brand.</t>
+          <t>&lt;p&gt;Dette moderne rulleskab med skuffer er en minimalistisk opbevaringsløsning, der let passer ind i enhver moderne bolig eller kontor. Det har et stilrent design med rene linjer og er let, hvilket gør det til et både fint og funktionelt møbel. Perfekt til at holde orden, giver dette skab en smart måde at opbevare personlige ting, papirer og meget mere, og balancerer form med funktion.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Kvalitetsmaterialer:&lt;/b&gt; Dette skab er lavet af massivt fyrretræ, så det er ikke bare flot, men også robust, hvilket sikrer lang holdbarhed i dit hjem. Den naturlige åre i træet giver en unik stil og tilfører en naturlig charme til indretningen.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Nem mobilitet:&lt;/b&gt; Med fire hjul kan skabet flyttes rundt uden besvær, hvilket gør det let at tilpasse indretningen. Det er ideelt til rum, hvor der er brug for fleksibilitet.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle skuffer:&lt;/b&gt; Skabet har flere skuffer med kantgreb, hvilket gør det nemt at få fat i tingene uden unødvendige fremspring, og giver et stilrent udseende. Det hjælper med at gemme rod væk og holder rummet pænt.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Simpel samling:&lt;/b&gt; Du skal bruge to personer og en skruetrækker for at samle det, hvilket gør det til en ligetil opgave. Det sikrer, at opsætningen er nem og passer til det moderne, brugervenlige design.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Indendørs brug:&lt;/b&gt; Passer perfekt til både hjemmet og kontoret, trives dette skab i stuer, soveværelser eller arbejdspladser, og giver en smart, effektiv opbevaringsløsning.&lt;/li&gt; &lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Klar lak&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 34 x 39 x 103 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 8 skuffer&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 8&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Rulleskab med skuffer&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720287229131_m_en_hd_1.jpg, https://vdxl.im/8720287229131_a_en_hd_1.jpg, https://vdxl.im/8720287229131_g_en_hd_1.jpg, https://vdxl.im/8720287229131_g_en_hd_2.jpg, https://vdxl.im/8720287229131_g_en_hd_3.jpg, https://vdxl.im/8720287229131_g_en_hd_4.jpg, https://vdxl.im/8720287229131_g_en_hd_5.jpg, https://vdxl.im/8720287229131_g_en_hd_6.jpg, https://vdxl.im/8720287229131_g_en_hd_7.jpg, https://vdxl.im/8720287229131_g_en_hd_8.jpg, https://vdxl.im/8720287229131_g_en_hd_9.jpg, https://vdxl.im/8720287229131_g_en_hd_10.jpg, https://vdxl.im/8720287229131_g_en_hd_11.jpg, https://vdxl.im/8720287229131_g_en_hd_12.jpg, https://vdxl.im/8720287229131_g_en_hd_13.jpg</t>
+          <t>https://vdxl.im/8721364737532_mo-im_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364737532_mo-im_en_px16_2.jpg, https://vdxl.im/8721364737532_wbg-an_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-si_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-ba_en_px16_1.jpg, https://vdxl.im/8721364737532_detail_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Sort og hvid</t>
+          <t>Brun</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Størrelse</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Med fodskammel</t>
+          <t>34 x 39 x 103 cm</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -786,7 +786,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gamingstol-med-fodstotte-kunstlaeder</t>
+          <t>skuffeskab-moss-massivt-fyrretrae-1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -796,25 +796,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3143705</t>
+          <t>4015782</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8720287229148</t>
+          <t>8721158359674</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>999</v>
+        <v>709</v>
       </c>
       <c r="F4" t="n">
-        <v>1339</v>
+        <v>949</v>
       </c>
       <c r="G4" t="n">
-        <v>587</v>
+        <v>415</v>
       </c>
       <c r="H4" t="n">
-        <v>16600</v>
+        <v>12000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>200</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720287229148_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158359674_a_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3143705</t>
+          <t>4015782</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>3143705</t>
+          <t>4015782</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd at sidde i denne unikke gamingstol, og opgradér din spiloplevelse med komfort!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Justerbart ryglæn og højde: Den er særligt designet med en lænefunktion, så du kan justere ryglænet og fodstøtten efter behov. Brug håndtaget til at justere sædehøjden.&lt;/li&gt;&lt;li&gt;Praktisk design: Det 360 graders drejelige design giver større bevægelsesfrihed. Derudover er det nemt at bevæge stolen rundt med de rullende hjul.&lt;/li&gt;&lt;li&gt;Robust og stabilt stel: Stellet i metal og krydsfiner sikrer robusthed og stabilitet&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort og orange&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75 % PVC, 5 % bomuld, 20 % polyester), metal, krydsfiner&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Produktmål: 67 x 58 x (118-128) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Liggemål: 67 x 127 x (103-113) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 37 x 41,5 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra gulvet: 40,5-50 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde fra jorden: 65-74,5 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde: 24,5 cm&lt;/li&gt;&lt;/ul&gt; Vær opmærksom på risikoen for åben ild og andre varmekilder i nærheden af ​​produktet. Maks. 110 kg pr. sæde. Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan medføre skader på produktet og potentiel risiko for brand.</t>
+          <t>&lt;p&gt;Dette skuffeskab hjælper dig med at holde dine ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Fleksible hjul: Hjulene gør det hurtigt og nemt at flytte rundt på skuffeskabet.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Arkivskabet giver rigelig med plads til at opbevare eller sortere dokumenter, bøger eller mapper. Det kan placeres under dit skrivebord for at få det meste ud af gulvpladsen. Håndtagene gør det nemt at trække hver skuffe ud, så du kan få fat i de ting, du skal bruge.&lt;/li&gt;&lt;li&gt;Massivt fyrretræ: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har lige åremønstre, og knuderne giver materialet sit karakteristiske, rustikke udseende.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Skuffeskabet har et enkelt design, så det passer godt ind i ethvert rum. Det er et praktisk opbevaringsmøbel, der kan bruges i stuen, soveværelset, køkkenet, garagen, på kontoret, i hobbyværelset mv.&lt;/li&gt;&lt;li&gt;Nem rengøring: Kontorskabet har en glat overfalde, som er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ, konstrueret træ, plastik&lt;/li&gt;&lt;li&gt;Mål: 34 x 39 x 65,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Udvendige mål, skuffe: 27,5 x 34 x 9 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Indvendige mål, skuffe: 26 x 33,5 x 7 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 skuffer&lt;/li&gt;&lt;li&gt;Sortiment: MOSS&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720287229148_m_en_hd_1.jpg, https://vdxl.im/8720287229148_a_en_hd_1.jpg, https://vdxl.im/8720287229148_g_en_hd_1.jpg, https://vdxl.im/8720287229148_g_en_hd_2.jpg, https://vdxl.im/8720287229148_g_en_hd_3.jpg, https://vdxl.im/8720287229148_g_en_hd_4.jpg, https://vdxl.im/8720287229148_g_en_hd_5.jpg, https://vdxl.im/8720287229148_g_en_hd_6.jpg, https://vdxl.im/8720287229148_g_en_hd_7.jpg, https://vdxl.im/8720287229148_g_en_hd_8.jpg, https://vdxl.im/8720287229148_g_en_hd_9.jpg, https://vdxl.im/8720287229148_g_en_hd_10.jpg, https://vdxl.im/8720287229148_g_en_hd_11.jpg, https://vdxl.im/8720287229148_g_en_hd_12.jpg, https://vdxl.im/8720287229148_g_en_hd_13.jpg</t>
+          <t>https://vdxl.im/8721158359674_a_en_hd_1.jpg, https://vdxl.im/8721158359674_g_en_hd_1.jpg, https://vdxl.im/8721158359674_g_en_hd_2.jpg, https://vdxl.im/8721158359674_g_en_hd_3.jpg, https://vdxl.im/8721158359674_g_en_hd_4.jpg, https://vdxl.im/8721158359674_g_en_hd_5.jpg, https://vdxl.im/8721158359674_g_en_hd_6.jpg, https://vdxl.im/8721158359674_g_en_hd_7.jpg, https://vdxl.im/8721158359674_g_en_hd_8.jpg, https://vdxl.im/8721158359674_g_en_hd_9.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sort og orange</t>
+          <t>Sort</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Størrelse</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Med fodskammel</t>
+          <t>34 x 39 x 65,5 cm</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -905,7 +905,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gamingstol-med-fodstotte-kunstlaeder</t>
+          <t>skuffeskab-moss-massivt-fyrretrae-1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -915,25 +915,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3143706</t>
+          <t>42032400</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8720287229155</t>
+          <t>8721364737518</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>979</v>
+        <v>759</v>
       </c>
       <c r="F5" t="n">
-        <v>1309</v>
+        <v>1019</v>
       </c>
       <c r="G5" t="n">
-        <v>574</v>
+        <v>447</v>
       </c>
       <c r="H5" t="n">
-        <v>16600</v>
+        <v>12160</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>23</v>
+        <v>195</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -970,12 +970,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720287229155_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364737518_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3143706</t>
+          <t>42032400</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>3143706</t>
+          <t>42032400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd at sidde i denne unikke gamingstol, og opgradér din spiloplevelse med komfort!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Justerbart ryglæn og højde: Den er særligt designet med en lænefunktion, så du kan justere ryglænet og fodstøtten efter behov. Brug håndtaget til at justere sædehøjden.&lt;/li&gt;&lt;li&gt;Praktisk design: Det 360 graders drejelige design giver større bevægelsesfrihed. Derudover er det nemt at bevæge stolen rundt med de rullende hjul.&lt;/li&gt;&lt;li&gt;Robust og stabilt stel: Stellet i metal og krydsfiner sikrer robusthed og stabilitet&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: sort og Vinrød&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75 % PVC, 5 % bomuld, 20 % polyester), metal, krydsfiner&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Produktmål: 67 x 58 x (118-128) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Liggemål: 67 x 127 x (103-113) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 37 x 41,5 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra gulvet: 40,5-50 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde fra jorden: 65-74,5 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde: 24,5 cm&lt;/li&gt;&lt;/ul&gt; Vær opmærksom på risikoen for åben ild og andre varmekilder i nærheden af ​​produktet. Maks. 110 kg pr. sæde. Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan medføre skader på produktet og potentiel risiko for brand.</t>
+          <t>&lt;p&gt;Dette moderne rulleskab med skuffer giver en stilren og praktisk løsning til opbevaring i dit hjem eller kontor. Med sit moderne design og rene linjer passer det perfekt ind i forskellige rum. Uanset om du har brug for at rydde op i stuen, soveværelset eller dit hjemmekontor, giver dette skab god plads, så du kan holde det pænt og organiseret.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Solidt fyrretræ:&lt;/b&gt; Dette skab er lavet af kvalitetsfyrretræ, som sikrer, at det holder i lang tid. Den robuste konstruktion kan klare hverdagens slid uden at miste stil eller integritet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Kantgreb:&lt;/b&gt; Med smukke kantgreb har dette skab et minimalistisk look og praktisk funktionalitet. Grebene er designet til at give et godt tag og et strømlinet udseende, der passer perfekt til moderne indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Fleksible hjul:&lt;/b&gt; De låsbare hjul gør det nemt at flytte rundt uden problemer. Det gør det lettere at omplacere skabet i stuen, soveværelset, eller kontoret og øger dets funktionalitet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Rummelige skuffer:&lt;/b&gt; Med flere skuffer tilbyder dette rulleskab masser af opbevaringsplads til alt fra filer og kontorartikler til tøj og accessories. Det hjælper med at holde orden ved at give specifikke pladser til forskellige ting.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem samling:&lt;/b&gt; Det kræver to personer og en skruetrækker, men samlingen er enkel. Dette gør det nemt for de fleste at samle det hurtigt, uden brug for professionel hjælp.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Klar lak&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 34 x 39 x 65,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 6 skuffer&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 6&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Rulleskab med skuffer&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720287229155_m_en_hd_1.jpg, https://vdxl.im/8720287229155_a_en_hd_1.jpg, https://vdxl.im/8720287229155_g_en_hd_1.jpg, https://vdxl.im/8720287229155_g_en_hd_2.jpg, https://vdxl.im/8720287229155_g_en_hd_3.jpg, https://vdxl.im/8720287229155_g_en_hd_4.jpg, https://vdxl.im/8720287229155_g_en_hd_5.jpg, https://vdxl.im/8720287229155_g_en_hd_6.jpg, https://vdxl.im/8720287229155_g_en_hd_7.jpg, https://vdxl.im/8720287229155_g_en_hd_8.jpg, https://vdxl.im/8720287229155_g_en_hd_9.jpg, https://vdxl.im/8720287229155_g_en_hd_10.jpg, https://vdxl.im/8720287229155_g_en_hd_11.jpg, https://vdxl.im/8720287229155_g_en_hd_12.jpg, https://vdxl.im/8720287229155_g_en_hd_13.jpg</t>
+          <t>https://vdxl.im/8721364737518_mo-im_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364737518_mo-im_en_px16_2.jpg, https://vdxl.im/8721364737518_wbg-an_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-si_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-ba_en_px16_1.jpg, https://vdxl.im/8721364737518_detail_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1005,378 +1005,21 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Sort og vinrød</t>
+          <t>Brun</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Størrelse</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Med fodskammel</t>
+          <t>34 x 39 x 65,5 cm</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>gamingstol-med-fodstotte-kunstlaeder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3143709</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8720287229186</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>989</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1319</v>
-      </c>
-      <c r="G6" t="n">
-        <v>582</v>
-      </c>
-      <c r="H6" t="n">
-        <v>16600</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>61</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720287229186_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>3143709</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>3143709</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Nyd at sidde i denne unikke gamingstol, og opgradér din spiloplevelse med komfort!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Justerbart ryglæn og højde: Den er særligt designet med en lænefunktion, så du kan justere ryglænet og fodstøtten efter behov. Brug håndtaget til at justere sædehøjden.&lt;/li&gt;&lt;li&gt;Praktisk design: Det 360 graders drejelige design giver større bevægelsesfrihed. Derudover er det nemt at bevæge stolen rundt med de rullende hjul.&lt;/li&gt;&lt;li&gt;Robust og stabilt stel: Stellet i metal og krydsfiner sikrer robusthed og stabilitet&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75 % PVC, 5 % bomuld, 20 % polyester), metal, krydsfiner&lt;/li&gt;&lt;li&gt;Materiale, fyld: Skum&lt;/li&gt;&lt;li&gt;Produktmål: 67 x 58 x (118-128) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Liggemål: 67 x 127 x (103-113) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 37 x 41,5 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra gulvet: 40,5-50 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde fra jorden: 65-74,5 cm&lt;/li&gt;&lt;li&gt;Armlænshøjde: 24,5 cm&lt;/li&gt;&lt;/ul&gt; Vær opmærksom på risikoen for åben ild og andre varmekilder i nærheden af ​​produktet. Maks. 110 kg pr. sæde. Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan medføre skader på produktet og potentiel risiko for brand.</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720287229186_m_en_hd_1.jpg, https://vdxl.im/8720287229186_a_en_hd_1.jpg, https://vdxl.im/8720287229186_g_en_hd_1.jpg, https://vdxl.im/8720287229186_g_en_hd_2.jpg, https://vdxl.im/8720287229186_g_en_hd_3.jpg, https://vdxl.im/8720287229186_g_en_hd_4.jpg, https://vdxl.im/8720287229186_g_en_hd_5.jpg, https://vdxl.im/8720287229186_g_en_hd_6.jpg, https://vdxl.im/8720287229186_g_en_hd_7.jpg, https://vdxl.im/8720287229186_g_en_hd_8.jpg, https://vdxl.im/8720287229186_g_en_hd_9.jpg, https://vdxl.im/8720287229186_g_en_hd_10.jpg, https://vdxl.im/8720287229186_g_en_hd_11.jpg, https://vdxl.im/8720287229186_g_en_hd_12.jpg, https://vdxl.im/8720287229186_g_en_hd_13.jpg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hvid og sort</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Med fodskammel</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>kontorstol-flojl</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>20569</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8720286663219</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1729</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2309</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1017</v>
-      </c>
-      <c r="H7" t="n">
-        <v>18800</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>21</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720286663219_a_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>20569</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>20569</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Denne kontorstol med lænefunktion er et glimrende supplement til dit kontor. Den er ergonomisk designet til at give den bedste komfort i løbet af en travl arbejdsdag.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Stolen har et højt ryglæn, buede armlæn og et tykt polstret sæde, så den giver komfort under lange arbejdssessioner. Det højdejusterbare design giver dig mulighed for at tilpasse stolen efter skrivebordets højde, så du opnår komfort og korrekt rygsøjleholdning. Denne lænestol er forsynet med nylonhjul, så du kan nemt flytte rundt på den.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), metal&lt;/li&gt;&lt;li&gt;Produktmål: 67 x 71 x (110-119) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædebredde: 51 cm&lt;/li&gt;&lt;li&gt;Sædedybde: 50 cm&lt;/li&gt;&lt;li&gt;Højde, ryglæn: 69 cm&lt;/li&gt;&lt;li&gt;Sædehøjde fra gulvet: 47-57 cm&lt;/li&gt;&lt;li&gt;Højdejusterbar&lt;/li&gt;&lt;li&gt;Gasløftmekanisme&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 110 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Maks. 110 kg per sæde. Vær opmærksom på risikoen ved åben ild og andre varmekilder i nærheden af produktet.</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720286663219_a_en_hd_1.jpg, https://vdxl.im/8720286663219_g_en_hd_1.jpg, https://vdxl.im/8720286663219_g_en_hd_2.jpg, https://vdxl.im/8720286663219_g_en_hd_3.jpg, https://vdxl.im/8720286663219_g_en_hd_4.jpg, https://vdxl.im/8720286663219_g_en_hd_5.jpg, https://vdxl.im/8720286663219_g_en_hd_6.jpg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>uden massagefunktion</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Mørkegrå</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>kontorstol-flojl</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>20570</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8720286663226</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1729</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2309</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1017</v>
-      </c>
-      <c r="H8" t="n">
-        <v>18800</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>17</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720286663226_a_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>20570</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>20570</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Denne kontorstol med lænefunktion er et glimrende supplement til dit kontor. Den er ergonomisk designet til at give den bedste komfort i løbet af en travl arbejdsdag.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Stolen har et højt ryglæn, buede armlæn og et tykt polstret sæde, så den giver komfort under lange arbejdssessioner. Det højdejusterbare design giver dig mulighed for at tilpasse stolen efter skrivebordets højde, så du opnår komfort og korrekt rygsøjleholdning. Denne lænestol er forsynet med nylonhjul, så du kan nemt flytte rundt på den.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Fløjl (100 % polyester), metal&lt;/li&gt;&lt;li&gt;Produktmål: 67 x 71 x (110-119) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædebredde: 51 cm&lt;/li&gt;&lt;li&gt;Sædedybde: 50 cm&lt;/li&gt;&lt;li&gt;Højde, ryglæn: 69 cm&lt;/li&gt;&lt;li&gt;Sædehøjde fra gulvet: 47-57 cm&lt;/li&gt;&lt;li&gt;Højdejusterbar&lt;/li&gt;&lt;li&gt;Gasløftmekanisme&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 110 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Maks. 110 kg per sæde. Vær opmærksom på risikoen ved åben ild og andre varmekilder i nærheden af produktet.</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720286663226_a_en_hd_1.jpg, https://vdxl.im/8720286663226_g_en_hd_1.jpg, https://vdxl.im/8720286663226_g_en_hd_2.jpg, https://vdxl.im/8720286663226_g_en_hd_3.jpg, https://vdxl.im/8720286663226_g_en_hd_4.jpg, https://vdxl.im/8720286663226_g_en_hd_5.jpg, https://vdxl.im/8720286663226_g_en_hd_6.jpg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>uden massagefunktion</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Lysegrå</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>skuffeskab-med-skrivebordsplade-moss-massivt-fyr-gyldenbrun</t>
+          <t>skab-med-glaslager-68x37x68-5-cm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42032404</t>
+          <t>836492</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8721364737556</t>
+          <t>8721012214422</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1409</v>
+        <v>619</v>
       </c>
       <c r="F2" t="n">
-        <v>1879</v>
+        <v>829</v>
       </c>
       <c r="G2" t="n">
-        <v>828</v>
+        <v>360</v>
       </c>
       <c r="H2" t="n">
-        <v>22390</v>
+        <v>24780</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364737556_mo-im_en_px16_1.jpg</t>
+          <t>https://vdxl.im/8721012214422_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42032404</t>
+          <t>836492</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>42032404</t>
+          <t>836492</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få et moderne touch med dette praktiske rulleskab med skrivebord, der er designet til at opfylde mange behov. Det enkle og funktionelle design gør det til den perfekte tilføjelse til ethvert hjem eller kontor. Dette stilfulde møbel bliver en uundgåelig hjælper for dem, der har brug for effektiv organisering og arbejdsplads. Den glatte rektangulære form sammen med den naturlige skønhed af massivt fyrretræ giver en moderne atmosfære, der løfter ethvert hjem eller arbejdsplads.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Moderne enkelhed:&lt;/b&gt; Rulleskabet med skrivebord er designet med fokus på enkelhed og funktionalitet. De rene linjer og manglen på dekor gør det til en attraktiv samt praktisk tilføjelse til ethvert rum. Det moderne look passer perfekt ind i nutidig indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Robust materiale:&lt;/b&gt; Skabet er lavet af massivt fyrretræ, som sikrer lang levetid og stabilitet. Det robuste materiale holder længe, selv med daglig brug, og gør det til en troværdig løsning til hjemmekontorer eller soveværelser.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Integreret design:&lt;/b&gt; Med et sammenfoldeligt skrivebord giver dette 2-i-1 design mulighed for pladsbesparelse, når det ikke er i brug. Uanset om det bruges som skrivebord eller opbevaringsskab, muliggør det funktionalitet og effektivitet for dem, der vil udnytte deres kvadratmeter bedst.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Praktiske funktioner:&lt;/b&gt; Skabet er let at flytte takket være de monterede hjul. Det gør det nemt at ændre indretningen, hvilket forbedrer rummets fleksibilitet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Unik opbevaringsløsning:&lt;/b&gt; Med minimalistiske greb får du nem adgang til opbevaringen uden at gå på kompromis med det ryddelige udseende. Grebene er placeret strategisk for at gøre det nemt at bruge. &lt;ul&gt;&lt;li&gt;Farve: Klar lak&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 105,5 x 39 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 7 skuffer&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 7&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Rulleskab med skrivebord&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette vægskab er flot og elegant. Det er ikke bare en glimrende løsning til dine vigtige ting og pyntegenstande, men også den perfekte udsmykning til dine tomme vægge, da det forvandler dem til et sandt blikfang.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Vægskabet har masser af plads takket være rummene. De giver plads til at holde ting såsom bøger pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Alsidigt design: Du kan ophænge opbevaringsskabet på væggen i værkstedet til praktisk opbevaring af værktøjer eller andre ting og sager. Det forvandler også en tom væg til et sandt blikfang.&lt;/li&gt;&lt;li&gt;Væghængt design: Opbevaringsskabet kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Praktiske glaslåger: Hold dit rum ryddeligt ved at gemme småting bag skabets låger. Glaslågerne giver dig desuden mulighed for at se ind i vægskabet, så du kan fremvise dine ting på smuk vis.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ og glas&lt;/li&gt;&lt;li&gt;Mål: 68 x 37 x 68,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 80 kg&lt;/li&gt;&lt;li&gt; Bæreevne pr. rum: 30 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364737556_mo-im_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364737556_mo-im_en_px16_2.jpg, https://vdxl.im/8721364737556_wbg-an_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-si_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-ba_en_px16_1.jpg, https://vdxl.im/8721364737556_detail_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-fu_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364737556_wbg-siz_en_px16_1.jpg</t>
+          <t>https://vdxl.im/8721012214422_m_en_hd_1.jpg, https://vdxl.im/8721012214422_a_en_hd_1.jpg, https://vdxl.im/8721012214422_g_en_hd_1.jpg, https://vdxl.im/8721012214422_g_en_hd_2.jpg, https://vdxl.im/8721012214422_g_en_hd_3.jpg, https://vdxl.im/8721012214422_g_en_hd_4.jpg, https://vdxl.im/8721012214422_g_en_hd_5.jpg, https://vdxl.im/8721012214422_g_en_hd_6.jpg, https://vdxl.im/8721012214422_g_en_hd_7.jpg, https://vdxl.im/8721012214422_g_en_hd_8.jpg, https://vdxl.im/8721012214422_g_en_hd_9.jpg, https://vdxl.im/8721012214422_g_en_hd_10.jpg, https://vdxl.im/8721012214422_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Brun</t>
+          <t>Sonoma-eg</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -667,7 +667,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>skuffeskab-moss-massivt-fyrretrae</t>
+          <t>skab-med-glaslager-68x37x68-5-cm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -677,25 +677,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42032402</t>
+          <t>836494</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8721364737532</t>
+          <t>8721012214446</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1169</v>
+        <v>669</v>
       </c>
       <c r="F3" t="n">
-        <v>1559</v>
+        <v>899</v>
       </c>
       <c r="G3" t="n">
-        <v>685</v>
+        <v>394</v>
       </c>
       <c r="H3" t="n">
-        <v>18040</v>
+        <v>24780</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -732,12 +732,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364737532_mo-im_en_px16_1.jpg</t>
+          <t>https://vdxl.im/8721012214446_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>42032402</t>
+          <t>836494</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>42032402</t>
+          <t>836494</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette moderne rulleskab med skuffer er en minimalistisk opbevaringsløsning, der let passer ind i enhver moderne bolig eller kontor. Det har et stilrent design med rene linjer og er let, hvilket gør det til et både fint og funktionelt møbel. Perfekt til at holde orden, giver dette skab en smart måde at opbevare personlige ting, papirer og meget mere, og balancerer form med funktion.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Kvalitetsmaterialer:&lt;/b&gt; Dette skab er lavet af massivt fyrretræ, så det er ikke bare flot, men også robust, hvilket sikrer lang holdbarhed i dit hjem. Den naturlige åre i træet giver en unik stil og tilfører en naturlig charme til indretningen.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Nem mobilitet:&lt;/b&gt; Med fire hjul kan skabet flyttes rundt uden besvær, hvilket gør det let at tilpasse indretningen. Det er ideelt til rum, hvor der er brug for fleksibilitet.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle skuffer:&lt;/b&gt; Skabet har flere skuffer med kantgreb, hvilket gør det nemt at få fat i tingene uden unødvendige fremspring, og giver et stilrent udseende. Det hjælper med at gemme rod væk og holder rummet pænt.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Simpel samling:&lt;/b&gt; Du skal bruge to personer og en skruetrækker for at samle det, hvilket gør det til en ligetil opgave. Det sikrer, at opsætningen er nem og passer til det moderne, brugervenlige design.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Indendørs brug:&lt;/b&gt; Passer perfekt til både hjemmet og kontoret, trives dette skab i stuer, soveværelser eller arbejdspladser, og giver en smart, effektiv opbevaringsløsning.&lt;/li&gt; &lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Klar lak&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 34 x 39 x 103 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 8 skuffer&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 8&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Rulleskab med skuffer&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette vægskab er flot og elegant. Det er ikke bare en glimrende løsning til dine vigtige ting og pyntegenstande, men også den perfekte udsmykning til dine tomme vægge, da det forvandler dem til et sandt blikfang.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Vægskabet har masser af plads takket være rummene. De giver plads til at holde ting såsom bøger pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Alsidigt design: Du kan ophænge opbevaringsskabet på væggen i værkstedet til praktisk opbevaring af værktøjer eller andre ting og sager. Det forvandler også en tom væg til et sandt blikfang.&lt;/li&gt;&lt;li&gt;Væghængt design: Opbevaringsskabet kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Praktiske glaslåger: Hold dit rum ryddeligt ved at gemme småting bag skabets låger. Glaslågerne giver dig desuden mulighed for at se ind i vægskabet, så du kan fremvise dine ting på smuk vis.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ og glas&lt;/li&gt;&lt;li&gt;Mål: 68 x 37 x 68,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 80 kg&lt;/li&gt;&lt;li&gt; Bæreevne pr. rum: 30 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364737532_mo-im_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364737532_mo-im_en_px16_2.jpg, https://vdxl.im/8721364737532_wbg-an_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-si_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-ba_en_px16_1.jpg, https://vdxl.im/8721364737532_detail_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364737532_wbg-siz_en_px16_1.jpg</t>
+          <t>https://vdxl.im/8721012214446_m_en_hd_1.jpg, https://vdxl.im/8721012214446_a_en_hd_1.jpg, https://vdxl.im/8721012214446_g_en_hd_1.jpg, https://vdxl.im/8721012214446_g_en_hd_2.jpg, https://vdxl.im/8721012214446_g_en_hd_3.jpg, https://vdxl.im/8721012214446_g_en_hd_4.jpg, https://vdxl.im/8721012214446_g_en_hd_5.jpg, https://vdxl.im/8721012214446_g_en_hd_6.jpg, https://vdxl.im/8721012214446_g_en_hd_7.jpg, https://vdxl.im/8721012214446_g_en_hd_8.jpg, https://vdxl.im/8721012214446_g_en_hd_9.jpg, https://vdxl.im/8721012214446_g_en_hd_10.jpg, https://vdxl.im/8721012214446_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -767,26 +767,18 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Brun</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>34 x 39 x 103 cm</t>
-        </is>
-      </c>
+          <t>Røget eg</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>skuffeskab-moss-massivt-fyrretrae-1</t>
+          <t>skab-med-glaslager-68x37x68-5-cm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -796,25 +788,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4015782</t>
+          <t>836495</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8721158359674</t>
+          <t>8721012214453</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>709</v>
+        <v>769</v>
       </c>
       <c r="F4" t="n">
-        <v>949</v>
+        <v>1029</v>
       </c>
       <c r="G4" t="n">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="H4" t="n">
-        <v>12000</v>
+        <v>24880</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -832,7 +824,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>200</v>
+        <v>38</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -851,12 +843,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158359674_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721012214453_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4015782</t>
+          <t>836495</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -866,17 +858,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>4015782</t>
+          <t>836495</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette skuffeskab hjælper dig med at holde dine ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Fleksible hjul: Hjulene gør det hurtigt og nemt at flytte rundt på skuffeskabet.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Arkivskabet giver rigelig med plads til at opbevare eller sortere dokumenter, bøger eller mapper. Det kan placeres under dit skrivebord for at få det meste ud af gulvpladsen. Håndtagene gør det nemt at trække hver skuffe ud, så du kan få fat i de ting, du skal bruge.&lt;/li&gt;&lt;li&gt;Massivt fyrretræ: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har lige åremønstre, og knuderne giver materialet sit karakteristiske, rustikke udseende.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Skuffeskabet har et enkelt design, så det passer godt ind i ethvert rum. Det er et praktisk opbevaringsmøbel, der kan bruges i stuen, soveværelset, køkkenet, garagen, på kontoret, i hobbyværelset mv.&lt;/li&gt;&lt;li&gt;Nem rengøring: Kontorskabet har en glat overfalde, som er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ, konstrueret træ, plastik&lt;/li&gt;&lt;li&gt;Mål: 34 x 39 x 65,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Udvendige mål, skuffe: 27,5 x 34 x 9 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Indvendige mål, skuffe: 26 x 33,5 x 7 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 skuffer&lt;/li&gt;&lt;li&gt;Sortiment: MOSS&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette vægskab er flot og elegant. Det er ikke bare en glimrende løsning til dine vigtige ting og pyntegenstande, men også den perfekte udsmykning til dine tomme vægge, da det forvandler dem til et sandt blikfang.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Vægskabet har masser af plads takket være rummene. De giver plads til at holde ting såsom bøger pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Alsidigt design: Du kan ophænge opbevaringsskabet på væggen i værkstedet til praktisk opbevaring af værktøjer eller andre ting og sager. Det forvandler også en tom væg til et sandt blikfang.&lt;/li&gt;&lt;li&gt;Væghængt design: Opbevaringsskabet kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Praktiske glaslåger: Hold dit rum ryddeligt ved at gemme småting bag skabets låger. Glaslågerne giver dig desuden mulighed for at se ind i vægskabet, så du kan fremvise dine ting på smuk vis.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ og glas&lt;/li&gt;&lt;li&gt;Mål: 68 x 37 x 68,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 80 kg&lt;/li&gt;&lt;li&gt; Bæreevne pr. rum: 30 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158359674_a_en_hd_1.jpg, https://vdxl.im/8721158359674_g_en_hd_1.jpg, https://vdxl.im/8721158359674_g_en_hd_2.jpg, https://vdxl.im/8721158359674_g_en_hd_3.jpg, https://vdxl.im/8721158359674_g_en_hd_4.jpg, https://vdxl.im/8721158359674_g_en_hd_5.jpg, https://vdxl.im/8721158359674_g_en_hd_6.jpg, https://vdxl.im/8721158359674_g_en_hd_7.jpg, https://vdxl.im/8721158359674_g_en_hd_8.jpg, https://vdxl.im/8721158359674_g_en_hd_9.jpg</t>
+          <t>https://vdxl.im/8721012214453_m_en_hd_1.jpg, https://vdxl.im/8721012214453_a_en_hd_1.jpg, https://vdxl.im/8721012214453_g_en_hd_1.jpg, https://vdxl.im/8721012214453_g_en_hd_2.jpg, https://vdxl.im/8721012214453_g_en_hd_3.jpg, https://vdxl.im/8721012214453_g_en_hd_4.jpg, https://vdxl.im/8721012214453_g_en_hd_5.jpg, https://vdxl.im/8721012214453_g_en_hd_6.jpg, https://vdxl.im/8721012214453_g_en_hd_7.jpg, https://vdxl.im/8721012214453_g_en_hd_8.jpg, https://vdxl.im/8721012214453_g_en_hd_9.jpg, https://vdxl.im/8721012214453_g_en_hd_10.jpg, https://vdxl.im/8721012214453_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -886,26 +878,18 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>34 x 39 x 65,5 cm</t>
-        </is>
-      </c>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>skuffeskab-moss-massivt-fyrretrae-1</t>
+          <t>skab-med-glaslager-68x37x68-5-cm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -915,25 +899,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42032400</t>
+          <t>882910</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8721364737518</t>
+          <t>8721288923868</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>759</v>
+        <v>639</v>
       </c>
       <c r="F5" t="n">
-        <v>1019</v>
+        <v>859</v>
       </c>
       <c r="G5" t="n">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="H5" t="n">
-        <v>12160</v>
+        <v>22870</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -951,7 +935,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -970,12 +954,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364737518_mo-im_en_px16_1.jpg</t>
+          <t>https://vdxl.im/8721288923868_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>42032400</t>
+          <t>882910</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -985,17 +969,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>42032400</t>
+          <t>882910</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette moderne rulleskab med skuffer giver en stilren og praktisk løsning til opbevaring i dit hjem eller kontor. Med sit moderne design og rene linjer passer det perfekt ind i forskellige rum. Uanset om du har brug for at rydde op i stuen, soveværelset eller dit hjemmekontor, giver dette skab god plads, så du kan holde det pænt og organiseret.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Solidt fyrretræ:&lt;/b&gt; Dette skab er lavet af kvalitetsfyrretræ, som sikrer, at det holder i lang tid. Den robuste konstruktion kan klare hverdagens slid uden at miste stil eller integritet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Kantgreb:&lt;/b&gt; Med smukke kantgreb har dette skab et minimalistisk look og praktisk funktionalitet. Grebene er designet til at give et godt tag og et strømlinet udseende, der passer perfekt til moderne indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Fleksible hjul:&lt;/b&gt; De låsbare hjul gør det nemt at flytte rundt uden problemer. Det gør det lettere at omplacere skabet i stuen, soveværelset, eller kontoret og øger dets funktionalitet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Rummelige skuffer:&lt;/b&gt; Med flere skuffer tilbyder dette rulleskab masser af opbevaringsplads til alt fra filer og kontorartikler til tøj og accessories. Det hjælper med at holde orden ved at give specifikke pladser til forskellige ting.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem samling:&lt;/b&gt; Det kræver to personer og en skruetrækker, men samlingen er enkel. Dette gør det nemt for de fleste at samle det hurtigt, uden brug for professionel hjælp.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Klar lak&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 34 x 39 x 65,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 6 skuffer&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 6&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Rulleskab med skuffer&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette træfarvede vægskab blander moderne elegance med funktionalitet, og det er perfekt til at give ekstra opbevaringsplads i ethvert rum. Med sin slanke form og vægmonterede design tilføjer det et stilfuldt og raffineret præg til rummet, samtidig med at det tilbyder praktiske opbevaringsmuligheder. Skabet er ideelt for dem, der elsker minimalistisk design, takket være sin glatte overflade og enkle linjer, der passer ind i moderne hjem.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Bygget af konstrueret træ:&lt;/b&gt; Det træfarvede vægskab er lavet af konstrueret træ, der har en glat tekstur og er holdbart. Det blander forskellige træsorter for at skabe et stærkt og pænt materiale, så skabet er et godt valg til dit rum. Denne konstruktion sikrer, at det holder længe uden at miste sit flotte udseende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Gennemsigtige glasskabe:&lt;/b&gt; Glasskabene giver et stilrent indtryk, så du nemt kan vise dine ting og gøre rummet mere åbent. Disse døre gør det let at se, hvad der er indeni, uden at skulle åbne skabet, hvilket både er praktisk og tilføjer et moderne touch.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vægmonteret design:&lt;/b&gt; Skabet er lavet til at hænge på væggen, hvilket er perfekt til små rum, da det sparer plads. Når det hænger oppe, får du nem adgang til indholdet, og samtidig ser rummet mere åbent og organiseret ud. Det er fantastisk til både hjem og kontorer, der har brug for pladsbesparende løsninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Rum til meget opbevaring:&lt;/b&gt; Hylderne indeni giver masser af plads til forskellige ting, fra bøger til dekoration eller køkkengrej. De er enkle og effektive, og de kan rumme ting af forskellig størrelse og vægt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse:&lt;/b&gt; Det er simpelt at holde skabet pænt; du skal blot tørre det af med en tør klud. Undgå skrappe kemikalier for at bevare den glatte finish, så det ser flot ud i dit hjem, også mens det er let at rengøre.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 68 x 37 x 68,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 4  hylder&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 4&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Vægskab&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364737518_mo-im_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364737518_mo-im_en_px16_2.jpg, https://vdxl.im/8721364737518_wbg-an_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-si_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-ba_en_px16_1.jpg, https://vdxl.im/8721364737518_detail_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364737518_wbg-siz_en_px16_1.jpg</t>
+          <t>https://vdxl.im/8721288923868_mo-im_en_hd_1.jpg, https://vdxl.im/8721288923868_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288923868_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288923868_mo-im_en_hd_2.jpg, https://vdxl.im/8721288923868_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288923868_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288923868_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288923868_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288923868_detail_en_hd_1.jpg, https://vdxl.im/8721288923868_detail_en_hd_2.jpg, https://vdxl.im/8721288923868_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288923868_wbg-siz_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1005,21 +989,7044 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Brun</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>34 x 39 x 65,5 cm</t>
-        </is>
-      </c>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>skab-med-glaslager-68x37x68-5-cm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>882911</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8721288923875</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>589</v>
+      </c>
+      <c r="F6" t="n">
+        <v>789</v>
+      </c>
+      <c r="G6" t="n">
+        <v>345</v>
+      </c>
+      <c r="H6" t="n">
+        <v>22870</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>115</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288923875_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>882911</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>882911</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette træfarvede vægskab blander moderne elegance med funktionalitet, og det er perfekt til at give ekstra opbevaringsplads i ethvert rum. Med sin slanke form og vægmonterede design tilføjer det et stilfuldt og raffineret præg til rummet, samtidig med at det tilbyder praktiske opbevaringsmuligheder. Skabet er ideelt for dem, der elsker minimalistisk design, takket være sin glatte overflade og enkle linjer, der passer ind i moderne hjem.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Bygget af konstrueret træ:&lt;/b&gt; Det træfarvede vægskab er lavet af konstrueret træ, der har en glat tekstur og er holdbart. Det blander forskellige træsorter for at skabe et stærkt og pænt materiale, så skabet er et godt valg til dit rum. Denne konstruktion sikrer, at det holder længe uden at miste sit flotte udseende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Gennemsigtige glasskabe:&lt;/b&gt; Glasskabene giver et stilrent indtryk, så du nemt kan vise dine ting og gøre rummet mere åbent. Disse døre gør det let at se, hvad der er indeni, uden at skulle åbne skabet, hvilket både er praktisk og tilføjer et moderne touch.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vægmonteret design:&lt;/b&gt; Skabet er lavet til at hænge på væggen, hvilket er perfekt til små rum, da det sparer plads. Når det hænger oppe, får du nem adgang til indholdet, og samtidig ser rummet mere åbent og organiseret ud. Det er fantastisk til både hjem og kontorer, der har brug for pladsbesparende løsninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Rum til meget opbevaring:&lt;/b&gt; Hylderne indeni giver masser af plads til forskellige ting, fra bøger til dekoration eller køkkengrej. De er enkle og effektive, og de kan rumme ting af forskellig størrelse og vægt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse:&lt;/b&gt; Det er simpelt at holde skabet pænt; du skal blot tørre det af med en tør klud. Undgå skrappe kemikalier for at bevare den glatte finish, så det ser flot ud i dit hjem, også mens det er let at rengøre.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 68 x 37 x 68,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 4  hylder&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 4&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Vægskab&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288923875_mo-im_en_hd_1.jpg, https://vdxl.im/8721288923875_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288923875_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288923875_mo-im_en_hd_2.jpg, https://vdxl.im/8721288923875_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288923875_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288923875_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288923875_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288923875_detail_en_hd_1.jpg, https://vdxl.im/8721288923875_detail_en_hd_2.jpg, https://vdxl.im/8721288923875_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288923875_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>skab-med-glaslager-68x37x68-5-cm</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>882912</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8721288923882</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>609</v>
+      </c>
+      <c r="F7" t="n">
+        <v>819</v>
+      </c>
+      <c r="G7" t="n">
+        <v>356</v>
+      </c>
+      <c r="H7" t="n">
+        <v>22870</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>116</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288923882_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>882912</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>882912</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette træfarvede vægskab blander moderne elegance med funktionalitet, og det er perfekt til at give ekstra opbevaringsplads i ethvert rum. Med sin slanke form og vægmonterede design tilføjer det et stilfuldt og raffineret præg til rummet, samtidig med at det tilbyder praktiske opbevaringsmuligheder. Skabet er ideelt for dem, der elsker minimalistisk design, takket være sin glatte overflade og enkle linjer, der passer ind i moderne hjem.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Bygget af konstrueret træ:&lt;/b&gt; Det træfarvede vægskab er lavet af konstrueret træ, der har en glat tekstur og er holdbart. Det blander forskellige træsorter for at skabe et stærkt og pænt materiale, så skabet er et godt valg til dit rum. Denne konstruktion sikrer, at det holder længe uden at miste sit flotte udseende.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Gennemsigtige glasskabe:&lt;/b&gt; Glasskabene giver et stilrent indtryk, så du nemt kan vise dine ting og gøre rummet mere åbent. Disse døre gør det let at se, hvad der er indeni, uden at skulle åbne skabet, hvilket både er praktisk og tilføjer et moderne touch.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vægmonteret design:&lt;/b&gt; Skabet er lavet til at hænge på væggen, hvilket er perfekt til små rum, da det sparer plads. Når det hænger oppe, får du nem adgang til indholdet, og samtidig ser rummet mere åbent og organiseret ud. Det er fantastisk til både hjem og kontorer, der har brug for pladsbesparende løsninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Rum til meget opbevaring:&lt;/b&gt; Hylderne indeni giver masser af plads til forskellige ting, fra bøger til dekoration eller køkkengrej. De er enkle og effektive, og de kan rumme ting af forskellig størrelse og vægt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse:&lt;/b&gt; Det er simpelt at holde skabet pænt; du skal blot tørre det af med en tør klud. Undgå skrappe kemikalier for at bevare den glatte finish, så det ser flot ud i dit hjem, også mens det er let at rengøre.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 68 x 37 x 68,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 4  hylder&lt;/li&gt;&lt;li&gt;Opbevaringsnummer: 4&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Vægskab&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288923882_mo-im_en_hd_1.jpg, https://vdxl.im/8721288923882_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288923882_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288923882_mo-im_en_hd_2.jpg, https://vdxl.im/8721288923882_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288923882_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288923882_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288923882_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288923882_detail_en_hd_1.jpg, https://vdxl.im/8721288923882_detail_en_hd_2.jpg, https://vdxl.im/8721288923882_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288923882_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3337677</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8721158295149</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>669</v>
+      </c>
+      <c r="F8" t="n">
+        <v>899</v>
+      </c>
+      <c r="G8" t="n">
+        <v>391</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>19</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295149_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3337677</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3337677</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295149_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295149_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295149_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295149_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295149_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295149_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295149_detail_en_hd_1.jpg, https://vdxl.im/8721158295149_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295149_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295149_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295149_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3337705</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8721158295422</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1789</v>
+      </c>
+      <c r="G9" t="n">
+        <v>783</v>
+      </c>
+      <c r="H9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295422_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3337705</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3337705</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 200 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295422_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295422_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295422_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295422_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295422_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295422_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295422_detail_en_hd_1.jpg, https://vdxl.im/8721158295422_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295422_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295422_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295422_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>200 cm</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3337678</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8721158295156</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>669</v>
+      </c>
+      <c r="F10" t="n">
+        <v>899</v>
+      </c>
+      <c r="G10" t="n">
+        <v>389</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>42</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295156_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3337678</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3337678</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295156_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295156_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295156_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295156_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295156_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295156_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295156_detail_en_hd_1.jpg, https://vdxl.im/8721158295156_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295156_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295156_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295156_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3337685</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8721158295224</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1469</v>
+      </c>
+      <c r="G11" t="n">
+        <v>647</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18200</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>52</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295224_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3337685</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3337685</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 144 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295224_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295224_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295224_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295224_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295224_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295224_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295224_detail_en_hd_1.jpg, https://vdxl.im/8721158295224_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295224_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295224_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295224_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>140 cm</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3337706</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8721158295439</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1329</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1779</v>
+      </c>
+      <c r="G12" t="n">
+        <v>778</v>
+      </c>
+      <c r="H12" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>20</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295439_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3337706</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3337706</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 200 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295439_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295439_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295439_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295439_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295439_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295439_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295439_detail_en_hd_1.jpg, https://vdxl.im/8721158295439_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295439_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295439_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295439_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>200 cm</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3337679</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8721158295163</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>659</v>
+      </c>
+      <c r="F13" t="n">
+        <v>879</v>
+      </c>
+      <c r="G13" t="n">
+        <v>386</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295163_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3337679</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3337679</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295163_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295163_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295163_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295163_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295163_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295163_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295163_detail_en_hd_1.jpg, https://vdxl.im/8721158295163_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295163_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295163_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295163_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3337707</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8721158295446</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1319</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1759</v>
+      </c>
+      <c r="G14" t="n">
+        <v>772</v>
+      </c>
+      <c r="H14" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295446_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3337707</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3337707</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 200 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295446_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295446_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295446_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295446_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295446_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295446_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295446_detail_en_hd_1.jpg, https://vdxl.im/8721158295446_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295446_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295446_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295446_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>200 cm</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3337687</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8721158295248</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1459</v>
+      </c>
+      <c r="G15" t="n">
+        <v>640</v>
+      </c>
+      <c r="H15" t="n">
+        <v>18200</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295248_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3337687</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3337687</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk brun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 144 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295248_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295248_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295248_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295248_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295248_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295248_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295248_detail_en_hd_1.jpg, https://vdxl.im/8721158295248_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295248_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295248_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295248_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>140 cm</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3337701</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8721158295385</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1709</v>
+      </c>
+      <c r="G16" t="n">
+        <v>751</v>
+      </c>
+      <c r="H16" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>5</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295385_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3337701</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3337701</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk brun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 180 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295385_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295385_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295385_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295385_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295385_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295385_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295385_detail_en_hd_1.jpg, https://vdxl.im/8721158295385_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295385_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295385_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295385_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>180 cm</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3337681</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8721158295187</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>659</v>
+      </c>
+      <c r="F17" t="n">
+        <v>879</v>
+      </c>
+      <c r="G17" t="n">
+        <v>386</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295187_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3337681</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3337681</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295187_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295187_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295187_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295187_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295187_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295187_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295187_detail_en_hd_1.jpg, https://vdxl.im/8721158295187_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295187_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295187_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295187_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3337682</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8721158295194</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>669</v>
+      </c>
+      <c r="F18" t="n">
+        <v>899</v>
+      </c>
+      <c r="G18" t="n">
+        <v>389</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>17</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295194_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3337682</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3337682</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295194_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295194_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295194_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295194_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295194_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295194_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295194_detail_en_hd_1.jpg, https://vdxl.im/8721158295194_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295194_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295194_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295194_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3337710</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8721158295477</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1329</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1779</v>
+      </c>
+      <c r="G19" t="n">
+        <v>778</v>
+      </c>
+      <c r="H19" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295477_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3337710</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3337710</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 200 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295477_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295477_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295477_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295477_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295477_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295477_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295477_detail_en_hd_1.jpg, https://vdxl.im/8721158295477_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295477_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295477_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295477_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>200 cm</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3337683</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8721158295200</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>659</v>
+      </c>
+      <c r="F20" t="n">
+        <v>879</v>
+      </c>
+      <c r="G20" t="n">
+        <v>388</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295200_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3337683</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3337683</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295200_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295200_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295200_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295200_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295200_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295200_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295200_detail_en_hd_1.jpg, https://vdxl.im/8721158295200_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295200_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295200_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295200_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3337711</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8721158295484</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1319</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1759</v>
+      </c>
+      <c r="G21" t="n">
+        <v>775</v>
+      </c>
+      <c r="H21" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295484_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3337711</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3337711</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 200 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295484_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295484_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295484_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295484_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295484_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295484_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295484_detail_en_hd_1.jpg, https://vdxl.im/8721158295484_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295484_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295484_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295484_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>200 cm</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3337663</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8721158295002</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>579</v>
+      </c>
+      <c r="F22" t="n">
+        <v>779</v>
+      </c>
+      <c r="G22" t="n">
+        <v>337</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>36</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295002_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3337663</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3337663</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295002_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295002_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295002_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295002_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295002_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295002_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295002_detail_en_hd_1.jpg, https://vdxl.im/8721158295002_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295002_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295002_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295002_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3337664</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8721158295019</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>579</v>
+      </c>
+      <c r="F23" t="n">
+        <v>779</v>
+      </c>
+      <c r="G23" t="n">
+        <v>337</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>55</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295019_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3337664</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3337664</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295019_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295019_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295019_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295019_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295019_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295019_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295019_detail_en_hd_1.jpg, https://vdxl.im/8721158295019_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295019_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295019_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295019_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3337665</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8721158295026</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>579</v>
+      </c>
+      <c r="F24" t="n">
+        <v>779</v>
+      </c>
+      <c r="G24" t="n">
+        <v>336</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>40</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295026_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>3337665</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>3337665</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295026_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295026_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295026_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295026_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295026_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295026_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295026_detail_en_hd_1.jpg, https://vdxl.im/8721158295026_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295026_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295026_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295026_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3337667</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8721158295040</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>609</v>
+      </c>
+      <c r="F25" t="n">
+        <v>819</v>
+      </c>
+      <c r="G25" t="n">
+        <v>356</v>
+      </c>
+      <c r="H25" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>11</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295040_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>3337667</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>3337667</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295040_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295040_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295040_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295040_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295040_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295040_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295040_detail_en_hd_1.jpg, https://vdxl.im/8721158295040_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295040_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295040_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295040_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3337668</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8721158295057</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>569</v>
+      </c>
+      <c r="F26" t="n">
+        <v>759</v>
+      </c>
+      <c r="G26" t="n">
+        <v>332</v>
+      </c>
+      <c r="H26" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>14</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295057_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>3337668</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>3337668</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295057_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295057_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295057_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295057_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295057_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295057_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295057_detail_en_hd_1.jpg, https://vdxl.im/8721158295057_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295057_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295057_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295057_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3337669</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8721158295064</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>579</v>
+      </c>
+      <c r="F27" t="n">
+        <v>779</v>
+      </c>
+      <c r="G27" t="n">
+        <v>338</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9900</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>18</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295064_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3337669</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3337669</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295064_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295064_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295064_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295064_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295064_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295064_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295064_detail_en_hd_1.jpg, https://vdxl.im/8721158295064_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295064_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295064_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295064_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3337670</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8721158295071</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>639</v>
+      </c>
+      <c r="F28" t="n">
+        <v>859</v>
+      </c>
+      <c r="G28" t="n">
+        <v>375</v>
+      </c>
+      <c r="H28" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>23</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295071_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>3337670</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>3337670</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295071_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295071_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295071_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295071_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295071_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295071_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295071_detail_en_hd_1.jpg, https://vdxl.im/8721158295071_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295071_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295071_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295071_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3337671</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8721158295088</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>639</v>
+      </c>
+      <c r="F29" t="n">
+        <v>859</v>
+      </c>
+      <c r="G29" t="n">
+        <v>375</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>47</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295088_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>3337671</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>3337671</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295088_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295088_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295088_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295088_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295088_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295088_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295088_detail_en_hd_1.jpg, https://vdxl.im/8721158295088_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295088_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295088_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295088_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3337672</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8721158295095</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>639</v>
+      </c>
+      <c r="F30" t="n">
+        <v>859</v>
+      </c>
+      <c r="G30" t="n">
+        <v>375</v>
+      </c>
+      <c r="H30" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>51</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295095_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>3337672</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>3337672</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295095_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295095_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295095_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295095_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295095_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295095_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295095_detail_en_hd_1.jpg, https://vdxl.im/8721158295095_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295095_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295095_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295095_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3337673</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8721158295101</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>639</v>
+      </c>
+      <c r="F31" t="n">
+        <v>859</v>
+      </c>
+      <c r="G31" t="n">
+        <v>375</v>
+      </c>
+      <c r="H31" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>11</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295101_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>3337673</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>3337673</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk brun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295101_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295101_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295101_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295101_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295101_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295101_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295101_detail_en_hd_1.jpg, https://vdxl.im/8721158295101_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295101_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295101_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295101_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3337674</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8721158295118</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>629</v>
+      </c>
+      <c r="F32" t="n">
+        <v>839</v>
+      </c>
+      <c r="G32" t="n">
+        <v>366</v>
+      </c>
+      <c r="H32" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>17</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295118_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>3337674</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>3337674</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295118_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295118_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295118_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295118_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295118_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295118_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295118_detail_en_hd_1.jpg, https://vdxl.im/8721158295118_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295118_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295118_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295118_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3337675</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8721158295125</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>639</v>
+      </c>
+      <c r="F33" t="n">
+        <v>859</v>
+      </c>
+      <c r="G33" t="n">
+        <v>375</v>
+      </c>
+      <c r="H33" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>29</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295125_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>3337675</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>3337675</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295125_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295125_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295125_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295125_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295125_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295125_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295125_detail_en_hd_1.jpg, https://vdxl.im/8721158295125_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295125_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295125_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295125_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3337676</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8721158295132</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>629</v>
+      </c>
+      <c r="F34" t="n">
+        <v>839</v>
+      </c>
+      <c r="G34" t="n">
+        <v>369</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11000</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>18</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295132_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>3337676</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>3337676</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295132_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295132_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295132_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295132_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295132_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295132_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295132_detail_en_hd_1.jpg, https://vdxl.im/8721158295132_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295132_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295132_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295132_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>90 cm</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3337680</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8721158295170</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>669</v>
+      </c>
+      <c r="F35" t="n">
+        <v>899</v>
+      </c>
+      <c r="G35" t="n">
+        <v>393</v>
+      </c>
+      <c r="H35" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>14</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295170_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>3337680</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>3337680</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk brun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295170_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295170_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295170_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295170_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295170_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295170_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295170_detail_en_hd_1.jpg, https://vdxl.im/8721158295170_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295170_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295170_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295170_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3337684</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8721158295217</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1469</v>
+      </c>
+      <c r="G36" t="n">
+        <v>643</v>
+      </c>
+      <c r="H36" t="n">
+        <v>18200</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>24</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295217_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>3337684</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>3337684</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 144 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295217_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295217_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295217_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295217_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295217_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295217_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295217_detail_en_hd_1.jpg, https://vdxl.im/8721158295217_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295217_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295217_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295217_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>140 cm</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3337686</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8721158295231</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1099</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1469</v>
+      </c>
+      <c r="G37" t="n">
+        <v>645</v>
+      </c>
+      <c r="H37" t="n">
+        <v>18200</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>31</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295231_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>3337686</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>3337686</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 144 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295231_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295231_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295231_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295231_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295231_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295231_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295231_detail_en_hd_1.jpg, https://vdxl.im/8721158295231_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295231_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295231_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295231_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>140 cm</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3337688</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8721158295255</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1439</v>
+      </c>
+      <c r="G38" t="n">
+        <v>634</v>
+      </c>
+      <c r="H38" t="n">
+        <v>18200</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>13</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295255_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3337688</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>3337688</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 144 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295255_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295255_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295255_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295255_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295255_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295255_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295255_detail_en_hd_1.jpg, https://vdxl.im/8721158295255_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295255_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295255_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295255_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>140 cm</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3337689</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8721158295262</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1459</v>
+      </c>
+      <c r="G39" t="n">
+        <v>637</v>
+      </c>
+      <c r="H39" t="n">
+        <v>18200</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>12</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295262_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>3337689</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>3337689</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 144 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295262_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295262_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295262_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295262_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295262_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295262_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295262_detail_en_hd_1.jpg, https://vdxl.im/8721158295262_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295262_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295262_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295262_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>140 cm</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3337690</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8721158295279</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1089</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1459</v>
+      </c>
+      <c r="G40" t="n">
+        <v>638</v>
+      </c>
+      <c r="H40" t="n">
+        <v>18200</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>12</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295279_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3337690</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3337690</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 144 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295279_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295279_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295279_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295279_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295279_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295279_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295279_detail_en_hd_1.jpg, https://vdxl.im/8721158295279_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295279_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295279_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295279_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>140 cm</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3337698</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8721158295354</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1709</v>
+      </c>
+      <c r="G41" t="n">
+        <v>751</v>
+      </c>
+      <c r="H41" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>11</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295354_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3337698</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3337698</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 180 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295354_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295354_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295354_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295354_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295354_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295354_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295354_detail_en_hd_1.jpg, https://vdxl.im/8721158295354_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295354_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295354_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295354_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>180 cm</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3337699</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8721158295361</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1709</v>
+      </c>
+      <c r="G42" t="n">
+        <v>751</v>
+      </c>
+      <c r="H42" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>23</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295361_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3337699</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3337699</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 180 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295361_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295361_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295361_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295361_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295361_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295361_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295361_detail_en_hd_1.jpg, https://vdxl.im/8721158295361_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295361_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295361_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295361_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>180 cm</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3337700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8721158295378</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1709</v>
+      </c>
+      <c r="G43" t="n">
+        <v>751</v>
+      </c>
+      <c r="H43" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>25</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295378_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3337700</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3337700</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 180 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295378_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295378_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295378_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295378_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295378_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295378_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295378_detail_en_hd_1.jpg, https://vdxl.im/8721158295378_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295378_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295378_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>180 cm</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3337702</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8721158295392</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1669</v>
+      </c>
+      <c r="G44" t="n">
+        <v>732</v>
+      </c>
+      <c r="H44" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>8</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295392_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3337702</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3337702</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 180 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295392_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295392_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295392_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295392_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295392_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295392_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295392_detail_en_hd_1.jpg, https://vdxl.im/8721158295392_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295392_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295392_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295392_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>180 cm</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3337703</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8721158295408</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1279</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1709</v>
+      </c>
+      <c r="G45" t="n">
+        <v>751</v>
+      </c>
+      <c r="H45" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>14</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295408_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3337703</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3337703</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Creme&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 180 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295408_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295408_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295408_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295408_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295408_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295408_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295408_detail_en_hd_1.jpg, https://vdxl.im/8721158295408_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295408_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295408_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295408_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>180 cm</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3337704</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8721158295415</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1259</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1679</v>
+      </c>
+      <c r="G46" t="n">
+        <v>737</v>
+      </c>
+      <c r="H46" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>8</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295415_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3337704</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3337704</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 180 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295415_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295415_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295415_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295415_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295415_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295415_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295415_detail_en_hd_1.jpg, https://vdxl.im/8721158295415_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295415_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295415_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295415_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>180 cm</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3337708</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8721158295453</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1789</v>
+      </c>
+      <c r="G47" t="n">
+        <v>785</v>
+      </c>
+      <c r="H47" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295453_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>3337708</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>3337708</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Mørk brun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 200 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295453_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295453_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295453_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158295453_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295453_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295453_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295453_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295453_detail_en_hd_1.jpg, https://vdxl.im/8721158295453_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295453_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295453_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295453_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>200 cm</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sengegavl-linjedesign-lysegra-100-cm-stof</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3337709</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8721158295460</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1319</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1759</v>
+      </c>
+      <c r="G48" t="n">
+        <v>771</v>
+      </c>
+      <c r="H48" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>10</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295460_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>3337709</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>3337709</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne justerbare sengegavl er både smart og praktisk og passer ind i moderne soveværelser. Med sit enkle design og rene linjer giver den en cool vibe, der komplementerer forskellige indretninger. Det bløde skumfyld giver god komfort, og den justerbare højde gør, at den kan tilpasses forskellige madrasser. Bygget af holdbart konstrueret træ og massivt fyrretræ, lover den lang holdbarhed.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Sengegavlen er lavet af en stærk kombination af konstrueret træ og massivt fyrretræ. Denne blanding sikrer holdbarhed og giver et moderne, rustikt præg. Stoffet tilføjer elegance og en blød tekstur, der giver varme til enhver atmosfære. Stofoverfladen er åndbar og venlig mod huden, så den er både stilfuld og behagelig.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sengegavlen har luksuriøs polstring med justerbart skum, der giver en dejlig og støttende følelse. De skumfyldte sektioner er bygget til at modstå slid, så de holder formen. Hver komponent er tænkt igennem for at sikre maksimal komfort og et godt design. Disse elementer sikrer, at du får den bedste afslapning og forvandler enhver seng til et hyggeligt sted.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner/Design:&lt;/b&gt; Senegavlen kan tilpasses og justeres til to forskellige højder, så den passer til mange sengestile. Det enkle, moderne design smelter sammen med andre møbler og skaber en luftig, harmonisk atmosfære.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Perfekt til alle soveværelser, der trænger til et moderne præg, den er ideel til master-suiter, gæsteværelser eller loftlejligheder. Dens justerbare funktion gør den egnet til børnesenge, så den kan vokse med barnet og passe til forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pasning &amp; Vedligeholdelse:&lt;/b&gt; Det er nemt at holde sengegavlen pæn. Bare giv den et hurtigt stryg med en tør klud for at fjerne støv og snavs. Den robuste konstruktion kræver lidt vedligeholdelse, så den forbliver smuk i mange år.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ, massivt fyrretræ&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 200 x 7 x 128 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;2 installationshøjde muligheder: 118/128 cm&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Hovedgærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158295460_mo-im_en_hd_1.jpg, https://vdxl.im/8721158295460_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158295460_mo-im_en_hd_2.jpg, https://vdxl.im/8721158295460_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158295460_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158295460_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158295460_detail_en_hd_1.jpg, https://vdxl.im/8721158295460_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158295460_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158295460_wbg-siz_en_hd_2.jpg, https://vdxl.im/8721158295460_wbg-siz_en_hd_3.jpg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>200 cm</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Høj hovedgærde</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>konsolbord-75x29x-konstrueret-trae-etraesfarve</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>834036</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8720845419875</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>449</v>
+      </c>
+      <c r="F49" t="n">
+        <v>599</v>
+      </c>
+      <c r="G49" t="n">
+        <v>262</v>
+      </c>
+      <c r="H49" t="n">
+        <v>16010</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>47</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845419875_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>834036</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>834036</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Tilføj et elegant præg i din entré, stue eller gang med dette stilfulde konsolbord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Sofabordet er fremstillet af konstrueret træ, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Entrébordet tilbyder rigelig med plads til at holde dine magasiner, bøger, pyntegenstande samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Justerbare fødder: Fire justerbare fødder med plastpuder holder entrébordet i balance på et ujævnt underlag og øger stabiliteten.&lt;/li&gt;&lt;li&gt;Metalstel: Metalstellet tilføjer en industriel stil i dit interiør, samtidig med at det giver holdbarhed og stabilitet.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 100 x 29 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845419875_m_en_hd_1.jpg, https://vdxl.im/8720845419875_a_en_hd_1.jpg, https://vdxl.im/8720845419875_g_en_hd_1.jpg, https://vdxl.im/8720845419875_g_en_hd_2.jpg, https://vdxl.im/8720845419875_g_en_hd_3.jpg, https://vdxl.im/8720845419875_g_en_hd_4.jpg, https://vdxl.im/8720845419875_g_en_hd_5.jpg, https://vdxl.im/8720845419875_g_en_hd_6.jpg, https://vdxl.im/8720845419875_g_en_hd_7.jpg, https://vdxl.im/8720845419875_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>konsolbord-75x29x-konstrueret-trae-etraesfarve</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>882199</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>8721288917669</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>449</v>
+      </c>
+      <c r="F50" t="n">
+        <v>599</v>
+      </c>
+      <c r="G50" t="n">
+        <v>264</v>
+      </c>
+      <c r="H50" t="n">
+        <v>13090</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>58</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288917669_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>882199</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>882199</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette slanke industrielle konsolbord blander moderne design med praktisk funktionalitet og forbedrer ethvert rum. Det trækker på inspiration fra urbane loftstile og bruger rå materialer til at skabe en chic tilføjelse til forskellig slags indretning. Dets smalle form passer godt til vægge og fungerer både som udstillingsplads og opbevaringssted, så du kan vise dine yndlingsgenstande eller have det vigtigste lige ved hånden.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Professionelt lavet af konstrueret træ, så dette konsolbord er holdbart og har en glat overflade, der holder til daglig brug. Den matte finish giver en elegant glans, der bidrager til en stilfuld atmosfære i din stue. Det udvalgte materiale sikrer et langtidsholdbart bord, der komplementerer mange indretningsstile.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Udstyret med praktiske hylder, giver konsolbordet masser af plads til opbevaring og visning af ting som bøger og pynt. Den pulverlakerede metalramme giver både stil og solid støtte, så dine ting står sikkert.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner / Design:&lt;/b&gt; Dette bord kombinerer industriel stil med funktionelt design, perfekt til et hjem, der vil have et moderne look. Det passer indendørs til moderne eller minimalistiske stilarter. De firkantede ben tilføjer et geometrisk præg og sikrer stabilitet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede brug:&lt;/b&gt; Ideelt til stuer, entreer eller gange, dette bord er ikke bare en flot detalje, men også praktisk til opbevaring og visning af vigtige ting. Dets slanke look gør det pladsbesparende og tilpasser sig forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Hold bordet flot ved blot at tørre det af med en fugtig klud og undgå hårde kemikalier. Denne nemme vedligeholdelse sikrer, at det forbliver et stilfuldt element i dit hjem i mange år frem. &lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 29 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 11,59 kg&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Konsolbord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288917669_mo-im_en_hd_1.jpg, https://vdxl.im/8721288917669_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288917669_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288917669_mo-im_en_hd_2.jpg, https://vdxl.im/8721288917669_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288917669_wbg-si_en_hd_4.jpg, https://vdxl.im/8721288917669_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721288917669_detail_en_hd_1.jpg, https://vdxl.im/8721288917669_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288917669_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288917669_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288917669_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>konsolbord-75x29x-konstrueret-trae-etraesfarve</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>882200</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8721288917676</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>439</v>
+      </c>
+      <c r="F51" t="n">
+        <v>589</v>
+      </c>
+      <c r="G51" t="n">
+        <v>257</v>
+      </c>
+      <c r="H51" t="n">
+        <v>13090</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>51</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288917676_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>882200</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>882200</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette slanke industrielle konsolbord blander moderne design med praktisk funktionalitet og forbedrer ethvert rum. Det trækker på inspiration fra urbane loftstile og bruger rå materialer til at skabe en chic tilføjelse til forskellig slags indretning. Dets smalle form passer godt til vægge og fungerer både som udstillingsplads og opbevaringssted, så du kan vise dine yndlingsgenstande eller have det vigtigste lige ved hånden.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Professionelt lavet af konstrueret træ, så dette konsolbord er holdbart og har en glat overflade, der holder til daglig brug. Den matte finish giver en elegant glans, der bidrager til en stilfuld atmosfære i din stue. Det udvalgte materiale sikrer et langtidsholdbart bord, der komplementerer mange indretningsstile.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Udstyret med praktiske hylder, giver konsolbordet masser af plads til opbevaring og visning af ting som bøger og pynt. Den pulverlakerede metalramme giver både stil og solid støtte, så dine ting står sikkert.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner / Design:&lt;/b&gt; Dette bord kombinerer industriel stil med funktionelt design, perfekt til et hjem, der vil have et moderne look. Det passer indendørs til moderne eller minimalistiske stilarter. De firkantede ben tilføjer et geometrisk præg og sikrer stabilitet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede brug:&lt;/b&gt; Ideelt til stuer, entreer eller gange, dette bord er ikke bare en flot detalje, men også praktisk til opbevaring og visning af vigtige ting. Dets slanke look gør det pladsbesparende og tilpasser sig forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Hold bordet flot ved blot at tørre det af med en fugtig klud og undgå hårde kemikalier. Denne nemme vedligeholdelse sikrer, at det forbliver et stilfuldt element i dit hjem i mange år frem. &lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 29 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 11,59 kg&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Konsolbord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288917676_mo-im_en_hd_1.jpg, https://vdxl.im/8721288917676_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288917676_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288917676_mo-im_en_hd_2.jpg, https://vdxl.im/8721288917676_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288917676_wbg-si_en_hd_4.jpg, https://vdxl.im/8721288917676_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721288917676_detail_en_hd_1.jpg, https://vdxl.im/8721288917676_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288917676_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288917676_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288917676_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>konsolbord-75x29x-konstrueret-trae-etraesfarve</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>882201</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8721288917683</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>459</v>
+      </c>
+      <c r="F52" t="n">
+        <v>619</v>
+      </c>
+      <c r="G52" t="n">
+        <v>270</v>
+      </c>
+      <c r="H52" t="n">
+        <v>13090</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>90</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288917683_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>882201</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>882201</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette slanke industrielle konsolbord blander moderne design med praktisk funktionalitet og forbedrer ethvert rum. Det trækker på inspiration fra urbane loftstile og bruger rå materialer til at skabe en chic tilføjelse til forskellig slags indretning. Dets smalle form passer godt til vægge og fungerer både som udstillingsplads og opbevaringssted, så du kan vise dine yndlingsgenstande eller have det vigtigste lige ved hånden.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Professionelt lavet af konstrueret træ, så dette konsolbord er holdbart og har en glat overflade, der holder til daglig brug. Den matte finish giver en elegant glans, der bidrager til en stilfuld atmosfære i din stue. Det udvalgte materiale sikrer et langtidsholdbart bord, der komplementerer mange indretningsstile.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Udstyret med praktiske hylder, giver konsolbordet masser af plads til opbevaring og visning af ting som bøger og pynt. Den pulverlakerede metalramme giver både stil og solid støtte, så dine ting står sikkert.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner / Design:&lt;/b&gt; Dette bord kombinerer industriel stil med funktionelt design, perfekt til et hjem, der vil have et moderne look. Det passer indendørs til moderne eller minimalistiske stilarter. De firkantede ben tilføjer et geometrisk præg og sikrer stabilitet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede brug:&lt;/b&gt; Ideelt til stuer, entreer eller gange, dette bord er ikke bare en flot detalje, men også praktisk til opbevaring og visning af vigtige ting. Dets slanke look gør det pladsbesparende og tilpasser sig forskellige rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Hold bordet flot ved blot at tørre det af med en fugtig klud og undgå hårde kemikalier. Denne nemme vedligeholdelse sikrer, at det forbliver et stilfuldt element i dit hjem i mange år frem. &lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 29 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 11,59 kg&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Metal&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Konsolbord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288917683_mo-im_en_hd_1.jpg, https://vdxl.im/8721288917683_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288917683_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288917683_mo-im_en_hd_2.jpg, https://vdxl.im/8721288917683_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721288917683_wbg-si_en_hd_4.jpg, https://vdxl.im/8721288917683_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721288917683_detail_en_hd_1.jpg, https://vdxl.im/8721288917683_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288917683_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288917683_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288917683_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Længde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>kokkenvogn-50x30x70-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>842359</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8721012376557</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>469</v>
+      </c>
+      <c r="F53" t="n">
+        <v>629</v>
+      </c>
+      <c r="G53" t="n">
+        <v>275</v>
+      </c>
+      <c r="H53" t="n">
+        <v>10400</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>66</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012376557_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>842359</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>842359</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et karakteristisk vintagepræg, og tilføj mere opbevaringsplads i dit køkken med denne køkkenvogn.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt; Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Stålstellet giver robusthed og stabilitet. &lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne grøntsagsvogn giver rigelig med plads til at holde mad, skåle, tallerkener, kogebøger og andre køkkenredskaber inden for rækkevidde. &lt;/li&gt;&lt;li&gt;Nem at flytte rundt: Denne madvogn har 4 hjul, og 2 af dem kan låses, så den er fleksibel og kan nemt parkeres. &lt;/li&gt;&lt;li&gt;Mange anvendelsesmuligheder: Denne opbevaringsvogn kan bruges i køkkenet, stuen , på badeværelset, kontoret og andre steder. Den kan bruges til ting og sager såsom krydderier, toiletartikler, bøger mv. &lt;/li&gt;&lt;li&gt;Fleksibel installation: Denne køkkenvogn kan bruges på to måder. Du kan sætte den på gulvet med justerbare fødder for stabilitet på ujævne underlag, eller du kan montere hjulene for nem bevægelse. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, stål&lt;/li&gt;&lt;li&gt;Mål (med hjul): 50 x 30 x 70 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 4 hjul, hvoraf 2 er udstyret med bremser&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012376557_m_en_hd_1.jpg, https://vdxl.im/8721012376557_a_en_hd_1.jpg, https://vdxl.im/8721012376557_g_en_hd_1.jpg, https://vdxl.im/8721012376557_g_en_hd_2.jpg, https://vdxl.im/8721012376557_g_en_hd_3.jpg, https://vdxl.im/8721012376557_g_en_hd_4.jpg, https://vdxl.im/8721012376557_g_en_hd_5.jpg, https://vdxl.im/8721012376557_g_en_hd_6.jpg, https://vdxl.im/8721012376557_g_en_hd_7.jpg, https://vdxl.im/8721012376557_g_en_hd_8.jpg, https://vdxl.im/8721012376557_g_en_hd_9.jpg, https://vdxl.im/8721012376557_g_en_hd_10.jpg, https://vdxl.im/8721012376557_g_en_hd_11.jpg, https://vdxl.im/8721012376557_g_en_hd_12.jpg, https://vdxl.im/8721012376557_g_en_hd_13.jpg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>kokkenvogn-50x30x70-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>869108</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8721158972477</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>529</v>
+      </c>
+      <c r="F54" t="n">
+        <v>709</v>
+      </c>
+      <c r="G54" t="n">
+        <v>310</v>
+      </c>
+      <c r="H54" t="n">
+        <v>9700</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>26</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158972477_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>869108</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>869108</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Den her trævogn til køkkenet er virkelig en blanding af stil og funktionalitet – et must-have i dit madlavningsområde. Med sit slanke og moderne design bliver den hurtigt et blikfang i dit køkken, der både tilføjer charme og praktisk brug. Den er primært lavet af konstrueret træ og fungerer godt til madlavning, servering og opbevaring. Den rektangulære form passer let ind i forskellige køkkener uden at tage for meget plads, så alt ser pænt og ordentligt ud.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret Træ&lt;/b&gt; Den her køkkenvogn er lavet af holdbart konstrueret træ, der er stærkt og pålideligt. Dette materiale er kendt for sin holdbarhed og modstandskraft, så den kan klare sig godt i alle køkkener. Det er ikke bare solidt, men ser også flot ud og passer til moderne indretninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Massive Opbevaringsmuligheder&lt;/b&gt; Vognen har meget opbevaringsplads med flere rum og hylder. Hver plads er gennemtænkt til at holde styr på dine køkkenudstyr, så alt er let tilgængeligt og pænt gemt væk, hvilket giver et ordenligt køkken.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne Design&lt;/b&gt; Med sin enkle og rektangulære form passer denne vogn perfekt til nutidens køkkenstile. Det minimalistiske design med rene linjer giver et stilfuldt touch, der løfter hele udseendet af dit køkken.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Kun til Indendørs Brug&lt;/b&gt; Denne vogn er designet til indendørs brug, så dit køkken er organiseret og funktionelt. Dens glatte overflade og trækonstruktion gør den perfekt til indendørs brug og hjælper med at bevare dens skønhed over tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem Vedligeholdelse&lt;/b&gt; For at holde din køkkenvogn i god stand, skal du bare tørre overfladen af med en klud med jævne mellemrum. Brug ikke hårde rengøringsmidler for at bevare den flotte overflade og sikre, at den ser godt ud i mange år fremover.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 50 x 30 x 70 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 8,2 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Køkkenvogn&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158972477_mo-im_en_hd_1.jpg, https://vdxl.im/8721158972477_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158972477_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158972477_mo-im_en_hd_2.jpg, https://vdxl.im/8721158972477_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158972477_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721158972477_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158972477_wbg-si_en_hd_5.jpg, https://vdxl.im/8721158972477_detail_en_hd_1.jpg, https://vdxl.im/8721158972477_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158972477_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158972477_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158972477_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>kokkenvogn-50x30x70-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>869109</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8721158941701</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>479</v>
+      </c>
+      <c r="F55" t="n">
+        <v>639</v>
+      </c>
+      <c r="G55" t="n">
+        <v>280</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9700</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>153</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158941701_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>869109</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>869109</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Den her trævogn til køkkenet er virkelig en blanding af stil og funktionalitet – et must-have i dit madlavningsområde. Med sit slanke og moderne design bliver den hurtigt et blikfang i dit køkken, der både tilføjer charme og praktisk brug. Den er primært lavet af konstrueret træ og fungerer godt til madlavning, servering og opbevaring. Den rektangulære form passer let ind i forskellige køkkener uden at tage for meget plads, så alt ser pænt og ordentligt ud.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret Træ&lt;/b&gt; Den her køkkenvogn er lavet af holdbart konstrueret træ, der er stærkt og pålideligt. Dette materiale er kendt for sin holdbarhed og modstandskraft, så den kan klare sig godt i alle køkkener. Det er ikke bare solidt, men ser også flot ud og passer til moderne indretninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Massive Opbevaringsmuligheder&lt;/b&gt; Vognen har meget opbevaringsplads med flere rum og hylder. Hver plads er gennemtænkt til at holde styr på dine køkkenudstyr, så alt er let tilgængeligt og pænt gemt væk, hvilket giver et ordenligt køkken.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne Design&lt;/b&gt; Med sin enkle og rektangulære form passer denne vogn perfekt til nutidens køkkenstile. Det minimalistiske design med rene linjer giver et stilfuldt touch, der løfter hele udseendet af dit køkken.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Kun til Indendørs Brug&lt;/b&gt; Denne vogn er designet til indendørs brug, så dit køkken er organiseret og funktionelt. Dens glatte overflade og trækonstruktion gør den perfekt til indendørs brug og hjælper med at bevare dens skønhed over tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem Vedligeholdelse&lt;/b&gt; For at holde din køkkenvogn i god stand, skal du bare tørre overfladen af med en klud med jævne mellemrum. Brug ikke hårde rengøringsmidler for at bevare den flotte overflade og sikre, at den ser godt ud i mange år fremover.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 50 x 30 x 70 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 8,2 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Køkkenvogn&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158941701_mo-im_en_hd_1.jpg, https://vdxl.im/8721158941701_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158941701_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158941701_mo-im_en_hd_2.jpg, https://vdxl.im/8721158941701_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158941701_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721158941701_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158941701_wbg-si_en_hd_5.jpg, https://vdxl.im/8721158941701_detail_en_hd_1.jpg, https://vdxl.im/8721158941701_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158941701_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158941701_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158941701_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>kokkenvogn-50x30x70-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>869110</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8721158941718</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>309</v>
+      </c>
+      <c r="F56" t="n">
+        <v>419</v>
+      </c>
+      <c r="G56" t="n">
+        <v>178</v>
+      </c>
+      <c r="H56" t="n">
+        <v>9700</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>200</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158941718_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>869110</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>869110</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Den her trævogn til køkkenet er virkelig en blanding af stil og funktionalitet – et must-have i dit madlavningsområde. Med sit slanke og moderne design bliver den hurtigt et blikfang i dit køkken, der både tilføjer charme og praktisk brug. Den er primært lavet af konstrueret træ og fungerer godt til madlavning, servering og opbevaring. Den rektangulære form passer let ind i forskellige køkkener uden at tage for meget plads, så alt ser pænt og ordentligt ud.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret Træ&lt;/b&gt; Den her køkkenvogn er lavet af holdbart konstrueret træ, der er stærkt og pålideligt. Dette materiale er kendt for sin holdbarhed og modstandskraft, så den kan klare sig godt i alle køkkener. Det er ikke bare solidt, men ser også flot ud og passer til moderne indretninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Massive Opbevaringsmuligheder&lt;/b&gt; Vognen har meget opbevaringsplads med flere rum og hylder. Hver plads er gennemtænkt til at holde styr på dine køkkenudstyr, så alt er let tilgængeligt og pænt gemt væk, hvilket giver et ordenligt køkken.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne Design&lt;/b&gt; Med sin enkle og rektangulære form passer denne vogn perfekt til nutidens køkkenstile. Det minimalistiske design med rene linjer giver et stilfuldt touch, der løfter hele udseendet af dit køkken.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Kun til Indendørs Brug&lt;/b&gt; Denne vogn er designet til indendørs brug, så dit køkken er organiseret og funktionelt. Dens glatte overflade og trækonstruktion gør den perfekt til indendørs brug og hjælper med at bevare dens skønhed over tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem Vedligeholdelse&lt;/b&gt; For at holde din køkkenvogn i god stand, skal du bare tørre overfladen af med en klud med jævne mellemrum. Brug ikke hårde rengøringsmidler for at bevare den flotte overflade og sikre, at den ser godt ud i mange år fremover.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 50 x 30 x 70 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 8,2 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Køkkenvogn&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158941718_mo-im_en_hd_1.jpg, https://vdxl.im/8721158941718_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158941718_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158941718_mo-im_en_hd_2.jpg, https://vdxl.im/8721158941718_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158941718_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721158941718_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158941718_wbg-si_en_hd_5.jpg, https://vdxl.im/8721158941718_detail_en_hd_1.jpg, https://vdxl.im/8721158941718_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158941718_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158941718_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158941718_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>spisebordssaet-til-haven-5-dele-massivt-teaktrae-2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3385961</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8721288759887</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2319</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3099</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1364</v>
+      </c>
+      <c r="H57" t="n">
+        <v>23700</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>54</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759887_wbg-fr_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>3385961</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>3385961</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette eksklusive havemøbelset emmer af moderne stil og kombinerer form og funktion, så det forbedrer ethvert udendørs rum. Det er perfekt til dem, der elsker minimalistisk design, og passer ind i enhver have eller terrasse. Den varme brune farve spiller godt sammen med naturen og skaber et hyggeligt sted til samvær eller stille øjeblikke. De smukke mønstre i akacietræ tilføjer et unikt præg, som garanteret vil sætte gang i snakken.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Fuld akaciekonstruktion&lt;/b&gt; Hele sættet er lavet af massivt akacietræ, som er kendt for at være super holdbart og modstandsdygtigt over for vejret. Den tætte åre og solidt byggeri klarer de skiftende årstider, så du får en siddeplads, der holder. Den taktile overflade giver et naturligt look og tilføjer en varm følelse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Elegant design&lt;/b&gt; Bordet og stolene har en smuk bagside, der gør, at de ser godt ud fra alle vinkler. Den slanke silhuet rammer essensen af moderne stil og elegance. Denne opmærksomhed på detaljerne sikrer, at sættet forbliver et stilfuldt indslag i enhver have.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Behagelige armlæn&lt;/b&gt; Stolene har armlæn i massivt akacietræ, som både er komfortable og passer godt ind i designet. De giver støtte til brugerne og gør det nemt at slappe af under måltider og samtaler.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse&lt;/b&gt; Det kræver ikke meget vedligeholdelse for at holde sættet flot. Tør overfladen af med en klud for at undgå støv og bevare dens naturlige skønhed. Denne enkle pleje sikrer, at træets luksuriøse udstråling forbliver intakt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem samling&lt;/b&gt; Sættet er nemt at samle med to personer og en skruetrækker. Den hurtige opsætning gør, at du hurtigt kan nyde dit nye spiseområde uden behov for specielle værktøjer eller færdigheder. Alle nødvendige dele og instruktioner er inkluderet for din bekvemmelighed.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Brun&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Pladser&lt;/li&gt;&lt;li&gt;Maks. vægt: 220 kg&lt;/li&gt;&lt;li&gt;Pladser: 2&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Havestol: 46 x 45 x 89 cm (LxWxH)&lt;/li&gt;&lt;li&gt;1 x Havetabel: 85 x 85 x 76 cm (LxWxH)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759887_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721288759887_wbg-siz_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Rund</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Uden armlæn</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>spisebordssaet-til-haven-5-dele-massivt-teaktrae-2</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3385962</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8721288759894</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2749</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24700</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>174</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759894_mo-im_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>3385962</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>3385962</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette eksklusive havemøbelset emmer af moderne stil og kombinerer form og funktion, så det forbedrer ethvert udendørs rum. Det er perfekt til dem, der elsker minimalistisk design, og passer ind i enhver have eller terrasse. Den varme brune farve spiller godt sammen med naturen og skaber et hyggeligt sted til samvær eller stille øjeblikke. De smukke mønstre i akacietræ tilføjer et unikt præg, som garanteret vil sætte gang i snakken.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Fuld akaciekonstruktion&lt;/b&gt; Hele sættet er lavet af massivt akacietræ, som er kendt for at være super holdbart og modstandsdygtigt over for vejret. Den tætte åre og solidt byggeri klarer de skiftende årstider, så du får en siddeplads, der holder. Den taktile overflade giver et naturligt look og tilføjer en varm følelse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Elegant design&lt;/b&gt; Bordet og stolene har en smuk bagside, der gør, at de ser godt ud fra alle vinkler. Den slanke silhuet rammer essensen af moderne stil og elegance. Denne opmærksomhed på detaljerne sikrer, at sættet forbliver et stilfuldt indslag i enhver have.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Behagelige armlæn&lt;/b&gt; Stolene har armlæn i massivt akacietræ, som både er komfortable og passer godt ind i designet. De giver støtte til brugerne og gør det nemt at slappe af under måltider og samtaler.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse&lt;/b&gt; Det kræver ikke meget vedligeholdelse for at holde sættet flot. Tør overfladen af med en klud for at undgå støv og bevare dens naturlige skønhed. Denne enkle pleje sikrer, at træets luksuriøse udstråling forbliver intakt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem samling&lt;/b&gt; Sættet er nemt at samle med to personer og en skruetrækker. Den hurtige opsætning gør, at du hurtigt kan nyde dit nye spiseområde uden behov for specielle værktøjer eller færdigheder. Alle nødvendige dele og instruktioner er inkluderet for din bekvemmelighed.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Brun&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Pladser&lt;/li&gt;&lt;li&gt;Maks. vægt: 220 kg&lt;/li&gt;&lt;li&gt;Pladser: 2&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;2 x Havestol: 46 x 45 x 89 cm (LxWxH)&lt;/li&gt;&lt;li&gt;1 x Havetabel: 85 x 85 x 76 cm (LxWxH)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288759894_mo-im_en_px16_1.jpg, https://vdxl.im/8721288759894_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288759894_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288759894_mo-im_en_px16_2.jpg, https://vdxl.im/8721288759894_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288759894_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288759894_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721288759894_wbg-to_en_px16_1.jpg, https://vdxl.im/8721288759894_detail_en_px16_1.jpg, https://vdxl.im/8721288759894_wbg-fu_en_px16_1.jpg, https://vdxl.im/8721288759894_wbg-fu_en_px16_2.jpg, https://vdxl.im/8721288759894_wbg-siz_en_px16_1.jpg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ottekantet</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Uden armlæn</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sidebord-45-cm-haerdet-glas-guldfarvet-og-transparent</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>331661</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8720286462584</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>619</v>
+      </c>
+      <c r="F59" t="n">
+        <v>829</v>
+      </c>
+      <c r="G59" t="n">
+        <v>362</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4710</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>71</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286462584_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>331661</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>331661</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Tilføj en enkel, smuk og moderne stil i dit hjem med dette sidebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Moderne stil: Føj et strejf af moderne stil til din boligindretning. Det moderne design har rene linjer, et minimalistisk look og en lys farve, der passer ind i indretningen.&lt;/li&gt;&lt;li&gt;Robust stel: Dette endebord er fremstillet af hærdet glas og pulverlakeret jern, hvilket gør det yderst robust og stabilt.&lt;/li&gt;&lt;li&gt;Praktisk bordplade: Den solide bordplade giver en sikker overflade, hvorpå du kan stille snacks, drikkevarer, vaser, frugtskåle og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Guld og transparent&lt;/li&gt;&lt;li&gt;Materiale: Hærdet glas, pulverlakeret jern&lt;/li&gt;&lt;li&gt;Produktmål: 45 x 58 cm (Diameter x H)&lt;/li&gt;&lt;li&gt;Tykkelse, glas: 5 mm&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286462584_m_en_hd_1.jpg, https://vdxl.im/8720286462584_a_en_hd_1.jpg, https://vdxl.im/8720286462584_g_en_hd_1.jpg, https://vdxl.im/8720286462584_g_en_hd_2.jpg, https://vdxl.im/8720286462584_g_en_hd_3.jpg, https://vdxl.im/8720286462584_g_en_hd_4.jpg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Guldfarvet og gennemsigtig</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sidebord-45-cm-haerdet-glas-guldfarvet-og-transparent</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>331662</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>8720286462591</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>499</v>
+      </c>
+      <c r="F60" t="n">
+        <v>669</v>
+      </c>
+      <c r="G60" t="n">
+        <v>292</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4710</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>38</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286462591_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>331662</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>331662</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Tilføj en enkel, smuk og moderne stil i dit hjem med dette sidebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Moderne stil: Føj et strejf af moderne stil til din boligindretning. Det moderne design har rene linjer, et minimalistisk look og en lys farve, der passer ind i indretningen.&lt;/li&gt;&lt;li&gt;Robust stel: Dette endebord er fremstillet af hærdet glas og pulverlakeret jern, hvilket gør det yderst robust og stabilt.&lt;/li&gt;&lt;li&gt;Praktisk bordplade: Den solide bordplade giver en sikker overflade, hvorpå du kan stille snacks, drikkevarer, vaser, frugtskåle og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Guldfarvet og sort&lt;/li&gt;&lt;li&gt;Materiale: Hærdet glas, pulverlakeret jern&lt;/li&gt;&lt;li&gt;Produktmål: 45 x 58 cm (Diameter x H)&lt;/li&gt;&lt;li&gt;Tykkelse, glas: 5 mm&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286462591_m_en_hd_1.jpg, https://vdxl.im/8720286462591_a_en_hd_1.jpg, https://vdxl.im/8720286462591_g_en_hd_1.jpg, https://vdxl.im/8720286462591_g_en_hd_2.jpg, https://vdxl.im/8720286462591_g_en_hd_3.jpg, https://vdxl.im/8720286462591_g_en_hd_4.jpg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Guldfarvet og sort</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sidebord-45-cm-haerdet-glas-guldfarvet-og-transparent</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>331664</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8720286462614</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>609</v>
+      </c>
+      <c r="F61" t="n">
+        <v>819</v>
+      </c>
+      <c r="G61" t="n">
+        <v>355</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4710</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>14</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286462614_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>331664</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>331664</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Tilføj en enkel, smuk og moderne stil i dit hjem med dette sidebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Moderne stil: Føj et strejf af moderne stil til din boligindretning. Det moderne design har rene linjer, et minimalistisk look og en lys farve, der passer ind i indretningen.&lt;/li&gt;&lt;li&gt;Robust stel: Dette endebord er fremstillet af hærdet glas og pulverlakeret jern, hvilket gør det yderst robust og stabilt.&lt;/li&gt;&lt;li&gt;Praktisk bordplade: Den solide bordplade giver en sikker overflade, hvorpå du kan stille snacks, drikkevarer, vaser, frugtskåle og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Guld og hvid marmoreffekt&lt;/li&gt;&lt;li&gt;Materiale: Hærdet glas, pulverlakeret jern&lt;/li&gt;&lt;li&gt;Produktmål: 45 x 58 cm (Diameter x H)&lt;/li&gt;&lt;li&gt;Tykkelse, glas: 5 mm&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286462614_m_en_hd_1.jpg, https://vdxl.im/8720286462614_a_en_hd_1.jpg, https://vdxl.im/8720286462614_g_en_hd_1.jpg, https://vdxl.im/8720286462614_g_en_hd_2.jpg, https://vdxl.im/8720286462614_g_en_hd_3.jpg, https://vdxl.im/8720286462614_g_en_hd_4.jpg, https://vdxl.im/8720286462614_g_en_hd_5.jpg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Guldfarvet og hvid marmor</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>loungesaet-til-haven-13-dele-med-gra-hynder-massivt-fyrretrae-3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3096959</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>8720286867334</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>10129</v>
+      </c>
+      <c r="F62" t="n">
+        <v>13509</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5955</v>
+      </c>
+      <c r="H62" t="n">
+        <v>163110</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>91</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286867334_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>3096959</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>3096959</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette haveloungesæt er et glimrende valg, når du vil slappe af og nyde vejret, tage en lur eller sidde og snakke med din familie eller venner. &lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Dette loungesæt til terrassen er lavet af massivt fyrretræ, hvilket gør det robust og stabilt. Hynderne giver ekstra komfort. Du kan kombinere det med andre modulelementer og dermed skabe dit helt eget personlige haveloungesæt.    &lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;&lt;strong&gt;Bemærk:&lt;/strong&gt; Vi anbefaler, at du rengør dine havemøbler regelmæssigt, og at du ikke efterlader dem udenfor uden overtræk for at forlænge deres levetid.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Rengøring:&lt;/strong&gt; Brug en mild sæbeopløsning.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Opbevaring: &lt;/strong&gt;Hvis det er muligt, skal produktet opbevares et køligt og tørt sted indenfor. Hvis produktet opbevares udenfor, skal du beskytte det med et vandtæt overtræk. Tør overskydende vand eller sne af flade overflader, når det har regnet eller sneet. Sørg for tilstrækkelig luftcirkulation for at undgå fugtrelaterede skader. &lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve, hynde: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ + stof (100 % polyester) &lt;/li&gt;&lt;li&gt;Mål, hjørnesofa: 63,5 x 63,5 x 62,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Mål, midtersofa: 63,5 x 63,5 x 62,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 60 x 60 x 5 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 60 x 32 x 5 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;7 x hjørnesofa&lt;/li&gt;&lt;li&gt;6 x midtersofa &lt;/li&gt;&lt;li&gt;13 x sædehynde&lt;/li&gt;&lt;li&gt;20 x ryghynde&lt;/li&gt;&lt;/ul&gt; Maks. 110 kg per sæde.</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286867334_m_en_hd_1.jpg, https://vdxl.im/8720286867334_a_en_hd_1.jpg, https://vdxl.im/8720286867334_g_en_hd_1.jpg, https://vdxl.im/8720286867334_g_en_hd_2.jpg, https://vdxl.im/8720286867334_g_en_hd_3.jpg, https://vdxl.im/8720286867334_g_en_hd_4.jpg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Brun og cremefarvet</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sengegaerde-81x4x104-cm-massivt-fyrretrae-1</t>
+          <t>sengeramme-uden-madras-massivt-fyr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>818176</t>
+          <t>3306487</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8720286952191</t>
+          <t>8721102977435</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>429</v>
+        <v>1809</v>
       </c>
       <c r="F2" t="n">
-        <v>579</v>
+        <v>2419</v>
       </c>
       <c r="G2" t="n">
-        <v>253</v>
+        <v>1062</v>
       </c>
       <c r="H2" t="n">
-        <v>4410</v>
+        <v>26900</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952191_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102977435_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>818176</t>
+          <t>3306487</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>818176</t>
+          <t>3306487</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette sengegærde i træ har et fashionabelt design, og det fuldender din sengerammes look og passer til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Materiale i høj kvalitet: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har et lige åremønster, og knuderne i træet giver det et unikt og rustikt look.&lt;/li&gt;&lt;li&gt;Lameldesign i træ: Dette sengegærde i træ har et flot lameldesign i træ, så det lader lyset strømme ind i rummet, og det føjer et strejf af moderne stil til ethvert soveværelse.&lt;/li&gt;&lt;li&gt;Komfortabel støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Mål: 106 x 4 x 104 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Nyd en god nattesøvn med dette sengestel i træ! Det er et praktisk og dekorativt supplement til dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Alsidig sengegavl: Denne sengeramme har en sengegavl, der giver fremragende rygstøtte, når du sidder op og læser eller ser tv. Den giver også et dekorativt præg.&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Produktmål: 219 x 96 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 90 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Mål, sengegavl: 96 x 19 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med opbevaringshylder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegærde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952191_m_en_hd_1.jpg, https://vdxl.im/8720286952191_a_en_hd_1.jpg, https://vdxl.im/8720286952191_g_en_hd_1.jpg, https://vdxl.im/8720286952191_g_en_hd_2.jpg, https://vdxl.im/8720286952191_g_en_hd_3.jpg, https://vdxl.im/8720286952191_g_en_hd_4.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663924059/test/Image%20with%20Text/8888%20solid%20wood/DKsolidwood.png</t>
+          <t>https://vdxl.im/8721102977435_m_en_hd_1.jpg, https://vdxl.im/8721102977435_a_en_hd_1.jpg, https://vdxl.im/8721102977435_g_en_hd_1.jpg, https://vdxl.im/8721102977435_g_en_hd_2.jpg, https://vdxl.im/8721102977435_g_en_hd_3.jpg, https://vdxl.im/8721102977435_g_en_hd_4.jpg, https://vdxl.im/8721102977435_g_en_hd_5.jpg, https://vdxl.im/8721102977435_g_en_hd_6.jpg, https://vdxl.im/8721102977435_g_en_hd_7.jpg, https://vdxl.im/8721102977435_g_en_hd_8.jpg, https://vdxl.im/8721102977435_g_en_hd_9.jpg, https://vdxl.im/8721102977435_g_en_hd_10.jpg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>106 x 104 cm</t>
+          <t>90 x 200 cm</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -675,7 +675,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sengegaerde-81x4x104-cm-massivt-fyrretrae-1</t>
+          <t>sengeramme-uden-madras-massivt-fyr</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -685,25 +685,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>818200</t>
+          <t>3306493</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8720286952436</t>
+          <t>8721102977497</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>489</v>
+        <v>2769</v>
       </c>
       <c r="F3" t="n">
-        <v>659</v>
+        <v>3699</v>
       </c>
       <c r="G3" t="n">
-        <v>284</v>
+        <v>1627</v>
       </c>
       <c r="H3" t="n">
-        <v>3990</v>
+        <v>41100</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952436_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102977497_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>818200</t>
+          <t>3306493</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -755,17 +755,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>818200</t>
+          <t>3306493</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette sengegærde i træ har et fashionabelt design, og det fuldender din sengerammes look og passer til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Materiale i høj kvalitet: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har et lige åremønster, og knuderne i træet giver det et unikt og rustikt look.&lt;/li&gt;&lt;li&gt;Lameldesign i træ: Dette sengegærde i træ har et flot lameldesign i træ, så det lader lyset strømme ind i rummet, og det føjer et strejf af moderne stil til ethvert soveværelse.&lt;/li&gt;&lt;li&gt;Komfortabel støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Mål: 166 x 4 x 104 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Nyd en god nattesøvn med dette sengestel i træ! Det er et praktisk og dekorativt supplement til dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Alsidig sengegavl: Denne dobbelte sengeramme har en sengegavl, der giver fremragende rygstøtte, når du sidder op og læser eller ser tv. Den giver også et dekorativt præg-&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Produktmål: 219 x 126 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 120 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Mål, sengegavl: 126 x 19 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med opbevaringshylder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegærde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952436_m_en_hd_1.jpg, https://vdxl.im/8720286952436_a_en_hd_1.jpg, https://vdxl.im/8720286952436_g_en_hd_1.jpg, https://vdxl.im/8720286952436_g_en_hd_2.jpg, https://vdxl.im/8720286952436_g_en_hd_3.jpg, https://vdxl.im/8720286952436_g_en_hd_4.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663924059/test/Image%20with%20Text/8888%20solid%20wood/DKsolidwood.png</t>
+          <t>https://vdxl.im/8721102977497_m_en_hd_1.jpg, https://vdxl.im/8721102977497_a_en_hd_1.jpg, https://vdxl.im/8721102977497_g_en_hd_1.jpg, https://vdxl.im/8721102977497_g_en_hd_2.jpg, https://vdxl.im/8721102977497_g_en_hd_3.jpg, https://vdxl.im/8721102977497_g_en_hd_4.jpg, https://vdxl.im/8721102977497_g_en_hd_5.jpg, https://vdxl.im/8721102977497_g_en_hd_6.jpg, https://vdxl.im/8721102977497_g_en_hd_7.jpg, https://vdxl.im/8721102977497_g_en_hd_8.jpg, https://vdxl.im/8721102977497_g_en_hd_9.jpg, https://vdxl.im/8721102977497_g_en_hd_10.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Naturfarvet</t>
+          <t>Hvid</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>166 x 104 cm</t>
+          <t>120 x 200 cm</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -794,7 +794,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sengegaerde-81x4x104-cm-massivt-fyrretrae-1</t>
+          <t>sengeramme-uden-madras-massivt-fyr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -804,25 +804,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>818201</t>
+          <t>3306495</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8720286952443</t>
+          <t>8721102977510</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>579</v>
+        <v>2539</v>
       </c>
       <c r="F4" t="n">
-        <v>779</v>
+        <v>3389</v>
       </c>
       <c r="G4" t="n">
-        <v>337</v>
+        <v>1490</v>
       </c>
       <c r="H4" t="n">
-        <v>3990</v>
+        <v>42000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -859,12 +859,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952443_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102977510_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>818201</t>
+          <t>3306495</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>818201</t>
+          <t>3306495</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette sengegærde i træ har et fashionabelt design, og det fuldender din sengerammes look og passer til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Flot look: Sengegærdets stilfulde farve og design passer nemt ind i din indretning.&lt;/li&gt;&lt;li&gt;Materiale i høj kvalitet: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har et lige åremønster, og knuderne i træet giver det et unikt og rustikt look.&lt;/li&gt;&lt;li&gt;Sengetyper: Sengegærdet bruges til senge uden sengegærde.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Mål: 166 x 4 x 104 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Nyd en god nattesøvn med dette sengestel i træ! Det er et praktisk og dekorativt supplement til dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Alsidig sengegavl: Denne dobbelte sengeramme har en sengegavl, der giver fremragende rygstøtte, når du sidder op og læser eller ser tv. Den giver også et dekorativt præg-&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Produktmål: 219 x 146 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 140 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Mål, sengegavl: 146 x 19 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med opbevaringshylder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegærde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952443_m_en_hd_1.jpg, https://vdxl.im/8720286952443_a_en_hd_1.jpg, https://vdxl.im/8720286952443_g_en_hd_1.jpg, https://vdxl.im/8720286952443_g_en_hd_2.jpg, https://vdxl.im/8720286952443_g_en_hd_3.jpg, https://vdxl.im/8720286952443_g_en_hd_4.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663924059/test/Image%20with%20Text/8888%20solid%20wood/DKsolidwood.png</t>
+          <t>https://vdxl.im/8721102977510_m_en_hd_1.jpg, https://vdxl.im/8721102977510_a_en_hd_1.jpg, https://vdxl.im/8721102977510_g_en_hd_1.jpg, https://vdxl.im/8721102977510_g_en_hd_2.jpg, https://vdxl.im/8721102977510_g_en_hd_3.jpg, https://vdxl.im/8721102977510_g_en_hd_4.jpg, https://vdxl.im/8721102977510_g_en_hd_5.jpg, https://vdxl.im/8721102977510_g_en_hd_6.jpg, https://vdxl.im/8721102977510_g_en_hd_7.jpg, https://vdxl.im/8721102977510_g_en_hd_8.jpg, https://vdxl.im/8721102977510_g_en_hd_9.jpg, https://vdxl.im/8721102977510_g_en_hd_10.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Hvid</t>
+          <t>Naturfarvet</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>166 x 104 cm</t>
+          <t>140 x 200 cm</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -913,7 +913,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sengegaerde-81x4x104-cm-massivt-fyrretrae-1</t>
+          <t>sengeramme-uden-madras-massivt-fyr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -923,25 +923,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>818205</t>
+          <t>3306507</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8720286952481</t>
+          <t>8721102977633</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>519</v>
+        <v>2909</v>
       </c>
       <c r="F5" t="n">
-        <v>699</v>
+        <v>3879</v>
       </c>
       <c r="G5" t="n">
-        <v>304</v>
+        <v>1712</v>
       </c>
       <c r="H5" t="n">
-        <v>3990</v>
+        <v>50500</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -978,12 +978,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952481_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102977633_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>818205</t>
+          <t>3306507</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>818205</t>
+          <t>3306507</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette sengegærde i træ har et fashionabelt design, og det fuldender din sengerammes look og passer til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Materiale i høj kvalitet: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har et lige åremønster, og knuderne i træet giver det et unikt og rustikt look.&lt;/li&gt;&lt;li&gt;Lameldesign i træ: Dette sengegærde i træ har et flot lameldesign i træ, så det lader lyset strømme ind i rummet, og det føjer et strejf af moderne stil til ethvert soveværelse.&lt;/li&gt;&lt;li&gt;Komfortabel støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Mål: 186 x 4 x 104 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Nyd en god nattesøvn med dette sengestel i træ! Det er et praktisk og dekorativt supplement til dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Alsidig sengegavl: Denne dobbelte sengeramme har en sengegavl, der giver fremragende rygstøtte, når du sidder op og læser eller ser tv. Den giver også et dekorativt præg-&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Produktmål: 219 x 206 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 200 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Mål, sengegavl: 206 x 19 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med opbevaringshylder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegærde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952481_m_en_hd_1.jpg, https://vdxl.im/8720286952481_a_en_hd_1.jpg, https://vdxl.im/8720286952481_g_en_hd_1.jpg, https://vdxl.im/8720286952481_g_en_hd_2.jpg, https://vdxl.im/8720286952481_g_en_hd_3.jpg, https://vdxl.im/8720286952481_g_en_hd_4.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663924059/test/Image%20with%20Text/8888%20solid%20wood/DKsolidwood.png</t>
+          <t>https://vdxl.im/8721102977633_m_en_hd_1.jpg, https://vdxl.im/8721102977633_a_en_hd_1.jpg, https://vdxl.im/8721102977633_g_en_hd_1.jpg, https://vdxl.im/8721102977633_g_en_hd_2.jpg, https://vdxl.im/8721102977633_g_en_hd_3.jpg, https://vdxl.im/8721102977633_g_en_hd_4.jpg, https://vdxl.im/8721102977633_g_en_hd_5.jpg, https://vdxl.im/8721102977633_g_en_hd_6.jpg, https://vdxl.im/8721102977633_g_en_hd_7.jpg, https://vdxl.im/8721102977633_g_en_hd_8.jpg, https://vdxl.im/8721102977633_g_en_hd_9.jpg, https://vdxl.im/8721102977633_g_en_hd_10.jpg, https://vdxl.im/8721102977633_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>186 x 104 cm</t>
+          <t>200 x 200 cm</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
@@ -1032,7 +1032,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sengegaerde-81x4x104-cm-massivt-fyrretrae-1</t>
+          <t>sengeramme-uden-madras-massivt-fyr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1042,25 +1042,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>818210</t>
+          <t>3306511</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8720286952535</t>
+          <t>8721102977671</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>549</v>
+        <v>1739</v>
       </c>
       <c r="F6" t="n">
-        <v>739</v>
+        <v>2319</v>
       </c>
       <c r="G6" t="n">
-        <v>322</v>
+        <v>1020</v>
       </c>
       <c r="H6" t="n">
-        <v>3990</v>
+        <v>24400</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952535_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102977671_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>818210</t>
+          <t>3306511</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1112,17 +1112,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>818210</t>
+          <t>3306511</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette sengegærde i træ har et fashionabelt design, og det fuldender din sengerammes look og passer til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Materiale i høj kvalitet: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har et lige åremønster, og knuderne i træet giver det et unikt og rustikt look.&lt;/li&gt;&lt;li&gt;Lameldesign i træ: Dette sengegærde i træ har et flot lameldesign i træ, så det lader lyset strømme ind i rummet, og det føjer et strejf af moderne stil til ethvert soveværelse.&lt;/li&gt;&lt;li&gt;Komfortabel støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Mål: 206 x 4 x 104 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Nyd en god nattesøvn med dette sengestel i træ! Det er et praktisk og dekorativt supplement til dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Alsidig sengegavl: Denne sengeramme har en sengegavl, der giver fremragende rygstøtte, når du sidder op og læser eller ser tv. Den giver også et dekorativt præg.&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Produktmål: 209 x 81 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 75 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Mål, sengegavl: 81 x 19 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med opbevaringshylder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegærde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286952535_m_en_hd_1.jpg, https://vdxl.im/8720286952535_a_en_hd_1.jpg, https://vdxl.im/8720286952535_g_en_hd_1.jpg, https://vdxl.im/8720286952535_g_en_hd_2.jpg, https://vdxl.im/8720286952535_g_en_hd_3.jpg, https://vdxl.im/8720286952535_g_en_hd_4.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663924059/test/Image%20with%20Text/8888%20solid%20wood/DKsolidwood.png</t>
+          <t>https://vdxl.im/8721102977671_m_en_hd_1.jpg, https://vdxl.im/8721102977671_a_en_hd_1.jpg, https://vdxl.im/8721102977671_g_en_hd_1.jpg, https://vdxl.im/8721102977671_g_en_hd_2.jpg, https://vdxl.im/8721102977671_g_en_hd_3.jpg, https://vdxl.im/8721102977671_g_en_hd_4.jpg, https://vdxl.im/8721102977671_g_en_hd_5.jpg, https://vdxl.im/8721102977671_g_en_hd_6.jpg, https://vdxl.im/8721102977671_g_en_hd_7.jpg, https://vdxl.im/8721102977671_g_en_hd_8.jpg, https://vdxl.im/8721102977671_g_en_hd_9.jpg, https://vdxl.im/8721102977671_g_en_hd_10.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Naturfarvet</t>
+          <t>Hvid</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>206 x 104 cm</t>
+          <t>75 x 190 cm</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
@@ -1151,7 +1151,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sofasaet-til-haven-7-dele-med-hynder-polyrattan-90</t>
+          <t>sengeramme-uden-madras-massivt-fyr</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1161,25 +1161,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3251725</t>
+          <t>3306514</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8721102307003</t>
+          <t>8721102977701</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4679</v>
+        <v>1779</v>
       </c>
       <c r="F7" t="n">
-        <v>6239</v>
+        <v>2379</v>
       </c>
       <c r="G7" t="n">
-        <v>2753</v>
+        <v>1043</v>
       </c>
       <c r="H7" t="n">
-        <v>62800</v>
+        <v>27000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721102307003_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102977701_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3251725</t>
+          <t>3306514</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1231,17 +1231,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3251725</t>
+          <t>3306514</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette havesofasæt er den perfekte tilføjelse til din have eller terrasse og giver et behageligt og indbydende sted at sidde og snakke med familie og venner eller bare slappe af og nyde udendørslivet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: PE-rattan, også kendt som polyrattan, er et stærkt syntetisk materiale, der ikke kræver meget vedligeholdelse, og det ligner naturlig rattan. Det er let i vægt, nemt at rengøre, og det anvendes ofte til udendørs møbler grundet dets holdbarhed og vejrbestandige egenskaber.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion med vandafvisende pose: Havesofaen har opbevaringsplads under sædet med en vandafvisende pose til opbevaring af hynder, legetøj og andre ting. De indvendige poser har et topdæksel og kan fastgøres sikkert til sæderne med velcrolukninger for ekstra stabilitet.&lt;/li&gt;&lt;li&gt;Komfortabel siddeoplevelse: Disse havemøbler leveres med tykt polstrede hynder, så de giver en komfortabel siddeoplevelse.&lt;/li&gt;&lt;li&gt;Aftagelige og vaskbare betræk: Disse sædehynder er forsynet med aftagelige betræk, så de nemt kan vaskes og vedligeholdes.&lt;/li&gt;&lt;li&gt;Modulært design: Dette havemøbelsæt har et modulært design, der gør det fleksibelt og nemt at flytte rundt på, så du kan skabe et skræddersyet havemøbelarrangement.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Vi anbefaler, at du beskytter dine udendørs møbler med et vandtæt overtræk for at sikre, at de forbliver smukke.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Maks. bæreevne (pr. sæde ): 110 kg&lt;/li&gt;&lt;li&gt;UV-resistent&lt;/li&gt;&lt;li&gt;Justerbare plastfødder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hjørnemodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 62 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midtermodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofa med armlæn:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 65,5 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;Armlænets højde fra gulvet: 55 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hynde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, parasoldug: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale, sædehynde: Skum&lt;/li&gt;&lt;li&gt;Fyldmateriale, ryghynde: Bomuldsfibre&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 55 x 55 x 3 cm (B x D x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 55 x 45 x 13 cm (L x B x T)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x hjørnemodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;3 x midtermodul med opbevaringsfunktion og vandafvisende taske&lt;/li&gt;&lt;li&gt;2 x sofamodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;9 x ryghynde&lt;/li&gt;&lt;li&gt;7 x sædehynde med aftageligt og vaskbart betræk&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Nyd en god nattesøvn med dette sengestel i træ! Det er et praktisk og dekorativt supplement til dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Alsidig sengegavl: Denne sengeramme har en sengegavl, der giver fremragende rygstøtte, når du sidder op og læser eller ser tv. Den giver også et dekorativt præg.&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Produktmål: 209 x 96 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 90 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Mål, sengegavl: 96 x 19 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med opbevaringshylder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegærde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721102307003_m_en_hd_1.jpg, https://vdxl.im/8721102307003_a_en_hd_1.jpg, https://vdxl.im/8721102307003_g_en_hd_1.jpg, https://res.cloudinary.com/vdxl/image/upload/v1709801887/VN%20rattan/1_Light_beige_Rattan_Premium_rattan_.png</t>
+          <t>https://vdxl.im/8721102977701_m_en_hd_1.jpg, https://vdxl.im/8721102977701_a_en_hd_1.jpg, https://vdxl.im/8721102977701_g_en_hd_1.jpg, https://vdxl.im/8721102977701_g_en_hd_2.jpg, https://vdxl.im/8721102977701_g_en_hd_3.jpg, https://vdxl.im/8721102977701_g_en_hd_4.jpg, https://vdxl.im/8721102977701_g_en_hd_5.jpg, https://vdxl.im/8721102977701_g_en_hd_6.jpg, https://vdxl.im/8721102977701_g_en_hd_7.jpg, https://vdxl.im/8721102977701_g_en_hd_8.jpg, https://vdxl.im/8721102977701_g_en_hd_9.jpg, https://vdxl.im/8721102977701_g_en_hd_10.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1251,13 +1251,7042 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>beige og cremefarvet</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>90 x 190 cm</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sengeramme-uden-madras-massivt-fyr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3306522</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8721102977787</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2489</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3319</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1462</v>
+      </c>
+      <c r="H8" t="n">
+        <v>41300</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>31</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721102977787_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3306522</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3306522</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en god nattesøvn med dette sengestel i træ! Det er et praktisk og dekorativt supplement til dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Alsidig sengegavl: Denne dobbelte sengeramme har en sengegavl, der giver fremragende rygstøtte, når du sidder op og læser eller ser tv. Den giver også et dekorativt præg-&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Produktmål: 209 x 146 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 140 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Mål, sengegavl: 146 x 19 x 82 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med opbevaringshylder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x sengegærde&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721102977787_m_en_hd_1.jpg, https://vdxl.im/8721102977787_a_en_hd_1.jpg, https://vdxl.im/8721102977787_g_en_hd_1.jpg, https://vdxl.im/8721102977787_g_en_hd_2.jpg, https://vdxl.im/8721102977787_g_en_hd_3.jpg, https://vdxl.im/8721102977787_g_en_hd_4.jpg, https://vdxl.im/8721102977787_g_en_hd_5.jpg, https://vdxl.im/8721102977787_g_en_hd_6.jpg, https://vdxl.im/8721102977787_g_en_hd_7.jpg, https://vdxl.im/8721102977787_g_en_hd_8.jpg, https://vdxl.im/8721102977787_g_en_hd_9.jpg, https://vdxl.im/8721102977787_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Naturfarvet</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>kaffebord-med-hylde-gra-sonoma-90x50x40-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>868234</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8721158248718</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>529</v>
+      </c>
+      <c r="F9" t="n">
+        <v>709</v>
+      </c>
+      <c r="G9" t="n">
+        <v>310</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12750</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>56</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248718_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>868234</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>868234</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette sofabord er den perfekte kombination af et moderne look og praktisk funktion, designet til at forny enhver stue. Den slanke rektangulære form med en glat mat finish udstråler enkelhed og elegance, samtidig med at den giver en ideel overflade til hverdagens aktiviteter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Bordrammen og benene er lavet af stærkt stål, som sikrer holdbarhed og stabilitet til daglig brug. Den konstruerede træoverflade har en mat finish, der passer perfekt til moderne stilarter og tilføjer elegance til ethvert rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Bordet kommer med stilrene stålben, der giver ekstra stabilitet og en solid ramme til at holde det stabilt på alle overflader. Den konstruerede træplade er ideel til at vise dine yndlingsmagasiner, dekorationer eller drinks.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Egenskaber / funktion / design:&lt;/b&gt; Bygget til at holde, dette bord giver en pålidelig midterpunkt i din stue. Det moderne design med rene linjer og en glat tekstur passer perfekt ind i minimalistisk indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Dette sofabord er klart til indendørs brug, specielt i stuer. Uanset om du har en hyggelig aften derhjemme med familien eller er til sammenkomst, er det et praktisk sted at sætte drinks, snacks, bøger og mere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde det pænt, skynd dig at tørre bordet af med en fugtig klud for at fjerne støv og spild. Undgå hårde rengøringsmidler for at beskytte bordets finish. Regelmæssig pleje holder det stilfuldt i dit hjem i mange år frem.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørtræ og stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 1 hylde&lt;/li&gt;&lt;li&gt;Maks. vægt: 75 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248718_mo-im_en_hd_1.jpg, https://vdxl.im/8721158248718_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158248718_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158248718_mo-im_en_hd_2.jpg, https://vdxl.im/8721158248718_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158248718_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158248718_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158248718_detail_en_hd_1.jpg, https://vdxl.im/8721158248718_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158248718_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158248718_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>90 x 50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>kaffebord-med-hylde-gra-sonoma-90x50x40-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>868235</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8721158248725</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>549</v>
+      </c>
+      <c r="F10" t="n">
+        <v>739</v>
+      </c>
+      <c r="G10" t="n">
+        <v>319</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12750</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>45</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248725_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>868235</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>868235</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette sofabord er den perfekte kombination af et moderne look og praktisk funktion, designet til at forny enhver stue. Den slanke rektangulære form med en glat mat finish udstråler enkelhed og elegance, samtidig med at den giver en ideel overflade til hverdagens aktiviteter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Bordrammen og benene er lavet af stærkt stål, som sikrer holdbarhed og stabilitet til daglig brug. Den konstruerede træoverflade har en mat finish, der passer perfekt til moderne stilarter og tilføjer elegance til ethvert rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Bordet kommer med stilrene stålben, der giver ekstra stabilitet og en solid ramme til at holde det stabilt på alle overflader. Den konstruerede træplade er ideel til at vise dine yndlingsmagasiner, dekorationer eller drinks.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Egenskaber / funktion / design:&lt;/b&gt; Bygget til at holde, dette bord giver en pålidelig midterpunkt i din stue. Det moderne design med rene linjer og en glat tekstur passer perfekt ind i minimalistisk indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Dette sofabord er klart til indendørs brug, specielt i stuer. Uanset om du har en hyggelig aften derhjemme med familien eller er til sammenkomst, er det et praktisk sted at sætte drinks, snacks, bøger og mere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde det pænt, skynd dig at tørre bordet af med en fugtig klud for at fjerne støv og spild. Undgå hårde rengøringsmidler for at beskytte bordets finish. Regelmæssig pleje holder det stilfuldt i dit hjem i mange år frem.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørtræ og stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 1 hylde&lt;/li&gt;&lt;li&gt;Maks. vægt: 75 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248725_mo-im_en_hd_1.jpg, https://vdxl.im/8721158248725_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158248725_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158248725_mo-im_en_hd_2.jpg, https://vdxl.im/8721158248725_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158248725_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158248725_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158248725_detail_en_hd_1.jpg, https://vdxl.im/8721158248725_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158248725_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158248725_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>90 x 50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>kaffebord-med-hylde-gra-sonoma-90x50x40-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>868236</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8721158248732</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>579</v>
+      </c>
+      <c r="F11" t="n">
+        <v>779</v>
+      </c>
+      <c r="G11" t="n">
+        <v>339</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12750</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>51</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248732_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>868236</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>868236</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette sofabord er den perfekte kombination af et moderne look og praktisk funktion, designet til at forny enhver stue. Den slanke rektangulære form med en glat mat finish udstråler enkelhed og elegance, samtidig med at den giver en ideel overflade til hverdagens aktiviteter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Bordrammen og benene er lavet af stærkt stål, som sikrer holdbarhed og stabilitet til daglig brug. Den konstruerede træoverflade har en mat finish, der passer perfekt til moderne stilarter og tilføjer elegance til ethvert rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Bordet kommer med stilrene stålben, der giver ekstra stabilitet og en solid ramme til at holde det stabilt på alle overflader. Den konstruerede træplade er ideel til at vise dine yndlingsmagasiner, dekorationer eller drinks.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Egenskaber / funktion / design:&lt;/b&gt; Bygget til at holde, dette bord giver en pålidelig midterpunkt i din stue. Det moderne design med rene linjer og en glat tekstur passer perfekt ind i minimalistisk indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Dette sofabord er klart til indendørs brug, specielt i stuer. Uanset om du har en hyggelig aften derhjemme med familien eller er til sammenkomst, er det et praktisk sted at sætte drinks, snacks, bøger og mere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde det pænt, skynd dig at tørre bordet af med en fugtig klud for at fjerne støv og spild. Undgå hårde rengøringsmidler for at beskytte bordets finish. Regelmæssig pleje holder det stilfuldt i dit hjem i mange år frem.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørtræ og stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 1 hylde&lt;/li&gt;&lt;li&gt;Maks. vægt: 75 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248732_mo-im_en_hd_1.jpg, https://vdxl.im/8721158248732_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158248732_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158248732_mo-im_en_hd_2.jpg, https://vdxl.im/8721158248732_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158248732_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158248732_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158248732_detail_en_hd_1.jpg, https://vdxl.im/8721158248732_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158248732_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158248732_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>90 x 50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>kaffebord-med-hylde-gra-sonoma-90x50x40-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>868231</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8721158248688</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>539</v>
+      </c>
+      <c r="F12" t="n">
+        <v>719</v>
+      </c>
+      <c r="G12" t="n">
+        <v>317</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12750</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>89</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248688_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>868231</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>868231</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette sofabord er den perfekte kombination af et moderne look og praktisk funktion, designet til at forny enhver stue. Den slanke rektangulære form med en glat mat finish udstråler enkelhed og elegance, samtidig med at den giver en ideel overflade til hverdagens aktiviteter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Bordrammen og benene er lavet af stærkt stål, som sikrer holdbarhed og stabilitet til daglig brug. Den konstruerede træoverflade har en mat finish, der passer perfekt til moderne stilarter og tilføjer elegance til ethvert rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Bordet kommer med stilrene stålben, der giver ekstra stabilitet og en solid ramme til at holde det stabilt på alle overflader. Den konstruerede træplade er ideel til at vise dine yndlingsmagasiner, dekorationer eller drinks.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Egenskaber / funktion / design:&lt;/b&gt; Bygget til at holde, dette bord giver en pålidelig midterpunkt i din stue. Det moderne design med rene linjer og en glat tekstur passer perfekt ind i minimalistisk indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Dette sofabord er klart til indendørs brug, specielt i stuer. Uanset om du har en hyggelig aften derhjemme med familien eller er til sammenkomst, er det et praktisk sted at sætte drinks, snacks, bøger og mere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde det pænt, skynd dig at tørre bordet af med en fugtig klud for at fjerne støv og spild. Undgå hårde rengøringsmidler for at beskytte bordets finish. Regelmæssig pleje holder det stilfuldt i dit hjem i mange år frem.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørtræ og stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 1 hylde&lt;/li&gt;&lt;li&gt;Maks. vægt: 75 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248688_mo-im_en_hd_1.jpg, https://vdxl.im/8721158248688_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158248688_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158248688_mo-im_en_hd_2.jpg, https://vdxl.im/8721158248688_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158248688_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158248688_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158248688_detail_en_hd_1.jpg, https://vdxl.im/8721158248688_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158248688_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158248688_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>90 x 50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>kaffebord-med-hylde-gra-sonoma-90x50x40-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>868232</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8721158248695</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>509</v>
+      </c>
+      <c r="F13" t="n">
+        <v>679</v>
+      </c>
+      <c r="G13" t="n">
+        <v>297</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12750</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>69</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248695_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>868232</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>868232</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette sofabord er den perfekte kombination af et moderne look og praktisk funktion, designet til at forny enhver stue. Den slanke rektangulære form med en glat mat finish udstråler enkelhed og elegance, samtidig med at den giver en ideel overflade til hverdagens aktiviteter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Bordrammen og benene er lavet af stærkt stål, som sikrer holdbarhed og stabilitet til daglig brug. Den konstruerede træoverflade har en mat finish, der passer perfekt til moderne stilarter og tilføjer elegance til ethvert rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Bordet kommer med stilrene stålben, der giver ekstra stabilitet og en solid ramme til at holde det stabilt på alle overflader. Den konstruerede træplade er ideel til at vise dine yndlingsmagasiner, dekorationer eller drinks.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Egenskaber / funktion / design:&lt;/b&gt; Bygget til at holde, dette bord giver en pålidelig midterpunkt i din stue. Det moderne design med rene linjer og en glat tekstur passer perfekt ind i minimalistisk indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Dette sofabord er klart til indendørs brug, specielt i stuer. Uanset om du har en hyggelig aften derhjemme med familien eller er til sammenkomst, er det et praktisk sted at sætte drinks, snacks, bøger og mere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde det pænt, skynd dig at tørre bordet af med en fugtig klud for at fjerne støv og spild. Undgå hårde rengøringsmidler for at beskytte bordets finish. Regelmæssig pleje holder det stilfuldt i dit hjem i mange år frem.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma eg&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørtræ og stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 1 hylde&lt;/li&gt;&lt;li&gt;Maks. vægt: 75 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248695_mo-im_en_hd_1.jpg, https://vdxl.im/8721158248695_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158248695_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158248695_mo-im_en_hd_2.jpg, https://vdxl.im/8721158248695_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158248695_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158248695_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158248695_detail_en_hd_1.jpg, https://vdxl.im/8721158248695_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158248695_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158248695_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>90 x 50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>kaffebord-med-hylde-gra-sonoma-90x50x40-cm-konstrueret-trae</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>868233</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8721158248701</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>529</v>
+      </c>
+      <c r="F14" t="n">
+        <v>709</v>
+      </c>
+      <c r="G14" t="n">
+        <v>307</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12750</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>54</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248701_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>868233</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>868233</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette sofabord er den perfekte kombination af et moderne look og praktisk funktion, designet til at forny enhver stue. Den slanke rektangulære form med en glat mat finish udstråler enkelhed og elegance, samtidig med at den giver en ideel overflade til hverdagens aktiviteter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Bordrammen og benene er lavet af stærkt stål, som sikrer holdbarhed og stabilitet til daglig brug. Den konstruerede træoverflade har en mat finish, der passer perfekt til moderne stilarter og tilføjer elegance til ethvert rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Bordet kommer med stilrene stålben, der giver ekstra stabilitet og en solid ramme til at holde det stabilt på alle overflader. Den konstruerede træplade er ideel til at vise dine yndlingsmagasiner, dekorationer eller drinks.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Egenskaber / funktion / design:&lt;/b&gt; Bygget til at holde, dette bord giver en pålidelig midterpunkt i din stue. Det moderne design med rene linjer og en glat tekstur passer perfekt ind i minimalistisk indretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Dette sofabord er klart til indendørs brug, specielt i stuer. Uanset om du har en hyggelig aften derhjemme med familien eller er til sammenkomst, er det et praktisk sted at sætte drinks, snacks, bøger og mere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vedligeholdelse:&lt;/b&gt; For at holde det pænt, skynd dig at tørre bordet af med en fugtig klud for at fjerne støv og spild. Undgå hårde rengøringsmidler for at beskytte bordets finish. Regelmæssig pleje holder det stilfuldt i dit hjem i mange år frem.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget eg&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørtræ og stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 90 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 1 hylde&lt;/li&gt;&lt;li&gt;Maks. vægt: 75 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158248701_mo-im_en_hd_1.jpg, https://vdxl.im/8721158248701_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158248701_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158248701_mo-im_en_hd_2.jpg, https://vdxl.im/8721158248701_wbg-fr_en_hd_3.jpg, https://vdxl.im/8721158248701_wbg-si_en_hd_4.jpg, https://vdxl.im/8721158248701_wbg-ba_en_hd_2.jpg, https://vdxl.im/8721158248701_detail_en_hd_1.jpg, https://vdxl.im/8721158248701_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158248701_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158248701_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Røget eg</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>90 x 50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>vaegreol-med-12-rum-konstrueret-trae-etraesfarve-1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>860014</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8721158650450</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>519</v>
+      </c>
+      <c r="F15" t="n">
+        <v>699</v>
+      </c>
+      <c r="G15" t="n">
+        <v>305</v>
+      </c>
+      <c r="H15" t="n">
+        <v>11490</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>37</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650450_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>860014</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>860014</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne væghylde er tænkt som en både dekorativ og praktisk udvidelse af din boligindretning.&lt;br /&gt;&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Væghylden har 15 rum, som giver praktisk opbevaringsplads, så du kan holde styr på dine forskellige daglige fornødenheder og have dem inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende kubehylde optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Brede anvendelsesmuligheder: Takket være sit tidløse design supplerer denne svævehylde ubesværet din indretning og kan bruges i stuen, soveværelset og meget mere.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Takket være den glatte overflade er denne wall cube-opbevaring nem at rengøre med en fugtig klud og kræver mindre vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;br /&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 70 x 18 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Mål på hvert rum: 13,5/26,5/27 x 18 x 23 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Antal rum: 12&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 60 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650450_m_en_hd_1.jpg, https://vdxl.im/8721158650450_a_en_hd_1.jpg, https://vdxl.im/8721158650450_g_en_hd_1.jpg, https://vdxl.im/8721158650450_g_en_hd_2.jpg, https://vdxl.im/8721158650450_g_en_hd_3.jpg, https://vdxl.im/8721158650450_g_en_hd_4.jpg, https://vdxl.im/8721158650450_g_en_hd_5.jpg, https://vdxl.im/8721158650450_g_en_hd_6.jpg, https://vdxl.im/8721158650450_g_en_hd_7.jpg, https://vdxl.im/8721158650450_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>vaegreol-med-12-rum-konstrueret-trae-etraesfarve-1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>860015</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8721158650467</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>409</v>
+      </c>
+      <c r="F16" t="n">
+        <v>549</v>
+      </c>
+      <c r="G16" t="n">
+        <v>239</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11700</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>165</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650467_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>860015</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>860015</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne væghylde er tænkt som en både dekorativ og praktisk udvidelse af din boligindretning.&lt;br /&gt;&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Væghylden har 15 rum, som giver praktisk opbevaringsplads, så du kan holde styr på dine forskellige daglige fornødenheder og have dem inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende kubehylde optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Brede anvendelsesmuligheder: Takket være sit tidløse design supplerer denne svævehylde ubesværet din indretning og kan bruges i stuen, soveværelset og meget mere.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Takket være den glatte overflade er denne wall cube-opbevaring nem at rengøre med en fugtig klud og kræver mindre vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;br /&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 70 x 18 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Mål på hvert rum: 13,5/26,5/27 x 18 x 23 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Antal rum: 12&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 60 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650467_m_en_hd_1.jpg, https://vdxl.im/8721158650467_a_en_hd_1.jpg, https://vdxl.im/8721158650467_g_en_hd_1.jpg, https://vdxl.im/8721158650467_g_en_hd_2.jpg, https://vdxl.im/8721158650467_g_en_hd_3.jpg, https://vdxl.im/8721158650467_g_en_hd_4.jpg, https://vdxl.im/8721158650467_g_en_hd_5.jpg, https://vdxl.im/8721158650467_g_en_hd_6.jpg, https://vdxl.im/8721158650467_g_en_hd_7.jpg, https://vdxl.im/8721158650467_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>vaegreol-med-12-rum-konstrueret-trae-etraesfarve-1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>860020</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8721158650511</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>469</v>
+      </c>
+      <c r="F17" t="n">
+        <v>629</v>
+      </c>
+      <c r="G17" t="n">
+        <v>276</v>
+      </c>
+      <c r="H17" t="n">
+        <v>11580</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>19</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650511_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>860020</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>860020</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne væghylde er tænkt som en både dekorativ og praktisk udvidelse af din boligindretning.&lt;br /&gt;&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Væghylden har 15 rum, som giver praktisk opbevaringsplads, så du kan holde styr på dine forskellige daglige fornødenheder og have dem inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende kubehylde optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Brede anvendelsesmuligheder: Takket være sit tidløse design supplerer denne svævehylde ubesværet din indretning og kan bruges i stuen, soveværelset og meget mere.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Takket være den glatte overflade er denne wall cube-opbevaring nem at rengøre med en fugtig klud og kræver mindre vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;br /&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: antikt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 70 x 18 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Mål på hvert rum: 13,5/26,5/27 x 18 x 23 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Antal rum: 12&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 60 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650511_m_en_hd_1.jpg, https://vdxl.im/8721158650511_a_en_hd_1.jpg, https://vdxl.im/8721158650511_g_en_hd_1.jpg, https://vdxl.im/8721158650511_g_en_hd_2.jpg, https://vdxl.im/8721158650511_g_en_hd_3.jpg, https://vdxl.im/8721158650511_g_en_hd_4.jpg, https://vdxl.im/8721158650511_g_en_hd_5.jpg, https://vdxl.im/8721158650511_g_en_hd_6.jpg, https://vdxl.im/8721158650511_g_en_hd_7.jpg, https://vdxl.im/8721158650511_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>vaegreol-med-12-rum-konstrueret-trae-etraesfarve-1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>860021</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8721158650528</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>459</v>
+      </c>
+      <c r="F18" t="n">
+        <v>619</v>
+      </c>
+      <c r="G18" t="n">
+        <v>270</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11600</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>38</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650528_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>860021</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>860021</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Denne væghylde er tænkt som en både dekorativ og praktisk udvidelse af din boligindretning.&lt;br /&gt;&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Væghylden har 15 rum, som giver praktisk opbevaringsplads, så du kan holde styr på dine forskellige daglige fornødenheder og have dem inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende kubehylde optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Brede anvendelsesmuligheder: Takket være sit tidløse design supplerer denne svævehylde ubesværet din indretning og kan bruges i stuen, soveværelset og meget mere.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Takket være den glatte overflade er denne wall cube-opbevaring nem at rengøre med en fugtig klud og kræver mindre vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;br /&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 70 x 18 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Mål på hvert rum: 13,5/26,5/27 x 18 x 23 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Antal rum: 12&lt;/li&gt;&lt;li&gt;Maks. bæreevne: 60 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158650528_m_en_hd_1.jpg, https://vdxl.im/8721158650528_a_en_hd_1.jpg, https://vdxl.im/8721158650528_g_en_hd_1.jpg, https://vdxl.im/8721158650528_g_en_hd_2.jpg, https://vdxl.im/8721158650528_g_en_hd_3.jpg, https://vdxl.im/8721158650528_g_en_hd_4.jpg, https://vdxl.im/8721158650528_g_en_hd_5.jpg, https://vdxl.im/8721158650528_g_en_hd_6.jpg, https://vdxl.im/8721158650528_g_en_hd_7.jpg, https://vdxl.im/8721158650528_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sofabord-100x50x35-cm-massivt-fyrretrae-1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>813420</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8720845579227</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1019</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1359</v>
+      </c>
+      <c r="G19" t="n">
+        <v>599</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16379</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>73</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845579227_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>813420</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>813420</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit hjem et strejf af elegance med dette stilfulde sofabord i træ.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Massivt fyrretræ: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har lige åremønstre, og knuderne giver materialet sit karakteristiske, rustikke udseende.&lt;/li&gt;&lt;li&gt;Løftetop: Dette sidebord er designet med en løftetop, der nemt kan justeres, så bordet har en komfortabel højde til brug af en laptop, når du skriver, eller når du spiser, mens du sidder i sofaen.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Dette sofabord har 2 store, skjulte rum under bordpladen til opbevaring af dine ting og sager. De beskytter dine ting mod støv, og de holder dit hjem pænt organiseret.&lt;/li&gt;&lt;li&gt;Stabilt stel: Stuebordets træstel giver robusthed og stabilitet.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Mål: 100 x 50 x 35 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845579227_m_en_hd_1.jpg, https://vdxl.im/8720845579227_a_en_hd_1.jpg, https://vdxl.im/8720845579227_g_en_hd_1.jpg, https://vdxl.im/8720845579227_g_en_hd_2.jpg, https://vdxl.im/8720845579227_g_en_hd_3.jpg, https://vdxl.im/8720845579227_g_en_hd_4.jpg, https://vdxl.im/8720845579227_g_en_hd_5.jpg, https://vdxl.im/8720845579227_g_en_hd_6.jpg, https://vdxl.im/8720845579227_g_en_hd_7.jpg, https://vdxl.im/8720845579227_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Naturfarvet</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sofabord-100x50x35-cm-massivt-fyrretrae-1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>813421</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8720845579234</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>989</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1319</v>
+      </c>
+      <c r="G20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H20" t="n">
+        <v>16379</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>88</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845579234_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>813421</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>813421</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit hjem et strejf af elegance med dette stilfulde sofabord i træ.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Massivt fyrretræ: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har lige åremønstre, og knuderne giver materialet sit karakteristiske, rustikke udseende.&lt;/li&gt;&lt;li&gt;Løftetop: Dette sidebord er designet med en løftetop, der nemt kan justeres, så bordet har en komfortabel højde til brug af en laptop, når du skriver, eller når du spiser, mens du sidder i sofaen.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Dette sofabord har 2 store, skjulte rum under bordpladen til opbevaring af dine ting og sager. De beskytter dine ting mod støv, og de holder dit hjem pænt organiseret.&lt;/li&gt;&lt;li&gt;Stabilt stel: Stuebordets træstel giver robusthed og stabilitet.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Mål: 100 x 50 x 35 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845579234_m_en_hd_1.jpg, https://vdxl.im/8720845579234_a_en_hd_1.jpg, https://vdxl.im/8720845579234_g_en_hd_1.jpg, https://vdxl.im/8720845579234_g_en_hd_2.jpg, https://vdxl.im/8720845579234_g_en_hd_3.jpg, https://vdxl.im/8720845579234_g_en_hd_4.jpg, https://vdxl.im/8720845579234_g_en_hd_5.jpg, https://vdxl.im/8720845579234_g_en_hd_6.jpg, https://vdxl.im/8720845579234_g_en_hd_7.jpg, https://vdxl.im/8720845579234_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sengebord-med-led-lys-vaeghaengt-1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>837133</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8721012257177</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>349</v>
+      </c>
+      <c r="F21" t="n">
+        <v>469</v>
+      </c>
+      <c r="G21" t="n">
+        <v>202</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7770</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>83</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012257177_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>837133</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>837133</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette tv-bord med LED-lys har et trendy, men praktisk design, og det bliver uden tvivl et fokuspunkt i rummet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Tv-møblet er fremstillet af konstrueret træ, så det er robust og holdbart.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Tv-enheden tilbyder god plads til at holde dine magasiner, bøger, fjernbetjeninger og andre småting pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;LED-lys med RGB-farver: Dette tv-bord er forsynet med LED-lys med RGB-farver, så du kan ændre lysfarven eller lade farven skifte automatisk.&lt;/li&gt;&lt;li&gt;Væghængt design: Dette medieskab kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;li&gt;Produktet har et USB-stik, der kræver en 5 V USB-strømkilde (medfølger ikke).&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 60 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Dette produkt må ikke anvendes, hvis nogen komponenter er ødelagte eller mangler. Dette produkt drives af DC 5V, men den certificerede 5V USB-strømkilde medfølger ikke. Højere spænding kan forårsage overophedning og medføre skader på enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012257177_m_en_hd_1.jpg, https://vdxl.im/8721012257177_a_en_hd_1.jpg, https://vdxl.im/8721012257177_g_en_hd_1.jpg, https://vdxl.im/8721012257177_g_en_hd_2.jpg, https://vdxl.im/8721012257177_g_en_hd_3.jpg, https://vdxl.im/8721012257177_g_en_hd_4.jpg, https://vdxl.im/8721012257177_g_en_hd_5.jpg, https://vdxl.im/8721012257177_g_en_hd_6.jpg, https://vdxl.im/8721012257177_g_en_hd_7.jpg, https://vdxl.im/8721012257177_g_en_hd_8.jpg, https://vdxl.im/8721012257177_g_en_hd_9.jpg, https://vdxl.im/8721012257177_g_en_hd_10.jpg, https://vdxl.im/8721012257177_g_en_hd_11.jpg, https://vdxl.im/8721012257177_g_en_hd_12.jpg, https://vdxl.im/8721012257177_g_en_hd_13.jpg, https://vdxl.im/8721012257177_g_en_hd_14.jpg, https://vdxl.im/8721012257177_g_en_hd_15.jpg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Betongrå</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sengebord-med-led-lys-vaeghaengt-1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>837135</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8721012257191</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>339</v>
+      </c>
+      <c r="F22" t="n">
+        <v>459</v>
+      </c>
+      <c r="G22" t="n">
+        <v>199</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7880</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>91</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012257191_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>837135</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>837135</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette tv-bord med LED-lys har et trendy, men praktisk design, og det bliver uden tvivl et fokuspunkt i rummet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Tv-møblet er fremstillet af konstrueret træ, så det er robust og holdbart.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Tv-enheden tilbyder god plads til at holde dine magasiner, bøger, fjernbetjeninger og andre småting pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;LED-lys med RGB-farver: Dette tv-bord er forsynet med LED-lys med RGB-farver, så du kan ændre lysfarven eller lade farven skifte automatisk.&lt;/li&gt;&lt;li&gt;Væghængt design: Dette medieskab kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;li&gt;Produktet har et USB-stik, der kræver en 5 V USB-strømkilde (medfølger ikke).&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 60 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Dette produkt må ikke anvendes, hvis nogen komponenter er ødelagte eller mangler. Dette produkt drives af DC 5V, men den certificerede 5V USB-strømkilde medfølger ikke. Højere spænding kan forårsage overophedning og medføre skader på enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012257191_m_en_hd_1.jpg, https://vdxl.im/8721012257191_a_en_hd_1.jpg, https://vdxl.im/8721012257191_g_en_hd_1.jpg, https://vdxl.im/8721012257191_g_en_hd_2.jpg, https://vdxl.im/8721012257191_g_en_hd_3.jpg, https://vdxl.im/8721012257191_g_en_hd_4.jpg, https://vdxl.im/8721012257191_g_en_hd_5.jpg, https://vdxl.im/8721012257191_g_en_hd_6.jpg, https://vdxl.im/8721012257191_g_en_hd_7.jpg, https://vdxl.im/8721012257191_g_en_hd_8.jpg, https://vdxl.im/8721012257191_g_en_hd_9.jpg, https://vdxl.im/8721012257191_g_en_hd_10.jpg, https://vdxl.im/8721012257191_g_en_hd_11.jpg, https://vdxl.im/8721012257191_g_en_hd_12.jpg, https://vdxl.im/8721012257191_g_en_hd_13.jpg, https://vdxl.im/8721012257191_g_en_hd_14.jpg, https://vdxl.im/8721012257191_g_en_hd_15.jpg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Røget eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sengebord-med-led-lys-vaeghaengt-1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>837137</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8721012257214</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>349</v>
+      </c>
+      <c r="F23" t="n">
+        <v>469</v>
+      </c>
+      <c r="G23" t="n">
+        <v>204</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7880</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>99</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012257214_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>837137</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>837137</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette tv-bord med LED-lys har et trendy, men praktisk design, og det bliver uden tvivl et fokuspunkt i rummet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Tv-møblet er fremstillet af konstrueret træ, så det er robust og holdbart.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Tv-enheden tilbyder god plads til at holde dine magasiner, bøger, fjernbetjeninger og andre småting pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;LED-lys med RGB-farver: Dette tv-bord er forsynet med LED-lys med RGB-farver, så du kan ændre lysfarven eller lade farven skifte automatisk.&lt;/li&gt;&lt;li&gt;Væghængt design: Dette medieskab kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;li&gt;Produktet har et USB-stik, der kræver en 5 V USB-strømkilde (medfølger ikke).&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 60 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Dette produkt må ikke anvendes, hvis nogen komponenter er ødelagte eller mangler. Dette produkt drives af DC 5V, men den certificerede 5V USB-strømkilde medfølger ikke. Højere spænding kan forårsage overophedning og medføre skader på enheden og potentiel risiko for brand.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012257214_m_en_hd_1.jpg, https://vdxl.im/8721012257214_a_en_hd_1.jpg, https://vdxl.im/8721012257214_g_en_hd_1.jpg, https://vdxl.im/8721012257214_g_en_hd_2.jpg, https://vdxl.im/8721012257214_g_en_hd_3.jpg, https://vdxl.im/8721012257214_g_en_hd_4.jpg, https://vdxl.im/8721012257214_g_en_hd_5.jpg, https://vdxl.im/8721012257214_g_en_hd_6.jpg, https://vdxl.im/8721012257214_g_en_hd_7.jpg, https://vdxl.im/8721012257214_g_en_hd_8.jpg, https://vdxl.im/8721012257214_g_en_hd_9.jpg, https://vdxl.im/8721012257214_g_en_hd_10.jpg, https://vdxl.im/8721012257214_g_en_hd_11.jpg, https://vdxl.im/8721012257214_g_en_hd_12.jpg, https://vdxl.im/8721012257214_g_en_hd_13.jpg, https://vdxl.im/8721012257214_g_en_hd_14.jpg, https://vdxl.im/8721012257214_g_en_hd_15.jpg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sengebord-med-led-lys-vaeghaengt-1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>882960</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8721288924360</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>359</v>
+      </c>
+      <c r="F24" t="n">
+        <v>479</v>
+      </c>
+      <c r="G24" t="n">
+        <v>212</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7160</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>45</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288924360_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>882960</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>882960</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette smarte vægmonterede LED TV-skabssæt tilføjer både stil og praktisk funktion til enhver stue. Med sin slanke, rektangulære form og moderne design passer det super godt ind i nutidige rum. Det er perfekt til folk, der gerne vil have både funktionalitet og stil. Dette TV-skab har et minimalistisk look, men maksimerer opbevaring og belysning. Når det hænges op, får du et strømlinet look, der frigiver gulvplads og skaber en følelse af moderne elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Skabet er lavet af konstrueret træ, så det både er holdbart og ser godt ud. Det er stærkt og modstandsdygtigt, altså perfekt til at holde sig pænt i mange år. Det passer ind i enhver moderne eller overgangsindretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Skabet har hylder af robust konstrueret træ og hængslede døre, der giver nem adgang. De medfølgende multicolor LED-strips, der drives via USB, tilføjer en moderne kant og kan sætte stemningen alt efter humør.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner /Design:&lt;/b&gt; Skabet er vægmonteret og sparer dermed plads. Du får mere gulvplads til andre ting, samtidig med at der er god opbevaring til medieudstyr, bøger og pynt. De minimalistiske linjer gør, at det passer ind i mange forskellige indretningsstile.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Fantastisk til stuer og underholdningscentre, er skabet perfekt til at samle TV og elektronik, samtidig med at det skaber orden og et pænt look. Det er ideelt til lejligheder og rum, hvor hver kvadratcentimeter tæller.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Hold skabet pænt ved at tørre det af med en tør klud for at undgå støv. Undgå skrappe kemikalier for at bevare finishen, og sørg for, at dit skab forbliver en flot del af dit hjem i mange år. Det kræver ikke meget vedligeholdelse, hvilket passer godt til travle liv.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 30 x 30 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 1  hylde&lt;/li&gt;&lt;li&gt;Lystype: Led-strips&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x TV-skab&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand. Bemærk venligst, at der kun må anvendes certificeret DC 5V-strømforsyning. Højere spænding kan medføre overophedning og skade enheden samt medføre risiko for brand. Tilslut ikke dette produkt til nogen anden strømforsyning end den, der er beskrevet i manualen, på typeskiltet eller specifikt anbefalet af . Denne enhed må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner, eller som mangler erfaring og viden om brugen af elektroniske apparater. Elektricitet er farligt. Skader og forkert installation, brug eller ændring (herunder udskiftning af enkelte komponenter) kan føre til skader på enheden, hvilket kan medføre elektrisk stød og fare for brugeren. Brug ikke dette produkt i eksplosive områder, såsom i nærheden af brandfarlige væsker, gasser eller støv, eller ved temperaturer over 50 grader celsius. Tænd ikke produktet, hvis forbindelseskablet eller strømforsyningen er synligt beskadiget. Hvis den udvendige fleksible ledning eller kabel på denne lampe er beskadiget, skal den udelukkende udskiftes af producenten, en autoriseret serviceagent eller en tilsvarende kvalificeret person for at undgå fare. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er afkølet. Lyskilden i denne lampe kan ikke udskiftes; når lyskilden når slutningen af sin levetid, skal hele lampen udskiftes. Kun til indendørs brug – brug ikke dette produkt udendørs.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288924360_mo-im_en_hd_1.jpg, https://vdxl.im/8721288924360_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288924360_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288924360_wbg-wa_en_hd_1.jpg, https://vdxl.im/8721288924360_mo-im_en_hd_2.jpg, https://vdxl.im/8721288924360_mo-im_en_hd_3.jpg, https://vdxl.im/8721288924360_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288924360_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288924360_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288924360_detail_en_hd_1.jpg, https://vdxl.im/8721288924360_detail_en_hd_2.jpg, https://vdxl.im/8721288924360_detail_en_hd_3.jpg, https://vdxl.im/8721288924360_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288924360_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sengebord-med-led-lys-vaeghaengt-1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>882962</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8721288924384</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>339</v>
+      </c>
+      <c r="F25" t="n">
+        <v>459</v>
+      </c>
+      <c r="G25" t="n">
+        <v>199</v>
+      </c>
+      <c r="H25" t="n">
+        <v>7160</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>92</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288924384_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>882962</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>882962</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette smarte vægmonterede LED TV-skabssæt tilføjer både stil og praktisk funktion til enhver stue. Med sin slanke, rektangulære form og moderne design passer det super godt ind i nutidige rum. Det er perfekt til folk, der gerne vil have både funktionalitet og stil. Dette TV-skab har et minimalistisk look, men maksimerer opbevaring og belysning. Når det hænges op, får du et strømlinet look, der frigiver gulvplads og skaber en følelse af moderne elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Skabet er lavet af konstrueret træ, så det både er holdbart og ser godt ud. Det er stærkt og modstandsdygtigt, altså perfekt til at holde sig pænt i mange år. Det passer ind i enhver moderne eller overgangsindretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Skabet har hylder af robust konstrueret træ og hængslede døre, der giver nem adgang. De medfølgende multicolor LED-strips, der drives via USB, tilføjer en moderne kant og kan sætte stemningen alt efter humør.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner /Design:&lt;/b&gt; Skabet er vægmonteret og sparer dermed plads. Du får mere gulvplads til andre ting, samtidig med at der er god opbevaring til medieudstyr, bøger og pynt. De minimalistiske linjer gør, at det passer ind i mange forskellige indretningsstile.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Fantastisk til stuer og underholdningscentre, er skabet perfekt til at samle TV og elektronik, samtidig med at det skaber orden og et pænt look. Det er ideelt til lejligheder og rum, hvor hver kvadratcentimeter tæller.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Hold skabet pænt ved at tørre det af med en tør klud for at undgå støv. Undgå skrappe kemikalier for at bevare finishen, og sørg for, at dit skab forbliver en flot del af dit hjem i mange år. Det kræver ikke meget vedligeholdelse, hvilket passer godt til travle liv.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 30 x 30 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 1  hylde&lt;/li&gt;&lt;li&gt;Lystype: Led-strips&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x TV-skab&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand. Bemærk venligst, at der kun må anvendes certificeret DC 5V-strømforsyning. Højere spænding kan medføre overophedning og skade enheden samt medføre risiko for brand. Tilslut ikke dette produkt til nogen anden strømforsyning end den, der er beskrevet i manualen, på typeskiltet eller specifikt anbefalet af . Denne enhed må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner, eller som mangler erfaring og viden om brugen af elektroniske apparater. Elektricitet er farligt. Skader og forkert installation, brug eller ændring (herunder udskiftning af enkelte komponenter) kan føre til skader på enheden, hvilket kan medføre elektrisk stød og fare for brugeren. Brug ikke dette produkt i eksplosive områder, såsom i nærheden af brandfarlige væsker, gasser eller støv, eller ved temperaturer over 50 grader celsius. Tænd ikke produktet, hvis forbindelseskablet eller strømforsyningen er synligt beskadiget. Hvis den udvendige fleksible ledning eller kabel på denne lampe er beskadiget, skal den udelukkende udskiftes af producenten, en autoriseret serviceagent eller en tilsvarende kvalificeret person for at undgå fare. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er afkølet. Lyskilden i denne lampe kan ikke udskiftes; når lyskilden når slutningen af sin levetid, skal hele lampen udskiftes. Kun til indendørs brug – brug ikke dette produkt udendørs.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288924384_mo-im_en_hd_1.jpg, https://vdxl.im/8721288924384_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288924384_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288924384_wbg-wa_en_hd_1.jpg, https://vdxl.im/8721288924384_mo-im_en_hd_2.jpg, https://vdxl.im/8721288924384_mo-im_en_hd_3.jpg, https://vdxl.im/8721288924384_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288924384_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288924384_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288924384_detail_en_hd_1.jpg, https://vdxl.im/8721288924384_detail_en_hd_2.jpg, https://vdxl.im/8721288924384_detail_en_hd_3.jpg, https://vdxl.im/8721288924384_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288924384_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sengebord-med-led-lys-vaeghaengt-1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>882964</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8721288924407</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>349</v>
+      </c>
+      <c r="F26" t="n">
+        <v>469</v>
+      </c>
+      <c r="G26" t="n">
+        <v>204</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7160</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>98</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288924407_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>882964</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>882964</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette smarte vægmonterede LED TV-skabssæt tilføjer både stil og praktisk funktion til enhver stue. Med sin slanke, rektangulære form og moderne design passer det super godt ind i nutidige rum. Det er perfekt til folk, der gerne vil have både funktionalitet og stil. Dette TV-skab har et minimalistisk look, men maksimerer opbevaring og belysning. Når det hænges op, får du et strømlinet look, der frigiver gulvplads og skaber en følelse af moderne elegance.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Skabet er lavet af konstrueret træ, så det både er holdbart og ser godt ud. Det er stærkt og modstandsdygtigt, altså perfekt til at holde sig pænt i mange år. Det passer ind i enhver moderne eller overgangsindretning.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Skabet har hylder af robust konstrueret træ og hængslede døre, der giver nem adgang. De medfølgende multicolor LED-strips, der drives via USB, tilføjer en moderne kant og kan sætte stemningen alt efter humør.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktioner /Design:&lt;/b&gt; Skabet er vægmonteret og sparer dermed plads. Du får mere gulvplads til andre ting, samtidig med at der er god opbevaring til medieudstyr, bøger og pynt. De minimalistiske linjer gør, at det passer ind i mange forskellige indretningsstile.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Fantastisk til stuer og underholdningscentre, er skabet perfekt til at samle TV og elektronik, samtidig med at det skaber orden og et pænt look. Det er ideelt til lejligheder og rum, hvor hver kvadratcentimeter tæller.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Hold skabet pænt ved at tørre det af med en tør klud for at undgå støv. Undgå skrappe kemikalier for at bevare finishen, og sørg for, at dit skab forbliver en flot del af dit hjem i mange år. Det kræver ikke meget vedligeholdelse, hvilket passer godt til travle liv.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 30 x 30 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 1  hylde&lt;/li&gt;&lt;li&gt;Lystype: Led-strips&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x TV-skab&lt;/li&gt;&lt;/ul&gt; Dette produkt er drevet af DC 5V, men den certificerede 5V USB-strømkilde er ikke inkluderet. Højere spænding kan forårsage overophedning og kan resultere i beskadigelse af enheden og potentiel risiko for brand. Bemærk venligst, at der kun må anvendes certificeret DC 5V-strømforsyning. Højere spænding kan medføre overophedning og skade enheden samt medføre risiko for brand. Tilslut ikke dette produkt til nogen anden strømforsyning end den, der er beskrevet i manualen, på typeskiltet eller specifikt anbefalet af . Denne enhed må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner, eller som mangler erfaring og viden om brugen af elektroniske apparater. Elektricitet er farligt. Skader og forkert installation, brug eller ændring (herunder udskiftning af enkelte komponenter) kan føre til skader på enheden, hvilket kan medføre elektrisk stød og fare for brugeren. Brug ikke dette produkt i eksplosive områder, såsom i nærheden af brandfarlige væsker, gasser eller støv, eller ved temperaturer over 50 grader celsius. Tænd ikke produktet, hvis forbindelseskablet eller strømforsyningen er synligt beskadiget. Hvis den udvendige fleksible ledning eller kabel på denne lampe er beskadiget, skal den udelukkende udskiftes af producenten, en autoriseret serviceagent eller en tilsvarende kvalificeret person for at undgå fare. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er afkølet. Lyskilden i denne lampe kan ikke udskiftes; når lyskilden når slutningen af sin levetid, skal hele lampen udskiftes. Kun til indendørs brug – brug ikke dette produkt udendørs.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288924407_mo-im_en_hd_1.jpg, https://vdxl.im/8721288924407_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288924407_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288924407_wbg-wa_en_hd_1.jpg, https://vdxl.im/8721288924407_mo-im_en_hd_2.jpg, https://vdxl.im/8721288924407_mo-im_en_hd_3.jpg, https://vdxl.im/8721288924407_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288924407_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288924407_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288924407_detail_en_hd_1.jpg, https://vdxl.im/8721288924407_detail_en_hd_2.jpg, https://vdxl.im/8721288924407_detail_en_hd_3.jpg, https://vdxl.im/8721288924407_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288924407_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>360542</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8720845699581</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>249</v>
+      </c>
+      <c r="F27" t="n">
+        <v>359</v>
+      </c>
+      <c r="G27" t="n">
+        <v>142</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>83</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699581_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>360542</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>360542</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699581_m_en_hd_1.jpg, https://vdxl.im/8720845699581_a_en_hd_1.jpg, https://vdxl.im/8720845699581_g_en_hd_1.jpg, https://vdxl.im/8720845699581_g_en_hd_2.jpg, https://vdxl.im/8720845699581_g_en_hd_3.jpg, https://vdxl.im/8720845699581_g_en_hd_4.jpg, https://vdxl.im/8720845699581_g_en_hd_5.jpg, https://vdxl.im/8720845699581_g_en_hd_6.jpg, https://vdxl.im/8720845699581_g_en_hd_7.jpg, https://vdxl.im/8720845699581_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>360543</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8720845699598</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>249</v>
+      </c>
+      <c r="F28" t="n">
+        <v>359</v>
+      </c>
+      <c r="G28" t="n">
+        <v>143</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>121</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699598_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>360543</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>360543</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699598_m_en_hd_1.jpg, https://vdxl.im/8720845699598_a_en_hd_1.jpg, https://vdxl.im/8720845699598_g_en_hd_1.jpg, https://vdxl.im/8720845699598_g_en_hd_2.jpg, https://vdxl.im/8720845699598_g_en_hd_3.jpg, https://vdxl.im/8720845699598_g_en_hd_4.jpg, https://vdxl.im/8720845699598_g_en_hd_5.jpg, https://vdxl.im/8720845699598_g_en_hd_6.jpg, https://vdxl.im/8720845699598_g_en_hd_7.jpg, https://vdxl.im/8720845699598_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>360544</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8720845699604</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>249</v>
+      </c>
+      <c r="F29" t="n">
+        <v>359</v>
+      </c>
+      <c r="G29" t="n">
+        <v>142</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>60</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699604_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>360544</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>360544</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Vinrød&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699604_m_en_hd_1.jpg, https://vdxl.im/8720845699604_a_en_hd_1.jpg, https://vdxl.im/8720845699604_g_en_hd_1.jpg, https://vdxl.im/8720845699604_g_en_hd_2.jpg, https://vdxl.im/8720845699604_g_en_hd_3.jpg, https://vdxl.im/8720845699604_g_en_hd_4.jpg, https://vdxl.im/8720845699604_g_en_hd_5.jpg, https://vdxl.im/8720845699604_g_en_hd_6.jpg, https://vdxl.im/8720845699604_g_en_hd_7.jpg, https://vdxl.im/8720845699604_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vinrød</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>360545</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8720845699611</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>239</v>
+      </c>
+      <c r="F30" t="n">
+        <v>349</v>
+      </c>
+      <c r="G30" t="n">
+        <v>141</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>38</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699611_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>360545</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>360545</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: kongeblå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699611_m_en_hd_1.jpg, https://vdxl.im/8720845699611_a_en_hd_1.jpg, https://vdxl.im/8720845699611_g_en_hd_1.jpg, https://vdxl.im/8720845699611_g_en_hd_2.jpg, https://vdxl.im/8720845699611_g_en_hd_3.jpg, https://vdxl.im/8720845699611_g_en_hd_4.jpg, https://vdxl.im/8720845699611_g_en_hd_5.jpg, https://vdxl.im/8720845699611_g_en_hd_6.jpg, https://vdxl.im/8720845699611_g_en_hd_7.jpg, https://vdxl.im/8720845699611_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kongeblå</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>360546</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8720845699628</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>239</v>
+      </c>
+      <c r="F31" t="n">
+        <v>349</v>
+      </c>
+      <c r="G31" t="n">
+        <v>136</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>25</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699628_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>360546</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>360546</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrøn&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699628_m_en_hd_1.jpg, https://vdxl.im/8720845699628_a_en_hd_1.jpg, https://vdxl.im/8720845699628_g_en_hd_1.jpg, https://vdxl.im/8720845699628_g_en_hd_2.jpg, https://vdxl.im/8720845699628_g_en_hd_3.jpg, https://vdxl.im/8720845699628_g_en_hd_4.jpg, https://vdxl.im/8720845699628_g_en_hd_5.jpg, https://vdxl.im/8720845699628_g_en_hd_6.jpg, https://vdxl.im/8720845699628_g_en_hd_7.jpg, https://vdxl.im/8720845699628_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lysegrøn</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>360547</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8720845699635</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>249</v>
+      </c>
+      <c r="F32" t="n">
+        <v>359</v>
+      </c>
+      <c r="G32" t="n">
+        <v>144</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>63</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699635_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>360547</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>360547</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Bladmønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699635_m_en_hd_1.jpg, https://vdxl.im/8720845699635_a_en_hd_1.jpg, https://vdxl.im/8720845699635_g_en_hd_1.jpg, https://vdxl.im/8720845699635_g_en_hd_2.jpg, https://vdxl.im/8720845699635_g_en_hd_3.jpg, https://vdxl.im/8720845699635_g_en_hd_4.jpg, https://vdxl.im/8720845699635_g_en_hd_5.jpg, https://vdxl.im/8720845699635_g_en_hd_6.jpg, https://vdxl.im/8720845699635_g_en_hd_7.jpg, https://vdxl.im/8720845699635_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bladmønster</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>360548</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8720845699642</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>249</v>
+      </c>
+      <c r="F33" t="n">
+        <v>359</v>
+      </c>
+      <c r="G33" t="n">
+        <v>144</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>21</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699642_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>360548</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>360548</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Rødetern mønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699642_m_en_hd_1.jpg, https://vdxl.im/8720845699642_a_en_hd_1.jpg, https://vdxl.im/8720845699642_g_en_hd_1.jpg, https://vdxl.im/8720845699642_g_en_hd_2.jpg, https://vdxl.im/8720845699642_g_en_hd_3.jpg, https://vdxl.im/8720845699642_g_en_hd_4.jpg, https://vdxl.im/8720845699642_g_en_hd_5.jpg, https://vdxl.im/8720845699642_g_en_hd_6.jpg, https://vdxl.im/8720845699642_g_en_hd_7.jpg, https://vdxl.im/8720845699642_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rødternet</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>360549</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8720845699659</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>239</v>
+      </c>
+      <c r="F34" t="n">
+        <v>349</v>
+      </c>
+      <c r="G34" t="n">
+        <v>138</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>31</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699659_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>360549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>360549</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Gråternet mønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699659_m_en_hd_1.jpg, https://vdxl.im/8720845699659_a_en_hd_1.jpg, https://vdxl.im/8720845699659_g_en_hd_1.jpg, https://vdxl.im/8720845699659_g_en_hd_2.jpg, https://vdxl.im/8720845699659_g_en_hd_3.jpg, https://vdxl.im/8720845699659_g_en_hd_4.jpg, https://vdxl.im/8720845699659_g_en_hd_5.jpg, https://vdxl.im/8720845699659_g_en_hd_6.jpg, https://vdxl.im/8720845699659_g_en_hd_7.jpg, https://vdxl.im/8720845699659_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gråternet</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>360551</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8720845699673</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229</v>
+      </c>
+      <c r="F35" t="n">
+        <v>329</v>
+      </c>
+      <c r="G35" t="n">
+        <v>134</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>14</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699673_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>360551</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>360551</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med sorte tern&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699673_m_en_hd_1.jpg, https://vdxl.im/8720845699673_a_en_hd_1.jpg, https://vdxl.im/8720845699673_g_en_hd_1.jpg, https://vdxl.im/8720845699673_g_en_hd_2.jpg, https://vdxl.im/8720845699673_g_en_hd_3.jpg, https://vdxl.im/8720845699673_g_en_hd_4.jpg, https://vdxl.im/8720845699673_g_en_hd_5.jpg, https://vdxl.im/8720845699673_g_en_hd_6.jpg, https://vdxl.im/8720845699673_g_en_hd_7.jpg, https://vdxl.im/8720845699673_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sortternet mønster</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>360552</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8720845699680</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>249</v>
+      </c>
+      <c r="F36" t="n">
+        <v>359</v>
+      </c>
+      <c r="G36" t="n">
+        <v>143</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699680_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>360552</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>360552</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med fugle, blade og blomster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699680_m_en_hd_1.jpg, https://vdxl.im/8720845699680_a_en_hd_1.jpg, https://vdxl.im/8720845699680_g_en_hd_1.jpg, https://vdxl.im/8720845699680_g_en_hd_2.jpg, https://vdxl.im/8720845699680_g_en_hd_3.jpg, https://vdxl.im/8720845699680_g_en_hd_4.jpg, https://vdxl.im/8720845699680_g_en_hd_5.jpg, https://vdxl.im/8720845699680_g_en_hd_6.jpg, https://vdxl.im/8720845699680_g_en_hd_7.jpg, https://vdxl.im/8720845699680_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Flerfarvet</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>360553</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8720845699697</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229</v>
+      </c>
+      <c r="F37" t="n">
+        <v>329</v>
+      </c>
+      <c r="G37" t="n">
+        <v>134</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>10</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699697_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>360553</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>360553</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med bladmønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699697_m_en_hd_1.jpg, https://vdxl.im/8720845699697_a_en_hd_1.jpg, https://vdxl.im/8720845699697_g_en_hd_1.jpg, https://vdxl.im/8720845699697_g_en_hd_2.jpg, https://vdxl.im/8720845699697_g_en_hd_3.jpg, https://vdxl.im/8720845699697_g_en_hd_4.jpg, https://vdxl.im/8720845699697_g_en_hd_5.jpg, https://vdxl.im/8720845699697_g_en_hd_6.jpg, https://vdxl.im/8720845699697_g_en_hd_7.jpg, https://vdxl.im/8720845699697_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hvid og grøn</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>360554</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8720845699703</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>249</v>
+      </c>
+      <c r="F38" t="n">
+        <v>359</v>
+      </c>
+      <c r="G38" t="n">
+        <v>144</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>50</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699703_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>360554</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>360554</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med bladmønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699703_m_en_hd_1.jpg, https://vdxl.im/8720845699703_a_en_hd_1.jpg, https://vdxl.im/8720845699703_g_en_hd_1.jpg, https://vdxl.im/8720845699703_g_en_hd_2.jpg, https://vdxl.im/8720845699703_g_en_hd_3.jpg, https://vdxl.im/8720845699703_g_en_hd_4.jpg, https://vdxl.im/8720845699703_g_en_hd_5.jpg, https://vdxl.im/8720845699703_g_en_hd_6.jpg, https://vdxl.im/8720845699703_g_en_hd_7.jpg, https://vdxl.im/8720845699703_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bladdesign</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>360556</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8720845699727</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>249</v>
+      </c>
+      <c r="F39" t="n">
+        <v>359</v>
+      </c>
+      <c r="G39" t="n">
+        <v>142</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>27</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699727_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>360556</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>360556</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Turkis&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699727_m_en_hd_1.jpg, https://vdxl.im/8720845699727_a_en_hd_1.jpg, https://vdxl.im/8720845699727_g_en_hd_1.jpg, https://vdxl.im/8720845699727_g_en_hd_2.jpg, https://vdxl.im/8720845699727_g_en_hd_3.jpg, https://vdxl.im/8720845699727_g_en_hd_4.jpg, https://vdxl.im/8720845699727_g_en_hd_5.jpg, https://vdxl.im/8720845699727_g_en_hd_6.jpg, https://vdxl.im/8720845699727_g_en_hd_7.jpg, https://vdxl.im/8720845699727_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Turkis</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>50 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>360564</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8720845699802</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>249</v>
+      </c>
+      <c r="F40" t="n">
+        <v>359</v>
+      </c>
+      <c r="G40" t="n">
+        <v>142</v>
+      </c>
+      <c r="H40" t="n">
+        <v>900</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>63</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699802_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>360564</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>360564</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699802_m_en_hd_1.jpg, https://vdxl.im/8720845699802_a_en_hd_1.jpg, https://vdxl.im/8720845699802_g_en_hd_1.jpg, https://vdxl.im/8720845699802_g_en_hd_2.jpg, https://vdxl.im/8720845699802_g_en_hd_3.jpg, https://vdxl.im/8720845699802_g_en_hd_4.jpg, https://vdxl.im/8720845699802_g_en_hd_5.jpg, https://vdxl.im/8720845699802_g_en_hd_6.jpg, https://vdxl.im/8720845699802_g_en_hd_7.jpg, https://vdxl.im/8720845699802_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>360566</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8720845699826</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>259</v>
+      </c>
+      <c r="F41" t="n">
+        <v>369</v>
+      </c>
+      <c r="G41" t="n">
+        <v>152</v>
+      </c>
+      <c r="H41" t="n">
+        <v>900</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>31</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699826_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>360566</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>360566</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Vinrød&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699826_m_en_hd_1.jpg, https://vdxl.im/8720845699826_a_en_hd_1.jpg, https://vdxl.im/8720845699826_g_en_hd_1.jpg, https://vdxl.im/8720845699826_g_en_hd_2.jpg, https://vdxl.im/8720845699826_g_en_hd_3.jpg, https://vdxl.im/8720845699826_g_en_hd_4.jpg, https://vdxl.im/8720845699826_g_en_hd_5.jpg, https://vdxl.im/8720845699826_g_en_hd_6.jpg, https://vdxl.im/8720845699826_g_en_hd_7.jpg, https://vdxl.im/8720845699826_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vinrød</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>360567</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8720845699833</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>249</v>
+      </c>
+      <c r="F42" t="n">
+        <v>359</v>
+      </c>
+      <c r="G42" t="n">
+        <v>144</v>
+      </c>
+      <c r="H42" t="n">
+        <v>900</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>22</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699833_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>360567</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>360567</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: kongeblå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699833_m_en_hd_1.jpg, https://vdxl.im/8720845699833_a_en_hd_1.jpg, https://vdxl.im/8720845699833_g_en_hd_1.jpg, https://vdxl.im/8720845699833_g_en_hd_2.jpg, https://vdxl.im/8720845699833_g_en_hd_3.jpg, https://vdxl.im/8720845699833_g_en_hd_4.jpg, https://vdxl.im/8720845699833_g_en_hd_5.jpg, https://vdxl.im/8720845699833_g_en_hd_6.jpg, https://vdxl.im/8720845699833_g_en_hd_7.jpg, https://vdxl.im/8720845699833_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kongeblå</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>360568</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8720845699840</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>249</v>
+      </c>
+      <c r="F43" t="n">
+        <v>359</v>
+      </c>
+      <c r="G43" t="n">
+        <v>145</v>
+      </c>
+      <c r="H43" t="n">
+        <v>900</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>14</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699840_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>360568</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>360568</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrøn&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699840_m_en_hd_1.jpg, https://vdxl.im/8720845699840_a_en_hd_1.jpg, https://vdxl.im/8720845699840_g_en_hd_1.jpg, https://vdxl.im/8720845699840_g_en_hd_2.jpg, https://vdxl.im/8720845699840_g_en_hd_3.jpg, https://vdxl.im/8720845699840_g_en_hd_4.jpg, https://vdxl.im/8720845699840_g_en_hd_5.jpg, https://vdxl.im/8720845699840_g_en_hd_6.jpg, https://vdxl.im/8720845699840_g_en_hd_7.jpg, https://vdxl.im/8720845699840_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lysegrøn</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>360569</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8720845699857</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>249</v>
+      </c>
+      <c r="F44" t="n">
+        <v>359</v>
+      </c>
+      <c r="G44" t="n">
+        <v>147</v>
+      </c>
+      <c r="H44" t="n">
+        <v>900</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>25</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699857_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>360569</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>360569</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Bladmønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699857_m_en_hd_1.jpg, https://vdxl.im/8720845699857_a_en_hd_1.jpg, https://vdxl.im/8720845699857_g_en_hd_1.jpg, https://vdxl.im/8720845699857_g_en_hd_2.jpg, https://vdxl.im/8720845699857_g_en_hd_3.jpg, https://vdxl.im/8720845699857_g_en_hd_4.jpg, https://vdxl.im/8720845699857_g_en_hd_5.jpg, https://vdxl.im/8720845699857_g_en_hd_6.jpg, https://vdxl.im/8720845699857_g_en_hd_7.jpg, https://vdxl.im/8720845699857_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bladmønster</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>360570</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8720845699864</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>249</v>
+      </c>
+      <c r="F45" t="n">
+        <v>359</v>
+      </c>
+      <c r="G45" t="n">
+        <v>147</v>
+      </c>
+      <c r="H45" t="n">
+        <v>900</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>10</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699864_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>360570</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>360570</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Rødetern mønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699864_m_en_hd_1.jpg, https://vdxl.im/8720845699864_a_en_hd_1.jpg, https://vdxl.im/8720845699864_g_en_hd_1.jpg, https://vdxl.im/8720845699864_g_en_hd_2.jpg, https://vdxl.im/8720845699864_g_en_hd_3.jpg, https://vdxl.im/8720845699864_g_en_hd_4.jpg, https://vdxl.im/8720845699864_g_en_hd_5.jpg, https://vdxl.im/8720845699864_g_en_hd_6.jpg, https://vdxl.im/8720845699864_g_en_hd_7.jpg, https://vdxl.im/8720845699864_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rødternet</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>360571</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8720845699871</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>249</v>
+      </c>
+      <c r="F46" t="n">
+        <v>359</v>
+      </c>
+      <c r="G46" t="n">
+        <v>144</v>
+      </c>
+      <c r="H46" t="n">
+        <v>900</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>19</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699871_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>360571</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>360571</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Gråternet mønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699871_m_en_hd_1.jpg, https://vdxl.im/8720845699871_a_en_hd_1.jpg, https://vdxl.im/8720845699871_g_en_hd_1.jpg, https://vdxl.im/8720845699871_g_en_hd_2.jpg, https://vdxl.im/8720845699871_g_en_hd_3.jpg, https://vdxl.im/8720845699871_g_en_hd_4.jpg, https://vdxl.im/8720845699871_g_en_hd_5.jpg, https://vdxl.im/8720845699871_g_en_hd_6.jpg, https://vdxl.im/8720845699871_g_en_hd_7.jpg, https://vdxl.im/8720845699871_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gråternet</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>360573</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8720845699895</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>239</v>
+      </c>
+      <c r="F47" t="n">
+        <v>349</v>
+      </c>
+      <c r="G47" t="n">
+        <v>138</v>
+      </c>
+      <c r="H47" t="n">
+        <v>900</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699895_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>360573</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>360573</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med sorte tern&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699895_m_en_hd_1.jpg, https://vdxl.im/8720845699895_a_en_hd_1.jpg, https://vdxl.im/8720845699895_g_en_hd_1.jpg, https://vdxl.im/8720845699895_g_en_hd_2.jpg, https://vdxl.im/8720845699895_g_en_hd_3.jpg, https://vdxl.im/8720845699895_g_en_hd_4.jpg, https://vdxl.im/8720845699895_g_en_hd_5.jpg, https://vdxl.im/8720845699895_g_en_hd_6.jpg, https://vdxl.im/8720845699895_g_en_hd_7.jpg, https://vdxl.im/8720845699895_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sortternet mønster</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>360574</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8720845699901</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>249</v>
+      </c>
+      <c r="F48" t="n">
+        <v>359</v>
+      </c>
+      <c r="G48" t="n">
+        <v>145</v>
+      </c>
+      <c r="H48" t="n">
+        <v>900</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>9</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699901_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>360574</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>360574</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 60 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med fugle, blade og blomster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845699901_m_en_hd_1.jpg, https://vdxl.im/8720845699901_a_en_hd_1.jpg, https://vdxl.im/8720845699901_g_en_hd_1.jpg, https://vdxl.im/8720845699901_g_en_hd_2.jpg, https://vdxl.im/8720845699901_g_en_hd_3.jpg, https://vdxl.im/8720845699901_g_en_hd_4.jpg, https://vdxl.im/8720845699901_g_en_hd_5.jpg, https://vdxl.im/8720845699901_g_en_hd_6.jpg, https://vdxl.im/8720845699901_g_en_hd_7.jpg, https://vdxl.im/8720845699901_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Flerfarvet</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>60 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>360602</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8720845700188</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>259</v>
+      </c>
+      <c r="F49" t="n">
+        <v>369</v>
+      </c>
+      <c r="G49" t="n">
+        <v>153</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>96</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700188_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>360602</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>360602</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700188_m_en_hd_1.jpg, https://vdxl.im/8720845700188_a_en_hd_1.jpg, https://vdxl.im/8720845700188_g_en_hd_1.jpg, https://vdxl.im/8720845700188_g_en_hd_2.jpg, https://vdxl.im/8720845700188_g_en_hd_3.jpg, https://vdxl.im/8720845700188_g_en_hd_4.jpg, https://vdxl.im/8720845700188_g_en_hd_5.jpg, https://vdxl.im/8720845700188_g_en_hd_6.jpg, https://vdxl.im/8720845700188_g_en_hd_7.jpg, https://vdxl.im/8720845700188_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Grå</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>360603</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>8720845700195</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>259</v>
+      </c>
+      <c r="F50" t="n">
+        <v>369</v>
+      </c>
+      <c r="G50" t="n">
+        <v>150</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>79</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700195_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>360603</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>360603</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700195_m_en_hd_1.jpg, https://vdxl.im/8720845700195_a_en_hd_1.jpg, https://vdxl.im/8720845700195_g_en_hd_1.jpg, https://vdxl.im/8720845700195_g_en_hd_2.jpg, https://vdxl.im/8720845700195_g_en_hd_3.jpg, https://vdxl.im/8720845700195_g_en_hd_4.jpg, https://vdxl.im/8720845700195_g_en_hd_5.jpg, https://vdxl.im/8720845700195_g_en_hd_6.jpg, https://vdxl.im/8720845700195_g_en_hd_7.jpg, https://vdxl.im/8720845700195_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>360604</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8720845700201</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>259</v>
+      </c>
+      <c r="F51" t="n">
+        <v>369</v>
+      </c>
+      <c r="G51" t="n">
+        <v>153</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>43</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700201_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>360604</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>360604</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700201_m_en_hd_1.jpg, https://vdxl.im/8720845700201_a_en_hd_1.jpg, https://vdxl.im/8720845700201_g_en_hd_1.jpg, https://vdxl.im/8720845700201_g_en_hd_2.jpg, https://vdxl.im/8720845700201_g_en_hd_3.jpg, https://vdxl.im/8720845700201_g_en_hd_4.jpg, https://vdxl.im/8720845700201_g_en_hd_5.jpg, https://vdxl.im/8720845700201_g_en_hd_6.jpg, https://vdxl.im/8720845700201_g_en_hd_7.jpg, https://vdxl.im/8720845700201_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Beige</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>360605</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8720845700218</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>259</v>
+      </c>
+      <c r="F52" t="n">
+        <v>369</v>
+      </c>
+      <c r="G52" t="n">
+        <v>153</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>27</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700218_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>360605</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>360605</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lyseblå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700218_m_en_hd_1.jpg, https://vdxl.im/8720845700218_a_en_hd_1.jpg, https://vdxl.im/8720845700218_g_en_hd_1.jpg, https://vdxl.im/8720845700218_g_en_hd_2.jpg, https://vdxl.im/8720845700218_g_en_hd_3.jpg, https://vdxl.im/8720845700218_g_en_hd_4.jpg, https://vdxl.im/8720845700218_g_en_hd_5.jpg, https://vdxl.im/8720845700218_g_en_hd_6.jpg, https://vdxl.im/8720845700218_g_en_hd_7.jpg, https://vdxl.im/8720845700218_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lyseblå</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>360606</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8720845700225</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>259</v>
+      </c>
+      <c r="F53" t="n">
+        <v>369</v>
+      </c>
+      <c r="G53" t="n">
+        <v>153</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>34</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700225_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>360606</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>360606</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grøn&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700225_m_en_hd_1.jpg, https://vdxl.im/8720845700225_a_en_hd_1.jpg, https://vdxl.im/8720845700225_g_en_hd_1.jpg, https://vdxl.im/8720845700225_g_en_hd_2.jpg, https://vdxl.im/8720845700225_g_en_hd_3.jpg, https://vdxl.im/8720845700225_g_en_hd_4.jpg, https://vdxl.im/8720845700225_g_en_hd_5.jpg, https://vdxl.im/8720845700225_g_en_hd_6.jpg, https://vdxl.im/8720845700225_g_en_hd_7.jpg, https://vdxl.im/8720845700225_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Grøn</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>360607</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8720845700232</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>259</v>
+      </c>
+      <c r="F54" t="n">
+        <v>369</v>
+      </c>
+      <c r="G54" t="n">
+        <v>151</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>24</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700232_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>360607</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>360607</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Rød&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700232_m_en_hd_1.jpg, https://vdxl.im/8720845700232_a_en_hd_1.jpg, https://vdxl.im/8720845700232_g_en_hd_1.jpg, https://vdxl.im/8720845700232_g_en_hd_2.jpg, https://vdxl.im/8720845700232_g_en_hd_3.jpg, https://vdxl.im/8720845700232_g_en_hd_4.jpg, https://vdxl.im/8720845700232_g_en_hd_5.jpg, https://vdxl.im/8720845700232_g_en_hd_6.jpg, https://vdxl.im/8720845700232_g_en_hd_7.jpg, https://vdxl.im/8720845700232_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Rød</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>360608</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8720845700249</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>259</v>
+      </c>
+      <c r="F55" t="n">
+        <v>369</v>
+      </c>
+      <c r="G55" t="n">
+        <v>153</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>44</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700249_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>360608</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>360608</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700249_m_en_hd_1.jpg, https://vdxl.im/8720845700249_a_en_hd_1.jpg, https://vdxl.im/8720845700249_g_en_hd_1.jpg, https://vdxl.im/8720845700249_g_en_hd_2.jpg, https://vdxl.im/8720845700249_g_en_hd_3.jpg, https://vdxl.im/8720845700249_g_en_hd_4.jpg, https://vdxl.im/8720845700249_g_en_hd_5.jpg, https://vdxl.im/8720845700249_g_en_hd_6.jpg, https://vdxl.im/8720845700249_g_en_hd_7.jpg, https://vdxl.im/8720845700249_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>360609</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8720845700256</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>259</v>
+      </c>
+      <c r="F56" t="n">
+        <v>369</v>
+      </c>
+      <c r="G56" t="n">
+        <v>150</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>52</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700256_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>360609</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>360609</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700256_m_en_hd_1.jpg, https://vdxl.im/8720845700256_a_en_hd_1.jpg, https://vdxl.im/8720845700256_g_en_hd_1.jpg, https://vdxl.im/8720845700256_g_en_hd_2.jpg, https://vdxl.im/8720845700256_g_en_hd_3.jpg, https://vdxl.im/8720845700256_g_en_hd_4.jpg, https://vdxl.im/8720845700256_g_en_hd_5.jpg, https://vdxl.im/8720845700256_g_en_hd_6.jpg, https://vdxl.im/8720845700256_g_en_hd_7.jpg, https://vdxl.im/8720845700256_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>360610</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8720845700263</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>259</v>
+      </c>
+      <c r="F57" t="n">
+        <v>369</v>
+      </c>
+      <c r="G57" t="n">
+        <v>150</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>21</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700263_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>360610</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>360610</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Vinrød&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700263_m_en_hd_1.jpg, https://vdxl.im/8720845700263_a_en_hd_1.jpg, https://vdxl.im/8720845700263_g_en_hd_1.jpg, https://vdxl.im/8720845700263_g_en_hd_2.jpg, https://vdxl.im/8720845700263_g_en_hd_3.jpg, https://vdxl.im/8720845700263_g_en_hd_4.jpg, https://vdxl.im/8720845700263_g_en_hd_5.jpg, https://vdxl.im/8720845700263_g_en_hd_6.jpg, https://vdxl.im/8720845700263_g_en_hd_7.jpg, https://vdxl.im/8720845700263_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vinrød</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>360611</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8720845700270</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>269</v>
+      </c>
+      <c r="F58" t="n">
+        <v>389</v>
+      </c>
+      <c r="G58" t="n">
+        <v>155</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>23</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700270_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>360611</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>360611</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: kongeblå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700270_m_en_hd_1.jpg, https://vdxl.im/8720845700270_a_en_hd_1.jpg, https://vdxl.im/8720845700270_g_en_hd_1.jpg, https://vdxl.im/8720845700270_g_en_hd_2.jpg, https://vdxl.im/8720845700270_g_en_hd_3.jpg, https://vdxl.im/8720845700270_g_en_hd_4.jpg, https://vdxl.im/8720845700270_g_en_hd_5.jpg, https://vdxl.im/8720845700270_g_en_hd_6.jpg, https://vdxl.im/8720845700270_g_en_hd_7.jpg, https://vdxl.im/8720845700270_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kongeblå</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>360612</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8720845700287</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>269</v>
+      </c>
+      <c r="F59" t="n">
+        <v>389</v>
+      </c>
+      <c r="G59" t="n">
+        <v>159</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>22</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700287_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>360612</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>360612</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrøn&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700287_m_en_hd_1.jpg, https://vdxl.im/8720845700287_a_en_hd_1.jpg, https://vdxl.im/8720845700287_g_en_hd_1.jpg, https://vdxl.im/8720845700287_g_en_hd_2.jpg, https://vdxl.im/8720845700287_g_en_hd_3.jpg, https://vdxl.im/8720845700287_g_en_hd_4.jpg, https://vdxl.im/8720845700287_g_en_hd_5.jpg, https://vdxl.im/8720845700287_g_en_hd_6.jpg, https://vdxl.im/8720845700287_g_en_hd_7.jpg, https://vdxl.im/8720845700287_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lysegrøn</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>360613</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>8720845700294</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>269</v>
+      </c>
+      <c r="F60" t="n">
+        <v>389</v>
+      </c>
+      <c r="G60" t="n">
+        <v>158</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>40</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700294_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>360613</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>360613</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Bladmønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700294_m_en_hd_1.jpg, https://vdxl.im/8720845700294_a_en_hd_1.jpg, https://vdxl.im/8720845700294_g_en_hd_1.jpg, https://vdxl.im/8720845700294_g_en_hd_2.jpg, https://vdxl.im/8720845700294_g_en_hd_3.jpg, https://vdxl.im/8720845700294_g_en_hd_4.jpg, https://vdxl.im/8720845700294_g_en_hd_5.jpg, https://vdxl.im/8720845700294_g_en_hd_6.jpg, https://vdxl.im/8720845700294_g_en_hd_7.jpg, https://vdxl.im/8720845700294_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bladmønster</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>360614</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8720845700300</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>269</v>
+      </c>
+      <c r="F61" t="n">
+        <v>389</v>
+      </c>
+      <c r="G61" t="n">
+        <v>157</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>5</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700300_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>360614</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>360614</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Rødetern mønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700300_m_en_hd_1.jpg, https://vdxl.im/8720845700300_a_en_hd_1.jpg, https://vdxl.im/8720845700300_g_en_hd_1.jpg, https://vdxl.im/8720845700300_g_en_hd_2.jpg, https://vdxl.im/8720845700300_g_en_hd_3.jpg, https://vdxl.im/8720845700300_g_en_hd_4.jpg, https://vdxl.im/8720845700300_g_en_hd_5.jpg, https://vdxl.im/8720845700300_g_en_hd_6.jpg, https://vdxl.im/8720845700300_g_en_hd_7.jpg, https://vdxl.im/8720845700300_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Rødternet</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>360615</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>8720845700317</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>269</v>
+      </c>
+      <c r="F62" t="n">
+        <v>389</v>
+      </c>
+      <c r="G62" t="n">
+        <v>157</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>13</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700317_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>360615</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>360615</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin originale facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: Hule fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Gråternet mønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700317_m_en_hd_1.jpg, https://vdxl.im/8720845700317_a_en_hd_1.jpg, https://vdxl.im/8720845700317_g_en_hd_1.jpg, https://vdxl.im/8720845700317_g_en_hd_2.jpg, https://vdxl.im/8720845700317_g_en_hd_3.jpg, https://vdxl.im/8720845700317_g_en_hd_4.jpg, https://vdxl.im/8720845700317_g_en_hd_5.jpg, https://vdxl.im/8720845700317_g_en_hd_6.jpg, https://vdxl.im/8720845700317_g_en_hd_7.jpg, https://vdxl.im/8720845700317_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Gråternet</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>360617</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>8720845700331</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>269</v>
+      </c>
+      <c r="F63" t="n">
+        <v>389</v>
+      </c>
+      <c r="G63" t="n">
+        <v>154</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>14</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700331_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>360617</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>360617</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med sorte tern&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700331_m_en_hd_1.jpg, https://vdxl.im/8720845700331_a_en_hd_1.jpg, https://vdxl.im/8720845700331_g_en_hd_1.jpg, https://vdxl.im/8720845700331_g_en_hd_2.jpg, https://vdxl.im/8720845700331_g_en_hd_3.jpg, https://vdxl.im/8720845700331_g_en_hd_4.jpg, https://vdxl.im/8720845700331_g_en_hd_5.jpg, https://vdxl.im/8720845700331_g_en_hd_6.jpg, https://vdxl.im/8720845700331_g_en_hd_7.jpg, https://vdxl.im/8720845700331_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sortternet mønster</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>360619</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>8720845700355</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>269</v>
+      </c>
+      <c r="F64" t="n">
+        <v>389</v>
+      </c>
+      <c r="G64" t="n">
+        <v>154</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>11</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700355_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>360619</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>360619</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med bladmønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700355_m_en_hd_1.jpg, https://vdxl.im/8720845700355_a_en_hd_1.jpg, https://vdxl.im/8720845700355_g_en_hd_1.jpg, https://vdxl.im/8720845700355_g_en_hd_2.jpg, https://vdxl.im/8720845700355_g_en_hd_3.jpg, https://vdxl.im/8720845700355_g_en_hd_4.jpg, https://vdxl.im/8720845700355_g_en_hd_5.jpg, https://vdxl.im/8720845700355_g_en_hd_6.jpg, https://vdxl.im/8720845700355_g_en_hd_7.jpg, https://vdxl.im/8720845700355_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Hvid og grøn</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>360620</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>8720845700362</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>279</v>
+      </c>
+      <c r="F65" t="n">
+        <v>399</v>
+      </c>
+      <c r="G65" t="n">
+        <v>160</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>17</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700362_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>360620</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>360620</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Med bladmønster&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700362_m_en_hd_1.jpg, https://vdxl.im/8720845700362_a_en_hd_1.jpg, https://vdxl.im/8720845700362_g_en_hd_1.jpg, https://vdxl.im/8720845700362_g_en_hd_2.jpg, https://vdxl.im/8720845700362_g_en_hd_3.jpg, https://vdxl.im/8720845700362_g_en_hd_4.jpg, https://vdxl.im/8720845700362_g_en_hd_5.jpg, https://vdxl.im/8720845700362_g_en_hd_6.jpg, https://vdxl.im/8720845700362_g_en_hd_7.jpg, https://vdxl.im/8720845700362_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bladdesign</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>pallehynde-stof-stribet</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>360622</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>8720845700386</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>259</v>
+      </c>
+      <c r="F66" t="n">
+        <v>369</v>
+      </c>
+      <c r="G66" t="n">
+        <v>153</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>23</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700386_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>360622</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>360622</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Giv dit uderum et nyt look på et øjeblik med disse komfortable pallehynder!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt stof: Polyester er et syntetisk materiale, der er kendt for sin UV-bestandighed og sin trækstyrke. Polyester er vandafvisende, hvilket gør det til det perfekte valg i fugtige eller regnfulde forhold, og det er let at rengøre.&lt;/li&gt;&lt;li&gt;Blødt fyld: Udendørshynden er fyldt med hule PP-fibre for ekstra blød og optimal siddekomfort. Sofahynden vender tilbage til sin oprindelige facon efter hver brug.&lt;/li&gt;&lt;li&gt;Bred anvendelse: Hynden er ikke kun egnet til udendørs brug på have- og terrassemøbler, men kan også bruges indendørs som en stolehynde eller i stuen. Hynden er en smuk dekoration, der vil give dit hjem et frisk look.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Produktet pakkes under vakuum, så det skal bruge lidt tid at udvide sig og komme tilbage til sin oprindelige form.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Turkis&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 40 x 12 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Vandafvisende&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845700386_m_en_hd_1.jpg, https://vdxl.im/8720845700386_a_en_hd_1.jpg, https://vdxl.im/8720845700386_g_en_hd_1.jpg, https://vdxl.im/8720845700386_g_en_hd_2.jpg, https://vdxl.im/8720845700386_g_en_hd_3.jpg, https://vdxl.im/8720845700386_g_en_hd_4.jpg, https://vdxl.im/8720845700386_g_en_hd_5.jpg, https://vdxl.im/8720845700386_g_en_hd_6.jpg, https://vdxl.im/8720845700386_g_en_hd_7.jpg, https://vdxl.im/8720845700386_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Turkis</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>80 x 40 x 12 cm</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>springmadras-m-pocket-fjedre-medium-fasthed</t>
+          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3206421</t>
+          <t>3185735</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8721012203563</t>
+          <t>8720845831202</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3789</v>
+        <v>1799</v>
       </c>
       <c r="F2" t="n">
-        <v>5059</v>
+        <v>2399</v>
       </c>
       <c r="G2" t="n">
-        <v>2227</v>
+        <v>1057</v>
       </c>
       <c r="H2" t="n">
-        <v>39050</v>
+        <v>59640</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012203563_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845831202_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3206421</t>
+          <t>3185735</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,38 +636,46 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3206421</t>
+          <t>3185735</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Denne springmadras med pocket-fjedre er designet til at give dig en god og behagelig soveoplevelse derhjemme.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt; Holdbarhed og lang levetid: Stoffet har et enkelt og rent look, samtidig med at det er åndbart, hudvenligt og langtidsholdbart. &lt;/li&gt;&lt;li&gt;Individuel støtte: Hver stofindkapslet spiralfjeder reagerer på dine trykpunkter, giver målrettet støtte og fordeler jævnt det tryk, din rygsøjle udsættes for. &lt;/li&gt;&lt;li&gt;Trykaflastende: Madrassen med pocket-fjedre har 7 liggezoner, som effektivt aflaster trykket og giver optimal støtte til alle områder af din krop som fødder, knæ, hofter, talje, ryg, skuldre og hoved. &lt;/li&gt;&lt;li&gt;Forbedret komfort: Springmadrassen er designet med flere lag, herunder et skumlag, et lag isoleringspude og et fjederlag. Denne kombination giver en blød til medium fornemmelse og vuggende komfort i alle sovestillinger. Derudover absorberer madrassen effektivt støj og vibrationer forårsaget af bevægelser i søvne, hvilket giver en fredelig og uforstyrret søvn. &lt;/li&gt;&lt;li&gt;Nem at bruge: Håndgrebene giver en sikker og nem måde at løfte og flytte en tung og uhåndterlig madras på, hvilket gør det lettere at flytte og placere den. Derudover har springmadrassen en lang lynlås, som gør det nemt at fjerne betrækket, når det skal vaskes. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Madrassens betræk kan vaskes ved op til 40 °C. Vær opmærksom på ikke at vaske det ofte. &lt;/li&gt;&lt;li&gt;For nemheds skyld er madrassen komprimeret og rullet i en kasse, så du nemt kan flytte den og stille den i soveværelset.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale: Pocket-fjedre, skum, isoleringspude&lt;/li&gt;&lt;li&gt;Mål: 200 x 200 x 25 cm (B x L x T)&lt;/li&gt;&lt;li&gt;Hårdhed: Medium fast&lt;/li&gt;&lt;li&gt;Jacquard- og quiltmønster&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012203563_a_en_hd_1.jpg, https://vdxl.im/8721012203563_g_en_hd_1.jpg, https://vdxl.im/8721012203563_g_en_hd_2.jpg, https://vdxl.im/8721012203563_g_en_hd_3.jpg, https://vdxl.im/8721012203563_g_en_hd_4.jpg, https://vdxl.im/8721012203563_g_en_hd_5.jpg, https://vdxl.im/8721012203563_g_en_hd_6.jpg, https://vdxl.im/8721012203563_g_en_hd_27.jpg, https://vdxl.im/8721012203563_g_en_hd_28.jpg</t>
+          <t>https://vdxl.im/8720845831202_m_en_hd_1.jpg, https://vdxl.im/8720845831202_a_en_hd_1.jpg, https://vdxl.im/8720845831202_g_en_hd_1.jpg, https://vdxl.im/8720845831202_g_en_hd_2.jpg, https://vdxl.im/8720845831202_g_en_hd_3.jpg, https://vdxl.im/8720845831202_g_en_hd_4.jpg, https://vdxl.im/8720845831202_g_en_hd_5.jpg, https://vdxl.im/8720845831202_g_en_hd_6.jpg, https://vdxl.im/8720845831202_g_en_hd_7.jpg, https://vdxl.im/8720845831202_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>200 x 200 cm</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>springmadras-m-pocket-fjedre-medium-fasthed</t>
+          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -677,25 +685,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>372836</t>
+          <t>3185738</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8721012204546</t>
+          <t>8720845831233</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1609</v>
+        <v>1789</v>
       </c>
       <c r="F3" t="n">
-        <v>2149</v>
+        <v>2389</v>
       </c>
       <c r="G3" t="n">
-        <v>944</v>
+        <v>1051</v>
       </c>
       <c r="H3" t="n">
-        <v>17900</v>
+        <v>59640</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -713,7 +721,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -732,12 +740,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012204546_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845831233_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>372836</t>
+          <t>3185738</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -747,33 +755,7015 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>372836</t>
+          <t>3185738</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Denne springmadras med pocket-fjedre er designet til at give dig en god og behagelig soveoplevelse derhjemme.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt; Holdbarhed og lang levetid: Stoffet har et enkelt og rent look, samtidig med at det er åndbart, hudvenligt og langtidsholdbart. &lt;/li&gt;&lt;li&gt;Individuel støtte: Hver stofindkapslet spiralfjeder reagerer på dine trykpunkter, giver målrettet støtte og fordeler jævnt det tryk, din rygsøjle udsættes for. &lt;/li&gt;&lt;li&gt;Trykaflastende: Madrassen med pocket-fjedre har 7 liggezoner, som effektivt aflaster trykket og giver optimal støtte til alle områder af din krop som fødder, knæ, hofter, talje, ryg, skuldre og hoved. &lt;/li&gt;&lt;li&gt;Forbedret komfort: Springmadrassen er designet med flere lag, herunder et skumlag, et lag isoleringspude og et fjederlag. Denne kombination giver en blød til medium fornemmelse og vuggende komfort i alle sovestillinger. Derudover absorberer madrassen effektivt støj og vibrationer forårsaget af bevægelser i søvne, hvilket giver en fredelig og uforstyrret søvn. &lt;/li&gt;&lt;li&gt;Nem at bruge: Håndgrebene giver en sikker og nem måde at løfte og flytte en tung og uhåndterlig madras på, hvilket gør det lettere at flytte og placere den. Derudover har springmadrassen en lang lynlås, som gør det nemt at fjerne betrækket, når det skal vaskes. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Madrassens betræk kan vaskes ved op til 40 °C. Vær opmærksom på ikke at vaske det ofte. &lt;/li&gt;&lt;li&gt;For nemheds skyld er madrassen komprimeret og rullet i en kasse, så du nemt kan flytte den og stille den i soveværelset.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale: Pocket-fjedre, skum, isoleringspude&lt;/li&gt;&lt;li&gt;Mål: 80 x 200 x 25 cm (B x L x T)&lt;/li&gt;&lt;li&gt;Hårdhed: Medium fast&lt;/li&gt;&lt;li&gt;Jacquard- og quiltmønster&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012204546_a_en_hd_1.jpg, https://vdxl.im/8721012204546_g_en_hd_1.jpg, https://vdxl.im/8721012204546_g_en_hd_2.jpg, https://vdxl.im/8721012204546_g_en_hd_3.jpg, https://vdxl.im/8721012204546_g_en_hd_4.jpg, https://vdxl.im/8721012204546_g_en_hd_5.jpg, https://vdxl.im/8721012204546_g_en_hd_6.jpg, https://vdxl.im/8721012204546_g_en_hd_7.jpg, https://vdxl.im/8721012204546_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845831233_m_en_hd_1.jpg, https://vdxl.im/8720845831233_a_en_hd_1.jpg, https://vdxl.im/8720845831233_g_en_hd_1.jpg, https://vdxl.im/8720845831233_g_en_hd_2.jpg, https://vdxl.im/8720845831233_g_en_hd_3.jpg, https://vdxl.im/8720845831233_g_en_hd_4.jpg, https://vdxl.im/8720845831233_g_en_hd_5.jpg, https://vdxl.im/8720845831233_g_en_hd_6.jpg, https://vdxl.im/8720845831233_g_en_hd_7.jpg, https://vdxl.im/8720845831233_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>80 x 200 cm</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3185739</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8720845831240</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1919</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2559</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1129</v>
+      </c>
+      <c r="H4" t="n">
+        <v>59640</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>21</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845831240_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3185739</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3185739</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845831240_m_en_hd_1.jpg, https://vdxl.im/8720845831240_a_en_hd_1.jpg, https://vdxl.im/8720845831240_g_en_hd_1.jpg, https://vdxl.im/8720845831240_g_en_hd_2.jpg, https://vdxl.im/8720845831240_g_en_hd_3.jpg, https://vdxl.im/8720845831240_g_en_hd_4.jpg, https://vdxl.im/8720845831240_g_en_hd_5.jpg, https://vdxl.im/8720845831240_g_en_hd_6.jpg, https://vdxl.im/8720845831240_g_en_hd_7.jpg, https://vdxl.im/8720845831240_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Betongrå</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3185741</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8720845831264</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1749</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2339</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1026</v>
+      </c>
+      <c r="H5" t="n">
+        <v>59640</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845831264_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3185741</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3185741</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845831264_m_en_hd_1.jpg, https://vdxl.im/8720845831264_a_en_hd_1.jpg, https://vdxl.im/8720845831264_g_en_hd_1.jpg, https://vdxl.im/8720845831264_g_en_hd_2.jpg, https://vdxl.im/8720845831264_g_en_hd_3.jpg, https://vdxl.im/8720845831264_g_en_hd_4.jpg, https://vdxl.im/8720845831264_g_en_hd_5.jpg, https://vdxl.im/8720845831264_g_en_hd_6.jpg, https://vdxl.im/8720845831264_g_en_hd_7.jpg, https://vdxl.im/8720845831264_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3415559</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8721364525146</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1619</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G6" t="n">
+        <v>949</v>
+      </c>
+      <c r="H6" t="n">
+        <v>51660</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>31</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721364525146_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3415559</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3415559</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Det flotte sideboard er en smart opbevaringsløsning, som passer perfekt til moderne hjem. Det er lavet med præcision og passer nemt ind i din spisestue eller stue. Her er der masser af plads til at holde dine ting organiseret, og samtidig ser det fantastisk ud. Med sin glatte overflade og simple design er det ideelt for dem, der ønsker praktiske løsninger med et moderne touch.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Materialer og bygning:&lt;/b&gt; Lavet af holdbart konstrueret træ, så sideboardet er bygget til at holde i mange år. Det stabile design gør det til et godt valg til opbevaring af tungere ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Designfunktioner:&lt;/b&gt; Sideboardets moderne stil har rene linjer og minimal dekoration, som passer godt til nutidig indretning. Den glatte overflade giver et elegant udtryk, og det enkle design sørger for, at det kan bruges i alle rum.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Opbevaring og komponenter:&lt;/b&gt; Med pladehylder, hængslede døre og rummelige rum giver dette sideboard mange opbevaringsmuligheder. Døre gør det nemt at komme til dine ting, og hylderne holder orden.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Montering og pleje:&lt;/b&gt; Montering kræver hjælp fra to personer og en skruetrækker. For vedligeholdelse, tør det blot af med en tør klud og undgå stærke kemikalier for at bevare dets flotte udseende.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Alsidighed:&lt;/b&gt; Perfekt til spisestuer og køkkener, denne opbevaringsløsning imødekommer forskellige behov, fra opbevaring af service og redskaber til bøger og elektronik, hvilket gør det praktisk til enhver situation.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 døre&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;3 x Sideboard&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721364525146_mo-im_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-an_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-si_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721364525146_detail_en_hd_1.jpg, https://vdxl.im/8721364525146_detail_en_hd_2.jpg, https://vdxl.im/8721364525146_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3415576</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8721364525313</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1589</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2119</v>
+      </c>
+      <c r="G7" t="n">
+        <v>934</v>
+      </c>
+      <c r="H7" t="n">
+        <v>51660</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>13</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721364525313_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3415576</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3415576</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Det flotte sideboard er en smart opbevaringsløsning, som passer perfekt til moderne hjem. Det er lavet med præcision og passer nemt ind i din spisestue eller stue. Her er der masser af plads til at holde dine ting organiseret, og samtidig ser det fantastisk ud. Med sin glatte overflade og simple design er det ideelt for dem, der ønsker praktiske løsninger med et moderne touch.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Materialer og bygning:&lt;/b&gt; Lavet af holdbart konstrueret træ, så sideboardet er bygget til at holde i mange år. Det stabile design gør det til et godt valg til opbevaring af tungere ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Designfunktioner:&lt;/b&gt; Sideboardets moderne stil har rene linjer og minimal dekoration, som passer godt til nutidig indretning. Den glatte overflade giver et elegant udtryk, og det enkle design sørger for, at det kan bruges i alle rum.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Opbevaring og komponenter:&lt;/b&gt; Med pladehylder, hængslede døre og rummelige rum giver dette sideboard mange opbevaringsmuligheder. Døre gør det nemt at komme til dine ting, og hylderne holder orden.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Montering og pleje:&lt;/b&gt; Montering kræver hjælp fra to personer og en skruetrækker. For vedligeholdelse, tør det blot af med en tør klud og undgå stærke kemikalier for at bevare dets flotte udseende.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Alsidighed:&lt;/b&gt; Perfekt til spisestuer og køkkener, denne opbevaringsløsning imødekommer forskellige behov, fra opbevaring af service og redskaber til bøger og elektronik, hvilket gør det praktisk til enhver situation.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 døre&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;3 x Sideboard&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721364525313_mo-im_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-an_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-si_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721364525313_detail_en_hd_1.jpg, https://vdxl.im/8721364525313_detail_en_hd_2.jpg, https://vdxl.im/8721364525313_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3415593</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8721364525481</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1589</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2119</v>
+      </c>
+      <c r="G8" t="n">
+        <v>931</v>
+      </c>
+      <c r="H8" t="n">
+        <v>51660</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>35</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721364525481_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3415593</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3415593</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Det flotte sideboard er en smart opbevaringsløsning, som passer perfekt til moderne hjem. Det er lavet med præcision og passer nemt ind i din spisestue eller stue. Her er der masser af plads til at holde dine ting organiseret, og samtidig ser det fantastisk ud. Med sin glatte overflade og simple design er det ideelt for dem, der ønsker praktiske løsninger med et moderne touch.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Materialer og bygning:&lt;/b&gt; Lavet af holdbart konstrueret træ, så sideboardet er bygget til at holde i mange år. Det stabile design gør det til et godt valg til opbevaring af tungere ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Designfunktioner:&lt;/b&gt; Sideboardets moderne stil har rene linjer og minimal dekoration, som passer godt til nutidig indretning. Den glatte overflade giver et elegant udtryk, og det enkle design sørger for, at det kan bruges i alle rum.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Opbevaring og komponenter:&lt;/b&gt; Med pladehylder, hængslede døre og rummelige rum giver dette sideboard mange opbevaringsmuligheder. Døre gør det nemt at komme til dine ting, og hylderne holder orden.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Montering og pleje:&lt;/b&gt; Montering kræver hjælp fra to personer og en skruetrækker. For vedligeholdelse, tør det blot af med en tør klud og undgå stærke kemikalier for at bevare dets flotte udseende.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Alsidighed:&lt;/b&gt; Perfekt til spisestuer og køkkener, denne opbevaringsløsning imødekommer forskellige behov, fra opbevaring af service og redskaber til bøger og elektronik, hvilket gør det praktisk til enhver situation.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 døre&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;3 x Sideboard&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721364525481_mo-im_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-an_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-si_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721364525481_detail_en_hd_1.jpg, https://vdxl.im/8721364525481_detail_en_hd_2.jpg, https://vdxl.im/8721364525481_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3069271</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8720286395950</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5009</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7159</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2947</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25240</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>31</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395950_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3069271</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3069271</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395950_m_en_hd_1.jpg, https://vdxl.im/8720286395950_a_en_hd_1.jpg, https://vdxl.im/8720286395950_g_en_hd_1.jpg, https://vdxl.im/8720286395950_g_en_hd_2.jpg, https://vdxl.im/8720286395950_g_en_hd_3.jpg, https://vdxl.im/8720286395950_g_en_hd_4.jpg, https://vdxl.im/8720286395950_g_en_hd_5.jpg, https://vdxl.im/8720286395950_g_en_hd_6.jpg, https://vdxl.im/8720286395950_g_en_hd_7.jpg, https://vdxl.im/8720286395950_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Blå og hvid</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3069272</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8720286395967</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4909</v>
+      </c>
+      <c r="F10" t="n">
+        <v>7019</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2885</v>
+      </c>
+      <c r="H10" t="n">
+        <v>25240</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>32</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395967_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3069272</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3069272</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286395967_doc_en_1.pdf?t=1773042783" href="https://vdxl.im/8720286395967_doc_en_1.pdf?t=1773042783" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395967_m_en_hd_1.jpg, https://vdxl.im/8720286395967_a_en_hd_1.jpg, https://vdxl.im/8720286395967_g_en_hd_1.jpg, https://vdxl.im/8720286395967_g_en_hd_2.jpg, https://vdxl.im/8720286395967_g_en_hd_3.jpg, https://vdxl.im/8720286395967_g_en_hd_4.jpg, https://vdxl.im/8720286395967_g_en_hd_5.jpg, https://vdxl.im/8720286395967_g_en_hd_6.jpg, https://vdxl.im/8720286395967_g_en_hd_7.jpg, https://vdxl.im/8720286395967_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3069273</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8720286395974</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4909</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7019</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2888</v>
+      </c>
+      <c r="H11" t="n">
+        <v>25220</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>32</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395974_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3069273</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3069273</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395974_m_en_hd_1.jpg, https://vdxl.im/8720286395974_a_en_hd_1.jpg, https://vdxl.im/8720286395974_g_en_hd_1.jpg, https://vdxl.im/8720286395974_g_en_hd_2.jpg, https://vdxl.im/8720286395974_g_en_hd_3.jpg, https://vdxl.im/8720286395974_g_en_hd_4.jpg, https://vdxl.im/8720286395974_g_en_hd_5.jpg, https://vdxl.im/8720286395974_g_en_hd_6.jpg, https://vdxl.im/8720286395974_g_en_hd_7.jpg, https://vdxl.im/8720286395974_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gul og hvid</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3069274</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8720286395981</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5019</v>
+      </c>
+      <c r="F12" t="n">
+        <v>7169</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2950</v>
+      </c>
+      <c r="H12" t="n">
+        <v>25160</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>32</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395981_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3069274</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3069274</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395981_m_en_hd_1.jpg, https://vdxl.im/8720286395981_a_en_hd_1.jpg, https://vdxl.im/8720286395981_g_en_hd_1.jpg, https://vdxl.im/8720286395981_g_en_hd_2.jpg, https://vdxl.im/8720286395981_g_en_hd_3.jpg, https://vdxl.im/8720286395981_g_en_hd_4.jpg, https://vdxl.im/8720286395981_g_en_hd_5.jpg, https://vdxl.im/8720286395981_g_en_hd_6.jpg, https://vdxl.im/8720286395981_g_en_hd_7.jpg, https://vdxl.im/8720286395981_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Antracitgrå</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3069275</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8720286395998</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4889</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6989</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2874</v>
+      </c>
+      <c r="H13" t="n">
+        <v>25180</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>32</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395998_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3069275</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3069275</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286395998_m_en_hd_1.jpg, https://vdxl.im/8720286395998_a_en_hd_1.jpg, https://vdxl.im/8720286395998_g_en_hd_1.jpg, https://vdxl.im/8720286395998_g_en_hd_2.jpg, https://vdxl.im/8720286395998_g_en_hd_3.jpg, https://vdxl.im/8720286395998_g_en_hd_4.jpg, https://vdxl.im/8720286395998_g_en_hd_5.jpg, https://vdxl.im/8720286395998_g_en_hd_6.jpg, https://vdxl.im/8720286395998_g_en_hd_7.jpg, https://vdxl.im/8720286395998_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>orange og brun</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3069291</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8720286396155</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5089</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7269</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2989</v>
+      </c>
+      <c r="H14" t="n">
+        <v>33440</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>34</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396155_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3069291</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3069291</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396155_m_en_hd_1.jpg, https://vdxl.im/8720286396155_a_en_hd_1.jpg, https://vdxl.im/8720286396155_g_en_hd_1.jpg, https://vdxl.im/8720286396155_g_en_hd_2.jpg, https://vdxl.im/8720286396155_g_en_hd_3.jpg, https://vdxl.im/8720286396155_g_en_hd_4.jpg, https://vdxl.im/8720286396155_g_en_hd_5.jpg, https://vdxl.im/8720286396155_g_en_hd_6.jpg, https://vdxl.im/8720286396155_g_en_hd_7.jpg, https://vdxl.im/8720286396155_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Blå og hvid</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3.5 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3069292</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8720286396162</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5189</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7419</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3052</v>
+      </c>
+      <c r="H15" t="n">
+        <v>27640</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>43</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396162_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3069292</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3069292</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396162_m_en_hd_1.jpg, https://vdxl.im/8720286396162_a_en_hd_1.jpg, https://vdxl.im/8720286396162_g_en_hd_1.jpg, https://vdxl.im/8720286396162_g_en_hd_2.jpg, https://vdxl.im/8720286396162_g_en_hd_3.jpg, https://vdxl.im/8720286396162_g_en_hd_4.jpg, https://vdxl.im/8720286396162_g_en_hd_5.jpg, https://vdxl.im/8720286396162_g_en_hd_6.jpg, https://vdxl.im/8720286396162_g_en_hd_7.jpg, https://vdxl.im/8720286396162_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3.5 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3069293</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8720286396179</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5189</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7419</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3051</v>
+      </c>
+      <c r="H16" t="n">
+        <v>27700</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>19</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396179_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3069293</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3069293</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396179_m_en_hd_1.jpg, https://vdxl.im/8720286396179_a_en_hd_1.jpg, https://vdxl.im/8720286396179_g_en_hd_1.jpg, https://vdxl.im/8720286396179_g_en_hd_2.jpg, https://vdxl.im/8720286396179_g_en_hd_3.jpg, https://vdxl.im/8720286396179_g_en_hd_4.jpg, https://vdxl.im/8720286396179_g_en_hd_5.jpg, https://vdxl.im/8720286396179_g_en_hd_6.jpg, https://vdxl.im/8720286396179_g_en_hd_7.jpg, https://vdxl.im/8720286396179_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gul og hvid</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3.5 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3069294</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8720286396186</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5189</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7419</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3048</v>
+      </c>
+      <c r="H17" t="n">
+        <v>27520</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>43</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396186_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3069294</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3069294</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286396186_doc_en_1.pdf?t=1773042823" href="https://vdxl.im/8720286396186_doc_en_1.pdf?t=1773042823" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396186_m_en_hd_1.jpg, https://vdxl.im/8720286396186_a_en_hd_1.jpg, https://vdxl.im/8720286396186_g_en_hd_1.jpg, https://vdxl.im/8720286396186_g_en_hd_2.jpg, https://vdxl.im/8720286396186_g_en_hd_3.jpg, https://vdxl.im/8720286396186_g_en_hd_4.jpg, https://vdxl.im/8720286396186_g_en_hd_5.jpg, https://vdxl.im/8720286396186_g_en_hd_6.jpg, https://vdxl.im/8720286396186_g_en_hd_7.jpg, https://vdxl.im/8720286396186_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Antracitgrå</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3.5 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3069295</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8720286396193</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5069</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7249</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2977</v>
+      </c>
+      <c r="H18" t="n">
+        <v>27760</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>25</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396193_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3069295</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3069295</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286396193_doc_en_1.pdf?t=1773042559" href="https://vdxl.im/8720286396193_doc_en_1.pdf?t=1773042559" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396193_m_en_hd_1.jpg, https://vdxl.im/8720286396193_a_en_hd_1.jpg, https://vdxl.im/8720286396193_g_en_hd_1.jpg, https://vdxl.im/8720286396193_g_en_hd_2.jpg, https://vdxl.im/8720286396193_g_en_hd_3.jpg, https://vdxl.im/8720286396193_g_en_hd_4.jpg, https://vdxl.im/8720286396193_g_en_hd_5.jpg, https://vdxl.im/8720286396193_g_en_hd_6.jpg, https://vdxl.im/8720286396193_g_en_hd_7.jpg, https://vdxl.im/8720286396193_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>orange og brun</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>3.5 x 2.5 m</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3069311</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8720286396353</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5869</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8389</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3449</v>
+      </c>
+      <c r="H19" t="n">
+        <v>34760</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>11</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396353_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3069311</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3069311</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396353_m_en_hd_1.jpg, https://vdxl.im/8720286396353_a_en_hd_1.jpg, https://vdxl.im/8720286396353_g_en_hd_1.jpg, https://vdxl.im/8720286396353_g_en_hd_2.jpg, https://vdxl.im/8720286396353_g_en_hd_3.jpg, https://vdxl.im/8720286396353_g_en_hd_4.jpg, https://vdxl.im/8720286396353_g_en_hd_5.jpg, https://vdxl.im/8720286396353_g_en_hd_6.jpg, https://vdxl.im/8720286396353_g_en_hd_7.jpg, https://vdxl.im/8720286396353_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Blå og hvid</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>4 x 3 m</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3069312</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8720286396360</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5859</v>
+      </c>
+      <c r="F20" t="n">
+        <v>8369</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3446</v>
+      </c>
+      <c r="H20" t="n">
+        <v>34760</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>22</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396360_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3069312</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3069312</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286396360_doc_en_1.pdf?t=1773042609" href="https://vdxl.im/8720286396360_doc_en_1.pdf?t=1773042609" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396360_m_en_hd_1.jpg, https://vdxl.im/8720286396360_a_en_hd_1.jpg, https://vdxl.im/8720286396360_g_en_hd_1.jpg, https://vdxl.im/8720286396360_g_en_hd_2.jpg, https://vdxl.im/8720286396360_g_en_hd_3.jpg, https://vdxl.im/8720286396360_g_en_hd_4.jpg, https://vdxl.im/8720286396360_g_en_hd_5.jpg, https://vdxl.im/8720286396360_g_en_hd_6.jpg, https://vdxl.im/8720286396360_g_en_hd_7.jpg, https://vdxl.im/8720286396360_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>4 x 3 m</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3069313</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8720286396377</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5859</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8369</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3445</v>
+      </c>
+      <c r="H21" t="n">
+        <v>34760</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>9</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396377_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3069313</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3069313</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Dette apparat kan bruges af børn fra 8 år og opefter samt af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring og viden, hvis de er under opsyn eller er blevet instrueret i brugen af apparatet på en sikker måde, og de forstår de involverede farer. Børn må ikke lege med apparatet. Rengøring og vedligeholdelse må kun udføres af børn uden opsyn. Hvis forsyningsledningen er beskadiget, skal den udskiftes af producenten, dennes serviceagent eller lignende kvalificerede personer for at undgå farer. ADVARSEL: Vigtige sikkerhedsinstruktioner. Det er vigtigt at overholde disse sikkerhedsinstruktioner af sikkerhedsmæssige årsager. Gem disse instruktioner. ADVARSEL: Vigtige sikkerhedsinstruktioner. Følg alle instruktioner, da forkert installation kan medføre alvorlige skade eller død. Lad ikke børn lege med kontrolenheden. Hold fjernbetjeningen væk fra børn. Markisen må ikke bruges under vedligeholdelse såsom vinduespudsning, der bliver udført i nærheden. Bevægelige dele i drevet skal installeres højere end 2,5 m over jorden eller andre niveauer, der kan give adgang. Før drevet installeres skal unødvendige ledninger og snore fjernes og udstyr skal frakobles, hvis det ikke er nødvendigt for brugen. Aktiveringselementet af en forspændt afbryder skal placeres inden for direkte syn af den drevne del, men væk fra bevægelige dele. Det skal monteres i en højde på minimum 1,5 m.Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner. Farlige ubeskyttede bevægelige dele af drevet skal installeres højere end 2,5 m over gulvet eller andre niveauer, der kan forhindre adgang til det. &lt;a title="https://vdxl.im/8720286396377_doc_en_1.pdf?t=1745012781" href="https://vdxl.im/8720286396377_doc_en_1.pdf?t=1745012781" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396377_m_en_hd_1.jpg, https://vdxl.im/8720286396377_a_en_hd_1.jpg, https://vdxl.im/8720286396377_g_en_hd_1.jpg, https://vdxl.im/8720286396377_g_en_hd_2.jpg, https://vdxl.im/8720286396377_g_en_hd_3.jpg, https://vdxl.im/8720286396377_g_en_hd_4.jpg, https://vdxl.im/8720286396377_g_en_hd_5.jpg, https://vdxl.im/8720286396377_g_en_hd_6.jpg, https://vdxl.im/8720286396377_g_en_hd_7.jpg, https://vdxl.im/8720286396377_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gul og hvid</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>4 x 3 m</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3069314</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8720286396384</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6129</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8759</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3601</v>
+      </c>
+      <c r="H22" t="n">
+        <v>34600</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396384_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3069314</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3069314</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396384_m_en_hd_1.jpg, https://vdxl.im/8720286396384_a_en_hd_1.jpg, https://vdxl.im/8720286396384_g_en_hd_1.jpg, https://vdxl.im/8720286396384_g_en_hd_2.jpg, https://vdxl.im/8720286396384_g_en_hd_3.jpg, https://vdxl.im/8720286396384_g_en_hd_4.jpg, https://vdxl.im/8720286396384_g_en_hd_5.jpg, https://vdxl.im/8720286396384_g_en_hd_6.jpg, https://vdxl.im/8720286396384_g_en_hd_7.jpg, https://vdxl.im/8720286396384_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Antracitgrå</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>4 x 3 m</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3069315</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8720286396391</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5729</v>
+      </c>
+      <c r="F23" t="n">
+        <v>8189</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3366</v>
+      </c>
+      <c r="H23" t="n">
+        <v>34660</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>22</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396391_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3069315</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3069315</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720286396391_m_en_hd_1.jpg, https://vdxl.im/8720286396391_a_en_hd_1.jpg, https://vdxl.im/8720286396391_g_en_hd_1.jpg, https://vdxl.im/8720286396391_g_en_hd_2.jpg, https://vdxl.im/8720286396391_g_en_hd_3.jpg, https://vdxl.im/8720286396391_g_en_hd_4.jpg, https://vdxl.im/8720286396391_g_en_hd_5.jpg, https://vdxl.im/8720286396391_g_en_hd_6.jpg, https://vdxl.im/8720286396391_g_en_hd_7.jpg, https://vdxl.im/8720286396391_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>orange og brun</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>4 x 3 m</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>859879</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8721158649102</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>529</v>
+      </c>
+      <c r="F24" t="n">
+        <v>759</v>
+      </c>
+      <c r="G24" t="n">
+        <v>311</v>
+      </c>
+      <c r="H24" t="n">
+        <v>15900</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>166</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649102_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>859879</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>859879</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649102_m_en_hd_1.jpg, https://vdxl.im/8721158649102_a_en_hd_1.jpg, https://vdxl.im/8721158649102_g_en_hd_1.jpg, https://vdxl.im/8721158649102_g_en_hd_2.jpg, https://vdxl.im/8721158649102_g_en_hd_3.jpg, https://vdxl.im/8721158649102_g_en_hd_4.jpg, https://vdxl.im/8721158649102_g_en_hd_5.jpg, https://vdxl.im/8721158649102_g_en_hd_6.jpg, https://vdxl.im/8721158649102_g_en_hd_7.jpg, https://vdxl.im/8721158649102_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>859870</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8721158649010</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>639</v>
+      </c>
+      <c r="F25" t="n">
+        <v>919</v>
+      </c>
+      <c r="G25" t="n">
+        <v>376</v>
+      </c>
+      <c r="H25" t="n">
+        <v>18700</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649010_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>859870</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>859870</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649010_m_en_hd_1.jpg, https://vdxl.im/8721158649010_a_en_hd_1.jpg, https://vdxl.im/8721158649010_g_en_hd_1.jpg, https://vdxl.im/8721158649010_g_en_hd_2.jpg, https://vdxl.im/8721158649010_g_en_hd_3.jpg, https://vdxl.im/8721158649010_g_en_hd_4.jpg, https://vdxl.im/8721158649010_g_en_hd_5.jpg, https://vdxl.im/8721158649010_g_en_hd_6.jpg, https://vdxl.im/8721158649010_g_en_hd_7.jpg, https://vdxl.im/8721158649010_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>859881</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8721158649126</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>559</v>
+      </c>
+      <c r="F26" t="n">
+        <v>799</v>
+      </c>
+      <c r="G26" t="n">
+        <v>326</v>
+      </c>
+      <c r="H26" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>78</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649126_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>859881</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>859881</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649126_m_en_hd_1.jpg, https://vdxl.im/8721158649126_a_en_hd_1.jpg, https://vdxl.im/8721158649126_g_en_hd_1.jpg, https://vdxl.im/8721158649126_g_en_hd_2.jpg, https://vdxl.im/8721158649126_g_en_hd_3.jpg, https://vdxl.im/8721158649126_g_en_hd_4.jpg, https://vdxl.im/8721158649126_g_en_hd_5.jpg, https://vdxl.im/8721158649126_g_en_hd_6.jpg, https://vdxl.im/8721158649126_g_en_hd_7.jpg, https://vdxl.im/8721158649126_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Betongrå</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>859872</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8721158649034</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>599</v>
+      </c>
+      <c r="F27" t="n">
+        <v>859</v>
+      </c>
+      <c r="G27" t="n">
+        <v>350</v>
+      </c>
+      <c r="H27" t="n">
+        <v>18650</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649034_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>859872</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>859872</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649034_m_en_hd_1.jpg, https://vdxl.im/8721158649034_a_en_hd_1.jpg, https://vdxl.im/8721158649034_g_en_hd_1.jpg, https://vdxl.im/8721158649034_g_en_hd_2.jpg, https://vdxl.im/8721158649034_g_en_hd_3.jpg, https://vdxl.im/8721158649034_g_en_hd_4.jpg, https://vdxl.im/8721158649034_g_en_hd_5.jpg, https://vdxl.im/8721158649034_g_en_hd_6.jpg, https://vdxl.im/8721158649034_g_en_hd_7.jpg, https://vdxl.im/8721158649034_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>100 cm</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Betongrå</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>859878</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8721158649096</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>499</v>
+      </c>
+      <c r="F28" t="n">
+        <v>719</v>
+      </c>
+      <c r="G28" t="n">
+        <v>291</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>113</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649096_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>859878</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>859878</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649096_m_en_hd_1.jpg, https://vdxl.im/8721158649096_a_en_hd_1.jpg, https://vdxl.im/8721158649096_g_en_hd_1.jpg, https://vdxl.im/8721158649096_g_en_hd_2.jpg, https://vdxl.im/8721158649096_g_en_hd_3.jpg, https://vdxl.im/8721158649096_g_en_hd_4.jpg, https://vdxl.im/8721158649096_g_en_hd_5.jpg, https://vdxl.im/8721158649096_g_en_hd_6.jpg, https://vdxl.im/8721158649096_g_en_hd_7.jpg, https://vdxl.im/8721158649096_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>859880</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8721158649119</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>449</v>
+      </c>
+      <c r="F29" t="n">
+        <v>649</v>
+      </c>
+      <c r="G29" t="n">
+        <v>262</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15700</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>172</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649119_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>859880</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>859880</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649119_m_en_hd_1.jpg, https://vdxl.im/8721158649119_a_en_hd_1.jpg, https://vdxl.im/8721158649119_g_en_hd_1.jpg, https://vdxl.im/8721158649119_g_en_hd_2.jpg, https://vdxl.im/8721158649119_g_en_hd_3.jpg, https://vdxl.im/8721158649119_g_en_hd_4.jpg, https://vdxl.im/8721158649119_g_en_hd_5.jpg, https://vdxl.im/8721158649119_g_en_hd_6.jpg, https://vdxl.im/8721158649119_g_en_hd_7.jpg, https://vdxl.im/8721158649119_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>859882</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8721158649133</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>529</v>
+      </c>
+      <c r="F30" t="n">
+        <v>759</v>
+      </c>
+      <c r="G30" t="n">
+        <v>309</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16100</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>53</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649133_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>859882</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>859882</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649133_m_en_hd_1.jpg, https://vdxl.im/8721158649133_a_en_hd_1.jpg, https://vdxl.im/8721158649133_g_en_hd_1.jpg, https://vdxl.im/8721158649133_g_en_hd_2.jpg, https://vdxl.im/8721158649133_g_en_hd_3.jpg, https://vdxl.im/8721158649133_g_en_hd_4.jpg, https://vdxl.im/8721158649133_g_en_hd_5.jpg, https://vdxl.im/8721158649133_g_en_hd_6.jpg, https://vdxl.im/8721158649133_g_en_hd_7.jpg, https://vdxl.im/8721158649133_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Røget eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>859883</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8721158649140</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>539</v>
+      </c>
+      <c r="F31" t="n">
+        <v>769</v>
+      </c>
+      <c r="G31" t="n">
+        <v>315</v>
+      </c>
+      <c r="H31" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>79</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649140_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>859883</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>859883</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649140_m_en_hd_1.jpg, https://vdxl.im/8721158649140_a_en_hd_1.jpg, https://vdxl.im/8721158649140_g_en_hd_1.jpg, https://vdxl.im/8721158649140_g_en_hd_2.jpg, https://vdxl.im/8721158649140_g_en_hd_3.jpg, https://vdxl.im/8721158649140_g_en_hd_4.jpg, https://vdxl.im/8721158649140_g_en_hd_5.jpg, https://vdxl.im/8721158649140_g_en_hd_6.jpg, https://vdxl.im/8721158649140_g_en_hd_7.jpg, https://vdxl.im/8721158649140_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>859885</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8721158649164</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>559</v>
+      </c>
+      <c r="F32" t="n">
+        <v>799</v>
+      </c>
+      <c r="G32" t="n">
+        <v>325</v>
+      </c>
+      <c r="H32" t="n">
+        <v>15800</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>65</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649164_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>859885</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>859885</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: antikt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649164_m_en_hd_1.jpg, https://vdxl.im/8721158649164_a_en_hd_1.jpg, https://vdxl.im/8721158649164_g_en_hd_1.jpg, https://vdxl.im/8721158649164_g_en_hd_2.jpg, https://vdxl.im/8721158649164_g_en_hd_3.jpg, https://vdxl.im/8721158649164_g_en_hd_4.jpg, https://vdxl.im/8721158649164_g_en_hd_5.jpg, https://vdxl.im/8721158649164_g_en_hd_6.jpg, https://vdxl.im/8721158649164_g_en_hd_7.jpg, https://vdxl.im/8721158649164_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>859886</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8721158649171</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>489</v>
+      </c>
+      <c r="F33" t="n">
+        <v>699</v>
+      </c>
+      <c r="G33" t="n">
+        <v>283</v>
+      </c>
+      <c r="H33" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>200</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649171_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>859886</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>859886</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158649171_m_en_hd_1.jpg, https://vdxl.im/8721158649171_a_en_hd_1.jpg, https://vdxl.im/8721158649171_g_en_hd_1.jpg, https://vdxl.im/8721158649171_g_en_hd_2.jpg, https://vdxl.im/8721158649171_g_en_hd_3.jpg, https://vdxl.im/8721158649171_g_en_hd_4.jpg, https://vdxl.im/8721158649171_g_en_hd_5.jpg, https://vdxl.im/8721158649171_g_en_hd_6.jpg, https://vdxl.im/8721158649171_g_en_hd_7.jpg, https://vdxl.im/8721158649171_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>81 cm</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3154423</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8720845714338</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2759</v>
+      </c>
+      <c r="F34" t="n">
+        <v>3949</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1618</v>
+      </c>
+      <c r="H34" t="n">
+        <v>20820</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>200</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714338_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>3154423</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>3154423</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714338_m_en_hd_1.jpg, https://vdxl.im/8720845714338_a_en_hd_1.jpg, https://vdxl.im/8720845714338_g_en_hd_1.jpg, https://vdxl.im/8720845714338_g_en_hd_2.jpg, https://vdxl.im/8720845714338_g_en_hd_3.jpg, https://vdxl.im/8720845714338_g_en_hd_4.jpg, https://vdxl.im/8720845714338_g_en_hd_5.jpg, https://vdxl.im/8720845714338_g_en_hd_6.jpg, https://vdxl.im/8720845714338_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Blå og hvid (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3154427</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8720845714376</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2389</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3419</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1405</v>
+      </c>
+      <c r="H35" t="n">
+        <v>16520</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>200</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714376_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>3154427</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>3154427</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 3,5 x 2,5 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714376_m_en_hd_1.jpg, https://vdxl.im/8720845714376_a_en_hd_1.jpg, https://vdxl.im/8720845714376_g_en_hd_1.jpg, https://vdxl.im/8720845714376_g_en_hd_2.jpg, https://vdxl.im/8720845714376_g_en_hd_3.jpg, https://vdxl.im/8720845714376_g_en_hd_4.jpg, https://vdxl.im/8720845714376_g_en_hd_5.jpg, https://vdxl.im/8720845714376_g_en_hd_6.jpg, https://vdxl.im/8720845714376_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>3,5 x 2,5 m</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3154428</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8720845714383</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2769</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3959</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1625</v>
+      </c>
+      <c r="H36" t="n">
+        <v>20820</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>200</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714383_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>3154428</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>3154428</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714383_m_en_hd_1.jpg, https://vdxl.im/8720845714383_a_en_hd_1.jpg, https://vdxl.im/8720845714383_g_en_hd_1.jpg, https://vdxl.im/8720845714383_g_en_hd_2.jpg, https://vdxl.im/8720845714383_g_en_hd_3.jpg, https://vdxl.im/8720845714383_g_en_hd_4.jpg, https://vdxl.im/8720845714383_g_en_hd_5.jpg, https://vdxl.im/8720845714383_g_en_hd_6.jpg, https://vdxl.im/8720845714383_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Cremefarvet (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3154429</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8720845714390</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>3019</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4319</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1774</v>
+      </c>
+      <c r="H37" t="n">
+        <v>23300</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>65</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714390_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>3154429</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>3154429</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4,5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714390_m_en_hd_1.jpg, https://vdxl.im/8720845714390_a_en_hd_1.jpg, https://vdxl.im/8720845714390_g_en_hd_1.jpg, https://vdxl.im/8720845714390_g_en_hd_2.jpg, https://vdxl.im/8720845714390_g_en_hd_3.jpg, https://vdxl.im/8720845714390_g_en_hd_4.jpg, https://vdxl.im/8720845714390_g_en_hd_5.jpg, https://vdxl.im/8720845714390_g_en_hd_6.jpg, https://vdxl.im/8720845714390_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Cremefarvet (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>4,5 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3154433</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8720845714437</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2699</v>
+      </c>
+      <c r="F38" t="n">
+        <v>3859</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1584</v>
+      </c>
+      <c r="H38" t="n">
+        <v>20820</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>200</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714437_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3154433</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>3154433</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner. &lt;a title="https://vdxl.im/8720845714437_doc_en_1.pdf?t=1755495686" href="https://vdxl.im/8720845714437_doc_en_1.pdf?t=1755495686" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714437_m_en_hd_1.jpg, https://vdxl.im/8720845714437_a_en_hd_1.jpg, https://vdxl.im/8720845714437_g_en_hd_1.jpg, https://vdxl.im/8720845714437_g_en_hd_2.jpg, https://vdxl.im/8720845714437_g_en_hd_3.jpg, https://vdxl.im/8720845714437_g_en_hd_4.jpg, https://vdxl.im/8720845714437_g_en_hd_5.jpg, https://vdxl.im/8720845714437_g_en_hd_6.jpg, https://vdxl.im/8720845714437_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gul og hvid (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3154438</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8720845714482</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3079</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4399</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1809</v>
+      </c>
+      <c r="H39" t="n">
+        <v>20720</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>200</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714482_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>3154438</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>3154438</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714482_m_en_hd_1.jpg, https://vdxl.im/8720845714482_a_en_hd_1.jpg, https://vdxl.im/8720845714482_g_en_hd_1.jpg, https://vdxl.im/8720845714482_g_en_hd_2.jpg, https://vdxl.im/8720845714482_g_en_hd_3.jpg, https://vdxl.im/8720845714482_g_en_hd_4.jpg, https://vdxl.im/8720845714482_g_en_hd_5.jpg, https://vdxl.im/8720845714482_g_en_hd_6.jpg, https://vdxl.im/8720845714482_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Antracitgrå (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3154443</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8720845714536</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2629</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3759</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1544</v>
+      </c>
+      <c r="H40" t="n">
+        <v>20720</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>57</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714536_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3154443</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3154443</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845714536_m_en_hd_1.jpg, https://vdxl.im/8720845714536_a_en_hd_1.jpg, https://vdxl.im/8720845714536_g_en_hd_1.jpg, https://vdxl.im/8720845714536_g_en_hd_2.jpg, https://vdxl.im/8720845714536_g_en_hd_3.jpg, https://vdxl.im/8720845714536_g_en_hd_4.jpg, https://vdxl.im/8720845714536_g_en_hd_5.jpg, https://vdxl.im/8720845714536_g_en_hd_6.jpg, https://vdxl.im/8720845714536_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Orange og brun (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3215295</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8721012415997</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2679</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3829</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1575</v>
+      </c>
+      <c r="H41" t="n">
+        <v>22710</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>200</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012415997_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3215295</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3215295</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Skab et dejligt og køligt sted på din terrasse, og beskyt dig selv mod UV-stråler med denne sammenrullelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Nem betjening: Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke markisen ved hjælp af håndsvinget.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den sammenrullelige har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve, stof: Bordeaux&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, stof (100 % polyester) med PU-coating&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (L x B)&lt;/li&gt;&lt;li&gt;Vand- og smudsafvisende&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012415997_m_en_hd_1.jpg, https://vdxl.im/8721012415997_a_en_hd_1.jpg, https://vdxl.im/8721012415997_g_en_hd_1.jpg, https://vdxl.im/8721012415997_g_en_hd_2.jpg, https://vdxl.im/8721012415997_g_en_hd_3.jpg, https://vdxl.im/8721012415997_g_en_hd_4.jpg, https://vdxl.im/8721012415997_g_en_hd_5.jpg, https://vdxl.im/8721012415997_g_en_hd_6.jpg, https://vdxl.im/8721012415997_g_en_hd_7.jpg, https://vdxl.im/8721012415997_g_en_hd_8.jpg, https://vdxl.im/8721012415997_g_en_hd_9.jpg, https://vdxl.im/8721012415997_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>burgundy (white frame)</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3216104</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8721012424081</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2329</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3329</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1366</v>
+      </c>
+      <c r="H42" t="n">
+        <v>16000</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>200</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424081_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3216104</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3216104</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 3,5 x 2,5 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 347 x 247 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424081_m_en_hd_1.jpg, https://vdxl.im/8721012424081_a_en_hd_1.jpg, https://vdxl.im/8721012424081_g_en_hd_1.jpg, https://vdxl.im/8721012424081_g_en_hd_2.jpg, https://vdxl.im/8721012424081_g_en_hd_3.jpg, https://vdxl.im/8721012424081_g_en_hd_4.jpg, https://vdxl.im/8721012424081_g_en_hd_5.jpg, https://vdxl.im/8721012424081_g_en_hd_6.jpg, https://vdxl.im/8721012424081_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>anthracite and white (white frame)</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>3,5 x 2,5 m</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3216105</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8721012424098</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2749</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3929</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1614</v>
+      </c>
+      <c r="H43" t="n">
+        <v>22020</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>200</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424098_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3216105</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3216105</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 397 x 296,5 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424098_m_en_hd_1.jpg, https://vdxl.im/8721012424098_a_en_hd_1.jpg, https://vdxl.im/8721012424098_g_en_hd_1.jpg, https://vdxl.im/8721012424098_g_en_hd_2.jpg, https://vdxl.im/8721012424098_g_en_hd_3.jpg, https://vdxl.im/8721012424098_g_en_hd_4.jpg, https://vdxl.im/8721012424098_g_en_hd_5.jpg, https://vdxl.im/8721012424098_g_en_hd_6.jpg, https://vdxl.im/8721012424098_g_en_hd_7.jpg, https://vdxl.im/8721012424098_g_en_hd_8.jpg, https://vdxl.im/8721012424098_g_en_hd_9.jpg, https://vdxl.im/8721012424098_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>anthracite and white (white frame)</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3216106</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8721012424104</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3019</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4319</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1771</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24500</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>37</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424104_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3216106</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3216106</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4,5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 447 x 297 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424104_m_en_hd_1.jpg, https://vdxl.im/8721012424104_a_en_hd_1.jpg, https://vdxl.im/8721012424104_g_en_hd_1.jpg, https://vdxl.im/8721012424104_g_en_hd_2.jpg, https://vdxl.im/8721012424104_g_en_hd_3.jpg, https://vdxl.im/8721012424104_g_en_hd_4.jpg, https://vdxl.im/8721012424104_g_en_hd_5.jpg, https://vdxl.im/8721012424104_g_en_hd_6.jpg, https://vdxl.im/8721012424104_g_en_hd_7.jpg, https://vdxl.im/8721012424104_g_en_hd_8.jpg, https://vdxl.im/8721012424104_g_en_hd_9.jpg, https://vdxl.im/8721012424104_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>anthracite and white (white frame)</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>4,5 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3216107</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8721012424111</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3329</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4759</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1958</v>
+      </c>
+      <c r="H45" t="n">
+        <v>25120</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>15</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424111_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3216107</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3216107</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 497,5 x 299,5 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424111_m_en_hd_1.jpg, https://vdxl.im/8721012424111_a_en_hd_1.jpg, https://vdxl.im/8721012424111_g_en_hd_1.jpg, https://vdxl.im/8721012424111_g_en_hd_2.jpg, https://vdxl.im/8721012424111_g_en_hd_3.jpg, https://vdxl.im/8721012424111_g_en_hd_4.jpg, https://vdxl.im/8721012424111_g_en_hd_5.jpg, https://vdxl.im/8721012424111_g_en_hd_6.jpg, https://vdxl.im/8721012424111_g_en_hd_7.jpg, https://vdxl.im/8721012424111_g_en_hd_8.jpg, https://vdxl.im/8721012424111_g_en_hd_9.jpg, https://vdxl.im/8721012424111_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>anthracite and white (white frame)</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>5 x 3 m</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3216112</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8721012424166</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3369</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4819</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1977</v>
+      </c>
+      <c r="H46" t="n">
+        <v>25120</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>15</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424166_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3216112</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3216112</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 497,5 x 299,5 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012424166_m_en_hd_1.jpg, https://vdxl.im/8721012424166_a_en_hd_1.jpg, https://vdxl.im/8721012424166_g_en_hd_1.jpg, https://vdxl.im/8721012424166_g_en_hd_2.jpg, https://vdxl.im/8721012424166_g_en_hd_3.jpg, https://vdxl.im/8721012424166_g_en_hd_4.jpg, https://vdxl.im/8721012424166_g_en_hd_5.jpg, https://vdxl.im/8721012424166_g_en_hd_6.jpg, https://vdxl.im/8721012424166_g_en_hd_7.jpg, https://vdxl.im/8721012424166_g_en_hd_8.jpg, https://vdxl.im/8721012424166_g_en_hd_9.jpg, https://vdxl.im/8721012424166_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Antracit og hvid (antracit ramme)</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>5 x 3 m</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3330599</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8721158809582</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2549</v>
+      </c>
+      <c r="F47" t="n">
+        <v>3649</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1495</v>
+      </c>
+      <c r="H47" t="n">
+        <v>20390</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>200</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158809582_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>3330599</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>3330599</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Den moderne udtrækkelige markise er en smart løsning til skygge, lavet til dem, der ønsker et stilfuldt fristed fra solen. Dens slanke rektangulære form passer perfekt til moderne terrasser og haver, med et fokus på enkelhed og minimalisme. Markisen strækker sig let ud og skaber et alsidigt rum, der er perfekt til sommeraftener eller afslapning alene. Den er lavet af 100% polyester, som giver en moderne vibe og beskytter mod hård sollys. Det er ikke bare en skygge, men et stilfuldt statement til dit udendørs rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Markisen er lavet af 100% polyester, hvilket sikrer holdbarhed og modstår vejret. Det stærke stof holder farverne klare og beskytter mod solens stråler, så den holder sig pæn i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hvad der er inkluderet:&lt;/b&gt; Pakken indeholder en stærk ramme og stofkomponent, der er omhyggeligt lavet for at sikre stabilitet og ensartet ydeevne. Rammen holder stoffet på plads, så det beholder sin form selv efter gentagen brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel udtrækningsmekanisme:&lt;/b&gt; Med en simpel manuel funktion kan du nemt justere markisen til den ønskede længde, som giver dig tilpasset skygge. Den er perfekt til enhver lejlighed, fra hyggelige aftener til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Brug:&lt;/b&gt; Markisen er designet til udendørs brug, perfekt til haven og terrassen. Den er ideel til sommeraftener, picnic eller bare afslapning. Den kan opgradere ethvert udendørs område betydeligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje:&lt;/b&gt; Det er nemt at holde markisen pæn. Tør den af med en fugtig klud for at fjerne snavs og sikre, at den holder sig flot og fungerer godt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Polyester med PU belægning&lt;/li&gt;&lt;li&gt;Rammemateriale: Pulverlakeret stål, aluminium&lt;/li&gt;&lt;li&gt;Størrelse: 400 × 300 cm&lt;/li&gt;&lt;li&gt;Længde på håndsving: 165&lt;/li&gt;&lt;li&gt;Vejrresistent stof&lt;/li&gt;&lt;li&gt;Korrosionsbestandig aluminiumrulle&lt;/li&gt;&lt;li&gt;Robuste udtrækkelige arme&lt;/li&gt;&lt;li&gt;Håndsving til nem udtrækning og indtrækning&lt;/li&gt;&lt;li&gt;Monteringsudstyr inkluderet&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Manuel Utrækkelig Markise&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158809582_mo-im_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721158809582_mo-im_en_hd_2.jpg, https://vdxl.im/8721158809582_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158809582_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158809582_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721158809582_detail_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-siz_en_hd_2.jpg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sort (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3330695</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8721158810540</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3669</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1512</v>
+      </c>
+      <c r="H48" t="n">
+        <v>20470</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>87</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158810540_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>3330695</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>3330695</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Den moderne udtrækkelige markise er en smart løsning til skygge, lavet til dem, der ønsker et stilfuldt fristed fra solen. Dens slanke rektangulære form passer perfekt til moderne terrasser og haver, med et fokus på enkelhed og minimalisme. Markisen strækker sig let ud og skaber et alsidigt rum, der er perfekt til sommeraftener eller afslapning alene. Den er lavet af 100% polyester, som giver en moderne vibe og beskytter mod hård sollys. Det er ikke bare en skygge, men et stilfuldt statement til dit udendørs rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Markisen er lavet af 100% polyester, hvilket sikrer holdbarhed og modstår vejret. Det stærke stof holder farverne klare og beskytter mod solens stråler, så den holder sig pæn i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hvad der er inkluderet:&lt;/b&gt; Pakken indeholder en stærk ramme og stofkomponent, der er omhyggeligt lavet for at sikre stabilitet og ensartet ydeevne. Rammen holder stoffet på plads, så det beholder sin form selv efter gentagen brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel udtrækningsmekanisme:&lt;/b&gt; Med en simpel manuel funktion kan du nemt justere markisen til den ønskede længde, som giver dig tilpasset skygge. Den er perfekt til enhver lejlighed, fra hyggelige aftener til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Brug:&lt;/b&gt; Markisen er designet til udendørs brug, perfekt til haven og terrassen. Den er ideel til sommeraftener, picnic eller bare afslapning. Den kan opgradere ethvert udendørs område betydeligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje:&lt;/b&gt; Det er nemt at holde markisen pæn. Tør den af med en fugtig klud for at fjerne snavs og sikre, at den holder sig flot og fungerer godt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Rød&lt;/li&gt;&lt;li&gt;Materiale: Polyester med PU belægning&lt;/li&gt;&lt;li&gt;Rammemateriale: Pulverlakeret stål, aluminium&lt;/li&gt;&lt;li&gt;Størrelse: 400 × 300 cm&lt;/li&gt;&lt;li&gt;Længde på håndsving: 165&lt;/li&gt;&lt;li&gt;Vejrresistent stof&lt;/li&gt;&lt;li&gt;Korrosionsbestandig aluminiumrulle&lt;/li&gt;&lt;li&gt;Robuste udtrækkelige arme&lt;/li&gt;&lt;li&gt;Håndsving til nem udtrækning og indtrækning&lt;/li&gt;&lt;li&gt;Monteringsudstyr inkluderet&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Manuel Utrækkelig Markise&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158810540_mo-im_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721158810540_mo-im_en_hd_2.jpg, https://vdxl.im/8721158810540_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158810540_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158810540_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721158810540_detail_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-siz_en_hd_2.jpg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rød (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>4 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3330935</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8721158812940</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3039</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4349</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1785</v>
+      </c>
+      <c r="H49" t="n">
+        <v>22180</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158812940_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>3330935</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>3330935</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Den moderne udtrækkelige markise er en smart løsning til skygge, lavet til dem, der ønsker et stilfuldt fristed fra solen. Dens slanke rektangulære form passer perfekt til moderne terrasser og haver, med et fokus på enkelhed og minimalisme. Markisen strækker sig let ud og skaber et alsidigt rum, der er perfekt til sommeraftener eller afslapning alene. Den er lavet af 100% polyester, som giver en moderne vibe og beskytter mod hård sollys. Det er ikke bare en skygge, men et stilfuldt statement til dit udendørs rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Markisen er lavet af 100% polyester, hvilket sikrer holdbarhed og modstår vejret. Det stærke stof holder farverne klare og beskytter mod solens stråler, så den holder sig pæn i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hvad der er inkluderet:&lt;/b&gt; Pakken indeholder en stærk ramme og stofkomponent, der er omhyggeligt lavet for at sikre stabilitet og ensartet ydeevne. Rammen holder stoffet på plads, så det beholder sin form selv efter gentagen brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel udtrækningsmekanisme:&lt;/b&gt; Med en simpel manuel funktion kan du nemt justere markisen til den ønskede længde, som giver dig tilpasset skygge. Den er perfekt til enhver lejlighed, fra hyggelige aftener til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Brug:&lt;/b&gt; Markisen er designet til udendørs brug, perfekt til haven og terrassen. Den er ideel til sommeraftener, picnic eller bare afslapning. Den kan opgradere ethvert udendørs område betydeligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje:&lt;/b&gt; Det er nemt at holde markisen pæn. Tør den af med en fugtig klud for at fjerne snavs og sikre, at den holder sig flot og fungerer godt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Flerfarvet&lt;/li&gt;&lt;li&gt;Materiale: Polyester med PU belægning&lt;/li&gt;&lt;li&gt;Rammemateriale: Pulverlakeret stål, aluminium&lt;/li&gt;&lt;li&gt;Størrelse: 450 × 300 cm&lt;/li&gt;&lt;li&gt;Længde på håndsving: 165&lt;/li&gt;&lt;li&gt;Vejrresistent stof&lt;/li&gt;&lt;li&gt;Korrosionsbestandig aluminiumrulle&lt;/li&gt;&lt;li&gt;Robuste udtrækkelige arme&lt;/li&gt;&lt;li&gt;Håndsving til nem udtrækning og indtrækning&lt;/li&gt;&lt;li&gt;Monteringsudstyr inkluderet&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Manuel Utrækkelig Markise&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158812940_mo-im_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721158812940_mo-im_en_hd_2.jpg, https://vdxl.im/8721158812940_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158812940_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158812940_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721158812940_detail_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-siz_en_hd_2.jpg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Flerfarvet (hvid ramme)</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>4,5 × 3 m</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>373080</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>8721012266186</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1039</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1389</v>
+      </c>
+      <c r="G50" t="n">
+        <v>607</v>
+      </c>
+      <c r="H50" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>5</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012266186_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>373080</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>373080</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Brun&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 85 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 80 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012266186_m_en_hd_1.jpg, https://vdxl.im/8721012266186_a_en_hd_1.jpg, https://vdxl.im/8721012266186_g_en_hd_1.jpg, https://vdxl.im/8721012266186_g_en_hd_2.jpg, https://vdxl.im/8721012266186_g_en_hd_3.jpg, https://vdxl.im/8721012266186_g_en_hd_4.jpg, https://vdxl.im/8721012266186_g_en_hd_5.jpg, https://vdxl.im/8721012266186_g_en_hd_6.jpg, https://vdxl.im/8721012266186_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Brun</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>80 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>373082</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8721012266209</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>839</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1119</v>
+      </c>
+      <c r="G51" t="n">
+        <v>489</v>
+      </c>
+      <c r="H51" t="n">
+        <v>22000</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>14</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012266209_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>373082</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>373082</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cappuccino&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 85 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 80 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012266209_m_en_hd_1.jpg, https://vdxl.im/8721012266209_a_en_hd_1.jpg, https://vdxl.im/8721012266209_g_en_hd_1.jpg, https://vdxl.im/8721012266209_g_en_hd_2.jpg, https://vdxl.im/8721012266209_g_en_hd_3.jpg, https://vdxl.im/8721012266209_g_en_hd_4.jpg, https://vdxl.im/8721012266209_g_en_hd_5.jpg, https://vdxl.im/8721012266209_g_en_hd_6.jpg, https://vdxl.im/8721012266209_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Cappuccino</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>80 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>373118</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8721012266568</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>889</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1189</v>
+      </c>
+      <c r="G52" t="n">
+        <v>519</v>
+      </c>
+      <c r="H52" t="n">
+        <v>22700</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>96</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012266568_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>373118</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>373118</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 90 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012266568_m_en_hd_1.jpg, https://vdxl.im/8721012266568_a_en_hd_1.jpg, https://vdxl.im/8721012266568_g_en_hd_1.jpg, https://vdxl.im/8721012266568_g_en_hd_2.jpg, https://vdxl.im/8721012266568_g_en_hd_3.jpg, https://vdxl.im/8721012266568_g_en_hd_4.jpg, https://vdxl.im/8721012266568_g_en_hd_5.jpg, https://vdxl.im/8721012266568_g_en_hd_6.jpg, https://vdxl.im/8721012266568_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>373181</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8721012267190</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1599</v>
+      </c>
+      <c r="G53" t="n">
+        <v>702</v>
+      </c>
+      <c r="H53" t="n">
+        <v>24450</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>22</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267190_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>373181</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>373181</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 140 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267190_m_en_hd_1.jpg, https://vdxl.im/8721012267190_a_en_hd_1.jpg, https://vdxl.im/8721012267190_g_en_hd_1.jpg, https://vdxl.im/8721012267190_g_en_hd_2.jpg, https://vdxl.im/8721012267190_g_en_hd_3.jpg, https://vdxl.im/8721012267190_g_en_hd_4.jpg, https://vdxl.im/8721012267190_g_en_hd_5.jpg, https://vdxl.im/8721012267190_g_en_hd_6.jpg, https://vdxl.im/8721012267190_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Grå</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>373183</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8721012267213</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1589</v>
+      </c>
+      <c r="G54" t="n">
+        <v>699</v>
+      </c>
+      <c r="H54" t="n">
+        <v>24450</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>44</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267213_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>373183</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>373183</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort og hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 140 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267213_m_en_hd_1.jpg, https://vdxl.im/8721012267213_a_en_hd_1.jpg, https://vdxl.im/8721012267213_g_en_hd_1.jpg, https://vdxl.im/8721012267213_g_en_hd_2.jpg, https://vdxl.im/8721012267213_g_en_hd_3.jpg, https://vdxl.im/8721012267213_g_en_hd_4.jpg, https://vdxl.im/8721012267213_g_en_hd_5.jpg, https://vdxl.im/8721012267213_g_en_hd_6.jpg, https://vdxl.im/8721012267213_g_en_hd_7.jpg, https://vdxl.im/8721012267213_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sort og hvid</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>373184</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8721012267220</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1509</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G55" t="n">
+        <v>883</v>
+      </c>
+      <c r="H55" t="n">
+        <v>24450</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>14</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267220_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>373184</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>373184</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 140 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267220_m_en_hd_1.jpg, https://vdxl.im/8721012267220_a_en_hd_1.jpg, https://vdxl.im/8721012267220_g_en_hd_1.jpg, https://vdxl.im/8721012267220_g_en_hd_2.jpg, https://vdxl.im/8721012267220_g_en_hd_3.jpg, https://vdxl.im/8721012267220_g_en_hd_4.jpg, https://vdxl.im/8721012267220_g_en_hd_5.jpg, https://vdxl.im/8721012267220_g_en_hd_6.jpg, https://vdxl.im/8721012267220_g_en_hd_7.jpg, https://vdxl.im/8721012267220_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Hvid og sort</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>373224</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8721012267626</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1999</v>
+      </c>
+      <c r="G56" t="n">
+        <v>877</v>
+      </c>
+      <c r="H56" t="n">
+        <v>26650</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>14</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267626_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>373224</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>373224</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 165 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 160 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267626_m_en_hd_1.jpg, https://vdxl.im/8721012267626_a_en_hd_1.jpg, https://vdxl.im/8721012267626_g_en_hd_1.jpg, https://vdxl.im/8721012267626_g_en_hd_2.jpg, https://vdxl.im/8721012267626_g_en_hd_3.jpg, https://vdxl.im/8721012267626_g_en_hd_4.jpg, https://vdxl.im/8721012267626_g_en_hd_5.jpg, https://vdxl.im/8721012267626_g_en_hd_6.jpg, https://vdxl.im/8721012267626_g_en_hd_7.jpg, https://vdxl.im/8721012267626_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Hvid og sort</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>160 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>373239</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>8721012267770</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1939</v>
+      </c>
+      <c r="G57" t="n">
+        <v>851</v>
+      </c>
+      <c r="H57" t="n">
+        <v>27300</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>63</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267770_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>373239</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>373239</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 185 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 180 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267770_m_en_hd_1.jpg, https://vdxl.im/8721012267770_a_en_hd_1.jpg, https://vdxl.im/8721012267770_g_en_hd_1.jpg, https://vdxl.im/8721012267770_g_en_hd_2.jpg, https://vdxl.im/8721012267770_g_en_hd_3.jpg, https://vdxl.im/8721012267770_g_en_hd_4.jpg, https://vdxl.im/8721012267770_g_en_hd_5.jpg, https://vdxl.im/8721012267770_g_en_hd_6.jpg, https://vdxl.im/8721012267770_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>373258</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>8721012267961</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1729</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2309</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1017</v>
+      </c>
+      <c r="H58" t="n">
+        <v>28350</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>34</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267961_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>373258</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>373258</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 200 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267961_m_en_hd_1.jpg, https://vdxl.im/8721012267961_a_en_hd_1.jpg, https://vdxl.im/8721012267961_g_en_hd_1.jpg, https://vdxl.im/8721012267961_g_en_hd_2.jpg, https://vdxl.im/8721012267961_g_en_hd_3.jpg, https://vdxl.im/8721012267961_g_en_hd_4.jpg, https://vdxl.im/8721012267961_g_en_hd_5.jpg, https://vdxl.im/8721012267961_g_en_hd_6.jpg, https://vdxl.im/8721012267961_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>200 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>373259</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>8721012267978</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2139</v>
+      </c>
+      <c r="G59" t="n">
+        <v>938</v>
+      </c>
+      <c r="H59" t="n">
+        <v>28350</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>24</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267978_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>373259</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>373259</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 200 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012267978_m_en_hd_1.jpg, https://vdxl.im/8721012267978_a_en_hd_1.jpg, https://vdxl.im/8721012267978_g_en_hd_1.jpg, https://vdxl.im/8721012267978_g_en_hd_2.jpg, https://vdxl.im/8721012267978_g_en_hd_3.jpg, https://vdxl.im/8721012267978_g_en_hd_4.jpg, https://vdxl.im/8721012267978_g_en_hd_5.jpg, https://vdxl.im/8721012267978_g_en_hd_6.jpg, https://vdxl.im/8721012267978_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>200 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>373263</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>8721012268012</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1719</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2299</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1011</v>
+      </c>
+      <c r="H60" t="n">
+        <v>28350</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>20</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012268012_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>373263</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>373263</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort og hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 200 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012268012_m_en_hd_1.jpg, https://vdxl.im/8721012268012_a_en_hd_1.jpg, https://vdxl.im/8721012268012_g_en_hd_1.jpg, https://vdxl.im/8721012268012_g_en_hd_2.jpg, https://vdxl.im/8721012268012_g_en_hd_3.jpg, https://vdxl.im/8721012268012_g_en_hd_4.jpg, https://vdxl.im/8721012268012_g_en_hd_5.jpg, https://vdxl.im/8721012268012_g_en_hd_6.jpg, https://vdxl.im/8721012268012_g_en_hd_7.jpg, https://vdxl.im/8721012268012_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sort og hvid</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>200 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sofasaet-til-haven-7-dele-med-hynder-polyrattan-sort-10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3260350</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8721102480447</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4489</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5989</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2636</v>
+      </c>
+      <c r="H61" t="n">
+        <v>65200</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>111</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721102480447_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>3260350</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>3260350</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette havesofasæt er den perfekte tilføjelse til din have eller terrasse og giver et behageligt og indbydende sted at sidde og snakke med familie og venner eller bare slappe af og nyde udendørslivet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: PE-rattan, også kendt som polyrattan, er et stærkt syntetisk materiale, der ikke kræver meget vedligeholdelse, og det ligner naturlig rattan. Det er let i vægt, nemt at rengøre, og det anvendes ofte til udendørs møbler grundet dets holdbarhed og vejrbestandige egenskaber.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion med vandafvisende pose: Havemøblet har opbevaringsplads under sædet med en vandafvisende pose til opbevaring af hynder, legetøj og andre ting. Den indvendige pose kan fastgøres sikkert til udendørs møblet med burrebåndslukninger for øget stabilitet.&lt;/li&gt;&lt;li&gt;Aftagelige og vaskbare betræk: Disse sædehynder er forsynet med aftagelige betræk, så de nemt kan vaskes og vedligeholdes.&lt;/li&gt;&lt;li&gt;Modulært design: Dette havemøbelsæt har et modulært design, der gør det fleksibelt og nemt at flytte rundt på, så du kan skabe et skræddersyet havemøbelarrangement.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Vi anbefaler, at du beskytter dine udendørs møbler med et vandtæt overtræk for at sikre, at de forbliver smukke.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Maks. bæreevne (pr. sæde ): 110 kg&lt;/li&gt;&lt;li&gt;UV-resistent&lt;/li&gt;&lt;li&gt;Justerbare plastfødder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hjørnemodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 62 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midtermodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofa med armlæn:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål, massivt akacietræ med en oliefinish&lt;/li&gt;&lt;li&gt;Mål: 59 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;Armlænets højde fra gulvet: 55 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hynde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, parasoldug: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale, sædehynde: Skum&lt;/li&gt;&lt;li&gt;Fyldmateriale, ryghynde: Bomuldsfibre&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 55 x 55 x 3 cm (B x D x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 55 x 45 x 13 cm (L x B x T)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x hjørnemodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;3 x midtermodul med opbevaringsfunktion og vandafvisende taske&lt;/li&gt;&lt;li&gt;2 x sofamodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;9 x ryghynde&lt;/li&gt;&lt;li&gt;7 x sædehynde med aftageligt og vaskbart betræk&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721102480447_m_en_hd_1.jpg, https://vdxl.im/8721102480447_a_en_hd_1.jpg, https://vdxl.im/8721102480447_g_en_hd_1.jpg, https://res.cloudinary.com/vdxl/image/upload/v1709801887/VN%20rattan/1_Light_beige_Rattan_Premium_rattan_.png</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>beige og cremefarvet</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA61"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+          <t>plantevogne-2-stk-o30x7-5-wpc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3185735</t>
+          <t>3143926</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8720845831202</t>
+          <t>8720845541262</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1799</v>
+        <v>849</v>
       </c>
       <c r="F2" t="n">
-        <v>2399</v>
+        <v>1219</v>
       </c>
       <c r="G2" t="n">
-        <v>1057</v>
+        <v>496</v>
       </c>
       <c r="H2" t="n">
-        <v>59640</v>
+        <v>7040</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831202_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845541262_a_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3185735</t>
+          <t>3143926</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3185735</t>
+          <t>3143926</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Du kan nemt og hurtigt flytte rundt på dine potteplanter ved hjælp af disse praktiske plantevogne.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Robust materiale: Plantevognen er fremstillet af WPC (træplastkomposit), så den er slidstærk, vejrbestandig og velegnet til udendørs brug.&lt;/li&gt;&lt;li&gt;Høj bæreevne: Plantevognen har en bæreevne på op til 100 kg, hvilket er ideelt til daglig brug.&lt;/li&gt;&lt;li&gt;Drejelige hjul: Plantevognen kan nemt flyttes rundt takket være hjulene, der kan dreje 360 grader.&lt;/li&gt;&lt;li&gt;Praktiske bremser: Blomstervognen kan nemt stoppes takket være bremserne på to af hjulene.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: WPC&lt;/li&gt;&lt;li&gt;Mål: 30 x 30 x 7,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Hjulene kan dreje 360°&lt;/li&gt;&lt;li&gt;2 hjul med bremser&lt;/li&gt;&lt;li&gt;Bæreevne (hver): 100 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;4 x plantevogn&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831202_m_en_hd_1.jpg, https://vdxl.im/8720845831202_a_en_hd_1.jpg, https://vdxl.im/8720845831202_g_en_hd_1.jpg, https://vdxl.im/8720845831202_g_en_hd_2.jpg, https://vdxl.im/8720845831202_g_en_hd_3.jpg, https://vdxl.im/8720845831202_g_en_hd_4.jpg, https://vdxl.im/8720845831202_g_en_hd_5.jpg, https://vdxl.im/8720845831202_g_en_hd_6.jpg, https://vdxl.im/8720845831202_g_en_hd_7.jpg, https://vdxl.im/8720845831202_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845541262_a_en_hd_1.jpg, https://vdxl.im/8720845541262_g_en_hd_1.jpg, https://vdxl.im/8720845541262_g_en_hd_2.jpg, https://vdxl.im/8720845541262_g_en_hd_3.jpg, https://vdxl.im/8720845541262_g_en_hd_4.jpg, https://vdxl.im/8720845541262_g_en_hd_5.jpg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -666,16 +666,24 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Hvid</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+          <t>Grå</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Firkantet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -685,25 +693,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3185738</t>
+          <t>830222</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8720845831233</t>
+          <t>8720845870577</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1789</v>
+        <v>869</v>
       </c>
       <c r="F3" t="n">
-        <v>2389</v>
+        <v>1159</v>
       </c>
       <c r="G3" t="n">
-        <v>1051</v>
+        <v>508</v>
       </c>
       <c r="H3" t="n">
-        <v>59640</v>
+        <v>26250</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -721,7 +729,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -740,12 +748,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831233_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845870577_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3185738</t>
+          <t>830222</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -755,46 +763,38 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3185738</t>
+          <t>830222</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk har et tidløst look og vil være en glimrende tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Du kan også sætte dine yndlingsbilleder, pyntegenstande eller blomster på toppen af dette opbevaringsskab for at forskønne dit liv.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid højglans&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 69,5 x 34 x 90 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831233_m_en_hd_1.jpg, https://vdxl.im/8720845831233_a_en_hd_1.jpg, https://vdxl.im/8720845831233_g_en_hd_1.jpg, https://vdxl.im/8720845831233_g_en_hd_2.jpg, https://vdxl.im/8720845831233_g_en_hd_3.jpg, https://vdxl.im/8720845831233_g_en_hd_4.jpg, https://vdxl.im/8720845831233_g_en_hd_5.jpg, https://vdxl.im/8720845831233_g_en_hd_6.jpg, https://vdxl.im/8720845831233_g_en_hd_7.jpg, https://vdxl.im/8720845831233_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845870577_m_en_hd_1.jpg, https://vdxl.im/8720845870577_a_en_hd_1.jpg, https://vdxl.im/8720845870577_g_en_hd_1.jpg, https://vdxl.im/8720845870577_g_en_hd_2.jpg, https://vdxl.im/8720845870577_g_en_hd_3.jpg, https://vdxl.im/8720845870577_g_en_hd_4.jpg, https://vdxl.im/8720845870577_g_en_hd_5.jpg, https://vdxl.im/8720845870577_g_en_hd_6.jpg, https://vdxl.im/8720845870577_g_en_hd_7.jpg, https://vdxl.im/8720845870577_g_en_hd_8.jpg, https://vdxl.im/8720845870577_g_en_hd_9.jpg, https://vdxl.im/8720845870577_g_en_hd_10.jpg, https://vdxl.im/8720845870577_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Sonoma-eg</t>
-        </is>
-      </c>
+          <t>Hvid højglans</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -804,25 +804,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3185739</t>
+          <t>830220</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8720845831240</t>
+          <t>8720845870553</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1919</v>
+        <v>829</v>
       </c>
       <c r="F4" t="n">
-        <v>2559</v>
+        <v>1109</v>
       </c>
       <c r="G4" t="n">
-        <v>1129</v>
+        <v>487</v>
       </c>
       <c r="H4" t="n">
-        <v>59640</v>
+        <v>25830</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -859,12 +859,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831240_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845870553_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>3185739</t>
+          <t>830220</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -874,46 +874,38 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>3185739</t>
+          <t>830220</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk har et tidløst look og vil være en glimrende tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Du kan også sætte dine yndlingsbilleder, pyntegenstande eller blomster på toppen af dette opbevaringsskab for at forskønne dit liv.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 69,5 x 34 x 90 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831240_m_en_hd_1.jpg, https://vdxl.im/8720845831240_a_en_hd_1.jpg, https://vdxl.im/8720845831240_g_en_hd_1.jpg, https://vdxl.im/8720845831240_g_en_hd_2.jpg, https://vdxl.im/8720845831240_g_en_hd_3.jpg, https://vdxl.im/8720845831240_g_en_hd_4.jpg, https://vdxl.im/8720845831240_g_en_hd_5.jpg, https://vdxl.im/8720845831240_g_en_hd_6.jpg, https://vdxl.im/8720845831240_g_en_hd_7.jpg, https://vdxl.im/8720845831240_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845870553_m_en_hd_1.jpg, https://vdxl.im/8720845870553_a_en_hd_1.jpg, https://vdxl.im/8720845870553_g_en_hd_1.jpg, https://vdxl.im/8720845870553_g_en_hd_2.jpg, https://vdxl.im/8720845870553_g_en_hd_3.jpg, https://vdxl.im/8720845870553_g_en_hd_4.jpg, https://vdxl.im/8720845870553_g_en_hd_5.jpg, https://vdxl.im/8720845870553_g_en_hd_6.jpg, https://vdxl.im/8720845870553_g_en_hd_7.jpg, https://vdxl.im/8720845870553_g_en_hd_8.jpg, https://vdxl.im/8720845870553_g_en_hd_9.jpg, https://vdxl.im/8720845870553_g_en_hd_10.jpg, https://vdxl.im/8720845870553_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Betongrå</t>
-        </is>
-      </c>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -923,25 +915,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3185741</t>
+          <t>830223</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8720845831264</t>
+          <t>8720845870584</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1749</v>
+        <v>699</v>
       </c>
       <c r="F5" t="n">
-        <v>2339</v>
+        <v>939</v>
       </c>
       <c r="G5" t="n">
-        <v>1026</v>
+        <v>408</v>
       </c>
       <c r="H5" t="n">
-        <v>59640</v>
+        <v>26250</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -959,7 +951,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -978,12 +970,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831264_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845870584_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>3185741</t>
+          <t>830223</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -993,46 +985,38 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>3185741</t>
+          <t>830223</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Disse trendy skænke har et elegant og klassisk design, og de vil i den grad forskønne din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Skabet er fremstillet af konstrueret træ, så det er let at rengøre med en fugtig klud.&lt;/li&gt;&lt;li&gt;Stor opbevaringsplads: Denne skænk har 4 rum og 2 låger så den tilbyder rigelig med plads til at holde dine magasiner, bøger, dvd'er, multimedieapparater samt andre ting og sager pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Træfødder: Fødderne i massivt eukalyptustræ giver opbevaringsskabet et naturligt og behageligt look, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;li&gt;Displayfunktion: Skabets top er det perfekte sted til fremvisning af potteplanter, billedrammer og andre pyntegenstande.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Lågerne kan monteres på to måder.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, massivt eukalyptustræ&lt;/li&gt;&lt;li&gt;Mål: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;3 x skænk&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk har et tidløst look og vil være en glimrende tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Du kan også sætte dine yndlingsbilleder, pyntegenstande eller blomster på toppen af dette opbevaringsskab for at forskønne dit liv.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 69,5 x 34 x 90 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845831264_m_en_hd_1.jpg, https://vdxl.im/8720845831264_a_en_hd_1.jpg, https://vdxl.im/8720845831264_g_en_hd_1.jpg, https://vdxl.im/8720845831264_g_en_hd_2.jpg, https://vdxl.im/8720845831264_g_en_hd_3.jpg, https://vdxl.im/8720845831264_g_en_hd_4.jpg, https://vdxl.im/8720845831264_g_en_hd_5.jpg, https://vdxl.im/8720845831264_g_en_hd_6.jpg, https://vdxl.im/8720845831264_g_en_hd_7.jpg, https://vdxl.im/8720845831264_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845870584_m_en_hd_1.jpg, https://vdxl.im/8720845870584_a_en_hd_1.jpg, https://vdxl.im/8720845870584_g_en_hd_1.jpg, https://vdxl.im/8720845870584_g_en_hd_2.jpg, https://vdxl.im/8720845870584_g_en_hd_3.jpg, https://vdxl.im/8720845870584_g_en_hd_4.jpg, https://vdxl.im/8720845870584_g_en_hd_5.jpg, https://vdxl.im/8720845870584_g_en_hd_6.jpg, https://vdxl.im/8720845870584_g_en_hd_7.jpg, https://vdxl.im/8720845870584_g_en_hd_8.jpg, https://vdxl.im/8720845870584_g_en_hd_9.jpg, https://vdxl.im/8720845870584_g_en_hd_10.jpg, https://vdxl.im/8720845870584_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Grå sonoma-eg</t>
-        </is>
-      </c>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1042,25 +1026,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3415559</t>
+          <t>830224</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8721364525146</t>
+          <t>8720845870591</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1619</v>
+        <v>709</v>
       </c>
       <c r="F6" t="n">
-        <v>2159</v>
+        <v>949</v>
       </c>
       <c r="G6" t="n">
-        <v>949</v>
+        <v>416</v>
       </c>
       <c r="H6" t="n">
-        <v>51660</v>
+        <v>24990</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1078,7 +1062,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1097,12 +1081,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364525146_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845870591_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3415559</t>
+          <t>830224</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1112,46 +1096,38 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3415559</t>
+          <t>830224</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Det flotte sideboard er en smart opbevaringsløsning, som passer perfekt til moderne hjem. Det er lavet med præcision og passer nemt ind i din spisestue eller stue. Her er der masser af plads til at holde dine ting organiseret, og samtidig ser det fantastisk ud. Med sin glatte overflade og simple design er det ideelt for dem, der ønsker praktiske løsninger med et moderne touch.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Materialer og bygning:&lt;/b&gt; Lavet af holdbart konstrueret træ, så sideboardet er bygget til at holde i mange år. Det stabile design gør det til et godt valg til opbevaring af tungere ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Designfunktioner:&lt;/b&gt; Sideboardets moderne stil har rene linjer og minimal dekoration, som passer godt til nutidig indretning. Den glatte overflade giver et elegant udtryk, og det enkle design sørger for, at det kan bruges i alle rum.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Opbevaring og komponenter:&lt;/b&gt; Med pladehylder, hængslede døre og rummelige rum giver dette sideboard mange opbevaringsmuligheder. Døre gør det nemt at komme til dine ting, og hylderne holder orden.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Montering og pleje:&lt;/b&gt; Montering kræver hjælp fra to personer og en skruetrækker. For vedligeholdelse, tør det blot af med en tør klud og undgå stærke kemikalier for at bevare dets flotte udseende.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Alsidighed:&lt;/b&gt; Perfekt til spisestuer og køkkener, denne opbevaringsløsning imødekommer forskellige behov, fra opbevaring af service og redskaber til bøger og elektronik, hvilket gør det praktisk til enhver situation.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 døre&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;3 x Sideboard&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk har et tidløst look og vil være en glimrende tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Du kan også sætte dine yndlingsbilleder, pyntegenstande eller blomster på toppen af dette opbevaringsskab for at forskønne dit liv.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 69,5 x 34 x 90 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364525146_mo-im_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-an_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-si_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721364525146_detail_en_hd_1.jpg, https://vdxl.im/8721364525146_detail_en_hd_2.jpg, https://vdxl.im/8721364525146_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721364525146_wbg-com_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845870591_m_en_hd_1.jpg, https://vdxl.im/8720845870591_a_en_hd_1.jpg, https://vdxl.im/8720845870591_g_en_hd_1.jpg, https://vdxl.im/8720845870591_g_en_hd_2.jpg, https://vdxl.im/8720845870591_g_en_hd_3.jpg, https://vdxl.im/8720845870591_g_en_hd_4.jpg, https://vdxl.im/8720845870591_g_en_hd_5.jpg, https://vdxl.im/8720845870591_g_en_hd_6.jpg, https://vdxl.im/8720845870591_g_en_hd_7.jpg, https://vdxl.im/8720845870591_g_en_hd_8.jpg, https://vdxl.im/8720845870591_g_en_hd_9.jpg, https://vdxl.im/8720845870591_g_en_hd_10.jpg, https://vdxl.im/8720845870591_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Gammelt træ</t>
-        </is>
-      </c>
+          <t>Betongrå</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1161,25 +1137,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3415576</t>
+          <t>830226</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8721364525313</t>
+          <t>8720845870614</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1589</v>
+        <v>699</v>
       </c>
       <c r="F7" t="n">
-        <v>2119</v>
+        <v>939</v>
       </c>
       <c r="G7" t="n">
-        <v>934</v>
+        <v>411</v>
       </c>
       <c r="H7" t="n">
-        <v>51660</v>
+        <v>26980</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1197,7 +1173,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1216,12 +1192,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364525313_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845870614_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3415576</t>
+          <t>830226</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1231,46 +1207,38 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3415576</t>
+          <t>830226</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Det flotte sideboard er en smart opbevaringsløsning, som passer perfekt til moderne hjem. Det er lavet med præcision og passer nemt ind i din spisestue eller stue. Her er der masser af plads til at holde dine ting organiseret, og samtidig ser det fantastisk ud. Med sin glatte overflade og simple design er det ideelt for dem, der ønsker praktiske løsninger med et moderne touch.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Materialer og bygning:&lt;/b&gt; Lavet af holdbart konstrueret træ, så sideboardet er bygget til at holde i mange år. Det stabile design gør det til et godt valg til opbevaring af tungere ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Designfunktioner:&lt;/b&gt; Sideboardets moderne stil har rene linjer og minimal dekoration, som passer godt til nutidig indretning. Den glatte overflade giver et elegant udtryk, og det enkle design sørger for, at det kan bruges i alle rum.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Opbevaring og komponenter:&lt;/b&gt; Med pladehylder, hængslede døre og rummelige rum giver dette sideboard mange opbevaringsmuligheder. Døre gør det nemt at komme til dine ting, og hylderne holder orden.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Montering og pleje:&lt;/b&gt; Montering kræver hjælp fra to personer og en skruetrækker. For vedligeholdelse, tør det blot af med en tør klud og undgå stærke kemikalier for at bevare dets flotte udseende.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Alsidighed:&lt;/b&gt; Perfekt til spisestuer og køkkener, denne opbevaringsløsning imødekommer forskellige behov, fra opbevaring af service og redskaber til bøger og elektronik, hvilket gør det praktisk til enhver situation.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 døre&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;3 x Sideboard&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk har et tidløst look og vil være en glimrende tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Du kan også sætte dine yndlingsbilleder, pyntegenstande eller blomster på toppen af dette opbevaringsskab for at forskønne dit liv.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dette produkt skal anvendes med det medfølgende vægmonteringsudstyr for at forhindre, at det vælter.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 69,5 x 34 x 90 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364525313_mo-im_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-an_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-si_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721364525313_detail_en_hd_1.jpg, https://vdxl.im/8721364525313_detail_en_hd_2.jpg, https://vdxl.im/8721364525313_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721364525313_wbg-com_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845870614_m_en_hd_1.jpg, https://vdxl.im/8720845870614_a_en_hd_1.jpg, https://vdxl.im/8720845870614_g_en_hd_1.jpg, https://vdxl.im/8720845870614_g_en_hd_2.jpg, https://vdxl.im/8720845870614_g_en_hd_3.jpg, https://vdxl.im/8720845870614_g_en_hd_4.jpg, https://vdxl.im/8720845870614_g_en_hd_5.jpg, https://vdxl.im/8720845870614_g_en_hd_6.jpg, https://vdxl.im/8720845870614_g_en_hd_7.jpg, https://vdxl.im/8720845870614_g_en_hd_8.jpg, https://vdxl.im/8720845870614_g_en_hd_9.jpg, https://vdxl.im/8720845870614_g_en_hd_10.jpg, https://vdxl.im/8720845870614_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>artisan eg</t>
-        </is>
-      </c>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>skaenke-2-stk-60x35x70-cm-konstrueret-trae-2</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1280,25 +1248,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3415593</t>
+          <t>881609</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8721364525481</t>
+          <t>8721288912602</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1589</v>
+        <v>729</v>
       </c>
       <c r="F8" t="n">
-        <v>2119</v>
+        <v>979</v>
       </c>
       <c r="G8" t="n">
-        <v>931</v>
+        <v>427</v>
       </c>
       <c r="H8" t="n">
-        <v>51660</v>
+        <v>23320</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1316,7 +1284,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1335,12 +1303,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364525481_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288912602_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3415593</t>
+          <t>881609</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1350,46 +1318,38 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3415593</t>
+          <t>881609</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Det flotte sideboard er en smart opbevaringsløsning, som passer perfekt til moderne hjem. Det er lavet med præcision og passer nemt ind i din spisestue eller stue. Her er der masser af plads til at holde dine ting organiseret, og samtidig ser det fantastisk ud. Med sin glatte overflade og simple design er det ideelt for dem, der ønsker praktiske løsninger med et moderne touch.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Materialer og bygning:&lt;/b&gt; Lavet af holdbart konstrueret træ, så sideboardet er bygget til at holde i mange år. Det stabile design gør det til et godt valg til opbevaring af tungere ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Designfunktioner:&lt;/b&gt; Sideboardets moderne stil har rene linjer og minimal dekoration, som passer godt til nutidig indretning. Den glatte overflade giver et elegant udtryk, og det enkle design sørger for, at det kan bruges i alle rum.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Opbevaring og komponenter:&lt;/b&gt; Med pladehylder, hængslede døre og rummelige rum giver dette sideboard mange opbevaringsmuligheder. Døre gør det nemt at komme til dine ting, og hylderne holder orden.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Montering og pleje:&lt;/b&gt; Montering kræver hjælp fra to personer og en skruetrækker. For vedligeholdelse, tør det blot af med en tør klud og undgå stærke kemikalier for at bevare dets flotte udseende.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Alsidighed:&lt;/b&gt; Perfekt til spisestuer og køkkener, denne opbevaringsløsning imødekommer forskellige behov, fra opbevaring af service og redskaber til bøger og elektronik, hvilket gør det praktisk til enhver situation.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 60 x 35 x 70 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Med 6 døre&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;3 x Sideboard&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette moderne sideboard er både funktionelt og stilfuldt, med sin enkle rektangulære form. Det passer perfekt til stuer eller spisestuer og tilføjer et lækkert præg, samtidig med at det nemt kan rumme forskellige ting. Det stærke træ og jern gør det til en holdbar del af din indretning.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Lavet af solidt træ og jern, så det er både stærkt og holdbart. Træoverfladen er glat og nem at rengøre, mens jern komplementerer styrken og stabiliteten.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sideboardet har indbyggede hylder og døre. Hylderne hjælper med at udnytte pladsen, mens dørene gør det nemt at få fat i det, du har brug for.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Design:&lt;/b&gt; Dette sideboard har et moderne look med rene linjer og en mat finish på håndtagene. Det enkle design passer perfekt ind i moderne hjem, og den nemme overflade gør det enkelt at holde orden.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Ideelt til stuer eller spisestuer, giver det masser af plads til service, bordduge og andre ting, så du kan holde dit hjem pænt og stilfuldt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Tør blot af med en fugtig klud for at holde det rent. Følg samlevejledningen, og sikr det til væggen for at undgå, at det vælter, så du kan have ro i sindet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørt træ og jern&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 69,5 x 34 x 90 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 2 døre&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Skab&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721364525481_mo-im_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-an_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-si_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721364525481_detail_en_hd_1.jpg, https://vdxl.im/8721364525481_detail_en_hd_2.jpg, https://vdxl.im/8721364525481_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721364525481_wbg-com_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288912602_mo-im_en_hd_1.jpg, https://vdxl.im/8721288912602_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288912602_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288912602_mo-im_en_hd_2.jpg, https://vdxl.im/8721288912602_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288912602_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288912602_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288912602_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288912602_detail_en_hd_1.jpg, https://vdxl.im/8721288912602_detail_en_hd_2.jpg, https://vdxl.im/8721288912602_detail_en_hd_3.jpg, https://vdxl.im/8721288912602_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288912602_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288912602_wbg-com_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Sort eg</t>
-        </is>
-      </c>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1399,25 +1359,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3069271</t>
+          <t>881610</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8720286395950</t>
+          <t>8721288912619</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5009</v>
+        <v>729</v>
       </c>
       <c r="F9" t="n">
-        <v>7159</v>
+        <v>979</v>
       </c>
       <c r="G9" t="n">
-        <v>2947</v>
+        <v>428</v>
       </c>
       <c r="H9" t="n">
-        <v>25240</v>
+        <v>23320</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1435,7 +1395,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1454,12 +1414,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395950_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288912619_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3069271</t>
+          <t>881610</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1469,17 +1429,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3069271</t>
+          <t>881610</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette moderne sideboard er både funktionelt og stilfuldt, med sin enkle rektangulære form. Det passer perfekt til stuer eller spisestuer og tilføjer et lækkert præg, samtidig med at det nemt kan rumme forskellige ting. Det stærke træ og jern gør det til en holdbar del af din indretning.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Lavet af solidt træ og jern, så det er både stærkt og holdbart. Træoverfladen er glat og nem at rengøre, mens jern komplementerer styrken og stabiliteten.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sideboardet har indbyggede hylder og døre. Hylderne hjælper med at udnytte pladsen, mens dørene gør det nemt at få fat i det, du har brug for.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Design:&lt;/b&gt; Dette sideboard har et moderne look med rene linjer og en mat finish på håndtagene. Det enkle design passer perfekt ind i moderne hjem, og den nemme overflade gør det enkelt at holde orden.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Ideelt til stuer eller spisestuer, giver det masser af plads til service, bordduge og andre ting, så du kan holde dit hjem pænt og stilfuldt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Tør blot af med en fugtig klud for at holde det rent. Følg samlevejledningen, og sikr det til væggen for at undgå, at det vælter, så du kan have ro i sindet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørt træ og jern&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 69,5 x 34 x 90 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 2 døre&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Skab&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395950_m_en_hd_1.jpg, https://vdxl.im/8720286395950_a_en_hd_1.jpg, https://vdxl.im/8720286395950_g_en_hd_1.jpg, https://vdxl.im/8720286395950_g_en_hd_2.jpg, https://vdxl.im/8720286395950_g_en_hd_3.jpg, https://vdxl.im/8720286395950_g_en_hd_4.jpg, https://vdxl.im/8720286395950_g_en_hd_5.jpg, https://vdxl.im/8720286395950_g_en_hd_6.jpg, https://vdxl.im/8720286395950_g_en_hd_7.jpg, https://vdxl.im/8720286395950_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288912619_mo-im_en_hd_1.jpg, https://vdxl.im/8721288912619_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288912619_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288912619_mo-im_en_hd_2.jpg, https://vdxl.im/8721288912619_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288912619_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288912619_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288912619_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288912619_detail_en_hd_1.jpg, https://vdxl.im/8721288912619_detail_en_hd_2.jpg, https://vdxl.im/8721288912619_detail_en_hd_3.jpg, https://vdxl.im/8721288912619_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288912619_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288912619_wbg-com_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1489,26 +1449,18 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Blå og hvid</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>3 x 2.5 m</t>
-        </is>
-      </c>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>skaenk-69-5x34x90-cm-konstrueret-trae-69</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1518,25 +1470,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3069272</t>
+          <t>881611</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8720286395967</t>
+          <t>8721288912626</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4909</v>
+        <v>709</v>
       </c>
       <c r="F10" t="n">
-        <v>7019</v>
+        <v>949</v>
       </c>
       <c r="G10" t="n">
-        <v>2885</v>
+        <v>415</v>
       </c>
       <c r="H10" t="n">
-        <v>25240</v>
+        <v>23320</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1554,7 +1506,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1573,12 +1525,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395967_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288912626_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3069272</t>
+          <t>881611</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1588,17 +1540,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3069272</t>
+          <t>881611</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286395967_doc_en_1.pdf?t=1773042783" href="https://vdxl.im/8720286395967_doc_en_1.pdf?t=1773042783" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+          <t>&lt;p&gt;Dette moderne sideboard er både funktionelt og stilfuldt, med sin enkle rektangulære form. Det passer perfekt til stuer eller spisestuer og tilføjer et lækkert præg, samtidig med at det nemt kan rumme forskellige ting. Det stærke træ og jern gør det til en holdbar del af din indretning.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Lavet af solidt træ og jern, så det er både stærkt og holdbart. Træoverfladen er glat og nem at rengøre, mens jern komplementerer styrken og stabiliteten.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Inkluderede komponenter:&lt;/b&gt; Sideboardet har indbyggede hylder og døre. Hylderne hjælper med at udnytte pladsen, mens dørene gør det nemt at få fat i det, du har brug for.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Design:&lt;/b&gt; Dette sideboard har et moderne look med rene linjer og en mat finish på håndtagene. Det enkle design passer perfekt ind i moderne hjem, og den nemme overflade gør det enkelt at holde orden.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Anbefalede anvendelser:&lt;/b&gt; Ideelt til stuer eller spisestuer, giver det masser af plads til service, bordduge og andre ting, så du kan holde dit hjem pænt og stilfuldt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje &amp; Vedligeholdelse:&lt;/b&gt; Tør blot af med en fugtig klud for at holde det rent. Følg samlevejledningen, og sikr det til væggen for at undgå, at det vælter, så du kan have ro i sindet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Ingeniørt træ og jern&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 69,5 x 34 x 90 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 2 døre&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Skab&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395967_m_en_hd_1.jpg, https://vdxl.im/8720286395967_a_en_hd_1.jpg, https://vdxl.im/8720286395967_g_en_hd_1.jpg, https://vdxl.im/8720286395967_g_en_hd_2.jpg, https://vdxl.im/8720286395967_g_en_hd_3.jpg, https://vdxl.im/8720286395967_g_en_hd_4.jpg, https://vdxl.im/8720286395967_g_en_hd_5.jpg, https://vdxl.im/8720286395967_g_en_hd_6.jpg, https://vdxl.im/8720286395967_g_en_hd_7.jpg, https://vdxl.im/8720286395967_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288912626_mo-im_en_hd_1.jpg, https://vdxl.im/8721288912626_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288912626_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288912626_mo-im_en_hd_2.jpg, https://vdxl.im/8721288912626_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288912626_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288912626_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288912626_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288912626_detail_en_hd_1.jpg, https://vdxl.im/8721288912626_detail_en_hd_2.jpg, https://vdxl.im/8721288912626_detail_en_hd_3.jpg, https://vdxl.im/8721288912626_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288912626_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288912626_wbg-com_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1608,26 +1560,18 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Creme</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>3 x 2.5 m</t>
-        </is>
-      </c>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sengegavl-med-opbevaring-massivt-fyrretrae</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1637,25 +1581,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3069273</t>
+          <t>855619</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8720286395974</t>
+          <t>8721158396327</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4909</v>
+        <v>1619</v>
       </c>
       <c r="F11" t="n">
-        <v>7019</v>
+        <v>2159</v>
       </c>
       <c r="G11" t="n">
-        <v>2888</v>
+        <v>950</v>
       </c>
       <c r="H11" t="n">
-        <v>25220</v>
+        <v>25000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1673,7 +1617,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1692,12 +1636,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395974_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158396327_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3069273</t>
+          <t>855619</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1707,17 +1651,17 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3069273</t>
+          <t>855619</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Denne stilfulde sengegavl fuldender sengerammens look, og den passer ind i ethvert rum.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har syv praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne sengegavl er en pladsbesparende løsning, der kan erstatte behovet for et sengebord, hvilket hjælper dig med at maksimere pladsen i soveværelset. Den er ideel til små rum, hvor der er begrænset med plads.&lt;/li&gt;&lt;li&gt;Fritstående sengegavl: Den fritstående sengegavl er en problemfri løsning, der er nem at tilføje uden behov for vægmontering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Mål: 206 x 24 x 82 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Passende madrasbredde: 200 cm&lt;/li&gt;&lt;li&gt;Med opbevaringsrum&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395974_m_en_hd_1.jpg, https://vdxl.im/8720286395974_a_en_hd_1.jpg, https://vdxl.im/8720286395974_g_en_hd_1.jpg, https://vdxl.im/8720286395974_g_en_hd_2.jpg, https://vdxl.im/8720286395974_g_en_hd_3.jpg, https://vdxl.im/8720286395974_g_en_hd_4.jpg, https://vdxl.im/8720286395974_g_en_hd_5.jpg, https://vdxl.im/8720286395974_g_en_hd_6.jpg, https://vdxl.im/8720286395974_g_en_hd_7.jpg, https://vdxl.im/8720286395974_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721158396327_m_en_hd_1.jpg, https://vdxl.im/8721158396327_a_en_hd_1.jpg, https://vdxl.im/8721158396327_g_en_hd_1.jpg, https://vdxl.im/8721158396327_g_en_hd_2.jpg, https://vdxl.im/8721158396327_g_en_hd_3.jpg, https://vdxl.im/8721158396327_g_en_hd_4.jpg, https://vdxl.im/8721158396327_g_en_hd_5.jpg, https://vdxl.im/8721158396327_g_en_hd_6.jpg, https://vdxl.im/8721158396327_g_en_hd_7.jpg, https://vdxl.im/8721158396327_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1727,7 +1671,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Gul og hvid</t>
+          <t>Hvid</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1737,7 +1681,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>3 x 2.5 m</t>
+          <t>200 cm</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr"/>
@@ -1746,7 +1690,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sengegavl-med-opbevaring-massivt-fyrretrae</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1756,25 +1700,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3069274</t>
+          <t>855630</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8720286395981</t>
+          <t>8721158396433</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5019</v>
+        <v>1589</v>
       </c>
       <c r="F12" t="n">
-        <v>7169</v>
+        <v>2119</v>
       </c>
       <c r="G12" t="n">
-        <v>2950</v>
+        <v>934</v>
       </c>
       <c r="H12" t="n">
-        <v>25160</v>
+        <v>17700</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1792,7 +1736,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1811,12 +1755,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395981_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158396433_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3069274</t>
+          <t>855630</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1826,17 +1770,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3069274</t>
+          <t>855630</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Denne stilfulde sengegavl fuldender sengerammens look, og den passer ind i ethvert rum.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har syv praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne sengegavl er en pladsbesparende løsning, der kan erstatte behovet for et sengebord, hvilket hjælper dig med at maksimere pladsen i soveværelset. Den er ideel til små rum, hvor der er begrænset med plads.&lt;/li&gt;&lt;li&gt;Fritstående sengegavl: Den fritstående sengegavl er en problemfri løsning, der er nem at tilføje uden behov for vægmontering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Materiale: Massivt fyrretræ (ubehandlet)&lt;/li&gt;&lt;li&gt;Mål: 146 x 24 x 82 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Passende madrasbredde: 140 cm&lt;/li&gt;&lt;li&gt;Med opbevaringsrum&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395981_m_en_hd_1.jpg, https://vdxl.im/8720286395981_a_en_hd_1.jpg, https://vdxl.im/8720286395981_g_en_hd_1.jpg, https://vdxl.im/8720286395981_g_en_hd_2.jpg, https://vdxl.im/8720286395981_g_en_hd_3.jpg, https://vdxl.im/8720286395981_g_en_hd_4.jpg, https://vdxl.im/8720286395981_g_en_hd_5.jpg, https://vdxl.im/8720286395981_g_en_hd_6.jpg, https://vdxl.im/8720286395981_g_en_hd_7.jpg, https://vdxl.im/8720286395981_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721158396433_m_en_hd_1.jpg, https://vdxl.im/8721158396433_a_en_hd_1.jpg, https://vdxl.im/8721158396433_g_en_hd_1.jpg, https://vdxl.im/8721158396433_g_en_hd_2.jpg, https://vdxl.im/8721158396433_g_en_hd_3.jpg, https://vdxl.im/8721158396433_g_en_hd_4.jpg, https://vdxl.im/8721158396433_g_en_hd_5.jpg, https://vdxl.im/8721158396433_g_en_hd_6.jpg, https://vdxl.im/8721158396433_g_en_hd_7.jpg, https://vdxl.im/8721158396433_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1846,7 +1790,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Antracitgrå</t>
+          <t>Naturfarvet</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1856,7 +1800,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>3 x 2.5 m</t>
+          <t>140 cm</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
@@ -1865,7 +1809,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sengegavl-med-opbevaring-massivt-fyrretrae</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1875,25 +1819,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3069275</t>
+          <t>855631</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8720286395998</t>
+          <t>8721158396440</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4889</v>
+        <v>1239</v>
       </c>
       <c r="F13" t="n">
-        <v>6989</v>
+        <v>1659</v>
       </c>
       <c r="G13" t="n">
-        <v>2874</v>
+        <v>725</v>
       </c>
       <c r="H13" t="n">
-        <v>25180</v>
+        <v>17700</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1911,7 +1855,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1930,12 +1874,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395998_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158396440_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3069275</t>
+          <t>855631</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1945,17 +1889,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3069275</t>
+          <t>855631</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 300 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 300 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Denne stilfulde sengegavl fuldender sengerammens look, og den passer ind i ethvert rum.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har syv praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne sengegavl er en pladsbesparende løsning, der kan erstatte behovet for et sengebord, hvilket hjælper dig med at maksimere pladsen i soveværelset. Den er ideel til små rum, hvor der er begrænset med plads.&lt;/li&gt;&lt;li&gt;Fritstående sengegavl: Den fritstående sengegavl er en problemfri løsning, der er nem at tilføje uden behov for vægmontering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Mål: 146 x 24 x 82 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Passende madrasbredde: 140 cm&lt;/li&gt;&lt;li&gt;Med opbevaringsrum&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286395998_m_en_hd_1.jpg, https://vdxl.im/8720286395998_a_en_hd_1.jpg, https://vdxl.im/8720286395998_g_en_hd_1.jpg, https://vdxl.im/8720286395998_g_en_hd_2.jpg, https://vdxl.im/8720286395998_g_en_hd_3.jpg, https://vdxl.im/8720286395998_g_en_hd_4.jpg, https://vdxl.im/8720286395998_g_en_hd_5.jpg, https://vdxl.im/8720286395998_g_en_hd_6.jpg, https://vdxl.im/8720286395998_g_en_hd_7.jpg, https://vdxl.im/8720286395998_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721158396440_m_en_hd_1.jpg, https://vdxl.im/8721158396440_a_en_hd_1.jpg, https://vdxl.im/8721158396440_g_en_hd_1.jpg, https://vdxl.im/8721158396440_g_en_hd_2.jpg, https://vdxl.im/8721158396440_g_en_hd_3.jpg, https://vdxl.im/8721158396440_g_en_hd_4.jpg, https://vdxl.im/8721158396440_g_en_hd_5.jpg, https://vdxl.im/8721158396440_g_en_hd_6.jpg, https://vdxl.im/8721158396440_g_en_hd_7.jpg, https://vdxl.im/8721158396440_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1965,7 +1909,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>orange og brun</t>
+          <t>Hvid</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1975,7 +1919,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3 x 2.5 m</t>
+          <t>140 cm</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr"/>
@@ -1984,7 +1928,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sengegavl-med-opbevaring-massivt-fyrretrae</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1994,25 +1938,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3069291</t>
+          <t>855637</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8720286396155</t>
+          <t>8721158396501</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5089</v>
+        <v>1489</v>
       </c>
       <c r="F14" t="n">
-        <v>7269</v>
+        <v>1989</v>
       </c>
       <c r="G14" t="n">
-        <v>2989</v>
+        <v>873</v>
       </c>
       <c r="H14" t="n">
-        <v>33440</v>
+        <v>16200</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2030,7 +1974,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2049,12 +1993,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396155_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158396501_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3069291</t>
+          <t>855637</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2064,17 +2008,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>3069291</t>
+          <t>855637</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Denne stilfulde sengegavl fuldender sengerammens look, og den passer ind i ethvert rum.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabil og langtidsholdbar ramme: Massivt fyrretræ er kendt for sin styrke og holdbarhed. De lige åremønstre og de karakteristiske knaster bidrager til den rustikke charme.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Denne elegante sengegavl har syv praktiske hylder, så den tilbyder rigelig med plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne sengegavl er en pladsbesparende løsning, der kan erstatte behovet for et sengebord, hvilket hjælper dig med at maksimere pladsen i soveværelset. Den er ideel til små rum, hvor der er begrænset med plads.&lt;/li&gt;&lt;li&gt;Fritstående sengegavl: Den fritstående sengegavl er en problemfri løsning, der er nem at tilføje uden behov for vægmontering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ&lt;/li&gt;&lt;li&gt;Mål: 126 x 24 x 82 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Passende madrasbredde: 120 cm&lt;/li&gt;&lt;li&gt;Med opbevaringsrum&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396155_m_en_hd_1.jpg, https://vdxl.im/8720286396155_a_en_hd_1.jpg, https://vdxl.im/8720286396155_g_en_hd_1.jpg, https://vdxl.im/8720286396155_g_en_hd_2.jpg, https://vdxl.im/8720286396155_g_en_hd_3.jpg, https://vdxl.im/8720286396155_g_en_hd_4.jpg, https://vdxl.im/8720286396155_g_en_hd_5.jpg, https://vdxl.im/8720286396155_g_en_hd_6.jpg, https://vdxl.im/8720286396155_g_en_hd_7.jpg, https://vdxl.im/8720286396155_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721158396501_m_en_hd_1.jpg, https://vdxl.im/8721158396501_a_en_hd_1.jpg, https://vdxl.im/8721158396501_g_en_hd_1.jpg, https://vdxl.im/8721158396501_g_en_hd_2.jpg, https://vdxl.im/8721158396501_g_en_hd_3.jpg, https://vdxl.im/8721158396501_g_en_hd_4.jpg, https://vdxl.im/8721158396501_g_en_hd_5.jpg, https://vdxl.im/8721158396501_g_en_hd_6.jpg, https://vdxl.im/8721158396501_g_en_hd_7.jpg, https://vdxl.im/8721158396501_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2084,7 +2028,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Blå og hvid</t>
+          <t>Hvid</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2094,7 +2038,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>3.5 x 2.5 m</t>
+          <t>120 cm</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr"/>
@@ -2103,7 +2047,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2113,25 +2057,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3069292</t>
+          <t>3374863</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8720286396162</t>
+          <t>8721288529275</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5189</v>
+        <v>4849</v>
       </c>
       <c r="F15" t="n">
-        <v>7419</v>
+        <v>6469</v>
       </c>
       <c r="G15" t="n">
-        <v>3052</v>
+        <v>2852</v>
       </c>
       <c r="H15" t="n">
-        <v>27640</v>
+        <v>83480</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2149,7 +2093,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2168,12 +2112,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396162_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529275_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>3069292</t>
+          <t>3374863</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2183,17 +2127,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>3069292</t>
+          <t>3374863</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og beige&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,06 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396162_m_en_hd_1.jpg, https://vdxl.im/8720286396162_a_en_hd_1.jpg, https://vdxl.im/8720286396162_g_en_hd_1.jpg, https://vdxl.im/8720286396162_g_en_hd_2.jpg, https://vdxl.im/8720286396162_g_en_hd_3.jpg, https://vdxl.im/8720286396162_g_en_hd_4.jpg, https://vdxl.im/8720286396162_g_en_hd_5.jpg, https://vdxl.im/8720286396162_g_en_hd_6.jpg, https://vdxl.im/8720286396162_g_en_hd_7.jpg, https://vdxl.im/8720286396162_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529275_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529275_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529275_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529275_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529275_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529275_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529275_detail_en_px16_1.jpg, https://vdxl.im/8721288529275_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529275_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529275_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2203,17 +2147,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Creme</t>
+          <t>Naturlig og beige</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>3.5 x 2.5 m</t>
+          <t>egnet til lejlighed</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr"/>
@@ -2222,7 +2166,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2232,25 +2176,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3069293</t>
+          <t>3374830</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8720286396179</t>
+          <t>8721288528940</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5189</v>
+        <v>4829</v>
       </c>
       <c r="F16" t="n">
-        <v>7419</v>
+        <v>6439</v>
       </c>
       <c r="G16" t="n">
-        <v>3051</v>
+        <v>2841</v>
       </c>
       <c r="H16" t="n">
-        <v>27700</v>
+        <v>85220</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2268,7 +2212,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2287,12 +2231,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396179_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288528940_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3069293</t>
+          <t>3374830</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2302,17 +2246,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>3069293</t>
+          <t>3374830</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og fløde&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,42 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 36 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 4 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396179_m_en_hd_1.jpg, https://vdxl.im/8720286396179_a_en_hd_1.jpg, https://vdxl.im/8720286396179_g_en_hd_1.jpg, https://vdxl.im/8720286396179_g_en_hd_2.jpg, https://vdxl.im/8720286396179_g_en_hd_3.jpg, https://vdxl.im/8720286396179_g_en_hd_4.jpg, https://vdxl.im/8720286396179_g_en_hd_5.jpg, https://vdxl.im/8720286396179_g_en_hd_6.jpg, https://vdxl.im/8720286396179_g_en_hd_7.jpg, https://vdxl.im/8720286396179_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288528940_mo-im_en_px16_1.jpg, https://vdxl.im/8721288528940_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288528940_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288528940_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288528940_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288528940_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288528940_detail_en_px16_1.jpg, https://vdxl.im/8721288528940_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288528940_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288528940_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2322,17 +2266,17 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Gul og hvid</t>
+          <t>Natur og cremefarvet</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>3.5 x 2.5 m</t>
+          <t>horisontale lameller</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr"/>
@@ -2341,7 +2285,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2351,25 +2295,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3069294</t>
+          <t>3374831</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8720286396186</t>
+          <t>8721288528957</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5189</v>
+        <v>4839</v>
       </c>
       <c r="F17" t="n">
-        <v>7419</v>
+        <v>6459</v>
       </c>
       <c r="G17" t="n">
-        <v>3048</v>
+        <v>2843</v>
       </c>
       <c r="H17" t="n">
-        <v>27520</v>
+        <v>83520</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2387,7 +2331,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2406,12 +2350,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396186_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288528957_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3069294</t>
+          <t>3374831</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2421,17 +2365,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3069294</t>
+          <t>3374831</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286396186_doc_en_1.pdf?t=1773042823" href="https://vdxl.im/8720286396186_doc_en_1.pdf?t=1773042823" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og lys grå&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,58 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 36 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 4 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396186_m_en_hd_1.jpg, https://vdxl.im/8720286396186_a_en_hd_1.jpg, https://vdxl.im/8720286396186_g_en_hd_1.jpg, https://vdxl.im/8720286396186_g_en_hd_2.jpg, https://vdxl.im/8720286396186_g_en_hd_3.jpg, https://vdxl.im/8720286396186_g_en_hd_4.jpg, https://vdxl.im/8720286396186_g_en_hd_5.jpg, https://vdxl.im/8720286396186_g_en_hd_6.jpg, https://vdxl.im/8720286396186_g_en_hd_7.jpg, https://vdxl.im/8720286396186_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288528957_mo-im_en_px16_1.jpg, https://vdxl.im/8721288528957_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288528957_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288528957_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288528957_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288528957_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288528957_detail_en_px16_1.jpg, https://vdxl.im/8721288528957_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288528957_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288528957_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2441,17 +2385,17 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Antracitgrå</t>
+          <t>Naturlig og lys grå</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>3.5 x 2.5 m</t>
+          <t>horisontale lameller</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr"/>
@@ -2460,7 +2404,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2470,25 +2414,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3069295</t>
+          <t>3374832</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8720286396193</t>
+          <t>8721288528964</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5069</v>
+        <v>4829</v>
       </c>
       <c r="F18" t="n">
-        <v>7249</v>
+        <v>6439</v>
       </c>
       <c r="G18" t="n">
-        <v>2977</v>
+        <v>2841</v>
       </c>
       <c r="H18" t="n">
-        <v>27760</v>
+        <v>83600</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2506,7 +2450,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2525,12 +2469,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396193_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288528964_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3069295</t>
+          <t>3374832</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2540,17 +2484,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>3069295</t>
+          <t>3374832</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Mål, markise: 350 x 250 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 350 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286396193_doc_en_1.pdf?t=1773042559" href="https://vdxl.im/8720286396193_doc_en_1.pdf?t=1773042559" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og antracit&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,76 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 36 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 4 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396193_m_en_hd_1.jpg, https://vdxl.im/8720286396193_a_en_hd_1.jpg, https://vdxl.im/8720286396193_g_en_hd_1.jpg, https://vdxl.im/8720286396193_g_en_hd_2.jpg, https://vdxl.im/8720286396193_g_en_hd_3.jpg, https://vdxl.im/8720286396193_g_en_hd_4.jpg, https://vdxl.im/8720286396193_g_en_hd_5.jpg, https://vdxl.im/8720286396193_g_en_hd_6.jpg, https://vdxl.im/8720286396193_g_en_hd_7.jpg, https://vdxl.im/8720286396193_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288528964_mo-im_en_px16_1.jpg, https://vdxl.im/8721288528964_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288528964_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288528964_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288528964_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288528964_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288528964_detail_en_px16_1.jpg, https://vdxl.im/8721288528964_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288528964_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288528964_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2560,17 +2504,17 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>orange og brun</t>
+          <t>Naturlig og antracit</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>3.5 x 2.5 m</t>
+          <t>horisontale lameller</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr"/>
@@ -2579,7 +2523,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2589,25 +2533,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3069311</t>
+          <t>3374833</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8720286396353</t>
+          <t>8721288528971</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5869</v>
+        <v>4829</v>
       </c>
       <c r="F19" t="n">
-        <v>8389</v>
+        <v>6439</v>
       </c>
       <c r="G19" t="n">
-        <v>3449</v>
+        <v>2841</v>
       </c>
       <c r="H19" t="n">
-        <v>34760</v>
+        <v>82800</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2625,7 +2569,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2644,12 +2588,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396353_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288528971_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3069311</t>
+          <t>3374833</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2659,17 +2603,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>3069311</t>
+          <t>3374833</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og beige&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,38 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 36 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 4 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396353_m_en_hd_1.jpg, https://vdxl.im/8720286396353_a_en_hd_1.jpg, https://vdxl.im/8720286396353_g_en_hd_1.jpg, https://vdxl.im/8720286396353_g_en_hd_2.jpg, https://vdxl.im/8720286396353_g_en_hd_3.jpg, https://vdxl.im/8720286396353_g_en_hd_4.jpg, https://vdxl.im/8720286396353_g_en_hd_5.jpg, https://vdxl.im/8720286396353_g_en_hd_6.jpg, https://vdxl.im/8720286396353_g_en_hd_7.jpg, https://vdxl.im/8720286396353_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288528971_mo-im_en_px16_1.jpg, https://vdxl.im/8721288528971_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288528971_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288528971_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288528971_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288528971_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288528971_detail_en_px16_1.jpg, https://vdxl.im/8721288528971_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288528971_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288528971_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2679,17 +2623,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Blå og hvid</t>
+          <t>Naturlig og beige</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>4 x 3 m</t>
+          <t>horisontale lameller</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr"/>
@@ -2698,7 +2642,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2708,25 +2652,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3069312</t>
+          <t>3374835</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8720286396360</t>
+          <t>8721288528995</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5859</v>
+        <v>4819</v>
       </c>
       <c r="F20" t="n">
-        <v>8369</v>
+        <v>6429</v>
       </c>
       <c r="G20" t="n">
-        <v>3446</v>
+        <v>2833</v>
       </c>
       <c r="H20" t="n">
-        <v>34760</v>
+        <v>84840</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2744,7 +2688,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2763,12 +2707,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396360_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288528995_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3069312</t>
+          <t>3374835</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2778,17 +2722,17 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>3069312</t>
+          <t>3374835</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; &lt;a title="https://vdxl.im/8720286396360_doc_en_1.pdf?t=1773042609" href="https://vdxl.im/8720286396360_doc_en_1.pdf?t=1773042609" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og fløde&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,04 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396360_m_en_hd_1.jpg, https://vdxl.im/8720286396360_a_en_hd_1.jpg, https://vdxl.im/8720286396360_g_en_hd_1.jpg, https://vdxl.im/8720286396360_g_en_hd_2.jpg, https://vdxl.im/8720286396360_g_en_hd_3.jpg, https://vdxl.im/8720286396360_g_en_hd_4.jpg, https://vdxl.im/8720286396360_g_en_hd_5.jpg, https://vdxl.im/8720286396360_g_en_hd_6.jpg, https://vdxl.im/8720286396360_g_en_hd_7.jpg, https://vdxl.im/8720286396360_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288528995_mo-im_en_px16_1.jpg, https://vdxl.im/8721288528995_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288528995_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288528995_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288528995_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288528995_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288528995_detail_en_px16_1.jpg, https://vdxl.im/8721288528995_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288528995_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2798,17 +2742,17 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Creme</t>
+          <t>Natur og cremefarvet</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>4 x 3 m</t>
+          <t>Åben ramme</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr"/>
@@ -2817,7 +2761,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2827,25 +2771,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3069313</t>
+          <t>3374836</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8720286396377</t>
+          <t>8721288529008</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5859</v>
+        <v>4819</v>
       </c>
       <c r="F21" t="n">
-        <v>8369</v>
+        <v>6429</v>
       </c>
       <c r="G21" t="n">
-        <v>3445</v>
+        <v>2834</v>
       </c>
       <c r="H21" t="n">
-        <v>34760</v>
+        <v>83140</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2863,7 +2807,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2882,12 +2826,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396377_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529008_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3069313</t>
+          <t>3374836</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2897,17 +2841,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>3069313</t>
+          <t>3374836</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Dette apparat kan bruges af børn fra 8 år og opefter samt af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring og viden, hvis de er under opsyn eller er blevet instrueret i brugen af apparatet på en sikker måde, og de forstår de involverede farer. Børn må ikke lege med apparatet. Rengøring og vedligeholdelse må kun udføres af børn uden opsyn. Hvis forsyningsledningen er beskadiget, skal den udskiftes af producenten, dennes serviceagent eller lignende kvalificerede personer for at undgå farer. ADVARSEL: Vigtige sikkerhedsinstruktioner. Det er vigtigt at overholde disse sikkerhedsinstruktioner af sikkerhedsmæssige årsager. Gem disse instruktioner. ADVARSEL: Vigtige sikkerhedsinstruktioner. Følg alle instruktioner, da forkert installation kan medføre alvorlige skade eller død. Lad ikke børn lege med kontrolenheden. Hold fjernbetjeningen væk fra børn. Markisen må ikke bruges under vedligeholdelse såsom vinduespudsning, der bliver udført i nærheden. Bevægelige dele i drevet skal installeres højere end 2,5 m over jorden eller andre niveauer, der kan give adgang. Før drevet installeres skal unødvendige ledninger og snore fjernes og udstyr skal frakobles, hvis det ikke er nødvendigt for brugen. Aktiveringselementet af en forspændt afbryder skal placeres inden for direkte syn af den drevne del, men væk fra bevægelige dele. Det skal monteres i en højde på minimum 1,5 m.Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner. Farlige ubeskyttede bevægelige dele af drevet skal installeres højere end 2,5 m over gulvet eller andre niveauer, der kan forhindre adgang til det. &lt;a title="https://vdxl.im/8720286396377_doc_en_1.pdf?t=1745012781" href="https://vdxl.im/8720286396377_doc_en_1.pdf?t=1745012781" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og lys grå&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,2 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396377_m_en_hd_1.jpg, https://vdxl.im/8720286396377_a_en_hd_1.jpg, https://vdxl.im/8720286396377_g_en_hd_1.jpg, https://vdxl.im/8720286396377_g_en_hd_2.jpg, https://vdxl.im/8720286396377_g_en_hd_3.jpg, https://vdxl.im/8720286396377_g_en_hd_4.jpg, https://vdxl.im/8720286396377_g_en_hd_5.jpg, https://vdxl.im/8720286396377_g_en_hd_6.jpg, https://vdxl.im/8720286396377_g_en_hd_7.jpg, https://vdxl.im/8720286396377_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529008_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529008_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529008_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529008_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529008_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529008_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529008_detail_en_px16_1.jpg, https://vdxl.im/8721288529008_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529008_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529008_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2917,17 +2861,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Gul og hvid</t>
+          <t>Naturlig og lys grå</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>4 x 3 m</t>
+          <t>Åben ramme</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr"/>
@@ -2936,7 +2880,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2946,25 +2890,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3069314</t>
+          <t>3374837</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8720286396384</t>
+          <t>8721288529015</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6129</v>
+        <v>4819</v>
       </c>
       <c r="F22" t="n">
-        <v>8759</v>
+        <v>6429</v>
       </c>
       <c r="G22" t="n">
-        <v>3601</v>
+        <v>2833</v>
       </c>
       <c r="H22" t="n">
-        <v>34600</v>
+        <v>83220</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2982,7 +2926,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -3001,12 +2945,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396384_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529015_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>3069314</t>
+          <t>3374837</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3016,17 +2960,17 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>3069314</t>
+          <t>3374837</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og antracit&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,38 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396384_m_en_hd_1.jpg, https://vdxl.im/8720286396384_a_en_hd_1.jpg, https://vdxl.im/8720286396384_g_en_hd_1.jpg, https://vdxl.im/8720286396384_g_en_hd_2.jpg, https://vdxl.im/8720286396384_g_en_hd_3.jpg, https://vdxl.im/8720286396384_g_en_hd_4.jpg, https://vdxl.im/8720286396384_g_en_hd_5.jpg, https://vdxl.im/8720286396384_g_en_hd_6.jpg, https://vdxl.im/8720286396384_g_en_hd_7.jpg, https://vdxl.im/8720286396384_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529015_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529015_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529015_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529015_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529015_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529015_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529015_detail_en_px16_1.jpg, https://vdxl.im/8721288529015_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529015_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529015_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3036,17 +2980,17 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Antracitgrå</t>
+          <t>Naturlig og antracit</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4 x 3 m</t>
+          <t>Åben ramme</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
@@ -3055,7 +2999,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>markise-m-gardin-led-vindsensor-3x2-5-m-automatisk</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3065,25 +3009,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3069315</t>
+          <t>3374838</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8720286396391</t>
+          <t>8721288529022</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5729</v>
+        <v>4819</v>
       </c>
       <c r="F23" t="n">
-        <v>8189</v>
+        <v>6429</v>
       </c>
       <c r="G23" t="n">
-        <v>3366</v>
+        <v>2833</v>
       </c>
       <c r="H23" t="n">
-        <v>34660</v>
+        <v>82420</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3101,7 +3045,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -3120,12 +3064,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396391_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529022_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3069315</t>
+          <t>3374838</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3135,17 +3079,17 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>3069315</t>
+          <t>3374838</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted i dine uderum med denne udtrækkelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Denne udendørsmarkise er bygget med et rustresistent, pulverlakeret aluminiumsstel, hvilket gør den let i vægt, men robust. Terrassemarkisens stof er lavet af polyester i høj densitet med en PU-belægning, så den er UV-resistent og vandafvisende. Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke den automatiske, sammenrullelige markise med den medfølgende fjernbetjening. Det lange håndsving kan også nemt styre markisen. Den er ligeledes forsynet med en vindsensor, som lukker din markise automatisk, når det blæser. Derudover giver LED-lysene energibesparende belysning om aftenen. Rullegardinet beskytter dig mod UV-stråler og giver ekstra privatliv.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, 100 % polyesterstof med PU-belægning&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (B x H)&lt;/li&gt;&lt;li&gt;Mål, rullegardin: 400 x 120 cm (B x H)&lt;/li&gt;&lt;li&gt;Spændingsforsyning: 230V~ , 0,68A; 50/60Hz&lt;/li&gt;&lt;li&gt;Effekt: 155 W&lt;/li&gt;&lt;li&gt;Drejningsmoment: 20 Nm&lt;/li&gt;&lt;li&gt;Hastighed: 13 omdr./min&lt;/li&gt;&lt;li&gt;LED-spænding: 12 V&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og beige&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 59 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720286396391_m_en_hd_1.jpg, https://vdxl.im/8720286396391_a_en_hd_1.jpg, https://vdxl.im/8720286396391_g_en_hd_1.jpg, https://vdxl.im/8720286396391_g_en_hd_2.jpg, https://vdxl.im/8720286396391_g_en_hd_3.jpg, https://vdxl.im/8720286396391_g_en_hd_4.jpg, https://vdxl.im/8720286396391_g_en_hd_5.jpg, https://vdxl.im/8720286396391_g_en_hd_6.jpg, https://vdxl.im/8720286396391_g_en_hd_7.jpg, https://vdxl.im/8720286396391_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529022_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529022_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529022_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529022_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529022_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529022_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529022_detail_en_px16_1.jpg, https://vdxl.im/8721288529022_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529022_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3155,17 +3099,17 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>orange og brun</t>
+          <t>Naturlig og beige</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>4 x 3 m</t>
+          <t>Åben ramme</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr"/>
@@ -3174,7 +3118,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3184,25 +3128,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>859879</t>
+          <t>3374840</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8721158649102</t>
+          <t>8721288529046</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>529</v>
+        <v>4879</v>
       </c>
       <c r="F24" t="n">
-        <v>759</v>
+        <v>6509</v>
       </c>
       <c r="G24" t="n">
-        <v>311</v>
+        <v>2869</v>
       </c>
       <c r="H24" t="n">
-        <v>15900</v>
+        <v>85640</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3220,7 +3164,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -3239,12 +3183,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649102_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529046_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>859879</t>
+          <t>3374840</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3254,54 +3198,46 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>859879</t>
+          <t>3374840</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og fløde&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,84 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649102_m_en_hd_1.jpg, https://vdxl.im/8721158649102_a_en_hd_1.jpg, https://vdxl.im/8721158649102_g_en_hd_1.jpg, https://vdxl.im/8721158649102_g_en_hd_2.jpg, https://vdxl.im/8721158649102_g_en_hd_3.jpg, https://vdxl.im/8721158649102_g_en_hd_4.jpg, https://vdxl.im/8721158649102_g_en_hd_5.jpg, https://vdxl.im/8721158649102_g_en_hd_6.jpg, https://vdxl.im/8721158649102_g_en_hd_7.jpg, https://vdxl.im/8721158649102_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529046_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529046_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529046_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529046_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529046_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529046_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529046_detail_en_px16_1.jpg, https://vdxl.im/8721288529046_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529046_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Natur og cremefarvet</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Sort</t>
-        </is>
-      </c>
+          <t>Lodrette lameller</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3311,25 +3247,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>859870</t>
+          <t>3374841</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8721158649010</t>
+          <t>8721288529053</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>639</v>
+        <v>4879</v>
       </c>
       <c r="F25" t="n">
-        <v>919</v>
+        <v>6509</v>
       </c>
       <c r="G25" t="n">
-        <v>376</v>
+        <v>2870</v>
       </c>
       <c r="H25" t="n">
-        <v>18700</v>
+        <v>83940</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3347,7 +3283,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -3366,12 +3302,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649010_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529053_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>859870</t>
+          <t>3374841</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3381,54 +3317,46 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>859870</t>
+          <t>3374841</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og lys grå&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649010_m_en_hd_1.jpg, https://vdxl.im/8721158649010_a_en_hd_1.jpg, https://vdxl.im/8721158649010_g_en_hd_1.jpg, https://vdxl.im/8721158649010_g_en_hd_2.jpg, https://vdxl.im/8721158649010_g_en_hd_3.jpg, https://vdxl.im/8721158649010_g_en_hd_4.jpg, https://vdxl.im/8721158649010_g_en_hd_5.jpg, https://vdxl.im/8721158649010_g_en_hd_6.jpg, https://vdxl.im/8721158649010_g_en_hd_7.jpg, https://vdxl.im/8721158649010_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529053_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529053_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529053_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529053_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529053_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529053_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529053_detail_en_px16_1.jpg, https://vdxl.im/8721288529053_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529053_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529053_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Naturlig og lys grå</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>100 cm</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Sort</t>
-        </is>
-      </c>
+          <t>Lodrette lameller</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3438,25 +3366,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>859881</t>
+          <t>3374842</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8721158649126</t>
+          <t>8721288529060</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>559</v>
+        <v>4879</v>
       </c>
       <c r="F26" t="n">
-        <v>799</v>
+        <v>6509</v>
       </c>
       <c r="G26" t="n">
-        <v>326</v>
+        <v>2869</v>
       </c>
       <c r="H26" t="n">
-        <v>16000</v>
+        <v>84020</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3474,7 +3402,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -3493,12 +3421,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649126_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529060_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>859881</t>
+          <t>3374842</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3508,54 +3436,46 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>859881</t>
+          <t>3374842</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og antracit&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,18 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649126_m_en_hd_1.jpg, https://vdxl.im/8721158649126_a_en_hd_1.jpg, https://vdxl.im/8721158649126_g_en_hd_1.jpg, https://vdxl.im/8721158649126_g_en_hd_2.jpg, https://vdxl.im/8721158649126_g_en_hd_3.jpg, https://vdxl.im/8721158649126_g_en_hd_4.jpg, https://vdxl.im/8721158649126_g_en_hd_5.jpg, https://vdxl.im/8721158649126_g_en_hd_6.jpg, https://vdxl.im/8721158649126_g_en_hd_7.jpg, https://vdxl.im/8721158649126_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529060_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529060_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529060_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529060_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529060_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529060_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529060_detail_en_px16_1.jpg, https://vdxl.im/8721288529060_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529060_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Naturlig og antracit</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>Betongrå</t>
-        </is>
-      </c>
+          <t>Lodrette lameller</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3565,25 +3485,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>859872</t>
+          <t>3374843</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8721158649034</t>
+          <t>8721288529077</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>599</v>
+        <v>4879</v>
       </c>
       <c r="F27" t="n">
-        <v>859</v>
+        <v>6509</v>
       </c>
       <c r="G27" t="n">
-        <v>350</v>
+        <v>2869</v>
       </c>
       <c r="H27" t="n">
-        <v>18650</v>
+        <v>83220</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3601,7 +3521,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -3620,12 +3540,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649034_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529077_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>859872</t>
+          <t>3374843</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3635,54 +3555,46 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>859872</t>
+          <t>3374843</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 100 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og beige&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,8 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649034_m_en_hd_1.jpg, https://vdxl.im/8721158649034_a_en_hd_1.jpg, https://vdxl.im/8721158649034_g_en_hd_1.jpg, https://vdxl.im/8721158649034_g_en_hd_2.jpg, https://vdxl.im/8721158649034_g_en_hd_3.jpg, https://vdxl.im/8721158649034_g_en_hd_4.jpg, https://vdxl.im/8721158649034_g_en_hd_5.jpg, https://vdxl.im/8721158649034_g_en_hd_6.jpg, https://vdxl.im/8721158649034_g_en_hd_7.jpg, https://vdxl.im/8721158649034_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529077_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529077_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529077_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529077_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529077_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529077_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529077_detail_en_px16_1.jpg, https://vdxl.im/8721288529077_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529077_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Naturlig og beige</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>100 cm</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Betongrå</t>
-        </is>
-      </c>
+          <t>Lodrette lameller</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3692,25 +3604,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>859878</t>
+          <t>3374845</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8721158649096</t>
+          <t>8721288529091</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>499</v>
+        <v>4879</v>
       </c>
       <c r="F28" t="n">
-        <v>719</v>
+        <v>6509</v>
       </c>
       <c r="G28" t="n">
-        <v>291</v>
+        <v>2868</v>
       </c>
       <c r="H28" t="n">
-        <v>15600</v>
+        <v>86540</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3728,7 +3640,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3747,12 +3659,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649096_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529091_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>859878</t>
+          <t>3374845</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3762,54 +3674,46 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>859878</t>
+          <t>3374845</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og fløde&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 55,74 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649096_m_en_hd_1.jpg, https://vdxl.im/8721158649096_a_en_hd_1.jpg, https://vdxl.im/8721158649096_g_en_hd_1.jpg, https://vdxl.im/8721158649096_g_en_hd_2.jpg, https://vdxl.im/8721158649096_g_en_hd_3.jpg, https://vdxl.im/8721158649096_g_en_hd_4.jpg, https://vdxl.im/8721158649096_g_en_hd_5.jpg, https://vdxl.im/8721158649096_g_en_hd_6.jpg, https://vdxl.im/8721158649096_g_en_hd_7.jpg, https://vdxl.im/8721158649096_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529091_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529091_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529091_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529091_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529091_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529091_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529091_detail_en_px16_1.jpg, https://vdxl.im/8721288529091_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529091_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529091_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Natur og cremefarvet</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Hvid</t>
-        </is>
-      </c>
+          <t>Skinne</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3819,25 +3723,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>859880</t>
+          <t>3374846</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8721158649119</t>
+          <t>8721288529107</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>449</v>
+        <v>4879</v>
       </c>
       <c r="F29" t="n">
-        <v>649</v>
+        <v>6509</v>
       </c>
       <c r="G29" t="n">
-        <v>262</v>
+        <v>2869</v>
       </c>
       <c r="H29" t="n">
-        <v>15700</v>
+        <v>84840</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3855,7 +3759,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -3874,12 +3778,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649119_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529107_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>859880</t>
+          <t>3374846</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3889,54 +3793,46 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>859880</t>
+          <t>3374846</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og lys grå&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,9 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649119_m_en_hd_1.jpg, https://vdxl.im/8721158649119_a_en_hd_1.jpg, https://vdxl.im/8721158649119_g_en_hd_1.jpg, https://vdxl.im/8721158649119_g_en_hd_2.jpg, https://vdxl.im/8721158649119_g_en_hd_3.jpg, https://vdxl.im/8721158649119_g_en_hd_4.jpg, https://vdxl.im/8721158649119_g_en_hd_5.jpg, https://vdxl.im/8721158649119_g_en_hd_6.jpg, https://vdxl.im/8721158649119_g_en_hd_7.jpg, https://vdxl.im/8721158649119_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529107_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529107_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529107_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529107_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529107_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529107_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529107_detail_en_px16_1.jpg, https://vdxl.im/8721288529107_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529107_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529107_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Naturlig og lys grå</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Sonoma-eg</t>
-        </is>
-      </c>
+          <t>Skinne</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3946,25 +3842,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>859882</t>
+          <t>3374847</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8721158649133</t>
+          <t>8721288529114</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>529</v>
+        <v>4879</v>
       </c>
       <c r="F30" t="n">
-        <v>759</v>
+        <v>6509</v>
       </c>
       <c r="G30" t="n">
-        <v>309</v>
+        <v>2868</v>
       </c>
       <c r="H30" t="n">
-        <v>16100</v>
+        <v>84920</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3982,7 +3878,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -4001,12 +3897,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649133_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529114_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>859882</t>
+          <t>3374847</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4016,54 +3912,46 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>859882</t>
+          <t>3374847</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og antracit&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 55,08 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649133_m_en_hd_1.jpg, https://vdxl.im/8721158649133_a_en_hd_1.jpg, https://vdxl.im/8721158649133_g_en_hd_1.jpg, https://vdxl.im/8721158649133_g_en_hd_2.jpg, https://vdxl.im/8721158649133_g_en_hd_3.jpg, https://vdxl.im/8721158649133_g_en_hd_4.jpg, https://vdxl.im/8721158649133_g_en_hd_5.jpg, https://vdxl.im/8721158649133_g_en_hd_6.jpg, https://vdxl.im/8721158649133_g_en_hd_7.jpg, https://vdxl.im/8721158649133_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529114_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529114_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529114_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529114_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529114_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529114_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529114_detail_en_px16_1.jpg, https://vdxl.im/8721288529114_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529114_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529114_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Naturlig og antracit</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Røget eg</t>
-        </is>
-      </c>
+          <t>Skinne</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4073,25 +3961,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>859883</t>
+          <t>3374848</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8721158649140</t>
+          <t>8721288529121</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>539</v>
+        <v>4879</v>
       </c>
       <c r="F31" t="n">
-        <v>769</v>
+        <v>6509</v>
       </c>
       <c r="G31" t="n">
-        <v>315</v>
+        <v>2868</v>
       </c>
       <c r="H31" t="n">
-        <v>15500</v>
+        <v>84120</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4109,7 +3997,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4128,12 +4016,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649140_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529121_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>859883</t>
+          <t>3374848</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4143,54 +4031,46 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>859883</t>
+          <t>3374848</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og beige&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,7 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649140_m_en_hd_1.jpg, https://vdxl.im/8721158649140_a_en_hd_1.jpg, https://vdxl.im/8721158649140_g_en_hd_1.jpg, https://vdxl.im/8721158649140_g_en_hd_2.jpg, https://vdxl.im/8721158649140_g_en_hd_3.jpg, https://vdxl.im/8721158649140_g_en_hd_4.jpg, https://vdxl.im/8721158649140_g_en_hd_5.jpg, https://vdxl.im/8721158649140_g_en_hd_6.jpg, https://vdxl.im/8721158649140_g_en_hd_7.jpg, https://vdxl.im/8721158649140_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529121_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529121_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529121_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529121_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529121_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529121_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529121_detail_en_px16_1.jpg, https://vdxl.im/8721288529121_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529121_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529121_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Naturlig og beige</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Grå sonoma-eg</t>
-        </is>
-      </c>
+          <t>Skinne</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4200,25 +4080,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>859885</t>
+          <t>3374850</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8721158649164</t>
+          <t>8721288529145</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>559</v>
+        <v>4869</v>
       </c>
       <c r="F32" t="n">
-        <v>799</v>
+        <v>6499</v>
       </c>
       <c r="G32" t="n">
-        <v>325</v>
+        <v>2865</v>
       </c>
       <c r="H32" t="n">
-        <v>15800</v>
+        <v>85260</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -4236,7 +4116,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4255,12 +4135,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649164_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529145_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>859885</t>
+          <t>3374850</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -4270,54 +4150,46 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>859885</t>
+          <t>3374850</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: antikt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og fløde&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,46 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 23 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 8 x 60 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649164_m_en_hd_1.jpg, https://vdxl.im/8721158649164_a_en_hd_1.jpg, https://vdxl.im/8721158649164_g_en_hd_1.jpg, https://vdxl.im/8721158649164_g_en_hd_2.jpg, https://vdxl.im/8721158649164_g_en_hd_3.jpg, https://vdxl.im/8721158649164_g_en_hd_4.jpg, https://vdxl.im/8721158649164_g_en_hd_5.jpg, https://vdxl.im/8721158649164_g_en_hd_6.jpg, https://vdxl.im/8721158649164_g_en_hd_7.jpg, https://vdxl.im/8721158649164_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529145_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529145_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529145_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529145_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529145_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529145_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529145_detail_en_px16_1.jpg, https://vdxl.im/8721288529145_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529145_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529145_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Natur og cremefarvet</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>Gammelt træ</t>
-        </is>
-      </c>
+          <t>Kurvet</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>skoreol-60x25x-konstrueret-trae-sort</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4327,25 +4199,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>859886</t>
+          <t>3374851</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8721158649171</t>
+          <t>8721288529152</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>489</v>
+        <v>4879</v>
       </c>
       <c r="F33" t="n">
-        <v>699</v>
+        <v>6509</v>
       </c>
       <c r="G33" t="n">
-        <v>283</v>
+        <v>2867</v>
       </c>
       <c r="H33" t="n">
-        <v>15600</v>
+        <v>83560</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -4363,7 +4235,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>200</v>
+        <v>38</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -4382,12 +4254,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649171_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529152_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>859886</t>
+          <t>3374851</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4397,54 +4269,46 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>859886</t>
+          <t>3374851</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Forhindr, at dine sko ligger og flyder, og skab ryddelige omgivelser med denne elegante skoreol.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skoreolen har hylder, hvilket giver rigelig med plads til opbevaring af sko. Med denne praktiske skoreol bliver du ikke længere generet af sko, der ligger og flyder på gulvet.&lt;/li&gt;&lt;li&gt;Praktisk top: Den robuste øverste hylde på skohylden er ideel til at udstille dekorative genstande, fotorammer eller opbevare ting som nøgler eller punge, som du måske har brug for inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Pladsbesparende design: Det slanke skostativ er designet til at passe perfekt til små rum som indgangspartier, gange, mudderrum osv.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Møblet er nemt at rengøre med en fugtig klud, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 60 x 25 x 81 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maksimal vægtkapacitet: 60 kg &lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og lys grå&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,62 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 23 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 8 x 60 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158649171_m_en_hd_1.jpg, https://vdxl.im/8721158649171_a_en_hd_1.jpg, https://vdxl.im/8721158649171_g_en_hd_1.jpg, https://vdxl.im/8721158649171_g_en_hd_2.jpg, https://vdxl.im/8721158649171_g_en_hd_3.jpg, https://vdxl.im/8721158649171_g_en_hd_4.jpg, https://vdxl.im/8721158649171_g_en_hd_5.jpg, https://vdxl.im/8721158649171_g_en_hd_6.jpg, https://vdxl.im/8721158649171_g_en_hd_7.jpg, https://vdxl.im/8721158649171_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721288529152_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529152_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529152_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529152_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529152_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529152_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529152_detail_en_px16_1.jpg, https://vdxl.im/8721288529152_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529152_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529152_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Bredde</t>
+          <t>Farve</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>Naturlig og lys grå</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Højde</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>81 cm</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>artisan eg</t>
-        </is>
-      </c>
+          <t>Kurvet</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4454,25 +4318,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3154423</t>
+          <t>3374852</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8720845714338</t>
+          <t>8721288529169</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2759</v>
+        <v>4869</v>
       </c>
       <c r="F34" t="n">
-        <v>3949</v>
+        <v>6499</v>
       </c>
       <c r="G34" t="n">
-        <v>1618</v>
+        <v>2865</v>
       </c>
       <c r="H34" t="n">
-        <v>20820</v>
+        <v>83640</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4490,7 +4354,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>200</v>
+        <v>84</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4509,12 +4373,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714338_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529169_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>3154423</t>
+          <t>3374852</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4524,17 +4388,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>3154423</t>
+          <t>3374852</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Blå og hvid&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og antracit&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,8 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 23 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 8 x 60 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714338_m_en_hd_1.jpg, https://vdxl.im/8720845714338_a_en_hd_1.jpg, https://vdxl.im/8720845714338_g_en_hd_1.jpg, https://vdxl.im/8720845714338_g_en_hd_2.jpg, https://vdxl.im/8720845714338_g_en_hd_3.jpg, https://vdxl.im/8720845714338_g_en_hd_4.jpg, https://vdxl.im/8720845714338_g_en_hd_5.jpg, https://vdxl.im/8720845714338_g_en_hd_6.jpg, https://vdxl.im/8720845714338_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529169_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529169_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529169_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529169_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529169_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529169_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529169_detail_en_px16_1.jpg, https://vdxl.im/8721288529169_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529169_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529169_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4544,17 +4408,17 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Blå og hvid (hvid ramme)</t>
+          <t>Naturlig og antracit</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
+          <t>Kurvet</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr"/>
@@ -4563,7 +4427,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4573,25 +4437,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3154427</t>
+          <t>3374853</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8720845714376</t>
+          <t>8721288529176</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2389</v>
+        <v>4869</v>
       </c>
       <c r="F35" t="n">
-        <v>3419</v>
+        <v>6499</v>
       </c>
       <c r="G35" t="n">
-        <v>1405</v>
+        <v>2865</v>
       </c>
       <c r="H35" t="n">
-        <v>16520</v>
+        <v>82840</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -4609,7 +4473,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>200</v>
+        <v>69</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -4628,12 +4492,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714376_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529176_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3154427</t>
+          <t>3374853</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4643,17 +4507,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>3154427</t>
+          <t>3374853</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 3,5 x 2,5 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og beige&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 53,42 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 23 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 8 x 60 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714376_m_en_hd_1.jpg, https://vdxl.im/8720845714376_a_en_hd_1.jpg, https://vdxl.im/8720845714376_g_en_hd_1.jpg, https://vdxl.im/8720845714376_g_en_hd_2.jpg, https://vdxl.im/8720845714376_g_en_hd_3.jpg, https://vdxl.im/8720845714376_g_en_hd_4.jpg, https://vdxl.im/8720845714376_g_en_hd_5.jpg, https://vdxl.im/8720845714376_g_en_hd_6.jpg, https://vdxl.im/8720845714376_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529176_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529176_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529176_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529176_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529176_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529176_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529176_detail_en_px16_1.jpg, https://vdxl.im/8721288529176_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529176_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529176_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4663,17 +4527,17 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Creme</t>
+          <t>Naturlig og beige</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>3,5 x 2,5 m</t>
+          <t>Kurvet</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr"/>
@@ -4682,7 +4546,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4692,25 +4556,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3154428</t>
+          <t>3374855</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8720845714383</t>
+          <t>8721288529190</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2769</v>
+        <v>5069</v>
       </c>
       <c r="F36" t="n">
-        <v>3959</v>
+        <v>6759</v>
       </c>
       <c r="G36" t="n">
-        <v>1625</v>
+        <v>2982</v>
       </c>
       <c r="H36" t="n">
-        <v>20820</v>
+        <v>91160</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -4728,7 +4592,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -4747,12 +4611,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714383_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529190_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3154428</t>
+          <t>3374855</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4762,17 +4626,17 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>3154428</t>
+          <t>3374855</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og fløde&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 60,36 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 10 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714383_m_en_hd_1.jpg, https://vdxl.im/8720845714383_a_en_hd_1.jpg, https://vdxl.im/8720845714383_g_en_hd_1.jpg, https://vdxl.im/8720845714383_g_en_hd_2.jpg, https://vdxl.im/8720845714383_g_en_hd_3.jpg, https://vdxl.im/8720845714383_g_en_hd_4.jpg, https://vdxl.im/8720845714383_g_en_hd_5.jpg, https://vdxl.im/8720845714383_g_en_hd_6.jpg, https://vdxl.im/8720845714383_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529190_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529190_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529190_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529190_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529190_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529190_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529190_detail_en_px16_1.jpg, https://vdxl.im/8721288529190_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529190_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529190_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4782,17 +4646,17 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Cremefarvet (hvid ramme)</t>
+          <t>Natur og cremefarvet</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
+          <t>Bred flad</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr"/>
@@ -4801,7 +4665,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4811,25 +4675,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3154429</t>
+          <t>3374856</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8720845714390</t>
+          <t>8721288529206</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3019</v>
+        <v>5079</v>
       </c>
       <c r="F37" t="n">
-        <v>4319</v>
+        <v>6779</v>
       </c>
       <c r="G37" t="n">
-        <v>1774</v>
+        <v>2984</v>
       </c>
       <c r="H37" t="n">
-        <v>23300</v>
+        <v>89460</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -4847,7 +4711,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -4866,12 +4730,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714390_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529206_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3154429</t>
+          <t>3374856</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4881,17 +4745,17 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>3154429</t>
+          <t>3374856</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4,5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og lys grå&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 59,52 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 10 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714390_m_en_hd_1.jpg, https://vdxl.im/8720845714390_a_en_hd_1.jpg, https://vdxl.im/8720845714390_g_en_hd_1.jpg, https://vdxl.im/8720845714390_g_en_hd_2.jpg, https://vdxl.im/8720845714390_g_en_hd_3.jpg, https://vdxl.im/8720845714390_g_en_hd_4.jpg, https://vdxl.im/8720845714390_g_en_hd_5.jpg, https://vdxl.im/8720845714390_g_en_hd_6.jpg, https://vdxl.im/8720845714390_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529206_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529206_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529206_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529206_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529206_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529206_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529206_detail_en_px16_1.jpg, https://vdxl.im/8721288529206_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529206_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529206_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4901,17 +4765,17 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>Cremefarvet (hvid ramme)</t>
+          <t>Naturlig og lys grå</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>4,5 × 3 m</t>
+          <t>Bred flad</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr"/>
@@ -4920,7 +4784,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4930,25 +4794,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3154433</t>
+          <t>3374857</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8720845714437</t>
+          <t>8721288529213</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2699</v>
+        <v>5069</v>
       </c>
       <c r="F38" t="n">
-        <v>3859</v>
+        <v>6759</v>
       </c>
       <c r="G38" t="n">
-        <v>1584</v>
+        <v>2982</v>
       </c>
       <c r="H38" t="n">
-        <v>20820</v>
+        <v>89540</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -4966,7 +4830,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>200</v>
+        <v>79</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -4985,12 +4849,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714437_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529213_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3154433</t>
+          <t>3374857</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -5000,17 +4864,17 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>3154433</t>
+          <t>3374857</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gul og hvid&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner. &lt;a title="https://vdxl.im/8720845714437_doc_en_1.pdf?t=1755495686" href="https://vdxl.im/8720845714437_doc_en_1.pdf?t=1755495686" target="_blank"&gt;GPSR&lt;/a&gt;</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og antracit&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 59,7 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 10 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714437_m_en_hd_1.jpg, https://vdxl.im/8720845714437_a_en_hd_1.jpg, https://vdxl.im/8720845714437_g_en_hd_1.jpg, https://vdxl.im/8720845714437_g_en_hd_2.jpg, https://vdxl.im/8720845714437_g_en_hd_3.jpg, https://vdxl.im/8720845714437_g_en_hd_4.jpg, https://vdxl.im/8720845714437_g_en_hd_5.jpg, https://vdxl.im/8720845714437_g_en_hd_6.jpg, https://vdxl.im/8720845714437_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529213_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529213_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529213_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529213_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529213_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529213_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529213_detail_en_px16_1.jpg, https://vdxl.im/8721288529213_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529213_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529213_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5020,17 +4884,17 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Gul og hvid (hvid ramme)</t>
+          <t>Naturlig og antracit</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
+          <t>Bred flad</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr"/>
@@ -5039,7 +4903,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5049,25 +4913,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3154438</t>
+          <t>3374858</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8720845714482</t>
+          <t>8721288529220</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3079</v>
+        <v>5069</v>
       </c>
       <c r="F39" t="n">
-        <v>4399</v>
+        <v>6759</v>
       </c>
       <c r="G39" t="n">
-        <v>1809</v>
+        <v>2982</v>
       </c>
       <c r="H39" t="n">
-        <v>20720</v>
+        <v>88740</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -5085,7 +4949,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>200</v>
+        <v>69</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -5104,12 +4968,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714482_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529220_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>3154438</t>
+          <t>3374858</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -5119,17 +4983,17 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>3154438</t>
+          <t>3374858</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og beige&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 59,32 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 58,5 x 10 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714482_m_en_hd_1.jpg, https://vdxl.im/8720845714482_a_en_hd_1.jpg, https://vdxl.im/8720845714482_g_en_hd_1.jpg, https://vdxl.im/8720845714482_g_en_hd_2.jpg, https://vdxl.im/8720845714482_g_en_hd_3.jpg, https://vdxl.im/8720845714482_g_en_hd_4.jpg, https://vdxl.im/8720845714482_g_en_hd_5.jpg, https://vdxl.im/8720845714482_g_en_hd_6.jpg, https://vdxl.im/8720845714482_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529220_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529220_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529220_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529220_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529220_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529220_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529220_detail_en_px16_1.jpg, https://vdxl.im/8721288529220_wbg-var_en_px16_1.jpg, https://vdxl.im/8721288529220_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529220_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -5139,17 +5003,17 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Antracitgrå (hvid ramme)</t>
+          <t>Naturlig og beige</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
+          <t>Bred flad</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr"/>
@@ -5158,7 +5022,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5168,25 +5032,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3154443</t>
+          <t>3374860</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8720845714536</t>
+          <t>8721288529244</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2629</v>
+        <v>4849</v>
       </c>
       <c r="F40" t="n">
-        <v>3759</v>
+        <v>6469</v>
       </c>
       <c r="G40" t="n">
-        <v>1544</v>
+        <v>2852</v>
       </c>
       <c r="H40" t="n">
-        <v>20720</v>
+        <v>85900</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -5204,7 +5068,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -5223,12 +5087,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714536_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529244_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>3154443</t>
+          <t>3374860</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -5238,17 +5102,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>3154443</t>
+          <t>3374860</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Markisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Orange og brun&lt;/li&gt;&lt;li&gt;Materiale, stel: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Materiale, markise: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x markise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og fløde&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 55,1 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845714536_m_en_hd_1.jpg, https://vdxl.im/8720845714536_a_en_hd_1.jpg, https://vdxl.im/8720845714536_g_en_hd_1.jpg, https://vdxl.im/8720845714536_g_en_hd_2.jpg, https://vdxl.im/8720845714536_g_en_hd_3.jpg, https://vdxl.im/8720845714536_g_en_hd_4.jpg, https://vdxl.im/8720845714536_g_en_hd_5.jpg, https://vdxl.im/8720845714536_g_en_hd_6.jpg, https://vdxl.im/8720845714536_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529244_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529244_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529244_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529244_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529244_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529244_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529244_detail_en_px16_1.jpg, https://vdxl.im/8721288529244_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529244_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -5258,17 +5122,17 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Orange og brun (hvid ramme)</t>
+          <t>Natur og cremefarvet</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
+          <t>egnet til lejlighed</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr"/>
@@ -5277,7 +5141,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5287,25 +5151,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3215295</t>
+          <t>3374861</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8721012415997</t>
+          <t>8721288529251</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2679</v>
+        <v>4859</v>
       </c>
       <c r="F41" t="n">
-        <v>3829</v>
+        <v>6479</v>
       </c>
       <c r="G41" t="n">
-        <v>1575</v>
+        <v>2854</v>
       </c>
       <c r="H41" t="n">
-        <v>22710</v>
+        <v>84200</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -5323,7 +5187,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>200</v>
+        <v>38</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -5342,12 +5206,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012415997_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529251_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3215295</t>
+          <t>3374861</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -5357,17 +5221,17 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>3215295</t>
+          <t>3374861</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Skab et dejligt og køligt sted på din terrasse, og beskyt dig selv mod UV-stråler med denne sammenrullelige markise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med PU-overfladebehandling er UV-bestandigt. Det vil beskytte din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Nem betjening: Vinklen og højden kan justeres efter behov. Du kan nemt åbne og lukke markisen ved hjælp af håndsvinget.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den sammenrullelige har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve, stof: Bordeaux&lt;/li&gt;&lt;li&gt;Farve, stel: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium, stof (100 % polyester) med PU-coating&lt;/li&gt;&lt;li&gt;Produktmål: 400 x 300 cm (L x B)&lt;/li&gt;&lt;li&gt;Vand- og smudsafvisende&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og lys grå&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,26 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012415997_m_en_hd_1.jpg, https://vdxl.im/8721012415997_a_en_hd_1.jpg, https://vdxl.im/8721012415997_g_en_hd_1.jpg, https://vdxl.im/8721012415997_g_en_hd_2.jpg, https://vdxl.im/8721012415997_g_en_hd_3.jpg, https://vdxl.im/8721012415997_g_en_hd_4.jpg, https://vdxl.im/8721012415997_g_en_hd_5.jpg, https://vdxl.im/8721012415997_g_en_hd_6.jpg, https://vdxl.im/8721012415997_g_en_hd_7.jpg, https://vdxl.im/8721012415997_g_en_hd_8.jpg, https://vdxl.im/8721012415997_g_en_hd_9.jpg, https://vdxl.im/8721012415997_g_en_hd_10.jpg</t>
+          <t>https://vdxl.im/8721288529251_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529251_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529251_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529251_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529251_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529251_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529251_detail_en_px16_1.jpg, https://vdxl.im/8721288529251_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529251_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -5377,17 +5241,17 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>burgundy (white frame)</t>
+          <t>Naturlig og lys grå</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
+          <t>egnet til lejlighed</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr"/>
@@ -5396,7 +5260,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>sofasaet-med-pude-6-dele-naturlig-og-beige-massivt-akacietrae</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5406,25 +5270,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3216104</t>
+          <t>3374862</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8721012424081</t>
+          <t>8721288529268</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2329</v>
+        <v>4849</v>
       </c>
       <c r="F42" t="n">
-        <v>3329</v>
+        <v>6469</v>
       </c>
       <c r="G42" t="n">
-        <v>1366</v>
+        <v>2852</v>
       </c>
       <c r="H42" t="n">
-        <v>16000</v>
+        <v>84280</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -5442,7 +5306,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -5461,12 +5325,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424081_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288529268_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3216104</t>
+          <t>3374862</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -5476,17 +5340,17 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>3216104</t>
+          <t>3374862</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 3,5 x 2,5 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 347 x 247 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Dette udendørs møbel sæt er både stilfuldt og funktionelt, og skaber et flot midtpunkt i enhver have eller på terrasse. Dets moderne design med rene linjer og minimalistering tilføjer elegance, perfekt til afslapning og socialt samvær udendørs. Lavet af solid akacietræ, sikrer det holdbarhed og et flot udseende, og er derfor et ideelt valg for dem, der ønsker både funktionalitet og stil i deres udendørs møbler.&lt;/p&gt; &lt;li&gt;&lt;b&gt;Slidstærk solid akacietræ:&lt;/b&gt; Møblerne er lavet af robust akacietræ, hvilket gør dem holdbare og modstandsdygtige overfor vejrforhold. Den stærke konstruktion sørger for stabil støtte og langvarig holdbarhed, mens den varme tone passer ind i enhver have eller terrasse.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vejrbestandigt design:&lt;/b&gt; Sættet har en lakeret overflade, der beskytter mod sol, let regn og andre udendørs forhold. Den polerede finish hjælper med at bevare både udseende og funktion, så de holder længe i din have eller på terrassen.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komponenter &amp; design:&lt;/b&gt; Hvert element er både stilfuldt og funktionelt designet. Støttende detaljer øger komforten, mens det sammenhængende design skaber et visuelt harmonisk ensemble, der er perfekt til udendørs anledninger.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Komfort &amp; alsidighed:&lt;/b&gt; Det modulære design giver fleksible konfigurationer, så det passer til forskellige rum og behov. Perfekt til afslapning, sociale sammenkomster eller en stille læsestund, tilpasser dette sæt sig let til ethvert udendørs miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Let pleje &amp; vedligeholdelse:&lt;/b&gt; For at holde møblerne pæne, skal du blot bruge en fugtig klud og undgå kraftige kemikalier. Regelmæssig pleje hjælper med at fastholde udseendet og forlænge levetiden af møblerne.&lt;/li&gt; &lt;ul&gt;&lt;li&gt;Farve: Naturlig og antracit&lt;/li&gt;&lt;li&gt;Materiale: Massivt akacietræ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 59 x 59 x 37 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 54,44 kg&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Nem at vedligeholde&lt;/li&gt;&lt;li&gt;Design med Sprækker&lt;/li&gt;&lt;li&gt;Naturlig træstruktur&lt;/li&gt;&lt;li&gt;Armlænets højde fra sædet: 24 cm&lt;/li&gt;&lt;li&gt;Fyldmateriale: Skum&lt;/li&gt;&lt;li&gt;Maks. vægt: 110 kg pr. sæde&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Bord: 59 x 59 x 37 cm (LxBxH)&lt;/li&gt;&lt;li&gt;1 x Hjørnesofa: 63 x 63 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;4 x Midtersofa: 63 x 59 x 73 cm (LxBxH)&lt;/li&gt;&lt;li&gt;2 x Armlæn: 60 x 6 x 61 cm (LxBxH)&lt;/li&gt;&lt;li&gt;5 x Sædepude: 60 x 60 x 8 cm (LxBxH)&lt;/li&gt;&lt;li&gt;6 x Rygpude: 60 x 40 x 10 cm (LxBxH)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424081_m_en_hd_1.jpg, https://vdxl.im/8721012424081_a_en_hd_1.jpg, https://vdxl.im/8721012424081_g_en_hd_1.jpg, https://vdxl.im/8721012424081_g_en_hd_2.jpg, https://vdxl.im/8721012424081_g_en_hd_3.jpg, https://vdxl.im/8721012424081_g_en_hd_4.jpg, https://vdxl.im/8721012424081_g_en_hd_5.jpg, https://vdxl.im/8721012424081_g_en_hd_6.jpg, https://vdxl.im/8721012424081_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721288529268_mo-im_en_px16_1.jpg, https://vdxl.im/8721288529268_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721288529268_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721288529268_wbg-an_en_px16_1.jpg, https://vdxl.im/8721288529268_wbg-an_en_px16_2.jpg, https://vdxl.im/8721288529268_wbg-an_en_px16_3.jpg, https://vdxl.im/8721288529268_detail_en_px16_1.jpg, https://vdxl.im/8721288529268_wbg-siz_en_px16_1.jpg, https://vdxl.im/8721288529268_wbg-siz_en_px16_2.jpg</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5496,17 +5360,17 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>anthracite and white (white frame)</t>
+          <t>Naturlig og antracit</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Variation Attribute 2</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>3,5 x 2,5 m</t>
+          <t>egnet til lejlighed</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr"/>
@@ -5515,7 +5379,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5525,25 +5389,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3216105</t>
+          <t>42018089</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8721012424098</t>
+          <t>8721364474802</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2749</v>
+        <v>569</v>
       </c>
       <c r="F43" t="n">
-        <v>3929</v>
+        <v>819</v>
       </c>
       <c r="G43" t="n">
-        <v>1614</v>
+        <v>334</v>
       </c>
       <c r="H43" t="n">
-        <v>22020</v>
+        <v>14900</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -5561,7 +5425,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -5580,12 +5444,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424098_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364474802_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3216105</t>
+          <t>42018089</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -5595,17 +5459,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>3216105</t>
+          <t>42018089</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 397 x 296,5 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Elfenben&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 160 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424098_m_en_hd_1.jpg, https://vdxl.im/8721012424098_a_en_hd_1.jpg, https://vdxl.im/8721012424098_g_en_hd_1.jpg, https://vdxl.im/8721012424098_g_en_hd_2.jpg, https://vdxl.im/8721012424098_g_en_hd_3.jpg, https://vdxl.im/8721012424098_g_en_hd_4.jpg, https://vdxl.im/8721012424098_g_en_hd_5.jpg, https://vdxl.im/8721012424098_g_en_hd_6.jpg, https://vdxl.im/8721012424098_g_en_hd_7.jpg, https://vdxl.im/8721012424098_g_en_hd_8.jpg, https://vdxl.im/8721012424098_g_en_hd_9.jpg, https://vdxl.im/8721012424098_g_en_hd_10.jpg</t>
+          <t>https://vdxl.im/8721364474802_mo-im_en_px16_1.jpg, https://vdxl.im/8721364474802_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364474802_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364474802_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364474802_detail_en_px16_1.jpg, https://vdxl.im/8721364474802_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364474802_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -5615,26 +5479,34 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>anthracite and white (white frame)</t>
+          <t>Elfenben</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
+          <t>160 cm</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5644,25 +5516,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3216106</t>
+          <t>42018091</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8721012424104</t>
+          <t>8721364474826</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3019</v>
+        <v>769</v>
       </c>
       <c r="F44" t="n">
-        <v>4319</v>
+        <v>1099</v>
       </c>
       <c r="G44" t="n">
-        <v>1771</v>
+        <v>450</v>
       </c>
       <c r="H44" t="n">
-        <v>24500</v>
+        <v>20140</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -5680,7 +5552,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -5699,12 +5571,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424104_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364474826_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>3216106</t>
+          <t>42018091</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -5714,17 +5586,17 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>3216106</t>
+          <t>42018091</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 4,5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 447 x 297 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Elfenben&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 240 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424104_m_en_hd_1.jpg, https://vdxl.im/8721012424104_a_en_hd_1.jpg, https://vdxl.im/8721012424104_g_en_hd_1.jpg, https://vdxl.im/8721012424104_g_en_hd_2.jpg, https://vdxl.im/8721012424104_g_en_hd_3.jpg, https://vdxl.im/8721012424104_g_en_hd_4.jpg, https://vdxl.im/8721012424104_g_en_hd_5.jpg, https://vdxl.im/8721012424104_g_en_hd_6.jpg, https://vdxl.im/8721012424104_g_en_hd_7.jpg, https://vdxl.im/8721012424104_g_en_hd_8.jpg, https://vdxl.im/8721012424104_g_en_hd_9.jpg, https://vdxl.im/8721012424104_g_en_hd_10.jpg</t>
+          <t>https://vdxl.im/8721364474826_mo-im_en_px16_1.jpg, https://vdxl.im/8721364474826_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364474826_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364474826_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364474826_detail_en_px16_1.jpg, https://vdxl.im/8721364474826_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364474826_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5734,26 +5606,34 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>anthracite and white (white frame)</t>
+          <t>Elfenben</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>4,5 × 3 m</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
+          <t>240 cm</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5763,25 +5643,25 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3216107</t>
+          <t>42018141</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>8721012424111</t>
+          <t>8721364475229</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3329</v>
+        <v>609</v>
       </c>
       <c r="F45" t="n">
-        <v>4759</v>
+        <v>869</v>
       </c>
       <c r="G45" t="n">
-        <v>1958</v>
+        <v>356</v>
       </c>
       <c r="H45" t="n">
-        <v>25120</v>
+        <v>14760</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -5799,7 +5679,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -5818,12 +5698,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424111_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364475229_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>3216107</t>
+          <t>42018141</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -5833,17 +5713,17 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>3216107</t>
+          <t>42018141</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 497,5 x 299,5 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 160 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424111_m_en_hd_1.jpg, https://vdxl.im/8721012424111_a_en_hd_1.jpg, https://vdxl.im/8721012424111_g_en_hd_1.jpg, https://vdxl.im/8721012424111_g_en_hd_2.jpg, https://vdxl.im/8721012424111_g_en_hd_3.jpg, https://vdxl.im/8721012424111_g_en_hd_4.jpg, https://vdxl.im/8721012424111_g_en_hd_5.jpg, https://vdxl.im/8721012424111_g_en_hd_6.jpg, https://vdxl.im/8721012424111_g_en_hd_7.jpg, https://vdxl.im/8721012424111_g_en_hd_8.jpg, https://vdxl.im/8721012424111_g_en_hd_9.jpg, https://vdxl.im/8721012424111_g_en_hd_10.jpg</t>
+          <t>https://vdxl.im/8721364475229_mo-im_en_px16_1.jpg, https://vdxl.im/8721364475229_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364475229_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364475229_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364475229_detail_en_px16_1.jpg, https://vdxl.im/8721364475229_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364475229_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5853,26 +5733,34 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>anthracite and white (white frame)</t>
+          <t>Lysegrå</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>5 x 3 m</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
+          <t>160 cm</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5882,25 +5770,25 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3216112</t>
+          <t>42018143</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8721012424166</t>
+          <t>8721364475243</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3369</v>
+        <v>769</v>
       </c>
       <c r="F46" t="n">
-        <v>4819</v>
+        <v>1099</v>
       </c>
       <c r="G46" t="n">
-        <v>1977</v>
+        <v>452</v>
       </c>
       <c r="H46" t="n">
-        <v>25120</v>
+        <v>19930</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -5918,7 +5806,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>15</v>
+        <v>191</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -5937,12 +5825,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424166_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364475243_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3216112</t>
+          <t>42018143</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5952,17 +5840,17 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>3216112</t>
+          <t>42018143</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Nyd en kølig drink, en velsmagende bid mad eller en god samtale på din terrasse med venner, mens du slapper af under denne fantastiske foldemarkise!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Markisestellet er lavet af pulverlakeret aluminium, som er robust og holdbart. Stoffet med en PU-overfladebehandling er UV-bestandigt. Det beskytter din familie eller gæster mod UV-stråler og blændende sollys.&lt;/li&gt;&lt;li&gt;Foldemarkise: Havemarkisen kan rulles ud og ind, så den opfylder dine forskellige behov. Den giver svalende skygge, når den er foldet ud, og blokerer ikke for udsigten, når den er rullet ind.&lt;/li&gt;&lt;li&gt;Vægmonteret design: Terrassemarkisen kan nemt monteres på væggen med de medfølgende vægbeslag og tager ikke gulvplads.&lt;/li&gt;&lt;li&gt;Bredt anvendelsesområde: Den udtrækkelige markise har et enkelt og stilfuldt design, der vil passe godt til dit hjem eller kommercielle omgivelser. Den er velegnet til mange forskellige steder, f.eks. altaner, terrasser, gårdhaver, restauranter, caféer, butikker og meget mere.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Markise:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå og hvid&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester) med PU-belægning&lt;/li&gt;&lt;li&gt;Mål: 5 x 3 m (L x B)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ramme:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret aluminium&lt;/li&gt;&lt;li&gt;Mål: 497,5 x 299,5 cm (L x B)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x foldemarkise&lt;/li&gt;&lt;li&gt;1 x stativ&lt;/li&gt;&lt;/ul&gt; Børn skal være under opsyn for at sikre, at de ikke leger med apparatet. Hold børn væk fra monteringsområdet. Bemærk: Læs instruktionerne omhyggeligt inden brug og behold dem til fremtidig brug.</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 240 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012424166_m_en_hd_1.jpg, https://vdxl.im/8721012424166_a_en_hd_1.jpg, https://vdxl.im/8721012424166_g_en_hd_1.jpg, https://vdxl.im/8721012424166_g_en_hd_2.jpg, https://vdxl.im/8721012424166_g_en_hd_3.jpg, https://vdxl.im/8721012424166_g_en_hd_4.jpg, https://vdxl.im/8721012424166_g_en_hd_5.jpg, https://vdxl.im/8721012424166_g_en_hd_6.jpg, https://vdxl.im/8721012424166_g_en_hd_7.jpg, https://vdxl.im/8721012424166_g_en_hd_8.jpg, https://vdxl.im/8721012424166_g_en_hd_9.jpg, https://vdxl.im/8721012424166_g_en_hd_10.jpg</t>
+          <t>https://vdxl.im/8721364475243_mo-im_en_px16_1.jpg, https://vdxl.im/8721364475243_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364475243_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364475243_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364475243_detail_en_px16_1.jpg, https://vdxl.im/8721364475243_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364475243_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5972,26 +5860,34 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Antracit og hvid (antracit ramme)</t>
+          <t>Lysegrå</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>5 x 3 m</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
+          <t>240 cm</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6001,25 +5897,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3330599</t>
+          <t>42018193</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8721158809582</t>
+          <t>8721364475649</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2549</v>
+        <v>669</v>
       </c>
       <c r="F47" t="n">
-        <v>3649</v>
+        <v>959</v>
       </c>
       <c r="G47" t="n">
-        <v>1495</v>
+        <v>393</v>
       </c>
       <c r="H47" t="n">
-        <v>20390</v>
+        <v>14760</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -6037,7 +5933,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -6056,12 +5952,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158809582_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364475649_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3330599</t>
+          <t>42018193</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -6071,17 +5967,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>3330599</t>
+          <t>42018193</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Den moderne udtrækkelige markise er en smart løsning til skygge, lavet til dem, der ønsker et stilfuldt fristed fra solen. Dens slanke rektangulære form passer perfekt til moderne terrasser og haver, med et fokus på enkelhed og minimalisme. Markisen strækker sig let ud og skaber et alsidigt rum, der er perfekt til sommeraftener eller afslapning alene. Den er lavet af 100% polyester, som giver en moderne vibe og beskytter mod hård sollys. Det er ikke bare en skygge, men et stilfuldt statement til dit udendørs rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Markisen er lavet af 100% polyester, hvilket sikrer holdbarhed og modstår vejret. Det stærke stof holder farverne klare og beskytter mod solens stråler, så den holder sig pæn i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hvad der er inkluderet:&lt;/b&gt; Pakken indeholder en stærk ramme og stofkomponent, der er omhyggeligt lavet for at sikre stabilitet og ensartet ydeevne. Rammen holder stoffet på plads, så det beholder sin form selv efter gentagen brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel udtrækningsmekanisme:&lt;/b&gt; Med en simpel manuel funktion kan du nemt justere markisen til den ønskede længde, som giver dig tilpasset skygge. Den er perfekt til enhver lejlighed, fra hyggelige aftener til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Brug:&lt;/b&gt; Markisen er designet til udendørs brug, perfekt til haven og terrassen. Den er ideel til sommeraftener, picnic eller bare afslapning. Den kan opgradere ethvert udendørs område betydeligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje:&lt;/b&gt; Det er nemt at holde markisen pæn. Tør den af med en fugtig klud for at fjerne snavs og sikre, at den holder sig flot og fungerer godt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Polyester med PU belægning&lt;/li&gt;&lt;li&gt;Rammemateriale: Pulverlakeret stål, aluminium&lt;/li&gt;&lt;li&gt;Størrelse: 400 × 300 cm&lt;/li&gt;&lt;li&gt;Længde på håndsving: 165&lt;/li&gt;&lt;li&gt;Vejrresistent stof&lt;/li&gt;&lt;li&gt;Korrosionsbestandig aluminiumrulle&lt;/li&gt;&lt;li&gt;Robuste udtrækkelige arme&lt;/li&gt;&lt;li&gt;Håndsving til nem udtrækning og indtrækning&lt;/li&gt;&lt;li&gt;Monteringsudstyr inkluderet&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Manuel Utrækkelig Markise&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 160 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158809582_mo-im_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721158809582_mo-im_en_hd_2.jpg, https://vdxl.im/8721158809582_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158809582_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158809582_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721158809582_detail_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158809582_wbg-siz_en_hd_2.jpg</t>
+          <t>https://vdxl.im/8721364475649_mo-im_en_px16_1.jpg, https://vdxl.im/8721364475649_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364475649_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364475649_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364475649_detail_en_px16_1.jpg, https://vdxl.im/8721364475649_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364475649_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -6091,26 +5987,34 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Sort (hvid ramme)</t>
+          <t>Antracit</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
+          <t>160 cm</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6120,25 +6024,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3330695</t>
+          <t>42018195</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8721158810540</t>
+          <t>8721364475663</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2569</v>
+        <v>859</v>
       </c>
       <c r="F48" t="n">
-        <v>3669</v>
+        <v>1229</v>
       </c>
       <c r="G48" t="n">
-        <v>1512</v>
+        <v>503</v>
       </c>
       <c r="H48" t="n">
-        <v>20470</v>
+        <v>19930</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -6156,7 +6060,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -6175,12 +6079,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158810540_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364475663_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3330695</t>
+          <t>42018195</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -6190,17 +6094,17 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>3330695</t>
+          <t>42018195</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Den moderne udtrækkelige markise er en smart løsning til skygge, lavet til dem, der ønsker et stilfuldt fristed fra solen. Dens slanke rektangulære form passer perfekt til moderne terrasser og haver, med et fokus på enkelhed og minimalisme. Markisen strækker sig let ud og skaber et alsidigt rum, der er perfekt til sommeraftener eller afslapning alene. Den er lavet af 100% polyester, som giver en moderne vibe og beskytter mod hård sollys. Det er ikke bare en skygge, men et stilfuldt statement til dit udendørs rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Markisen er lavet af 100% polyester, hvilket sikrer holdbarhed og modstår vejret. Det stærke stof holder farverne klare og beskytter mod solens stråler, så den holder sig pæn i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hvad der er inkluderet:&lt;/b&gt; Pakken indeholder en stærk ramme og stofkomponent, der er omhyggeligt lavet for at sikre stabilitet og ensartet ydeevne. Rammen holder stoffet på plads, så det beholder sin form selv efter gentagen brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel udtrækningsmekanisme:&lt;/b&gt; Med en simpel manuel funktion kan du nemt justere markisen til den ønskede længde, som giver dig tilpasset skygge. Den er perfekt til enhver lejlighed, fra hyggelige aftener til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Brug:&lt;/b&gt; Markisen er designet til udendørs brug, perfekt til haven og terrassen. Den er ideel til sommeraftener, picnic eller bare afslapning. Den kan opgradere ethvert udendørs område betydeligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje:&lt;/b&gt; Det er nemt at holde markisen pæn. Tør den af med en fugtig klud for at fjerne snavs og sikre, at den holder sig flot og fungerer godt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Rød&lt;/li&gt;&lt;li&gt;Materiale: Polyester med PU belægning&lt;/li&gt;&lt;li&gt;Rammemateriale: Pulverlakeret stål, aluminium&lt;/li&gt;&lt;li&gt;Størrelse: 400 × 300 cm&lt;/li&gt;&lt;li&gt;Længde på håndsving: 165&lt;/li&gt;&lt;li&gt;Vejrresistent stof&lt;/li&gt;&lt;li&gt;Korrosionsbestandig aluminiumrulle&lt;/li&gt;&lt;li&gt;Robuste udtrækkelige arme&lt;/li&gt;&lt;li&gt;Håndsving til nem udtrækning og indtrækning&lt;/li&gt;&lt;li&gt;Monteringsudstyr inkluderet&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Manuel Utrækkelig Markise&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 240 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158810540_mo-im_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721158810540_mo-im_en_hd_2.jpg, https://vdxl.im/8721158810540_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158810540_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158810540_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721158810540_detail_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158810540_wbg-siz_en_hd_2.jpg</t>
+          <t>https://vdxl.im/8721364475663_mo-im_en_px16_1.jpg, https://vdxl.im/8721364475663_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364475663_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364475663_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364475663_detail_en_px16_1.jpg, https://vdxl.im/8721364475663_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364475663_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -6210,26 +6114,34 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Rød (hvid ramme)</t>
+          <t>Antracit</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>4 × 3 m</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
+          <t>240 cm</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>foldemarkise-manuel-betjening-3x25-m-stof-aluminium-blaa-hvid</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6239,25 +6151,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3330935</t>
+          <t>42018245</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8721158812940</t>
+          <t>8721364476066</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3039</v>
+        <v>659</v>
       </c>
       <c r="F49" t="n">
-        <v>4349</v>
+        <v>949</v>
       </c>
       <c r="G49" t="n">
-        <v>1785</v>
+        <v>384</v>
       </c>
       <c r="H49" t="n">
-        <v>22180</v>
+        <v>14760</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -6275,7 +6187,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>188</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -6294,12 +6206,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158812940_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364476066_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3330935</t>
+          <t>42018245</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -6309,17 +6221,17 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>3330935</t>
+          <t>42018245</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Den moderne udtrækkelige markise er en smart løsning til skygge, lavet til dem, der ønsker et stilfuldt fristed fra solen. Dens slanke rektangulære form passer perfekt til moderne terrasser og haver, med et fokus på enkelhed og minimalisme. Markisen strækker sig let ud og skaber et alsidigt rum, der er perfekt til sommeraftener eller afslapning alene. Den er lavet af 100% polyester, som giver en moderne vibe og beskytter mod hård sollys. Det er ikke bare en skygge, men et stilfuldt statement til dit udendørs rum.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materialer:&lt;/b&gt; Markisen er lavet af 100% polyester, hvilket sikrer holdbarhed og modstår vejret. Det stærke stof holder farverne klare og beskytter mod solens stråler, så den holder sig pæn i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hvad der er inkluderet:&lt;/b&gt; Pakken indeholder en stærk ramme og stofkomponent, der er omhyggeligt lavet for at sikre stabilitet og ensartet ydeevne. Rammen holder stoffet på plads, så det beholder sin form selv efter gentagen brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Manuel udtrækningsmekanisme:&lt;/b&gt; Med en simpel manuel funktion kan du nemt justere markisen til den ønskede længde, som giver dig tilpasset skygge. Den er perfekt til enhver lejlighed, fra hyggelige aftener til solrige dage.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Brug:&lt;/b&gt; Markisen er designet til udendørs brug, perfekt til haven og terrassen. Den er ideel til sommeraftener, picnic eller bare afslapning. Den kan opgradere ethvert udendørs område betydeligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pleje:&lt;/b&gt; Det er nemt at holde markisen pæn. Tør den af med en fugtig klud for at fjerne snavs og sikre, at den holder sig flot og fungerer godt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Flerfarvet&lt;/li&gt;&lt;li&gt;Materiale: Polyester med PU belægning&lt;/li&gt;&lt;li&gt;Rammemateriale: Pulverlakeret stål, aluminium&lt;/li&gt;&lt;li&gt;Størrelse: 450 × 300 cm&lt;/li&gt;&lt;li&gt;Længde på håndsving: 165&lt;/li&gt;&lt;li&gt;Vejrresistent stof&lt;/li&gt;&lt;li&gt;Korrosionsbestandig aluminiumrulle&lt;/li&gt;&lt;li&gt;Robuste udtrækkelige arme&lt;/li&gt;&lt;li&gt;Håndsving til nem udtrækning og indtrækning&lt;/li&gt;&lt;li&gt;Monteringsudstyr inkluderet&lt;/li&gt;&lt;li&gt;Kun til udendørs brug&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Manuel Utrækkelig Markise&lt;/li&gt;&lt;/ul&gt; Advarsel! Der er en kraftig spænding i fjederen, når der åbnes. Fjern IKKE dette reb, medmindre du har gennemført alle trin i monteringen, alle bolte er fastgjort, og produktet er fastgjort til væggen! Advarsel! Vær forsigtig, når du løsner armene, da de er under spænding! En pludselig frigørelse af armen på en foldemarkise kan forårsage skader. Advarsel: Operatørens anvisninger skal læses før brug af produktet. Advarsel: Anvendelse i frostvejr kan beskadige produktet. Til udendørs brug på bygninger og andre konstruktioner.</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grøn&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 160 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158812940_mo-im_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721158812940_mo-im_en_hd_2.jpg, https://vdxl.im/8721158812940_wbg-an_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158812940_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158812940_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721158812940_detail_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158812940_wbg-siz_en_hd_2.jpg</t>
+          <t>https://vdxl.im/8721364476066_mo-im_en_px16_1.jpg, https://vdxl.im/8721364476066_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364476066_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364476066_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364476066_detail_en_px16_1.jpg, https://vdxl.im/8721364476066_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364476066_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -6329,26 +6241,34 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Flerfarvet (hvid ramme)</t>
+          <t>Grøn</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>4,5 × 3 m</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
+          <t>160 cm</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6358,25 +6278,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>373080</t>
+          <t>42018247</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8721012266186</t>
+          <t>8721364476080</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1039</v>
+        <v>889</v>
       </c>
       <c r="F50" t="n">
-        <v>1389</v>
+        <v>1269</v>
       </c>
       <c r="G50" t="n">
-        <v>607</v>
+        <v>521</v>
       </c>
       <c r="H50" t="n">
-        <v>22000</v>
+        <v>20140</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -6394,7 +6314,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -6413,12 +6333,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012266186_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364476080_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>373080</t>
+          <t>42018247</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -6428,17 +6348,17 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>373080</t>
+          <t>42018247</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Brun&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 85 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 80 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grøn&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 240 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012266186_m_en_hd_1.jpg, https://vdxl.im/8721012266186_a_en_hd_1.jpg, https://vdxl.im/8721012266186_g_en_hd_1.jpg, https://vdxl.im/8721012266186_g_en_hd_2.jpg, https://vdxl.im/8721012266186_g_en_hd_3.jpg, https://vdxl.im/8721012266186_g_en_hd_4.jpg, https://vdxl.im/8721012266186_g_en_hd_5.jpg, https://vdxl.im/8721012266186_g_en_hd_6.jpg, https://vdxl.im/8721012266186_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721364476080_mo-im_en_px16_1.jpg, https://vdxl.im/8721364476080_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364476080_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364476080_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364476080_detail_en_px16_1.jpg, https://vdxl.im/8721364476080_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364476080_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -6448,26 +6368,34 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Brun</t>
+          <t>Grøn</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>80 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
+          <t>240 cm</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6477,25 +6405,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>373082</t>
+          <t>42018093</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8721012266209</t>
+          <t>8721364474840</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>839</v>
+        <v>909</v>
       </c>
       <c r="F51" t="n">
-        <v>1119</v>
+        <v>1299</v>
       </c>
       <c r="G51" t="n">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="H51" t="n">
-        <v>22000</v>
+        <v>25360</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -6513,7 +6441,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -6532,12 +6460,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012266209_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364474840_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>373082</t>
+          <t>42018093</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -6547,17 +6475,17 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>373082</t>
+          <t>42018093</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Cappuccino&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 85 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 80 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Elfenben&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 320 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012266209_m_en_hd_1.jpg, https://vdxl.im/8721012266209_a_en_hd_1.jpg, https://vdxl.im/8721012266209_g_en_hd_1.jpg, https://vdxl.im/8721012266209_g_en_hd_2.jpg, https://vdxl.im/8721012266209_g_en_hd_3.jpg, https://vdxl.im/8721012266209_g_en_hd_4.jpg, https://vdxl.im/8721012266209_g_en_hd_5.jpg, https://vdxl.im/8721012266209_g_en_hd_6.jpg, https://vdxl.im/8721012266209_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721364474840_mo-im_en_px16_1.jpg, https://vdxl.im/8721364474840_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364474840_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364474840_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364474840_detail_en_px16_1.jpg, https://vdxl.im/8721364474840_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364474840_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -6567,26 +6495,34 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>Cappuccino</t>
+          <t>Elfenben</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>80 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
+          <t>320 cm</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6596,25 +6532,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>373118</t>
+          <t>42018145</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8721012266568</t>
+          <t>8721364475267</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>889</v>
+        <v>969</v>
       </c>
       <c r="F52" t="n">
-        <v>1189</v>
+        <v>1389</v>
       </c>
       <c r="G52" t="n">
-        <v>519</v>
+        <v>569</v>
       </c>
       <c r="H52" t="n">
-        <v>22700</v>
+        <v>25280</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -6632,7 +6568,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>96</v>
+        <v>193</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -6651,12 +6587,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012266568_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364475267_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>373118</t>
+          <t>42018145</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -6666,17 +6602,17 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>373118</t>
+          <t>42018145</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 90 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 320 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012266568_m_en_hd_1.jpg, https://vdxl.im/8721012266568_a_en_hd_1.jpg, https://vdxl.im/8721012266568_g_en_hd_1.jpg, https://vdxl.im/8721012266568_g_en_hd_2.jpg, https://vdxl.im/8721012266568_g_en_hd_3.jpg, https://vdxl.im/8721012266568_g_en_hd_4.jpg, https://vdxl.im/8721012266568_g_en_hd_5.jpg, https://vdxl.im/8721012266568_g_en_hd_6.jpg, https://vdxl.im/8721012266568_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721364475267_mo-im_en_px16_1.jpg, https://vdxl.im/8721364475267_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364475267_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364475267_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364475267_detail_en_px16_1.jpg, https://vdxl.im/8721364475267_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364475267_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -6686,26 +6622,34 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Lysegrå</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>90 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
+          <t>320 cm</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6715,25 +6659,25 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>373181</t>
+          <t>42018197</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8721012267190</t>
+          <t>8721364475687</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1199</v>
+        <v>1069</v>
       </c>
       <c r="F53" t="n">
-        <v>1599</v>
+        <v>1529</v>
       </c>
       <c r="G53" t="n">
-        <v>702</v>
+        <v>629</v>
       </c>
       <c r="H53" t="n">
-        <v>24450</v>
+        <v>25280</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -6751,7 +6695,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -6770,12 +6714,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012267190_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364475687_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>373181</t>
+          <t>42018197</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -6785,17 +6729,17 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>373181</t>
+          <t>42018197</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 140 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 320 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012267190_m_en_hd_1.jpg, https://vdxl.im/8721012267190_a_en_hd_1.jpg, https://vdxl.im/8721012267190_g_en_hd_1.jpg, https://vdxl.im/8721012267190_g_en_hd_2.jpg, https://vdxl.im/8721012267190_g_en_hd_3.jpg, https://vdxl.im/8721012267190_g_en_hd_4.jpg, https://vdxl.im/8721012267190_g_en_hd_5.jpg, https://vdxl.im/8721012267190_g_en_hd_6.jpg, https://vdxl.im/8721012267190_g_en_hd_7.jpg</t>
+          <t>https://vdxl.im/8721364475687_mo-im_en_px16_1.jpg, https://vdxl.im/8721364475687_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364475687_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364475687_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364475687_detail_en_px16_1.jpg, https://vdxl.im/8721364475687_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364475687_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -6805,26 +6749,34 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>Grå</t>
+          <t>Antracit</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
+          <t>320 cm</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
+          <t>plantekasse-160-x-80-x-staal</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6834,25 +6786,25 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>373183</t>
+          <t>42018249</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8721012267213</t>
+          <t>8721364476103</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1189</v>
+        <v>1059</v>
       </c>
       <c r="F54" t="n">
-        <v>1589</v>
+        <v>1519</v>
       </c>
       <c r="G54" t="n">
-        <v>699</v>
+        <v>618</v>
       </c>
       <c r="H54" t="n">
-        <v>24450</v>
+        <v>25280</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6870,7 +6822,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>197</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -6889,12 +6841,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012267213_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721364476103_mo-im_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>373183</t>
+          <t>42018249</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6904,17 +6856,17 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>373183</t>
+          <t>42018249</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort og hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 140 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne moderne plantekasse er lavet af stål og plastik og tilføjer et sleek og stilfuldt look til enhver have eller terrasse. Den er lavet til at være praktisk og ser godt ud, så den kan bruges både indendørs og udendørs. Dens industrielle stil passer perfekt til nutidige hjem og giver et solidt hjem for dine planter.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Robuste materialer:&lt;/b&gt; Primært lavet af stærkt stål, som er kendt for sin holdbarhed. Tilsammen med plastgrovinstrumenter giver det en solid og langtidsholdbar plantekasse, som modstår både vejr og daglig brug. Den robuste struktur sikrer, at dine planter holdes sikkert og trygt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle komponenter:&lt;/b&gt; Denne plantekasse kommer med en standard potte, som er god til både indendørs og udendørs planter. Uanset om du planter blomstrende eller dekorative planter, får de plads til at trives. Dens smarte design gør, at planterne har plads nok.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne design:&lt;/b&gt; Med fokus på minimalisme viser plantekassen en moderne stil med rene linjer. Den elegant fungerer godt i enhver have- eller indendørsindretning og smelter let sammen med moderne stil. Den slanke form giver et sofistikeret look i alle rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Flere anvendelser:&lt;/b&gt; Plantekassen er fantastisk til både haver og terrasser, men kan også bruges indendørs. Det er en praktisk og flot løsning for planteelskere, der gerne vil indrette med grønne planter. Denne alsidighed sikrer, at den er egnet til forskellige situationer og årstider.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Plejevejledning:&lt;/b&gt; At samle den er simpelt og kræver blot to personer og en skruetrækker. Sørg for at følge de klare instrukser for at få den samlet korrekt. Regelmæssig pleje involverer at sørge for den rette placering, så planterne får nok lys og vand.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grøn&lt;/li&gt;&lt;li&gt;Materiale: Stål&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 320 x 80 x 75 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Advarsel! Beskyttelseshandsker skal bæres. Brug venligst sikkerhedsbriller, handsker, sikkerhedssko og hovedbeskyttelse, når du installerer plantekassen.</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721012267213_m_en_hd_1.jpg, https://vdxl.im/8721012267213_a_en_hd_1.jpg, https://vdxl.im/8721012267213_g_en_hd_1.jpg, https://vdxl.im/8721012267213_g_en_hd_2.jpg, https://vdxl.im/8721012267213_g_en_hd_3.jpg, https://vdxl.im/8721012267213_g_en_hd_4.jpg, https://vdxl.im/8721012267213_g_en_hd_5.jpg, https://vdxl.im/8721012267213_g_en_hd_6.jpg, https://vdxl.im/8721012267213_g_en_hd_7.jpg, https://vdxl.im/8721012267213_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721364476103_mo-im_en_px16_1.jpg, https://vdxl.im/8721364476103_wbg-an-m_en_px16_1.jpg, https://vdxl.im/8721364476103_wbg-mo_en_px16_1.jpg, https://vdxl.im/8721364476103_wbg-fr_en_px16_1.jpg, https://vdxl.im/8721364476103_detail_en_px16_1.jpg, https://vdxl.im/8721364476103_wbg-ma_en_px16_1.jpg, https://vdxl.im/8721364476103_wbg-siz_en_px16_1.jpg</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6924,846 +6876,29 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>Sort og hvid</t>
+          <t>Grøn</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Længde</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>373184</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>8721012267220</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>1509</v>
-      </c>
-      <c r="F55" t="n">
-        <v>2019</v>
-      </c>
-      <c r="G55" t="n">
-        <v>883</v>
-      </c>
-      <c r="H55" t="n">
-        <v>24450</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>14</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267220_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>373184</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>373184</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 140 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267220_m_en_hd_1.jpg, https://vdxl.im/8721012267220_a_en_hd_1.jpg, https://vdxl.im/8721012267220_g_en_hd_1.jpg, https://vdxl.im/8721012267220_g_en_hd_2.jpg, https://vdxl.im/8721012267220_g_en_hd_3.jpg, https://vdxl.im/8721012267220_g_en_hd_4.jpg, https://vdxl.im/8721012267220_g_en_hd_5.jpg, https://vdxl.im/8721012267220_g_en_hd_6.jpg, https://vdxl.im/8721012267220_g_en_hd_7.jpg, https://vdxl.im/8721012267220_g_en_hd_8.jpg</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Hvid og sort</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>373224</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>8721012267626</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>1499</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1999</v>
-      </c>
-      <c r="G56" t="n">
-        <v>877</v>
-      </c>
-      <c r="H56" t="n">
-        <v>26650</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>14</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267626_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>373224</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>373224</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid og sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 165 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 160 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267626_m_en_hd_1.jpg, https://vdxl.im/8721012267626_a_en_hd_1.jpg, https://vdxl.im/8721012267626_g_en_hd_1.jpg, https://vdxl.im/8721012267626_g_en_hd_2.jpg, https://vdxl.im/8721012267626_g_en_hd_3.jpg, https://vdxl.im/8721012267626_g_en_hd_4.jpg, https://vdxl.im/8721012267626_g_en_hd_5.jpg, https://vdxl.im/8721012267626_g_en_hd_6.jpg, https://vdxl.im/8721012267626_g_en_hd_7.jpg, https://vdxl.im/8721012267626_g_en_hd_8.jpg</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Hvid og sort</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>160 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>373239</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>8721012267770</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>1449</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1939</v>
-      </c>
-      <c r="G57" t="n">
-        <v>851</v>
-      </c>
-      <c r="H57" t="n">
-        <v>27300</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>63</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267770_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>373239</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>373239</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 185 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 180 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267770_m_en_hd_1.jpg, https://vdxl.im/8721012267770_a_en_hd_1.jpg, https://vdxl.im/8721012267770_g_en_hd_1.jpg, https://vdxl.im/8721012267770_g_en_hd_2.jpg, https://vdxl.im/8721012267770_g_en_hd_3.jpg, https://vdxl.im/8721012267770_g_en_hd_4.jpg, https://vdxl.im/8721012267770_g_en_hd_5.jpg, https://vdxl.im/8721012267770_g_en_hd_6.jpg, https://vdxl.im/8721012267770_g_en_hd_7.jpg</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Hvid</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>180 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>373258</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>8721012267961</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>1729</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2309</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1017</v>
-      </c>
-      <c r="H58" t="n">
-        <v>28350</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>34</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267961_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>373258</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>373258</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 200 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267961_m_en_hd_1.jpg, https://vdxl.im/8721012267961_a_en_hd_1.jpg, https://vdxl.im/8721012267961_g_en_hd_1.jpg, https://vdxl.im/8721012267961_g_en_hd_2.jpg, https://vdxl.im/8721012267961_g_en_hd_3.jpg, https://vdxl.im/8721012267961_g_en_hd_4.jpg, https://vdxl.im/8721012267961_g_en_hd_5.jpg, https://vdxl.im/8721012267961_g_en_hd_6.jpg, https://vdxl.im/8721012267961_g_en_hd_7.jpg</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>200 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>373259</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>8721012267978</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>1599</v>
-      </c>
-      <c r="F59" t="n">
-        <v>2139</v>
-      </c>
-      <c r="G59" t="n">
-        <v>938</v>
-      </c>
-      <c r="H59" t="n">
-        <v>28350</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>24</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267978_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>373259</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>373259</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 200 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012267978_m_en_hd_1.jpg, https://vdxl.im/8721012267978_a_en_hd_1.jpg, https://vdxl.im/8721012267978_g_en_hd_1.jpg, https://vdxl.im/8721012267978_g_en_hd_2.jpg, https://vdxl.im/8721012267978_g_en_hd_3.jpg, https://vdxl.im/8721012267978_g_en_hd_4.jpg, https://vdxl.im/8721012267978_g_en_hd_5.jpg, https://vdxl.im/8721012267978_g_en_hd_6.jpg, https://vdxl.im/8721012267978_g_en_hd_7.jpg</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Hvid</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>200 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>sengeramme-med-sengegavl-kunstlaeder</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>373263</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>8721012268012</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1719</v>
-      </c>
-      <c r="F60" t="n">
-        <v>2299</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1011</v>
-      </c>
-      <c r="H60" t="n">
-        <v>28350</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>20</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012268012_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>373263</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>373263</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme med sengegavl! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt kunstlæder: Kunstlæder i høj kvalitet er et yderst slidstærkt materiale. Det er modstandsdygtigt over for pletter, så det er let at rengøre med en fugtig klud. Den glatte overflade har også et luksuriøst udseende og ægte læders skønhed.&lt;/li&gt;&lt;li&gt;Støttende ben: Sengen understøttes af robuste ben, som giver stabilitet, sikkerhed og robusthed.&lt;/li&gt;&lt;li&gt;Lameller i krydsfiner: Lamellerne i krydsfiner giver god vægtfordeling, hvilket sikrer, at madrassen forbliver, hvor den skal, også selvom du vender og drejer dig i løbet af natten.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Dette sengegærde giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se film.&lt;/li&gt;&lt;li&gt;Bølget sidedesign: Sengerammens bølgede look er stilfuldt og sofistikeret, hvilket føjer et moderne og elegant touch til din indretning og gør den til omdrejningspunktet i dit soveværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort og hvid&lt;/li&gt;&lt;li&gt;Materiale: Kunstlæder (75% polyvinylchlorid, 5% bomuld, 20% polyester), metal, massivt fyrretræ, krydsfiner&lt;/li&gt;&lt;li&gt;Samlede mål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passig madrasstørrelse: 200 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Passig madrastykkelse: &gt;/= 15 cm&lt;/li&gt;&lt;li&gt;Serienavn: Dover&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721012268012_m_en_hd_1.jpg, https://vdxl.im/8721012268012_a_en_hd_1.jpg, https://vdxl.im/8721012268012_g_en_hd_1.jpg, https://vdxl.im/8721012268012_g_en_hd_2.jpg, https://vdxl.im/8721012268012_g_en_hd_3.jpg, https://vdxl.im/8721012268012_g_en_hd_4.jpg, https://vdxl.im/8721012268012_g_en_hd_5.jpg, https://vdxl.im/8721012268012_g_en_hd_6.jpg, https://vdxl.im/8721012268012_g_en_hd_7.jpg, https://vdxl.im/8721012268012_g_en_hd_8.jpg</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Sort og hvid</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>200 x 200 cm</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>sofasaet-til-haven-7-dele-med-hynder-polyrattan-sort-10</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3260350</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>8721102480447</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>4489</v>
-      </c>
-      <c r="F61" t="n">
-        <v>5989</v>
-      </c>
-      <c r="G61" t="n">
-        <v>2636</v>
-      </c>
-      <c r="H61" t="n">
-        <v>65200</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>111</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721102480447_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>3260350</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>3260350</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Dette havesofasæt er den perfekte tilføjelse til din have eller terrasse og giver et behageligt og indbydende sted at sidde og snakke med familie og venner eller bare slappe af og nyde udendørslivet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: PE-rattan, også kendt som polyrattan, er et stærkt syntetisk materiale, der ikke kræver meget vedligeholdelse, og det ligner naturlig rattan. Det er let i vægt, nemt at rengøre, og det anvendes ofte til udendørs møbler grundet dets holdbarhed og vejrbestandige egenskaber.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion med vandafvisende pose: Havemøblet har opbevaringsplads under sædet med en vandafvisende pose til opbevaring af hynder, legetøj og andre ting. Den indvendige pose kan fastgøres sikkert til udendørs møblet med burrebåndslukninger for øget stabilitet.&lt;/li&gt;&lt;li&gt;Aftagelige og vaskbare betræk: Disse sædehynder er forsynet med aftagelige betræk, så de nemt kan vaskes og vedligeholdes.&lt;/li&gt;&lt;li&gt;Modulært design: Dette havemøbelsæt har et modulært design, der gør det fleksibelt og nemt at flytte rundt på, så du kan skabe et skræddersyet havemøbelarrangement.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Vi anbefaler, at du beskytter dine udendørs møbler med et vandtæt overtræk for at sikre, at de forbliver smukke.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Maks. bæreevne (pr. sæde ): 110 kg&lt;/li&gt;&lt;li&gt;UV-resistent&lt;/li&gt;&lt;li&gt;Justerbare plastfødder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hjørnemodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 62 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midtermodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofa med armlæn:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål, massivt akacietræ med en oliefinish&lt;/li&gt;&lt;li&gt;Mål: 59 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;Armlænets højde fra gulvet: 55 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hynde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, parasoldug: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale, sædehynde: Skum&lt;/li&gt;&lt;li&gt;Fyldmateriale, ryghynde: Bomuldsfibre&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 55 x 55 x 3 cm (B x D x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 55 x 45 x 13 cm (L x B x T)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x hjørnemodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;3 x midtermodul med opbevaringsfunktion og vandafvisende taske&lt;/li&gt;&lt;li&gt;2 x sofamodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;9 x ryghynde&lt;/li&gt;&lt;li&gt;7 x sædehynde med aftageligt og vaskbart betræk&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721102480447_m_en_hd_1.jpg, https://vdxl.im/8721102480447_a_en_hd_1.jpg, https://vdxl.im/8721102480447_g_en_hd_1.jpg, https://res.cloudinary.com/vdxl/image/upload/v1709801887/VN%20rattan/1_Light_beige_Rattan_Premium_rattan_.png</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>beige og cremefarvet</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
+          <t>320 cm</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Højde</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>75 cm</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>vaeghaengt-sengebord-35x35x20-cm-10</t>
+          <t>sofasaet-til-haven-10-dele-med-hynder-polyrattan-sort-39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>829860</t>
+          <t>3251825</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8720845947019</t>
+          <t>8721102308000</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>269</v>
+        <v>6199</v>
       </c>
       <c r="F2" t="n">
-        <v>359</v>
+        <v>8269</v>
       </c>
       <c r="G2" t="n">
-        <v>157</v>
+        <v>3644</v>
       </c>
       <c r="H2" t="n">
-        <v>6930</v>
+        <v>86600</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845947019_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102308000_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>829860</t>
+          <t>3251825</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>829860</t>
+          <t>3251825</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette væghængte natbord er en dekorativ såvel som en praktisk tilføjelse til din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende sengebord optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 35 x 35 x 20 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette havesofasæt er den perfekte tilføjelse til din have eller terrasse og giver et behageligt og indbydende sted at sidde og snakke med familie og venner eller bare slappe af og nyde udendørslivet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: PE-rattan, også kendt som polyrattan, er et stærkt syntetisk materiale, der ikke kræver meget vedligeholdelse, og det ligner naturlig rattan. Det er let i vægt, nemt at rengøre, og det anvendes ofte til udendørs møbler grundet dets holdbarhed og vejrbestandige egenskaber.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion med vandafvisende pose: Havesofaen har opbevaringsplads under sædet med en vandafvisende pose til opbevaring af hynder, legetøj og andre ting. De indvendige poser har et topdæksel og kan fastgøres sikkert til sæderne med velcrolukninger for ekstra stabilitet.&lt;/li&gt;&lt;li&gt;Aftagelige og vaskbare betræk: Disse sædehynder er forsynet med aftagelige betræk, så de nemt kan vaskes og vedligeholdes.&lt;/li&gt;&lt;li&gt;Modulært design: Dette havemøbelsæt har et modulært design, der gør det fleksibelt og nemt at flytte rundt på, så du kan skabe et skræddersyet havemøbelarrangement.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Vi anbefaler, at du beskytter dine udendørs møbler med et vandtæt overtræk for at sikre, at de forbliver smukke.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Maks. bæreevne (pr. sæde ): 110 kg&lt;/li&gt;&lt;li&gt;UV-resistent&lt;/li&gt;&lt;li&gt;Justerbare plastfødder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hjørnemodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 62 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midtermodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofa med armlæn:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 65,5 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;Armlænets højde fra gulvet: 55 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hynde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, parasoldug: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale, sædehynde: Skum&lt;/li&gt;&lt;li&gt;Fyldmateriale, ryghynde: Bomuldsfibre&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 55 x 55 x 3 cm (B x D x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 55 x 45 x 13 cm (L x B x T)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x hjørnemodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;6 x midtermodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;2 x sofamodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;12 x ryghynde&lt;/li&gt;&lt;li&gt;10 x sædehynde med aftageligt og vaskbart betræk&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845947019_m_en_hd_1.jpg, https://vdxl.im/8720845947019_a_en_hd_1.jpg, https://vdxl.im/8720845947019_g_en_hd_1.jpg, https://vdxl.im/8720845947019_g_en_hd_2.jpg, https://vdxl.im/8720845947019_g_en_hd_3.jpg, https://vdxl.im/8720845947019_g_en_hd_4.jpg, https://vdxl.im/8720845947019_g_en_hd_5.jpg, https://vdxl.im/8720845947019_g_en_hd_6.jpg, https://vdxl.im/8720845947019_g_en_hd_7.jpg, https://vdxl.im/8720845947019_g_en_hd_8.jpg, https://vdxl.im/8720845947019_g_en_hd_9.jpg, https://vdxl.im/8720845947019_g_en_hd_10.jpg</t>
+          <t>https://vdxl.im/8721102308000_m_en_hd_1.jpg, https://vdxl.im/8721102308000_a_en_hd_1.jpg, https://vdxl.im/8721102308000_g_en_hd_1.jpg, https://res.cloudinary.com/vdxl/image/upload/v1709801887/VN%20rattan/1_Light_beige_Rattan_Premium_rattan_.png</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -656,17 +656,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Betongrå</t>
+          <t>beige og cremefarvet</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Uden bord</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -675,7 +675,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vaeghaengt-sengebord-35x35x20-cm-10</t>
+          <t>havesofasaet-7-dele-med-hynder-polyrattan-beige-153</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -685,25 +685,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>829852</t>
+          <t>3263796</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8720845946937</t>
+          <t>8721102508912</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>279</v>
+        <v>3669</v>
       </c>
       <c r="F3" t="n">
-        <v>379</v>
+        <v>4899</v>
       </c>
       <c r="G3" t="n">
-        <v>163</v>
+        <v>2157</v>
       </c>
       <c r="H3" t="n">
-        <v>6930</v>
+        <v>50600</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845946937_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102508912_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>829852</t>
+          <t>3263796</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -755,17 +755,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>829852</t>
+          <t>3263796</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette væghængte natbord er en dekorativ såvel som en praktisk tilføjelse til din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende sengebord optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 35 x 35 x 20 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette havesofasæt er den perfekte tilføjelse til din have eller terrasse og giver et behageligt og indbydende sted at sidde og snakke med familie og venner eller bare slappe af og nyde udendørslivet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: PE-rattan, også kendt som polyrattan, er et stærkt syntetisk materiale, der ikke kræver meget vedligeholdelse, og det ligner naturlig rattan. Det er let i vægt, nemt at rengøre, og det anvendes ofte til udendørs møbler grundet dets holdbarhed og vejrbestandige egenskaber.&lt;/li&gt;&lt;li&gt;Komfortabel siddeoplevelse: Disse havemøbler leveres med tykt polstrede hynder, så de giver en komfortabel siddeoplevelse.&lt;/li&gt;&lt;li&gt;Aftagelige og vaskbare betræk: Disse sædehynder er forsynet med aftagelige betræk, så de nemt kan vaskes og vedligeholdes.&lt;/li&gt;&lt;li&gt;Robust og stabil ramme: Den pulverlakerede stålramme gør havemøblet stærkt og stabilt til daglig udendørs brug.&lt;/li&gt;&lt;li&gt;Modulært design: Dette havemøbelsæt har et modulært design, der gør det fleksibelt og nemt at flytte rundt på, så du kan skabe et skræddersyet havemøbelarrangement.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Vi anbefaler, at du beskytter dine udendørs møbler med et vandtæt overtræk for at sikre, at de forbliver smukke.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Maks. bæreevne (pr. sæde ): 110 kg&lt;/li&gt;&lt;li&gt;UV-resistent&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hjørnemodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 62 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midtermodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofa med armlæn:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 61,5 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;Armlænets højde fra gulvet: 55 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Fodskammel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 55 x 37 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hynde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale, parasoldug: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale, sædehynde: Skum&lt;/li&gt;&lt;li&gt;Fyldmateriale, ryghynde: Bomuldsfibre&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 55 x 55 x 3 cm (B x D x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 55 x 45 x 13 cm (L x B x T)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x hjørnedel til sofa&lt;/li&gt;&lt;li&gt;2 x midtersofa&lt;/li&gt;&lt;li&gt;2 x sofamodul&lt;/li&gt;&lt;li&gt;1 x fodskammel&lt;/li&gt;&lt;li&gt;7 x ryghynde&lt;/li&gt;&lt;li&gt;6 x sædehynde med aftageligt og vaskbart betræk&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8720845946937_m_en_hd_1.jpg, https://vdxl.im/8720845946937_a_en_hd_1.jpg, https://vdxl.im/8720845946937_g_en_hd_1.jpg, https://vdxl.im/8720845946937_g_en_hd_2.jpg, https://vdxl.im/8720845946937_g_en_hd_3.jpg, https://vdxl.im/8720845946937_g_en_hd_4.jpg, https://vdxl.im/8720845946937_g_en_hd_5.jpg, https://vdxl.im/8720845946937_g_en_hd_6.jpg, https://vdxl.im/8720845946937_g_en_hd_7.jpg, https://vdxl.im/8720845946937_g_en_hd_8.jpg, https://vdxl.im/8720845946937_g_en_hd_9.jpg, https://vdxl.im/8720845946937_g_en_hd_10.jpg</t>
+          <t>https://vdxl.im/8721102508912_m_en_hd_1.jpg, https://vdxl.im/8721102508912_a_en_hd_1.jpg, https://vdxl.im/8721102508912_g_en_hd_1.jpg, https://vdxl.im/8721102508912_g_en_hd_2.jpg, https://res.cloudinary.com/vdxl/image/upload/v1709801872/VN%20rattan/1_Grey_2_Rattan_Premium_rattan_.png</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -775,616 +775,21 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Hvid</t>
+          <t>Grå</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Antal i pakke</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>uden opbevaring</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>vaeghaengt-sengebord-35x35x20-cm-10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>829858</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>8720845946999</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>269</v>
-      </c>
-      <c r="F4" t="n">
-        <v>359</v>
-      </c>
-      <c r="G4" t="n">
-        <v>158</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6930</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>200</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720845946999_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>829858</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>829858</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Dette væghængte natbord er en dekorativ såvel som en praktisk tilføjelse til din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende sengebord optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 35 x 35 x 20 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720845946999_m_en_hd_1.jpg, https://vdxl.im/8720845946999_a_en_hd_1.jpg, https://vdxl.im/8720845946999_g_en_hd_1.jpg, https://vdxl.im/8720845946999_g_en_hd_2.jpg, https://vdxl.im/8720845946999_g_en_hd_3.jpg, https://vdxl.im/8720845946999_g_en_hd_4.jpg, https://vdxl.im/8720845946999_g_en_hd_5.jpg, https://vdxl.im/8720845946999_g_en_hd_6.jpg, https://vdxl.im/8720845946999_g_en_hd_7.jpg, https://vdxl.im/8720845946999_g_en_hd_8.jpg, https://vdxl.im/8720845946999_g_en_hd_9.jpg, https://vdxl.im/8720845946999_g_en_hd_10.jpg</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Sonoma-eg</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Antal i pakke</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>vaeghaengt-sengebord-35x35x20-cm-10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>829862</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>8720845947033</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>269</v>
-      </c>
-      <c r="F5" t="n">
-        <v>359</v>
-      </c>
-      <c r="G5" t="n">
-        <v>157</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6820</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>11</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720845947033_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>829862</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>829862</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Dette væghængte natbord er en dekorativ såvel som en praktisk tilføjelse til din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende sengebord optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 35 x 35 x 20 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720845947033_m_en_hd_1.jpg, https://vdxl.im/8720845947033_a_en_hd_1.jpg, https://vdxl.im/8720845947033_g_en_hd_1.jpg, https://vdxl.im/8720845947033_g_en_hd_2.jpg, https://vdxl.im/8720845947033_g_en_hd_3.jpg, https://vdxl.im/8720845947033_g_en_hd_4.jpg, https://vdxl.im/8720845947033_g_en_hd_5.jpg, https://vdxl.im/8720845947033_g_en_hd_6.jpg, https://vdxl.im/8720845947033_g_en_hd_7.jpg, https://vdxl.im/8720845947033_g_en_hd_8.jpg, https://vdxl.im/8720845947033_g_en_hd_9.jpg, https://vdxl.im/8720845947033_g_en_hd_10.jpg</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Røget eg</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Antal i pakke</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>vaeghaengt-sengebord-35x35x20-cm-10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>829864</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8720845947057</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>329</v>
-      </c>
-      <c r="F6" t="n">
-        <v>439</v>
-      </c>
-      <c r="G6" t="n">
-        <v>190</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6820</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>80</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720845947057_m_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>829864</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>829864</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Dette væghængte natbord er en dekorativ såvel som en praktisk tilføjelse til din indretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Skabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Det svævende sengebord optager ikke gulvplads og er nemt at hænge op på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 35 x 35 x 20 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8720845947057_m_en_hd_1.jpg, https://vdxl.im/8720845947057_a_en_hd_1.jpg, https://vdxl.im/8720845947057_g_en_hd_1.jpg, https://vdxl.im/8720845947057_g_en_hd_2.jpg, https://vdxl.im/8720845947057_g_en_hd_3.jpg, https://vdxl.im/8720845947057_g_en_hd_4.jpg, https://vdxl.im/8720845947057_g_en_hd_5.jpg, https://vdxl.im/8720845947057_g_en_hd_6.jpg, https://vdxl.im/8720845947057_g_en_hd_7.jpg, https://vdxl.im/8720845947057_g_en_hd_8.jpg, https://vdxl.im/8720845947057_g_en_hd_9.jpg, https://vdxl.im/8720845947057_g_en_hd_10.jpg</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Grå sonoma-eg</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Antal i pakke</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>vaeghaengt-sengebord-35x35x20-cm-10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>882402</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>8721288919298</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>269</v>
-      </c>
-      <c r="F7" t="n">
-        <v>359</v>
-      </c>
-      <c r="G7" t="n">
-        <v>157</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6710</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>155</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721288919298_mo-im_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>882402</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>882402</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Dette væghængte natbordskab kombinerer praktisk funktion med rustik charme. Det er lavet af konstrueret træ og kan let monteres på enhver væg, hvilket sparer værdifuld gulvplads og passer perfekt ind i dit soveværelse. Den firkantede form og den dybe brune finish tilføjer varme og stil, ideelt til et roligt og ryddeligt soveområde.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materiale i konstrueret træ&lt;/b&gt;: Skabet er lavet af kvalitets konstrueret træ, så det holder i mange år og bevarer sin rustikke stil. Med lidt pleje ser det stadig nyt ud i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Robuste komponenter&lt;/b&gt;: Skuffen er godt lavet af konstrueret træ og har metal d-greb, hvilket gør det nemt at tilgå. Designet sikrer, at alt fungerer glat til daglig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pladsbesparende væghængt design&lt;/b&gt;: Det væghængte design sparer gulvplads og gør dit rum mere indbydende. Et perfekt valg til små opholdsrum, hvor hver kvadratmeter tæller.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige opbevaringsløsninger&lt;/b&gt;: Med en rummelig skuffe kan skabet opbevare alt fra bøger til gadgets og holde alt i orden, så du kan skabe et ryddeligt og fredeligt miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Minimal vedligeholdelse&lt;/b&gt;: Plejen er super enkelt – bare tør det af med en klud for at holde det pænt til daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 35 x 35 x 20 CM (L x B x H)&lt;/li&gt;&lt;li&gt;Med skuffe&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Monteringstype: Vægmonteret&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721288919298_mo-im_en_hd_1.jpg, https://vdxl.im/8721288919298_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288919298_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288919298_mo-im_en_hd_2.jpg, https://vdxl.im/8721288919298_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288919298_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288919298_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288919298_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288919298_detail_en_hd_1.jpg, https://vdxl.im/8721288919298_detail_en_hd_2.jpg, https://vdxl.im/8721288919298_detail_en_hd_3.jpg, https://vdxl.im/8721288919298_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288919298_wbg-siz_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>artisan eg</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Antal i pakke</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>vaeghaengt-sengebord-35x35x20-cm-10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MERGE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>882404</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8721288919311</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>279</v>
-      </c>
-      <c r="F8" t="n">
-        <v>379</v>
-      </c>
-      <c r="G8" t="n">
-        <v>163</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6710</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>shopify</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>deny</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>162</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721288919311_mo-im_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>882404</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>882404</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Dette væghængte natbordskab kombinerer praktisk funktion med rustik charme. Det er lavet af konstrueret træ og kan let monteres på enhver væg, hvilket sparer værdifuld gulvplads og passer perfekt ind i dit soveværelse. Den firkantede form og den dybe brune finish tilføjer varme og stil, ideelt til et roligt og ryddeligt soveområde.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Materiale i konstrueret træ&lt;/b&gt;: Skabet er lavet af kvalitets konstrueret træ, så det holder i mange år og bevarer sin rustikke stil. Med lidt pleje ser det stadig nyt ud i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Robuste komponenter&lt;/b&gt;: Skuffen er godt lavet af konstrueret træ og har metal d-greb, hvilket gør det nemt at tilgå. Designet sikrer, at alt fungerer glat til daglig brug.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Pladsbesparende væghængt design&lt;/b&gt;: Det væghængte design sparer gulvplads og gør dit rum mere indbydende. Et perfekt valg til små opholdsrum, hvor hver kvadratmeter tæller.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige opbevaringsløsninger&lt;/b&gt;: Med en rummelig skuffe kan skabet opbevare alt fra bøger til gadgets og holde alt i orden, så du kan skabe et ryddeligt og fredeligt miljø.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Minimal vedligeholdelse&lt;/b&gt;: Plejen er super enkelt – bare tør det af med en klud for at holde det pænt til daglig brug.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 35 x 35 x 20 CM (L x B x H)&lt;/li&gt;&lt;li&gt;Med skuffe&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Monteringstype: Vægmonteret&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>https://vdxl.im/8721288919311_mo-im_en_hd_1.jpg, https://vdxl.im/8721288919311_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288919311_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288919311_mo-im_en_hd_2.jpg, https://vdxl.im/8721288919311_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288919311_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288919311_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288919311_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288919311_detail_en_hd_1.jpg, https://vdxl.im/8721288919311_detail_en_hd_2.jpg, https://vdxl.im/8721288919311_detail_en_hd_3.jpg, https://vdxl.im/8721288919311_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288919311_wbg-siz_en_hd_1.jpg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Farve</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Sort eg</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Antal i pakke</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sofasaet-til-haven-10-dele-med-hynder-polyrattan-sort-39</t>
+          <t>sofabordben-edderkopform-stal</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3251825</t>
+          <t>4013110</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8721102308000</t>
+          <t>8721158317704</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6199</v>
+        <v>1119</v>
       </c>
       <c r="F2" t="n">
-        <v>8269</v>
+        <v>1499</v>
       </c>
       <c r="G2" t="n">
-        <v>3644</v>
+        <v>652</v>
       </c>
       <c r="H2" t="n">
-        <v>86600</v>
+        <v>13100</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721102308000_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158317704_a_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>3251825</t>
+          <t>4013110</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>3251825</t>
+          <t>4013110</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette havesofasæt er den perfekte tilføjelse til din have eller terrasse og giver et behageligt og indbydende sted at sidde og snakke med familie og venner eller bare slappe af og nyde udendørslivet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: PE-rattan, også kendt som polyrattan, er et stærkt syntetisk materiale, der ikke kræver meget vedligeholdelse, og det ligner naturlig rattan. Det er let i vægt, nemt at rengøre, og det anvendes ofte til udendørs møbler grundet dets holdbarhed og vejrbestandige egenskaber.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion med vandafvisende pose: Havesofaen har opbevaringsplads under sædet med en vandafvisende pose til opbevaring af hynder, legetøj og andre ting. De indvendige poser har et topdæksel og kan fastgøres sikkert til sæderne med velcrolukninger for ekstra stabilitet.&lt;/li&gt;&lt;li&gt;Aftagelige og vaskbare betræk: Disse sædehynder er forsynet med aftagelige betræk, så de nemt kan vaskes og vedligeholdes.&lt;/li&gt;&lt;li&gt;Modulært design: Dette havemøbelsæt har et modulært design, der gør det fleksibelt og nemt at flytte rundt på, så du kan skabe et skræddersyet havemøbelarrangement.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Vi anbefaler, at du beskytter dine udendørs møbler med et vandtæt overtræk for at sikre, at de forbliver smukke.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Maks. bæreevne (pr. sæde ): 110 kg&lt;/li&gt;&lt;li&gt;UV-resistent&lt;/li&gt;&lt;li&gt;Justerbare plastfødder&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hjørnemodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 62 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midtermodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofa med armlæn:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Beige&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 65,5 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;Armlænets højde fra gulvet: 55 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hynde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale, parasoldug: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale, sædehynde: Skum&lt;/li&gt;&lt;li&gt;Fyldmateriale, ryghynde: Bomuldsfibre&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 55 x 55 x 3 cm (B x D x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 55 x 45 x 13 cm (L x B x T)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x hjørnemodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;6 x midtermodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;2 x sofamodul med opbevaringsfunktion og vandafvisende pose&lt;/li&gt;&lt;li&gt;12 x ryghynde&lt;/li&gt;&lt;li&gt;10 x sædehynde med aftageligt og vaskbart betræk&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette sofabordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit sofabord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 98 x 58 x (42-43) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 580 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Anbefalet brug: sofabord&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sofabordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721102308000_m_en_hd_1.jpg, https://vdxl.im/8721102308000_a_en_hd_1.jpg, https://vdxl.im/8721102308000_g_en_hd_1.jpg, https://res.cloudinary.com/vdxl/image/upload/v1709801887/VN%20rattan/1_Light_beige_Rattan_Premium_rattan_.png</t>
+          <t>https://vdxl.im/8721158317704_a_en_hd_1.jpg, https://vdxl.im/8721158317704_g_en_hd_1.jpg, https://vdxl.im/8721158317704_g_en_hd_2.jpg, https://vdxl.im/8721158317704_g_en_hd_3.jpg, https://vdxl.im/8721158317704_g_en_hd_4.jpg, https://vdxl.im/8721158317704_g_en_hd_5.jpg, https://vdxl.im/8721158317704_g_en_hd_6.jpg, https://vdxl.im/8721158317704_g_en_hd_7.jpg, https://vdxl.im/8721158317704_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -656,17 +656,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>beige og cremefarvet</t>
+          <t>Antracitgrå</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Størrelse</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Uden bord</t>
+          <t>98 x 58 x (42-43) cm</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -675,7 +675,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>havesofasaet-7-dele-med-hynder-polyrattan-beige-153</t>
+          <t>sofabordben-edderkopform-stal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -685,25 +685,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3263796</t>
+          <t>4013111</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8721102508912</t>
+          <t>8721158317711</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3669</v>
+        <v>1119</v>
       </c>
       <c r="F3" t="n">
-        <v>4899</v>
+        <v>1499</v>
       </c>
       <c r="G3" t="n">
-        <v>2157</v>
+        <v>653</v>
       </c>
       <c r="H3" t="n">
-        <v>50600</v>
+        <v>13050</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721102508912_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158317711_a_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3263796</t>
+          <t>4013111</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -755,17 +755,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>3263796</t>
+          <t>4013111</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette havesofasæt er den perfekte tilføjelse til din have eller terrasse og giver et behageligt og indbydende sted at sidde og snakke med familie og venner eller bare slappe af og nyde udendørslivet.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: PE-rattan, også kendt som polyrattan, er et stærkt syntetisk materiale, der ikke kræver meget vedligeholdelse, og det ligner naturlig rattan. Det er let i vægt, nemt at rengøre, og det anvendes ofte til udendørs møbler grundet dets holdbarhed og vejrbestandige egenskaber.&lt;/li&gt;&lt;li&gt;Komfortabel siddeoplevelse: Disse havemøbler leveres med tykt polstrede hynder, så de giver en komfortabel siddeoplevelse.&lt;/li&gt;&lt;li&gt;Aftagelige og vaskbare betræk: Disse sædehynder er forsynet med aftagelige betræk, så de nemt kan vaskes og vedligeholdes.&lt;/li&gt;&lt;li&gt;Robust og stabil ramme: Den pulverlakerede stålramme gør havemøblet stærkt og stabilt til daglig udendørs brug.&lt;/li&gt;&lt;li&gt;Modulært design: Dette havemøbelsæt har et modulært design, der gør det fleksibelt og nemt at flytte rundt på, så du kan skabe et skræddersyet havemøbelarrangement.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Vi anbefaler, at du beskytter dine udendørs møbler med et vandtæt overtræk for at sikre, at de forbliver smukke.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Maks. bæreevne (pr. sæde ): 110 kg&lt;/li&gt;&lt;li&gt;UV-resistent&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hjørnemodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 62 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Midtermodul:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sofa med armlæn:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 61,5 x 62 x 69 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;Armlænets højde fra gulvet: 55 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Fodskammel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Grå&lt;/li&gt;&lt;li&gt;Materiale: Polyrattan, pulverlakeret stål&lt;/li&gt;&lt;li&gt;Mål: 55 x 55 x 37 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Sædemål: 55 x 55 cm (B x D)&lt;/li&gt;&lt;li&gt;Sædehøjde fra jorden: 37 cm&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hynde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale, parasoldug: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Fyldmateriale, sædehynde: Skum&lt;/li&gt;&lt;li&gt;Fyldmateriale, ryghynde: Bomuldsfibre&lt;/li&gt;&lt;li&gt;Mål, sædehynde: 55 x 55 x 3 cm (B x D x T)&lt;/li&gt;&lt;li&gt;Mål, ryghynde: 55 x 45 x 13 cm (L x B x T)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x hjørnedel til sofa&lt;/li&gt;&lt;li&gt;2 x midtersofa&lt;/li&gt;&lt;li&gt;2 x sofamodul&lt;/li&gt;&lt;li&gt;1 x fodskammel&lt;/li&gt;&lt;li&gt;7 x ryghynde&lt;/li&gt;&lt;li&gt;6 x sædehynde med aftageligt og vaskbart betræk&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette sofabordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit sofabord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 98 x 58 x (42-43) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 580 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Anbefalet brug: sofabord&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sofabordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721102508912_m_en_hd_1.jpg, https://vdxl.im/8721102508912_a_en_hd_1.jpg, https://vdxl.im/8721102508912_g_en_hd_1.jpg, https://vdxl.im/8721102508912_g_en_hd_2.jpg, https://res.cloudinary.com/vdxl/image/upload/v1709801872/VN%20rattan/1_Grey_2_Rattan_Premium_rattan_.png</t>
+          <t>https://vdxl.im/8721158317711_a_en_hd_1.jpg, https://vdxl.im/8721158317711_g_en_hd_1.jpg, https://vdxl.im/8721158317711_g_en_hd_2.jpg, https://vdxl.im/8721158317711_g_en_hd_3.jpg, https://vdxl.im/8721158317711_g_en_hd_4.jpg, https://vdxl.im/8721158317711_g_en_hd_5.jpg, https://vdxl.im/8721158317711_g_en_hd_6.jpg, https://vdxl.im/8721158317711_g_en_hd_7.jpg, https://vdxl.im/8721158317711_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -775,21 +775,6304 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Grå</t>
+          <t>Naturfarvet</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Størrelse</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>uden opbevaring</t>
+          <t>98 x 58 x (42-43) cm</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sofabordben-edderkopform-stal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4013116</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8721158317766</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1379</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1839</v>
+      </c>
+      <c r="G4" t="n">
+        <v>802</v>
+      </c>
+      <c r="H4" t="n">
+        <v>17800</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>200</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317766_a_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4013116</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4013116</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317766_a_en_hd_1.jpg, https://vdxl.im/8721158317766_g_en_hd_1.jpg, https://vdxl.im/8721158317766_g_en_hd_2.jpg, https://vdxl.im/8721158317766_g_en_hd_3.jpg, https://vdxl.im/8721158317766_g_en_hd_4.jpg, https://vdxl.im/8721158317766_g_en_hd_5.jpg, https://vdxl.im/8721158317766_g_en_hd_6.jpg, https://vdxl.im/8721158317766_g_en_hd_7.jpg, https://vdxl.im/8721158317766_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>150 x 78 x (72-73) cm</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sofabordben-edderkopform-stal</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4013117</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8721158317773</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G5" t="n">
+        <v>585</v>
+      </c>
+      <c r="H5" t="n">
+        <v>20560</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>200</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317773_a_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4013117</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4013117</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317773_a_en_hd_1.jpg, https://vdxl.im/8721158317773_g_en_hd_1.jpg, https://vdxl.im/8721158317773_g_en_hd_2.jpg, https://vdxl.im/8721158317773_g_en_hd_3.jpg, https://vdxl.im/8721158317773_g_en_hd_4.jpg, https://vdxl.im/8721158317773_g_en_hd_5.jpg, https://vdxl.im/8721158317773_g_en_hd_6.jpg, https://vdxl.im/8721158317773_g_en_hd_7.jpg, https://vdxl.im/8721158317773_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>150 x 78 x (72-73) cm</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sofabordben-edderkopform-stal</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4013118</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8721158317780</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1619</v>
+      </c>
+      <c r="G6" t="n">
+        <v>704</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17800</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>92</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317780_a_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4013118</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4013118</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317780_a_en_hd_1.jpg, https://vdxl.im/8721158317780_g_en_hd_1.jpg, https://vdxl.im/8721158317780_g_en_hd_2.jpg, https://vdxl.im/8721158317780_g_en_hd_3.jpg, https://vdxl.im/8721158317780_g_en_hd_4.jpg, https://vdxl.im/8721158317780_g_en_hd_5.jpg, https://vdxl.im/8721158317780_g_en_hd_6.jpg, https://vdxl.im/8721158317780_g_en_hd_7.jpg, https://vdxl.im/8721158317780_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Antracitgrå</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>150 x 78 x (72-73) cm</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sofabordben-edderkopform-stal</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4013119</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8721158317797</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1219</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1629</v>
+      </c>
+      <c r="G7" t="n">
+        <v>708</v>
+      </c>
+      <c r="H7" t="n">
+        <v>20560</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>137</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317797_a_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4013119</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4013119</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317797_a_en_hd_1.jpg, https://vdxl.im/8721158317797_g_en_hd_1.jpg, https://vdxl.im/8721158317797_g_en_hd_2.jpg, https://vdxl.im/8721158317797_g_en_hd_3.jpg, https://vdxl.im/8721158317797_g_en_hd_4.jpg, https://vdxl.im/8721158317797_g_en_hd_5.jpg, https://vdxl.im/8721158317797_g_en_hd_6.jpg, https://vdxl.im/8721158317797_g_en_hd_7.jpg, https://vdxl.im/8721158317797_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Naturfarvet</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>150 x 78 x (72-73) cm</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sofabordben-edderkopform-stal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4013120</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8721158317803</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1509</v>
+      </c>
+      <c r="G8" t="n">
+        <v>657</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16200</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>39</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317803_a_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4013120</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4013120</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 85 x 85 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 850 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317803_a_en_hd_1.jpg, https://vdxl.im/8721158317803_g_en_hd_1.jpg, https://vdxl.im/8721158317803_g_en_hd_2.jpg, https://vdxl.im/8721158317803_g_en_hd_3.jpg, https://vdxl.im/8721158317803_g_en_hd_4.jpg, https://vdxl.im/8721158317803_g_en_hd_5.jpg, https://vdxl.im/8721158317803_g_en_hd_6.jpg, https://vdxl.im/8721158317803_g_en_hd_7.jpg, https://vdxl.im/8721158317803_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>85 x 85 x (72-73) cm</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sofabordben-edderkopform-stal</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4013123</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8721158317834</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1169</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1559</v>
+      </c>
+      <c r="G9" t="n">
+        <v>683</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16100</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>15</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317834_a_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4013123</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4013123</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 85 x 85 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 850 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158317834_a_en_hd_1.jpg, https://vdxl.im/8721158317834_g_en_hd_1.jpg, https://vdxl.im/8721158317834_g_en_hd_2.jpg, https://vdxl.im/8721158317834_g_en_hd_3.jpg, https://vdxl.im/8721158317834_g_en_hd_4.jpg, https://vdxl.im/8721158317834_g_en_hd_5.jpg, https://vdxl.im/8721158317834_g_en_hd_6.jpg, https://vdxl.im/8721158317834_g_en_hd_7.jpg, https://vdxl.im/8721158317834_g_en_hd_8.jpg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Naturfarvet</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>85 x 85 x (72-73) cm</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>makeupbord-med-led-lys-80x41x134-5-cm</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>871537</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8721288519887</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>959</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1279</v>
+      </c>
+      <c r="G10" t="n">
+        <v>557</v>
+      </c>
+      <c r="H10" t="n">
+        <v>29800</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>107</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288519887_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>871537</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>871537</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette moderne sminkebord fungerer som et midtpunkt i dit soveværelse med sit smukke design og gode opbevaringsplads. Den slanke, rektangulære form giver et moderne look og kombinerer funktionalitet med stil til dit klædeområde. De indbyggede LED-spejllamper sikrer godt lys, hvilket gør det super nemt at pleje og style.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ:&lt;/b&gt; Dette sminkebord er lavet af konstrueret træ og er både stærkt og holdbart, perfekt til dit soveværelse. Den glatte overflade gør det nemt at placere i moderne rum. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Integrerede komponenter:&lt;/b&gt; Bordet har et fladt spejl til personlig pleje og LED-lamper, der sørger for godt lys. Den smarte knap gør det let at styre lyset. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle funktioner:&lt;/b&gt; Flere skuffer og en stor hylde giver dig mulighed for at opbevare dine ting ordentligt, mens det holder rummet ryddeligt. Det gennemtænkte design gør det nemt at bruge dagligt. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Alsidig brug:&lt;/b&gt; Perfekt til soveværelser eller klædeskabe, dette bord kan rumme mange genstande som kosmetik, tilbehør og plejeprodukter. Den slanke stil gør det til en god pasform i alle moderne rum og komplementerer indretningen i dit soveværelse. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Pleje &amp; vedligeholdelse:&lt;/b&gt; Tør det let af med en tør klud for at holde det pænt. Husk at tjekke spejllamperne og USB-opkoblingen med jævne mellemrum for at sikre, at bordet holder sig i topform.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 41 x 134,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 28,3 kg&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Strømkilde: USB&lt;/li&gt;&lt;li&gt;Lystype: Spejllamper&lt;/li&gt;&lt;li&gt;Med 2 skuffer&lt;/li&gt;&lt;li&gt;Planspejl&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Sminkebord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Der må kun bruges et certificeret DC 5V-input. Højere spænding kan forårsage overophedning og kan resultere i skader på enheden og potentiel risiko for brand. Tilslut ikke dette produkt til nogen form for strømforsyning, andet en den der er beskrevet i manualen, på typeskiltet, eller som er specifikt anbefalet af . Dette apparat må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring angående brugen af elektroniske apparater. Elektricitet er farlig. Skader og forkert installation, brug eller ændring (udskiftning af individuelle dele) kan medføre skader på enheden, hvilket kan resultere i elektrisk stød og personskader. Dette produkt må ikke betjenes i eksplosive omgivelser, såsom i nærheden af brandbare væsker, gasser og støv, eller over 50 grader celsius. Tænd ikke for produktet, hvis tilslutningskablet eller strømforsyningen er synligt beskadiget. Hvis armaturets eksterne fleksible kabel er beskadiget, må det kun udskiftes af producenten eller dennes serviceagent eller en lignende kvalificeret person for at undgå skader. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er nedkølede. Armaturets lyskilde kan ikke udskiftes; når lyskilden ikke længere virker, skal hele armaturet udskiftes. Kun til indendørs brug. Brug ikke dette produkt udenfor.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288519887_mo-im_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288519887_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288519887_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288519887_detail_en_hd_1.jpg, https://vdxl.im/8721288519887_detail_en_hd_2.jpg, https://vdxl.im/8721288519887_detail_en_hd_3.jpg, https://vdxl.im/8721288519887_detail_en_hd_4.jpg, https://vdxl.im/8721288519887_detail_en_hd_5.jpg, https://vdxl.im/8721288519887_detail_en_hd_6.jpg, https://vdxl.im/8721288519887_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>makeupbord-med-led-lys-80x41x134-5-cm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>871538</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8721288519894</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1029</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1379</v>
+      </c>
+      <c r="G11" t="n">
+        <v>602</v>
+      </c>
+      <c r="H11" t="n">
+        <v>29800</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>29</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288519894_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>871538</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>871538</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette moderne sminkebord fungerer som et midtpunkt i dit soveværelse med sit smukke design og gode opbevaringsplads. Den slanke, rektangulære form giver et moderne look og kombinerer funktionalitet med stil til dit klædeområde. De indbyggede LED-spejllamper sikrer godt lys, hvilket gør det super nemt at pleje og style.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ:&lt;/b&gt; Dette sminkebord er lavet af konstrueret træ og er både stærkt og holdbart, perfekt til dit soveværelse. Den glatte overflade gør det nemt at placere i moderne rum. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Integrerede komponenter:&lt;/b&gt; Bordet har et fladt spejl til personlig pleje og LED-lamper, der sørger for godt lys. Den smarte knap gør det let at styre lyset. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle funktioner:&lt;/b&gt; Flere skuffer og en stor hylde giver dig mulighed for at opbevare dine ting ordentligt, mens det holder rummet ryddeligt. Det gennemtænkte design gør det nemt at bruge dagligt. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Alsidig brug:&lt;/b&gt; Perfekt til soveværelser eller klædeskabe, dette bord kan rumme mange genstande som kosmetik, tilbehør og plejeprodukter. Den slanke stil gør det til en god pasform i alle moderne rum og komplementerer indretningen i dit soveværelse. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Pleje &amp; vedligeholdelse:&lt;/b&gt; Tør det let af med en tør klud for at holde det pænt. Husk at tjekke spejllamperne og USB-opkoblingen med jævne mellemrum for at sikre, at bordet holder sig i topform.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 41 x 134,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 28,3 kg&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Strømkilde: USB&lt;/li&gt;&lt;li&gt;Lystype: Spejllamper&lt;/li&gt;&lt;li&gt;Med 2 skuffer&lt;/li&gt;&lt;li&gt;Planspejl&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Sminkebord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Der må kun bruges et certificeret DC 5V-input. Højere spænding kan forårsage overophedning og kan resultere i skader på enheden og potentiel risiko for brand. Tilslut ikke dette produkt til nogen form for strømforsyning, andet en den der er beskrevet i manualen, på typeskiltet, eller som er specifikt anbefalet af . Dette apparat må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring angående brugen af elektroniske apparater. Elektricitet er farlig. Skader og forkert installation, brug eller ændring (udskiftning af individuelle dele) kan medføre skader på enheden, hvilket kan resultere i elektrisk stød og personskader. Dette produkt må ikke betjenes i eksplosive omgivelser, såsom i nærheden af brandbare væsker, gasser og støv, eller over 50 grader celsius. Tænd ikke for produktet, hvis tilslutningskablet eller strømforsyningen er synligt beskadiget. Hvis armaturets eksterne fleksible kabel er beskadiget, må det kun udskiftes af producenten eller dennes serviceagent eller en lignende kvalificeret person for at undgå skader. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er nedkølede. Armaturets lyskilde kan ikke udskiftes; når lyskilden ikke længere virker, skal hele armaturet udskiftes. Kun til indendørs brug. Brug ikke dette produkt udenfor.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288519894_mo-im_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288519894_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288519894_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288519894_detail_en_hd_1.jpg, https://vdxl.im/8721288519894_detail_en_hd_2.jpg, https://vdxl.im/8721288519894_detail_en_hd_3.jpg, https://vdxl.im/8721288519894_detail_en_hd_4.jpg, https://vdxl.im/8721288519894_detail_en_hd_5.jpg, https://vdxl.im/8721288519894_detail_en_hd_6.jpg, https://vdxl.im/8721288519894_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>makeupbord-med-led-lys-80x41x134-5-cm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>871539</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8721288519900</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>919</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1229</v>
+      </c>
+      <c r="G12" t="n">
+        <v>537</v>
+      </c>
+      <c r="H12" t="n">
+        <v>29800</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>200</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288519900_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>871539</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>871539</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette moderne sminkebord fungerer som et midtpunkt i dit soveværelse med sit smukke design og gode opbevaringsplads. Den slanke, rektangulære form giver et moderne look og kombinerer funktionalitet med stil til dit klædeområde. De indbyggede LED-spejllamper sikrer godt lys, hvilket gør det super nemt at pleje og style.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ:&lt;/b&gt; Dette sminkebord er lavet af konstrueret træ og er både stærkt og holdbart, perfekt til dit soveværelse. Den glatte overflade gør det nemt at placere i moderne rum. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Integrerede komponenter:&lt;/b&gt; Bordet har et fladt spejl til personlig pleje og LED-lamper, der sørger for godt lys. Den smarte knap gør det let at styre lyset. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle funktioner:&lt;/b&gt; Flere skuffer og en stor hylde giver dig mulighed for at opbevare dine ting ordentligt, mens det holder rummet ryddeligt. Det gennemtænkte design gør det nemt at bruge dagligt. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Alsidig brug:&lt;/b&gt; Perfekt til soveværelser eller klædeskabe, dette bord kan rumme mange genstande som kosmetik, tilbehør og plejeprodukter. Den slanke stil gør det til en god pasform i alle moderne rum og komplementerer indretningen i dit soveværelse. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Pleje &amp; vedligeholdelse:&lt;/b&gt; Tør det let af med en tør klud for at holde det pænt. Husk at tjekke spejllamperne og USB-opkoblingen med jævne mellemrum for at sikre, at bordet holder sig i topform.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 41 x 134,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 28,3 kg&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Strømkilde: USB&lt;/li&gt;&lt;li&gt;Lystype: Spejllamper&lt;/li&gt;&lt;li&gt;Med 2 skuffer&lt;/li&gt;&lt;li&gt;Planspejl&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Sminkebord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Der må kun bruges et certificeret DC 5V-input. Højere spænding kan forårsage overophedning og kan resultere i skader på enheden og potentiel risiko for brand. Tilslut ikke dette produkt til nogen form for strømforsyning, andet en den der er beskrevet i manualen, på typeskiltet, eller som er specifikt anbefalet af . Dette apparat må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring angående brugen af elektroniske apparater. Elektricitet er farlig. Skader og forkert installation, brug eller ændring (udskiftning af individuelle dele) kan medføre skader på enheden, hvilket kan resultere i elektrisk stød og personskader. Dette produkt må ikke betjenes i eksplosive omgivelser, såsom i nærheden af brandbare væsker, gasser og støv, eller over 50 grader celsius. Tænd ikke for produktet, hvis tilslutningskablet eller strømforsyningen er synligt beskadiget. Hvis armaturets eksterne fleksible kabel er beskadiget, må det kun udskiftes af producenten eller dennes serviceagent eller en lignende kvalificeret person for at undgå skader. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er nedkølede. Armaturets lyskilde kan ikke udskiftes; når lyskilden ikke længere virker, skal hele armaturet udskiftes. Kun til indendørs brug. Brug ikke dette produkt udenfor.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288519900_mo-im_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288519900_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288519900_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288519900_detail_en_hd_1.jpg, https://vdxl.im/8721288519900_detail_en_hd_2.jpg, https://vdxl.im/8721288519900_detail_en_hd_3.jpg, https://vdxl.im/8721288519900_detail_en_hd_4.jpg, https://vdxl.im/8721288519900_detail_en_hd_5.jpg, https://vdxl.im/8721288519900_detail_en_hd_6.jpg, https://vdxl.im/8721288519900_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-com_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3310494</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8721158430922</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2589</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3459</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1511</v>
+      </c>
+      <c r="H13" t="n">
+        <v>31950</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430922_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3310494</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3310494</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 85 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 80 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430922_m_en_hd_1.jpg, https://vdxl.im/8721158430922_a_en_hd_1.jpg, https://vdxl.im/8721158430922_g_en_hd_1.jpg, https://vdxl.im/8721158430922_g_en_hd_2.jpg, https://vdxl.im/8721158430922_g_en_hd_3.jpg, https://vdxl.im/8721158430922_g_en_hd_4.jpg, https://vdxl.im/8721158430922_g_en_hd_5.jpg, https://vdxl.im/8721158430922_g_en_hd_6.jpg, https://vdxl.im/8721158430922_g_en_hd_7.jpg, https://vdxl.im/8721158430922_g_en_hd_8.jpg, https://vdxl.im/8721158430922_g_en_hd_9.jpg, https://vdxl.im/8721158430922_g_en_hd_10.jpg, https://vdxl.im/8721158430922_g_en_hd_11.jpg, https://vdxl.im/8721158430922_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>80 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3310499</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8721158430977</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2659</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3549</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1552</v>
+      </c>
+      <c r="H14" t="n">
+        <v>32750</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430977_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3310499</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3310499</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkebrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkebrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430977_m_en_hd_1.jpg, https://vdxl.im/8721158430977_a_en_hd_1.jpg, https://vdxl.im/8721158430977_g_en_hd_1.jpg, https://vdxl.im/8721158430977_g_en_hd_2.jpg, https://vdxl.im/8721158430977_g_en_hd_3.jpg, https://vdxl.im/8721158430977_g_en_hd_4.jpg, https://vdxl.im/8721158430977_g_en_hd_5.jpg, https://vdxl.im/8721158430977_g_en_hd_6.jpg, https://vdxl.im/8721158430977_g_en_hd_7.jpg, https://vdxl.im/8721158430977_g_en_hd_8.jpg, https://vdxl.im/8721158430977_g_en_hd_9.jpg, https://vdxl.im/8721158430977_g_en_hd_10.jpg, https://vdxl.im/8721158430977_g_en_hd_11.jpg, https://vdxl.im/8721158430977_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mørkebrun</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>90 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3310500</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8721158430984</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2699</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3599</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1574</v>
+      </c>
+      <c r="H15" t="n">
+        <v>32750</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>12</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430984_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3310500</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3310500</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430984_m_en_hd_1.jpg, https://vdxl.im/8721158430984_a_en_hd_1.jpg, https://vdxl.im/8721158430984_g_en_hd_1.jpg, https://vdxl.im/8721158430984_g_en_hd_2.jpg, https://vdxl.im/8721158430984_g_en_hd_3.jpg, https://vdxl.im/8721158430984_g_en_hd_4.jpg, https://vdxl.im/8721158430984_g_en_hd_5.jpg, https://vdxl.im/8721158430984_g_en_hd_6.jpg, https://vdxl.im/8721158430984_g_en_hd_7.jpg, https://vdxl.im/8721158430984_g_en_hd_8.jpg, https://vdxl.im/8721158430984_g_en_hd_9.jpg, https://vdxl.im/8721158430984_g_en_hd_10.jpg, https://vdxl.im/8721158430984_g_en_hd_11.jpg, https://vdxl.im/8721158430984_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>90 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3310501</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8721158430991</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2479</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3309</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1445</v>
+      </c>
+      <c r="H16" t="n">
+        <v>32750</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430991_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3310501</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3310501</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få en bedre og afslappende nats søvn med denne seng med madras! Den er en indbydende tilføjelse til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og slidstærkt materiale: Polyesterstof tilbyder en kombination af blødhed, åndbarhed og holdbarhed, hvilket sikrer, at du oplever ultimativ komfort og hygge.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har lag af skum, der former sig efter din krop og aflaster trykket på følsomme søvnområder som nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelse om natten.&lt;/li&gt;&lt;li&gt;Ingen boxmadras nødvendig: Sengestellet har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boxmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Hovedgærdepuden er fyldt med PP-fiber for ultrablød og optimal komfort, hvilket giver dig fremragende rygstøtte, mens du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Stabile og holdbare ben: Denne seng understøttes af robuste ben, der sikrer stabilitet, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Denne sengestel har et lamelbundsdesign og inkluderer lamellerne.&lt;/li&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen fjernes eller åbnes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158430991_m_en_hd_1.jpg, https://vdxl.im/8721158430991_a_en_hd_1.jpg, https://vdxl.im/8721158430991_g_en_hd_1.jpg, https://vdxl.im/8721158430991_g_en_hd_2.jpg, https://vdxl.im/8721158430991_g_en_hd_3.jpg, https://vdxl.im/8721158430991_g_en_hd_4.jpg, https://vdxl.im/8721158430991_g_en_hd_5.jpg, https://vdxl.im/8721158430991_g_en_hd_6.jpg, https://vdxl.im/8721158430991_g_en_hd_7.jpg, https://vdxl.im/8721158430991_g_en_hd_8.jpg, https://vdxl.im/8721158430991_g_en_hd_9.jpg, https://vdxl.im/8721158430991_g_en_hd_10.jpg, https://vdxl.im/8721158430991_g_en_hd_11.jpg, https://vdxl.im/8721158430991_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>90 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3310502</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8721158431004</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2659</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3549</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1552</v>
+      </c>
+      <c r="H17" t="n">
+        <v>32750</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>10</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431004_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3310502</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3310502</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431004_m_en_hd_1.jpg, https://vdxl.im/8721158431004_a_en_hd_1.jpg, https://vdxl.im/8721158431004_g_en_hd_1.jpg, https://vdxl.im/8721158431004_g_en_hd_2.jpg, https://vdxl.im/8721158431004_g_en_hd_3.jpg, https://vdxl.im/8721158431004_g_en_hd_4.jpg, https://vdxl.im/8721158431004_g_en_hd_5.jpg, https://vdxl.im/8721158431004_g_en_hd_6.jpg, https://vdxl.im/8721158431004_g_en_hd_7.jpg, https://vdxl.im/8721158431004_g_en_hd_8.jpg, https://vdxl.im/8721158431004_g_en_hd_9.jpg, https://vdxl.im/8721158431004_g_en_hd_10.jpg, https://vdxl.im/8721158431004_g_en_hd_11.jpg, https://vdxl.im/8721158431004_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>90 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3310507</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>8721158431059</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2679</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3579</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1566</v>
+      </c>
+      <c r="H18" t="n">
+        <v>33450</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>17</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431059_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3310507</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3310507</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431059_m_en_hd_1.jpg, https://vdxl.im/8721158431059_a_en_hd_1.jpg, https://vdxl.im/8721158431059_g_en_hd_1.jpg, https://vdxl.im/8721158431059_g_en_hd_2.jpg, https://vdxl.im/8721158431059_g_en_hd_3.jpg, https://vdxl.im/8721158431059_g_en_hd_4.jpg, https://vdxl.im/8721158431059_g_en_hd_5.jpg, https://vdxl.im/8721158431059_g_en_hd_6.jpg, https://vdxl.im/8721158431059_g_en_hd_7.jpg, https://vdxl.im/8721158431059_g_en_hd_8.jpg, https://vdxl.im/8721158431059_g_en_hd_9.jpg, https://vdxl.im/8721158431059_g_en_hd_10.jpg, https://vdxl.im/8721158431059_g_en_hd_11.jpg, https://vdxl.im/8721158431059_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3310508</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>8721158431066</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3829</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1677</v>
+      </c>
+      <c r="H19" t="n">
+        <v>33450</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431066_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3310508</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3310508</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få en bedre og afslappende nats søvn med denne seng med madras! Den er en indbydende tilføjelse til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og slidstærkt materiale: Polyesterstof tilbyder en kombination af blødhed, åndbarhed og holdbarhed, hvilket sikrer, at du oplever ultimativ komfort og hygge.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har lag af skum, der former sig efter din krop og aflaster trykket på følsomme søvnområder som nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelse om natten.&lt;/li&gt;&lt;li&gt;Ingen boxmadras nødvendig: Sengestellet har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boxmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Hovedgærdepuden er fyldt med PP-fiber for ultrablød og optimal komfort, hvilket giver dig fremragende rygstøtte, mens du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Stabile og holdbare ben: Denne seng understøttes af robuste ben, der sikrer stabilitet, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Denne sengestel har et lamelbundsdesign og inkluderer lamellerne.&lt;/li&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen fjernes eller åbnes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431066_m_en_hd_1.jpg, https://vdxl.im/8721158431066_a_en_hd_1.jpg, https://vdxl.im/8721158431066_g_en_hd_1.jpg, https://vdxl.im/8721158431066_g_en_hd_2.jpg, https://vdxl.im/8721158431066_g_en_hd_3.jpg, https://vdxl.im/8721158431066_g_en_hd_4.jpg, https://vdxl.im/8721158431066_g_en_hd_5.jpg, https://vdxl.im/8721158431066_g_en_hd_6.jpg, https://vdxl.im/8721158431066_g_en_hd_7.jpg, https://vdxl.im/8721158431066_g_en_hd_8.jpg, https://vdxl.im/8721158431066_g_en_hd_9.jpg, https://vdxl.im/8721158431066_g_en_hd_10.jpg, https://vdxl.im/8721158431066_g_en_hd_11.jpg, https://vdxl.im/8721158431066_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3310509</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8721158431073</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2879</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3839</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1682</v>
+      </c>
+      <c r="H20" t="n">
+        <v>33450</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>19</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431073_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3310509</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3310509</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431073_m_en_hd_1.jpg, https://vdxl.im/8721158431073_a_en_hd_1.jpg, https://vdxl.im/8721158431073_g_en_hd_1.jpg, https://vdxl.im/8721158431073_g_en_hd_2.jpg, https://vdxl.im/8721158431073_g_en_hd_3.jpg, https://vdxl.im/8721158431073_g_en_hd_4.jpg, https://vdxl.im/8721158431073_g_en_hd_5.jpg, https://vdxl.im/8721158431073_g_en_hd_6.jpg, https://vdxl.im/8721158431073_g_en_hd_7.jpg, https://vdxl.im/8721158431073_g_en_hd_8.jpg, https://vdxl.im/8721158431073_g_en_hd_9.jpg, https://vdxl.im/8721158431073_g_en_hd_10.jpg, https://vdxl.im/8721158431073_g_en_hd_11.jpg, https://vdxl.im/8721158431073_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>90 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3310515</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>8721158431134</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3119</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4159</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1822</v>
+      </c>
+      <c r="H21" t="n">
+        <v>34600</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>16</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431134_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3310515</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3310515</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 105 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 100 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 100 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431134_m_en_hd_1.jpg, https://vdxl.im/8721158431134_a_en_hd_1.jpg, https://vdxl.im/8721158431134_g_en_hd_1.jpg, https://vdxl.im/8721158431134_g_en_hd_2.jpg, https://vdxl.im/8721158431134_g_en_hd_3.jpg, https://vdxl.im/8721158431134_g_en_hd_4.jpg, https://vdxl.im/8721158431134_g_en_hd_5.jpg, https://vdxl.im/8721158431134_g_en_hd_6.jpg, https://vdxl.im/8721158431134_g_en_hd_7.jpg, https://vdxl.im/8721158431134_g_en_hd_8.jpg, https://vdxl.im/8721158431134_g_en_hd_9.jpg, https://vdxl.im/8721158431134_g_en_hd_10.jpg, https://vdxl.im/8721158431134_g_en_hd_11.jpg, https://vdxl.im/8721158431134_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Creme</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>100 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3310516</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>8721158431141</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2969</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3959</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1737</v>
+      </c>
+      <c r="H22" t="n">
+        <v>34600</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>14</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431141_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3310516</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3310516</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 105 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 100 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 100 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431141_m_en_hd_1.jpg, https://vdxl.im/8721158431141_a_en_hd_1.jpg, https://vdxl.im/8721158431141_g_en_hd_1.jpg, https://vdxl.im/8721158431141_g_en_hd_2.jpg, https://vdxl.im/8721158431141_g_en_hd_3.jpg, https://vdxl.im/8721158431141_g_en_hd_4.jpg, https://vdxl.im/8721158431141_g_en_hd_5.jpg, https://vdxl.im/8721158431141_g_en_hd_6.jpg, https://vdxl.im/8721158431141_g_en_hd_7.jpg, https://vdxl.im/8721158431141_g_en_hd_8.jpg, https://vdxl.im/8721158431141_g_en_hd_9.jpg, https://vdxl.im/8721158431141_g_en_hd_10.jpg, https://vdxl.im/8721158431141_g_en_hd_11.jpg, https://vdxl.im/8721158431141_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>100 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3310517</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8721158431158</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3449</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4599</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="H23" t="n">
+        <v>36650</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>31</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431158_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3310517</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3310517</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 125 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 120 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 120 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431158_m_en_hd_1.jpg, https://vdxl.im/8721158431158_a_en_hd_1.jpg, https://vdxl.im/8721158431158_g_en_hd_1.jpg, https://vdxl.im/8721158431158_g_en_hd_2.jpg, https://vdxl.im/8721158431158_g_en_hd_3.jpg, https://vdxl.im/8721158431158_g_en_hd_4.jpg, https://vdxl.im/8721158431158_g_en_hd_5.jpg, https://vdxl.im/8721158431158_g_en_hd_6.jpg, https://vdxl.im/8721158431158_g_en_hd_7.jpg, https://vdxl.im/8721158431158_g_en_hd_8.jpg, https://vdxl.im/8721158431158_g_en_hd_9.jpg, https://vdxl.im/8721158431158_g_en_hd_10.jpg, https://vdxl.im/8721158431158_g_en_hd_11.jpg, https://vdxl.im/8721158431158_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>120 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3310518</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>8721158431165</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3249</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4339</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1898</v>
+      </c>
+      <c r="H24" t="n">
+        <v>36650</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>54</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431165_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>3310518</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>3310518</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 125 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 120 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 120 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431165_m_en_hd_1.jpg, https://vdxl.im/8721158431165_a_en_hd_1.jpg, https://vdxl.im/8721158431165_g_en_hd_1.jpg, https://vdxl.im/8721158431165_g_en_hd_2.jpg, https://vdxl.im/8721158431165_g_en_hd_3.jpg, https://vdxl.im/8721158431165_g_en_hd_4.jpg, https://vdxl.im/8721158431165_g_en_hd_5.jpg, https://vdxl.im/8721158431165_g_en_hd_6.jpg, https://vdxl.im/8721158431165_g_en_hd_7.jpg, https://vdxl.im/8721158431165_g_en_hd_8.jpg, https://vdxl.im/8721158431165_g_en_hd_9.jpg, https://vdxl.im/8721158431165_g_en_hd_10.jpg, https://vdxl.im/8721158431165_g_en_hd_11.jpg, https://vdxl.im/8721158431165_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>120 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3310519</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>8721158431172</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3789</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5059</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2214</v>
+      </c>
+      <c r="H25" t="n">
+        <v>36650</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>40</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431172_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>3310519</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>3310519</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 125 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 120 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 120 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431172_m_en_hd_1.jpg, https://vdxl.im/8721158431172_a_en_hd_1.jpg, https://vdxl.im/8721158431172_g_en_hd_1.jpg, https://vdxl.im/8721158431172_g_en_hd_2.jpg, https://vdxl.im/8721158431172_g_en_hd_3.jpg, https://vdxl.im/8721158431172_g_en_hd_4.jpg, https://vdxl.im/8721158431172_g_en_hd_5.jpg, https://vdxl.im/8721158431172_g_en_hd_6.jpg, https://vdxl.im/8721158431172_g_en_hd_7.jpg, https://vdxl.im/8721158431172_g_en_hd_8.jpg, https://vdxl.im/8721158431172_g_en_hd_9.jpg, https://vdxl.im/8721158431172_g_en_hd_10.jpg, https://vdxl.im/8721158431172_g_en_hd_11.jpg, https://vdxl.im/8721158431172_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>120 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3310524</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8721158431226</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3139</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4189</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1834</v>
+      </c>
+      <c r="H26" t="n">
+        <v>40250</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>15</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431226_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>3310524</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>3310524</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431226_m_en_hd_1.jpg, https://vdxl.im/8721158431226_a_en_hd_1.jpg, https://vdxl.im/8721158431226_g_en_hd_1.jpg, https://vdxl.im/8721158431226_g_en_hd_2.jpg, https://vdxl.im/8721158431226_g_en_hd_3.jpg, https://vdxl.im/8721158431226_g_en_hd_4.jpg, https://vdxl.im/8721158431226_g_en_hd_5.jpg, https://vdxl.im/8721158431226_g_en_hd_6.jpg, https://vdxl.im/8721158431226_g_en_hd_7.jpg, https://vdxl.im/8721158431226_g_en_hd_8.jpg, https://vdxl.im/8721158431226_g_en_hd_9.jpg, https://vdxl.im/8721158431226_g_en_hd_10.jpg, https://vdxl.im/8721158431226_g_en_hd_11.jpg, https://vdxl.im/8721158431226_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3310525</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>8721158431233</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>3149</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4199</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1841</v>
+      </c>
+      <c r="H27" t="n">
+        <v>40250</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>15</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431233_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>3310525</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3310525</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431233_m_en_hd_1.jpg, https://vdxl.im/8721158431233_a_en_hd_1.jpg, https://vdxl.im/8721158431233_g_en_hd_1.jpg, https://vdxl.im/8721158431233_g_en_hd_2.jpg, https://vdxl.im/8721158431233_g_en_hd_3.jpg, https://vdxl.im/8721158431233_g_en_hd_4.jpg, https://vdxl.im/8721158431233_g_en_hd_5.jpg, https://vdxl.im/8721158431233_g_en_hd_6.jpg, https://vdxl.im/8721158431233_g_en_hd_7.jpg, https://vdxl.im/8721158431233_g_en_hd_8.jpg, https://vdxl.im/8721158431233_g_en_hd_9.jpg, https://vdxl.im/8721158431233_g_en_hd_10.jpg, https://vdxl.im/8721158431233_g_en_hd_11.jpg, https://vdxl.im/8721158431233_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3310526</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>8721158431240</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>3539</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4719</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2065</v>
+      </c>
+      <c r="H28" t="n">
+        <v>40250</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>15</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431240_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>3310526</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>3310526</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431240_m_en_hd_1.jpg, https://vdxl.im/8721158431240_a_en_hd_1.jpg, https://vdxl.im/8721158431240_g_en_hd_1.jpg, https://vdxl.im/8721158431240_g_en_hd_2.jpg, https://vdxl.im/8721158431240_g_en_hd_3.jpg, https://vdxl.im/8721158431240_g_en_hd_4.jpg, https://vdxl.im/8721158431240_g_en_hd_5.jpg, https://vdxl.im/8721158431240_g_en_hd_6.jpg, https://vdxl.im/8721158431240_g_en_hd_7.jpg, https://vdxl.im/8721158431240_g_en_hd_8.jpg, https://vdxl.im/8721158431240_g_en_hd_9.jpg, https://vdxl.im/8721158431240_g_en_hd_10.jpg, https://vdxl.im/8721158431240_g_en_hd_11.jpg, https://vdxl.im/8721158431240_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3310528</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>8721158431264</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>3149</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4199</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1838</v>
+      </c>
+      <c r="H29" t="n">
+        <v>40250</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431264_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>3310528</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>3310528</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431264_m_en_hd_1.jpg, https://vdxl.im/8721158431264_a_en_hd_1.jpg, https://vdxl.im/8721158431264_g_en_hd_1.jpg, https://vdxl.im/8721158431264_g_en_hd_2.jpg, https://vdxl.im/8721158431264_g_en_hd_3.jpg, https://vdxl.im/8721158431264_g_en_hd_4.jpg, https://vdxl.im/8721158431264_g_en_hd_5.jpg, https://vdxl.im/8721158431264_g_en_hd_6.jpg, https://vdxl.im/8721158431264_g_en_hd_7.jpg, https://vdxl.im/8721158431264_g_en_hd_8.jpg, https://vdxl.im/8721158431264_g_en_hd_9.jpg, https://vdxl.im/8721158431264_g_en_hd_10.jpg, https://vdxl.im/8721158431264_g_en_hd_11.jpg, https://vdxl.im/8721158431264_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gråbrun</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3310530</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>8721158431288</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3119</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4159</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1822</v>
+      </c>
+      <c r="H30" t="n">
+        <v>40250</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>15</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431288_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>3310530</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>3310530</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431288_m_en_hd_1.jpg, https://vdxl.im/8721158431288_a_en_hd_1.jpg, https://vdxl.im/8721158431288_g_en_hd_1.jpg, https://vdxl.im/8721158431288_g_en_hd_2.jpg, https://vdxl.im/8721158431288_g_en_hd_3.jpg, https://vdxl.im/8721158431288_g_en_hd_4.jpg, https://vdxl.im/8721158431288_g_en_hd_5.jpg, https://vdxl.im/8721158431288_g_en_hd_6.jpg, https://vdxl.im/8721158431288_g_en_hd_7.jpg, https://vdxl.im/8721158431288_g_en_hd_8.jpg, https://vdxl.im/8721158431288_g_en_hd_9.jpg, https://vdxl.im/8721158431288_g_en_hd_10.jpg, https://vdxl.im/8721158431288_g_en_hd_11.jpg, https://vdxl.im/8721158431288_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Blå</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>140 x 190 cm</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3310531</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8721158431295</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>3429</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4579</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2002</v>
+      </c>
+      <c r="H31" t="n">
+        <v>41150</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>40</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431295_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>3310531</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>3310531</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431295_m_en_hd_1.jpg, https://vdxl.im/8721158431295_a_en_hd_1.jpg, https://vdxl.im/8721158431295_g_en_hd_1.jpg, https://vdxl.im/8721158431295_g_en_hd_2.jpg, https://vdxl.im/8721158431295_g_en_hd_3.jpg, https://vdxl.im/8721158431295_g_en_hd_4.jpg, https://vdxl.im/8721158431295_g_en_hd_5.jpg, https://vdxl.im/8721158431295_g_en_hd_6.jpg, https://vdxl.im/8721158431295_g_en_hd_7.jpg, https://vdxl.im/8721158431295_g_en_hd_8.jpg, https://vdxl.im/8721158431295_g_en_hd_9.jpg, https://vdxl.im/8721158431295_g_en_hd_10.jpg, https://vdxl.im/8721158431295_g_en_hd_11.jpg, https://vdxl.im/8721158431295_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3310532</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>8721158431301</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3469</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4629</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H32" t="n">
+        <v>41150</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>40</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431301_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>3310532</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>3310532</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431301_m_en_hd_1.jpg, https://vdxl.im/8721158431301_a_en_hd_1.jpg, https://vdxl.im/8721158431301_g_en_hd_1.jpg, https://vdxl.im/8721158431301_g_en_hd_2.jpg, https://vdxl.im/8721158431301_g_en_hd_3.jpg, https://vdxl.im/8721158431301_g_en_hd_4.jpg, https://vdxl.im/8721158431301_g_en_hd_5.jpg, https://vdxl.im/8721158431301_g_en_hd_6.jpg, https://vdxl.im/8721158431301_g_en_hd_7.jpg, https://vdxl.im/8721158431301_g_en_hd_8.jpg, https://vdxl.im/8721158431301_g_en_hd_9.jpg, https://vdxl.im/8721158431301_g_en_hd_10.jpg, https://vdxl.im/8721158431301_g_en_hd_11.jpg, https://vdxl.im/8721158431301_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3310533</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>8721158431318</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3639</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4859</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2125</v>
+      </c>
+      <c r="H33" t="n">
+        <v>41150</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>40</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431318_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>3310533</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>3310533</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431318_m_en_hd_1.jpg, https://vdxl.im/8721158431318_a_en_hd_1.jpg, https://vdxl.im/8721158431318_g_en_hd_1.jpg, https://vdxl.im/8721158431318_g_en_hd_2.jpg, https://vdxl.im/8721158431318_g_en_hd_3.jpg, https://vdxl.im/8721158431318_g_en_hd_4.jpg, https://vdxl.im/8721158431318_g_en_hd_5.jpg, https://vdxl.im/8721158431318_g_en_hd_6.jpg, https://vdxl.im/8721158431318_g_en_hd_7.jpg, https://vdxl.im/8721158431318_g_en_hd_8.jpg, https://vdxl.im/8721158431318_g_en_hd_9.jpg, https://vdxl.im/8721158431318_g_en_hd_10.jpg, https://vdxl.im/8721158431318_g_en_hd_11.jpg, https://vdxl.im/8721158431318_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>140 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3310545</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8721158431431</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>4259</v>
+      </c>
+      <c r="F34" t="n">
+        <v>5679</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2491</v>
+      </c>
+      <c r="H34" t="n">
+        <v>47750</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>18</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431431_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>3310545</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>3310545</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 185 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 180 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431431_m_en_hd_1.jpg, https://vdxl.im/8721158431431_a_en_hd_1.jpg, https://vdxl.im/8721158431431_g_en_hd_1.jpg, https://vdxl.im/8721158431431_g_en_hd_2.jpg, https://vdxl.im/8721158431431_g_en_hd_3.jpg, https://vdxl.im/8721158431431_g_en_hd_4.jpg, https://vdxl.im/8721158431431_g_en_hd_5.jpg, https://vdxl.im/8721158431431_g_en_hd_6.jpg, https://vdxl.im/8721158431431_g_en_hd_7.jpg, https://vdxl.im/8721158431431_g_en_hd_8.jpg, https://vdxl.im/8721158431431_g_en_hd_9.jpg, https://vdxl.im/8721158431431_g_en_hd_10.jpg, https://vdxl.im/8721158431431_g_en_hd_11.jpg, https://vdxl.im/8721158431431_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3310546</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8721158431448</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3839</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5119</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2245</v>
+      </c>
+      <c r="H35" t="n">
+        <v>47750</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>18</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431448_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>3310546</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>3310546</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 185 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 180 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431448_m_en_hd_1.jpg, https://vdxl.im/8721158431448_a_en_hd_1.jpg, https://vdxl.im/8721158431448_g_en_hd_1.jpg, https://vdxl.im/8721158431448_g_en_hd_2.jpg, https://vdxl.im/8721158431448_g_en_hd_3.jpg, https://vdxl.im/8721158431448_g_en_hd_4.jpg, https://vdxl.im/8721158431448_g_en_hd_5.jpg, https://vdxl.im/8721158431448_g_en_hd_6.jpg, https://vdxl.im/8721158431448_g_en_hd_7.jpg, https://vdxl.im/8721158431448_g_en_hd_8.jpg, https://vdxl.im/8721158431448_g_en_hd_9.jpg, https://vdxl.im/8721158431448_g_en_hd_10.jpg, https://vdxl.im/8721158431448_g_en_hd_11.jpg, https://vdxl.im/8721158431448_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>180 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3310552</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8721158431509</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4409</v>
+      </c>
+      <c r="F36" t="n">
+        <v>5879</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2578</v>
+      </c>
+      <c r="H36" t="n">
+        <v>51100</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431509_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>3310552</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>3310552</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 200 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 200 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431509_m_en_hd_1.jpg, https://vdxl.im/8721158431509_a_en_hd_1.jpg, https://vdxl.im/8721158431509_g_en_hd_1.jpg, https://vdxl.im/8721158431509_g_en_hd_2.jpg, https://vdxl.im/8721158431509_g_en_hd_3.jpg, https://vdxl.im/8721158431509_g_en_hd_4.jpg, https://vdxl.im/8721158431509_g_en_hd_5.jpg, https://vdxl.im/8721158431509_g_en_hd_6.jpg, https://vdxl.im/8721158431509_g_en_hd_7.jpg, https://vdxl.im/8721158431509_g_en_hd_8.jpg, https://vdxl.im/8721158431509_g_en_hd_9.jpg, https://vdxl.im/8721158431509_g_en_hd_10.jpg, https://vdxl.im/8721158431509_g_en_hd_11.jpg, https://vdxl.im/8721158431509_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lysegrå</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>200 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>3310553</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8721158431516</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4039</v>
+      </c>
+      <c r="F37" t="n">
+        <v>5389</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2362</v>
+      </c>
+      <c r="H37" t="n">
+        <v>51100</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>12</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431516_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>3310553</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>3310553</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 200 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 200 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431516_m_en_hd_1.jpg, https://vdxl.im/8721158431516_a_en_hd_1.jpg, https://vdxl.im/8721158431516_g_en_hd_1.jpg, https://vdxl.im/8721158431516_g_en_hd_2.jpg, https://vdxl.im/8721158431516_g_en_hd_3.jpg, https://vdxl.im/8721158431516_g_en_hd_4.jpg, https://vdxl.im/8721158431516_g_en_hd_5.jpg, https://vdxl.im/8721158431516_g_en_hd_6.jpg, https://vdxl.im/8721158431516_g_en_hd_7.jpg, https://vdxl.im/8721158431516_g_en_hd_8.jpg, https://vdxl.im/8721158431516_g_en_hd_9.jpg, https://vdxl.im/8721158431516_g_en_hd_10.jpg, https://vdxl.im/8721158431516_g_en_hd_11.jpg, https://vdxl.im/8721158431516_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mørkegrå</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>200 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>seng-med-madras-stof-2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3310554</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8721158431523</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4209</v>
+      </c>
+      <c r="F38" t="n">
+        <v>5619</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2457</v>
+      </c>
+      <c r="H38" t="n">
+        <v>51100</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>35</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431523_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3310554</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>3310554</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 205 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 200 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 200 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721158431523_m_en_hd_1.jpg, https://vdxl.im/8721158431523_a_en_hd_1.jpg, https://vdxl.im/8721158431523_g_en_hd_1.jpg, https://vdxl.im/8721158431523_g_en_hd_2.jpg, https://vdxl.im/8721158431523_g_en_hd_3.jpg, https://vdxl.im/8721158431523_g_en_hd_4.jpg, https://vdxl.im/8721158431523_g_en_hd_5.jpg, https://vdxl.im/8721158431523_g_en_hd_6.jpg, https://vdxl.im/8721158431523_g_en_hd_7.jpg, https://vdxl.im/8721158431523_g_en_hd_8.jpg, https://vdxl.im/8721158431523_g_en_hd_9.jpg, https://vdxl.im/8721158431523_g_en_hd_10.jpg, https://vdxl.im/8721158431523_g_en_hd_11.jpg, https://vdxl.im/8721158431523_g_en_hd_12.jpg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>200 x 200 cm</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3214503</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8721012404984</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>969</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1299</v>
+      </c>
+      <c r="G39" t="n">
+        <v>562</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7620</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>164</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012404984_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>3214503</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>3214503</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 100 x 30 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 30 x 2,5 x 15,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012404984_m_en_hd_1.jpg, https://vdxl.im/8721012404984_a_en_hd_1.jpg, https://vdxl.im/8721012404984_g_en_hd_1.jpg, https://vdxl.im/8721012404984_g_en_hd_2.jpg, https://vdxl.im/8721012404984_g_en_hd_3.jpg, https://vdxl.im/8721012404984_g_en_hd_4.jpg, https://vdxl.im/8721012404984_g_en_hd_5.jpg, https://vdxl.im/8721012404984_g_en_hd_6.jpg, https://vdxl.im/8721012404984_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sølv</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>100 x 30 cm</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3214506</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8721012405011</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>829</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1109</v>
+      </c>
+      <c r="G40" t="n">
+        <v>482</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6340</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>80</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405011_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3214506</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>3214506</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 75 x 30 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 30 x 2,5 x 15,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405011_m_en_hd_1.jpg, https://vdxl.im/8721012405011_a_en_hd_1.jpg, https://vdxl.im/8721012405011_g_en_hd_1.jpg, https://vdxl.im/8721012405011_g_en_hd_2.jpg, https://vdxl.im/8721012405011_g_en_hd_3.jpg, https://vdxl.im/8721012405011_g_en_hd_4.jpg, https://vdxl.im/8721012405011_g_en_hd_5.jpg, https://vdxl.im/8721012405011_g_en_hd_6.jpg, https://vdxl.im/8721012405011_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sølv</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>75 x 30 cm</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3214508</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8721012405035</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>889</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1189</v>
+      </c>
+      <c r="G41" t="n">
+        <v>515</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6620</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>21</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405035_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3214508</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>3214508</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 40 x 2,5 x 25 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405035_m_en_hd_1.jpg, https://vdxl.im/8721012405035_a_en_hd_1.jpg, https://vdxl.im/8721012405035_g_en_hd_1.jpg, https://vdxl.im/8721012405035_g_en_hd_2.jpg, https://vdxl.im/8721012405035_g_en_hd_3.jpg, https://vdxl.im/8721012405035_g_en_hd_4.jpg, https://vdxl.im/8721012405035_g_en_hd_5.jpg, https://vdxl.im/8721012405035_g_en_hd_6.jpg, https://vdxl.im/8721012405035_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sølv</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3214509</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8721012405042</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>689</v>
+      </c>
+      <c r="F42" t="n">
+        <v>919</v>
+      </c>
+      <c r="G42" t="n">
+        <v>400</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5020</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>85</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405042_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3214509</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3214509</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 50 x 30 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sølvfarvet&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med en børstet finish&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 30 x 2,5 x 15,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405042_m_en_hd_1.jpg, https://vdxl.im/8721012405042_a_en_hd_1.jpg, https://vdxl.im/8721012405042_g_en_hd_1.jpg, https://vdxl.im/8721012405042_g_en_hd_2.jpg, https://vdxl.im/8721012405042_g_en_hd_3.jpg, https://vdxl.im/8721012405042_g_en_hd_4.jpg, https://vdxl.im/8721012405042_g_en_hd_5.jpg, https://vdxl.im/8721012405042_g_en_hd_6.jpg, https://vdxl.im/8721012405042_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sølv</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>50 x 30 cm</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3214511</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8721012405066</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1009</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1349</v>
+      </c>
+      <c r="G43" t="n">
+        <v>587</v>
+      </c>
+      <c r="H43" t="n">
+        <v>9700</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>12</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405066_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3214511</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>3214511</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 100 x 40 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 40 x 2,5 x 25 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405066_m_en_hd_1.jpg, https://vdxl.im/8721012405066_a_en_hd_1.jpg, https://vdxl.im/8721012405066_g_en_hd_1.jpg, https://vdxl.im/8721012405066_g_en_hd_2.jpg, https://vdxl.im/8721012405066_g_en_hd_3.jpg, https://vdxl.im/8721012405066_g_en_hd_4.jpg, https://vdxl.im/8721012405066_g_en_hd_5.jpg, https://vdxl.im/8721012405066_g_en_hd_6.jpg, https://vdxl.im/8721012405066_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>100 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3214512</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8721012405073</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>999</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1339</v>
+      </c>
+      <c r="G44" t="n">
+        <v>583</v>
+      </c>
+      <c r="H44" t="n">
+        <v>7620</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>35</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405073_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3214512</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>3214512</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 100 x 30 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 30 x 2,5 x 15,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405073_m_en_hd_1.jpg, https://vdxl.im/8721012405073_a_en_hd_1.jpg, https://vdxl.im/8721012405073_g_en_hd_1.jpg, https://vdxl.im/8721012405073_g_en_hd_2.jpg, https://vdxl.im/8721012405073_g_en_hd_3.jpg, https://vdxl.im/8721012405073_g_en_hd_4.jpg, https://vdxl.im/8721012405073_g_en_hd_5.jpg, https://vdxl.im/8721012405073_g_en_hd_6.jpg, https://vdxl.im/8721012405073_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>100 x 30 cm</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3214517</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8721012405127</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>729</v>
+      </c>
+      <c r="F45" t="n">
+        <v>979</v>
+      </c>
+      <c r="G45" t="n">
+        <v>423</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6620</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>58</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405127_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3214517</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>3214517</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 50 x 40 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 40 x 2,5 x 25 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405127_m_en_hd_1.jpg, https://vdxl.im/8721012405127_a_en_hd_1.jpg, https://vdxl.im/8721012405127_g_en_hd_1.jpg, https://vdxl.im/8721012405127_g_en_hd_2.jpg, https://vdxl.im/8721012405127_g_en_hd_3.jpg, https://vdxl.im/8721012405127_g_en_hd_4.jpg, https://vdxl.im/8721012405127_g_en_hd_5.jpg, https://vdxl.im/8721012405127_g_en_hd_6.jpg, https://vdxl.im/8721012405127_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>50 x 40 cm</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>vaeghylder-2-stk-75x23-5-cm-rustfrit-stal-farvet</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3214518</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8721012405134</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>799</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1069</v>
+      </c>
+      <c r="G46" t="n">
+        <v>465</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5020</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>35</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405134_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3214518</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>3214518</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Disse væghylder har et praktisk design, og de bliver fokuspunktet i din stue, dit soveværelse mv.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærk og langtidsholdbar: Væghylden er fremstillet af rustfrit stål, så den er slidstærk, korrosionsbestandig og langtidsholdbar.&lt;/li&gt;&lt;li&gt;Pladsbesparende: Denne væghylde kan hænges på væggen for at give ekstra opbevaringsplads. Du kan dermed maksimere gulvpladsen og holde området ryddet.&lt;/li&gt;&lt;li&gt;Nem montering: Væghylden er nem at montere takket være det medfølgende monteringstilbehør.&lt;/li&gt;&lt;li&gt;Multifunktionel væghylde: Væghylden er velegnet til både udsmykning og opbevaring. Du kan bruge den til at fremvise dine kollektioner, bøger, billedrammer, planter, modeller eller cd'er i forskellige rum såsom i stuen eller på kontoret.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Væghylde:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 0,6 mm&lt;/li&gt;&lt;li&gt;Mål: 50 x 30 x 3 cm (L x B x T)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hyldebeslag:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Rustfrit stål med sort belægning&lt;/li&gt;&lt;li&gt;Tykkelse, rustfrit stål: 3 mm&lt;/li&gt;&lt;li&gt;Mål: 30 x 2,5 x 15,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Belastningskapacitet: 50 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x væghylde&lt;/li&gt;&lt;li&gt;4 x beslag&lt;/li&gt;&lt;li&gt;1 x skruenøgle&lt;/li&gt;&lt;li&gt;8 x skrue&lt;/li&gt;&lt;li&gt;8 x skrue med rawlplug&lt;/li&gt;&lt;li&gt;2 par handsker&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721012405134_m_en_hd_1.jpg, https://vdxl.im/8721012405134_a_en_hd_1.jpg, https://vdxl.im/8721012405134_g_en_hd_1.jpg, https://vdxl.im/8721012405134_g_en_hd_2.jpg, https://vdxl.im/8721012405134_g_en_hd_3.jpg, https://vdxl.im/8721012405134_g_en_hd_4.jpg, https://vdxl.im/8721012405134_g_en_hd_5.jpg, https://vdxl.im/8721012405134_g_en_hd_6.jpg, https://vdxl.im/8721012405134_g_en_hd_7.jpg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>50 x 30 cm</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>vaegskab-60x36-5x35-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>830116</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>8720845949570</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>479</v>
+      </c>
+      <c r="F47" t="n">
+        <v>639</v>
+      </c>
+      <c r="G47" t="n">
+        <v>278</v>
+      </c>
+      <c r="H47" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>15</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949570_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>830116</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>830116</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette vægskab er et dekorativt og praktisk supplement til din boligindretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Vægskabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Opbevaringsskabet optager ikke plads på gulvet. Du kan nemt hænge det på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 100 x 36,5 x 35 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949570_m_en_hd_1.jpg, https://vdxl.im/8720845949570_a_en_hd_1.jpg, https://vdxl.im/8720845949570_g_en_hd_1.jpg, https://vdxl.im/8720845949570_g_en_hd_2.jpg, https://vdxl.im/8720845949570_g_en_hd_3.jpg, https://vdxl.im/8720845949570_g_en_hd_4.jpg, https://vdxl.im/8720845949570_g_en_hd_5.jpg, https://vdxl.im/8720845949570_g_en_hd_6.jpg, https://vdxl.im/8720845949570_g_en_hd_7.jpg, https://vdxl.im/8720845949570_g_en_hd_8.jpg, https://vdxl.im/8720845949570_g_en_hd_9.jpg, https://vdxl.im/8720845949570_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>100 x 36.5 x 35 cm</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>vaegskab-60x36-5x35-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>830119</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>8720845949600</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>459</v>
+      </c>
+      <c r="F48" t="n">
+        <v>619</v>
+      </c>
+      <c r="G48" t="n">
+        <v>266</v>
+      </c>
+      <c r="H48" t="n">
+        <v>18900</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>7</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949600_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>830119</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>830119</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette vægskab er et dekorativt og praktisk supplement til din boligindretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Vægskabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Opbevaringsskabet optager ikke plads på gulvet. Du kan nemt hænge det på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 100 x 36,5 x 35 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949600_m_en_hd_1.jpg, https://vdxl.im/8720845949600_a_en_hd_1.jpg, https://vdxl.im/8720845949600_g_en_hd_1.jpg, https://vdxl.im/8720845949600_g_en_hd_2.jpg, https://vdxl.im/8720845949600_g_en_hd_3.jpg, https://vdxl.im/8720845949600_g_en_hd_4.jpg, https://vdxl.im/8720845949600_g_en_hd_5.jpg, https://vdxl.im/8720845949600_g_en_hd_6.jpg, https://vdxl.im/8720845949600_g_en_hd_7.jpg, https://vdxl.im/8720845949600_g_en_hd_8.jpg, https://vdxl.im/8720845949600_g_en_hd_9.jpg, https://vdxl.im/8720845949600_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>100 x 36.5 x 35 cm</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>vaegskab-60x36-5x35-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>830120</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>8720845949617</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>459</v>
+      </c>
+      <c r="F49" t="n">
+        <v>619</v>
+      </c>
+      <c r="G49" t="n">
+        <v>268</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19000</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>18</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949617_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>830120</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>830120</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette vægskab er et dekorativt og praktisk supplement til din boligindretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Vægskabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Opbevaringsskabet optager ikke plads på gulvet. Du kan nemt hænge det på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 100 x 36,5 x 35 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949617_m_en_hd_1.jpg, https://vdxl.im/8720845949617_a_en_hd_1.jpg, https://vdxl.im/8720845949617_g_en_hd_1.jpg, https://vdxl.im/8720845949617_g_en_hd_2.jpg, https://vdxl.im/8720845949617_g_en_hd_3.jpg, https://vdxl.im/8720845949617_g_en_hd_4.jpg, https://vdxl.im/8720845949617_g_en_hd_5.jpg, https://vdxl.im/8720845949617_g_en_hd_6.jpg, https://vdxl.im/8720845949617_g_en_hd_7.jpg, https://vdxl.im/8720845949617_g_en_hd_8.jpg, https://vdxl.im/8720845949617_g_en_hd_9.jpg, https://vdxl.im/8720845949617_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Betongrå</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>100 x 36.5 x 35 cm</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>vaegskab-60x36-5x35-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>830121</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>8720845949624</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>449</v>
+      </c>
+      <c r="F50" t="n">
+        <v>599</v>
+      </c>
+      <c r="G50" t="n">
+        <v>263</v>
+      </c>
+      <c r="H50" t="n">
+        <v>19110</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>18</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949624_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>830121</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>830121</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette vægskab er et dekorativt og praktisk supplement til din boligindretning.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Vægskabet giver god opbevaringsplads, så du kan holde dine forskellige ting og sager pænt organiseret og inden for nem rækkevidde.&lt;/li&gt;&lt;li&gt;Vægmonteret: Opbevaringsskabet optager ikke plads på gulvet. Du kan nemt hænge det på væggen.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sengebordet for at gøre din indretning smuk og personlig.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 100 x 36,5 x 35 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720845949624_m_en_hd_1.jpg, https://vdxl.im/8720845949624_a_en_hd_1.jpg, https://vdxl.im/8720845949624_g_en_hd_1.jpg, https://vdxl.im/8720845949624_g_en_hd_2.jpg, https://vdxl.im/8720845949624_g_en_hd_3.jpg, https://vdxl.im/8720845949624_g_en_hd_4.jpg, https://vdxl.im/8720845949624_g_en_hd_5.jpg, https://vdxl.im/8720845949624_g_en_hd_6.jpg, https://vdxl.im/8720845949624_g_en_hd_7.jpg, https://vdxl.im/8720845949624_g_en_hd_8.jpg, https://vdxl.im/8720845949624_g_en_hd_9.jpg, https://vdxl.im/8720845949624_g_en_hd_10.jpg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Røget eg</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>100 x 36.5 x 35 cm</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>vaegskab-60x36-5x35-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>879564</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8721288762900</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>479</v>
+      </c>
+      <c r="F51" t="n">
+        <v>639</v>
+      </c>
+      <c r="G51" t="n">
+        <v>279</v>
+      </c>
+      <c r="H51" t="n">
+        <v>16750</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>56</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288762900_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>879564</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>879564</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Det væghængte skab i konstrueret træ er et super valg for dem, der vil organisere deres rum med stil. Denne rektangulære vægmonterede løsning fungerer godt i stuer, soveværelser og gange. Med sit rustikke look viser skabet naturlig charme og passer godt ind i ethvert hjem. Det sparer gulvplads med sit smarte design og tilføjer lidt elegance, der kombinerer funktionalitet med flot udseende.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstruktion i konstrueret træ:&lt;/b&gt; Lavet af konstrueret træ, så det er stærkt og holdbart. Det betyder, at det holder i lang tid, og den grove tekstur ser fed ud og føles godt. Her får du balance mellem funktionalitet og stil.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vægmonteret design:&lt;/b&gt; Du kan let hænge dette skab op, hvilket udnytter den lodrette plads smart og frigiver gulvplads til andre ting. Ideelt til små rum, hvor pladsen skal bruges klogt. Plus, det gør rengøringen under skabet nemmere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hængslede døre:&lt;/b&gt; De robuste hængslede døre lavet af konstrueret træ åbner nemt, så du hurtigt kan komme til dine ting. De holder alt pænt gemt væk, så du får et ryddeligt look i rummet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;D-greb:&lt;/b&gt; Let tilgængelige D-greb gør det til en leg at åbne og lukke skabet. De guldfarvede håndtag giver ikke kun et godt greb, men tilføjer også lidt elegance til designet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse:&lt;/b&gt; At samle skabet er let, du skal bare bruge en skruetrækker og en boremaskine efter instruktionerne. Så kan du hurtigt nyde din nye opbevaringsløsning uden besvær.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 36.5 x 35 CM (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Vægskab&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288762900_mo-im_en_hd_1.jpg, https://vdxl.im/8721288762900_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288762900_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288762900_mo-im_en_hd_2.jpg, https://vdxl.im/8721288762900_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288762900_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288762900_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288762900_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288762900_detail_en_hd_1.jpg, https://vdxl.im/8721288762900_detail_en_hd_2.jpg, https://vdxl.im/8721288762900_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288762900_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>100 x 36.5 x 35 cm</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>vaegskab-60x36-5x35-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>879565</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>8721288762917</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>489</v>
+      </c>
+      <c r="F52" t="n">
+        <v>659</v>
+      </c>
+      <c r="G52" t="n">
+        <v>281</v>
+      </c>
+      <c r="H52" t="n">
+        <v>16750</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>82</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288762917_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>879565</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>879565</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Det væghængte skab i konstrueret træ er et super valg for dem, der vil organisere deres rum med stil. Denne rektangulære vægmonterede løsning fungerer godt i stuer, soveværelser og gange. Med sit rustikke look viser skabet naturlig charme og passer godt ind i ethvert hjem. Det sparer gulvplads med sit smarte design og tilføjer lidt elegance, der kombinerer funktionalitet med flot udseende.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstruktion i konstrueret træ:&lt;/b&gt; Lavet af konstrueret træ, så det er stærkt og holdbart. Det betyder, at det holder i lang tid, og den grove tekstur ser fed ud og føles godt. Her får du balance mellem funktionalitet og stil.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vægmonteret design:&lt;/b&gt; Du kan let hænge dette skab op, hvilket udnytter den lodrette plads smart og frigiver gulvplads til andre ting. Ideelt til små rum, hvor pladsen skal bruges klogt. Plus, det gør rengøringen under skabet nemmere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hængslede døre:&lt;/b&gt; De robuste hængslede døre lavet af konstrueret træ åbner nemt, så du hurtigt kan komme til dine ting. De holder alt pænt gemt væk, så du får et ryddeligt look i rummet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;D-greb:&lt;/b&gt; Let tilgængelige D-greb gør det til en leg at åbne og lukke skabet. De guldfarvede håndtag giver ikke kun et godt greb, men tilføjer også lidt elegance til designet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse:&lt;/b&gt; At samle skabet er let, du skal bare bruge en skruetrækker og en boremaskine efter instruktionerne. Så kan du hurtigt nyde din nye opbevaringsløsning uden besvær.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 36.5 x 35 CM (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Vægskab&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288762917_mo-im_en_hd_1.jpg, https://vdxl.im/8721288762917_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288762917_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288762917_mo-im_en_hd_2.jpg, https://vdxl.im/8721288762917_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288762917_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288762917_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288762917_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288762917_detail_en_hd_1.jpg, https://vdxl.im/8721288762917_detail_en_hd_2.jpg, https://vdxl.im/8721288762917_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288762917_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>100 x 36.5 x 35 cm</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>vaegskab-60x36-5x35-cm-konstrueret-trae-2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>879566</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>8721288762924</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>519</v>
+      </c>
+      <c r="F53" t="n">
+        <v>699</v>
+      </c>
+      <c r="G53" t="n">
+        <v>302</v>
+      </c>
+      <c r="H53" t="n">
+        <v>16750</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>59</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288762924_mo-im_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>879566</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>879566</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Det væghængte skab i konstrueret træ er et super valg for dem, der vil organisere deres rum med stil. Denne rektangulære vægmonterede løsning fungerer godt i stuer, soveværelser og gange. Med sit rustikke look viser skabet naturlig charme og passer godt ind i ethvert hjem. Det sparer gulvplads med sit smarte design og tilføjer lidt elegance, der kombinerer funktionalitet med flot udseende.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstruktion i konstrueret træ:&lt;/b&gt; Lavet af konstrueret træ, så det er stærkt og holdbart. Det betyder, at det holder i lang tid, og den grove tekstur ser fed ud og føles godt. Her får du balance mellem funktionalitet og stil.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Vægmonteret design:&lt;/b&gt; Du kan let hænge dette skab op, hvilket udnytter den lodrette plads smart og frigiver gulvplads til andre ting. Ideelt til små rum, hvor pladsen skal bruges klogt. Plus, det gør rengøringen under skabet nemmere.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Hængslede døre:&lt;/b&gt; De robuste hængslede døre lavet af konstrueret træ åbner nemt, så du hurtigt kan komme til dine ting. De holder alt pænt gemt væk, så du får et ryddeligt look i rummet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;D-greb:&lt;/b&gt; Let tilgængelige D-greb gør det til en leg at åbne og lukke skabet. De guldfarvede håndtag giver ikke kun et godt greb, men tilføjer også lidt elegance til designet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem vedligeholdelse:&lt;/b&gt; At samle skabet er let, du skal bare bruge en skruetrækker og en boremaskine efter instruktionerne. Så kan du hurtigt nyde din nye opbevaringsløsning uden besvær.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 100 x 36.5 x 35 CM (L x B x H)&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Vægskab&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8721288762924_mo-im_en_hd_1.jpg, https://vdxl.im/8721288762924_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288762924_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288762924_mo-im_en_hd_2.jpg, https://vdxl.im/8721288762924_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288762924_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288762924_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288762924_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288762924_detail_en_hd_1.jpg, https://vdxl.im/8721288762924_detail_en_hd_2.jpg, https://vdxl.im/8721288762924_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288762924_wbg-siz_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Størrelse</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>100 x 36.5 x 35 cm</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>tv-skabssaet-6-dele-konstrueret-trae-10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3114598</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>8720287107446</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2269</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3029</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1327</v>
+      </c>
+      <c r="H54" t="n">
+        <v>69360</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>55</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287107446_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>3114598</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>3114598</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette klassiske tv-skabssæt er designet til at blive fokuspunktet i dit rum takket være det trendy, men praktiske design.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Robust materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Tv-sættet giver rigelig med plads til at holde dine magasiner, dvd'er samt andre ting og sager pænt organiseret.&lt;/li&gt;&lt;li&gt;Væghængt design: Tv-møblet optager ikke gulvplads. Du kan nemt hænge det på væggen.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til brug i væggen er ikke inkluderet. Brug kun skruer og rawlplugs, der passer til dine vægge. Hvis du er usikker, så søg professionel rådgivning. Læs og følg hvert trin i instruktionen omhyggeligt.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;4 x tv-skab 80 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;li&gt;2 x tv-skab: 60 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287107446_m_en_hd_1.jpg, https://vdxl.im/8720287107446_a_en_hd_1.jpg, https://vdxl.im/8720287107446_g_en_hd_1.jpg, https://vdxl.im/8720287107446_g_en_hd_2.jpg, https://vdxl.im/8720287107446_g_en_hd_3.jpg, https://vdxl.im/8720287107446_g_en_hd_4.jpg, https://vdxl.im/8720287107446_g_en_hd_5.jpg, https://vdxl.im/8720287107446_g_en_hd_6.jpg, https://vdxl.im/8720287107446_g_en_hd_7.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663923940/test/Image%20with%20Text/8888%20engineered%20wood/DKengineeredwood.png</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>tv-skabssaet-6-dele-konstrueret-trae-10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3114603</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8720287107491</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1679</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2239</v>
+      </c>
+      <c r="G55" t="n">
+        <v>980</v>
+      </c>
+      <c r="H55" t="n">
+        <v>75380</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>110</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287107491_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>3114603</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>3114603</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette klassiske tv-skabssæt er designet til at blive fokuspunktet i dit rum takket være det trendy, men praktiske design.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Robust materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Tv-sættet giver rigelig med plads til at holde dine magasiner, dvd'er samt andre ting og sager pænt organiseret.&lt;/li&gt;&lt;li&gt;Væghængt design: Tv-møblet optager ikke gulvplads. Du kan nemt hænge det på væggen.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til brug i væggen er ikke inkluderet. Brug kun skruer og rawlplugs, der passer til dine vægge. Hvis du er usikker, så søg professionel rådgivning. Læs og følg hvert trin i instruktionen omhyggeligt.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;4 x tv-skab 80 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;li&gt;2 x tv-skab: 60 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287107491_m_en_hd_1.jpg, https://vdxl.im/8720287107491_a_en_hd_1.jpg, https://vdxl.im/8720287107491_g_en_hd_1.jpg, https://vdxl.im/8720287107491_g_en_hd_2.jpg, https://vdxl.im/8720287107491_g_en_hd_3.jpg, https://vdxl.im/8720287107491_g_en_hd_4.jpg, https://vdxl.im/8720287107491_g_en_hd_5.jpg, https://vdxl.im/8720287107491_g_en_hd_6.jpg, https://vdxl.im/8720287107491_g_en_hd_7.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663923940/test/Image%20with%20Text/8888%20engineered%20wood/DKengineeredwood.png</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Røget eg</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>tv-skabssaet-6-dele-konstrueret-trae-10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MERGE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3114604</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>8720287107507</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1849</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2469</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1079</v>
+      </c>
+      <c r="H56" t="n">
+        <v>73440</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>deny</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>58</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287107507_m_en_hd_1.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>3114604</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>3114604</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dette klassiske tv-skabssæt er designet til at blive fokuspunktet i dit rum takket være det trendy, men praktiske design.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Robust materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Tv-sættet giver rigelig med plads til at holde dine magasiner, dvd'er samt andre ting og sager pænt organiseret.&lt;/li&gt;&lt;li&gt;Væghængt design: Tv-møblet optager ikke gulvplads. Du kan nemt hænge det på væggen.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til brug i væggen er ikke inkluderet. Brug kun skruer og rawlplugs, der passer til dine vægge. Hvis du er usikker, så søg professionel rådgivning. Læs og følg hvert trin i instruktionen omhyggeligt.&lt;/li&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;4 x tv-skab 80 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;li&gt;2 x tv-skab: 60 x 30 x 30 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://vdxl.im/8720287107507_m_en_hd_1.jpg, https://vdxl.im/8720287107507_a_en_hd_1.jpg, https://vdxl.im/8720287107507_g_en_hd_1.jpg, https://vdxl.im/8720287107507_g_en_hd_2.jpg, https://vdxl.im/8720287107507_g_en_hd_3.jpg, https://vdxl.im/8720287107507_g_en_hd_4.jpg, https://vdxl.im/8720287107507_g_en_hd_5.jpg, https://vdxl.im/8720287107507_g_en_hd_6.jpg, https://vdxl.im/8720287107507_g_en_hd_7.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663923940/test/Image%20with%20Text/8888%20engineered%20wood/DKengineeredwood.png</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Bredde</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>80 cm</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Farve</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/matrixify_create_merge.xlsx
+++ b/output/matrixify_create_merge.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA56"/>
+  <dimension ref="A1:AA58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>sengeramme-med-sengegavl-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -566,25 +566,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4013110</t>
+          <t>3295549</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8721158317704</t>
+          <t>8721102855535</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1119</v>
+        <v>2389</v>
       </c>
       <c r="F2" t="n">
-        <v>1499</v>
+        <v>3189</v>
       </c>
       <c r="G2" t="n">
-        <v>652</v>
+        <v>1393</v>
       </c>
       <c r="H2" t="n">
-        <v>13100</v>
+        <v>56400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317704_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102855535_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4013110</t>
+          <t>3295549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -636,17 +636,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>4013110</t>
+          <t>3295549</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette sofabordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit sofabord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 98 x 58 x (42-43) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 580 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Anbefalet brug: sofabord&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sofabordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Sengerammen er fremstillet af konstrueret træ. Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion: Denne sengeramme tilbyder skuffer til at holde dine magasiner, bøger, legetøj og andre småting pænt organiserede.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Sengerammens sengegavl giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se fjernsyn.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale, sengeramme: Konstrueret træ&lt;/li&gt;&lt;li&gt;Materiale, lameller: Krydsfiner&lt;/li&gt;&lt;li&gt;Produktmål: 203 x 163 x 69 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Mål, hver skuffe: 82 x 28,5 x 19 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 160 x 200 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317704_a_en_hd_1.jpg, https://vdxl.im/8721158317704_g_en_hd_1.jpg, https://vdxl.im/8721158317704_g_en_hd_2.jpg, https://vdxl.im/8721158317704_g_en_hd_3.jpg, https://vdxl.im/8721158317704_g_en_hd_4.jpg, https://vdxl.im/8721158317704_g_en_hd_5.jpg, https://vdxl.im/8721158317704_g_en_hd_6.jpg, https://vdxl.im/8721158317704_g_en_hd_7.jpg, https://vdxl.im/8721158317704_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721102855535_m_en_hd_1.jpg, https://vdxl.im/8721102855535_a_en_hd_1.jpg, https://vdxl.im/8721102855535_g_en_hd_1.jpg, https://vdxl.im/8721102855535_g_en_hd_2.jpg, https://vdxl.im/8721102855535_g_en_hd_3.jpg, https://vdxl.im/8721102855535_g_en_hd_4.jpg, https://vdxl.im/8721102855535_g_en_hd_5.jpg, https://vdxl.im/8721102855535_g_en_hd_6.jpg, https://vdxl.im/8721102855535_g_en_hd_7.jpg, https://vdxl.im/8721102855535_g_en_hd_8.jpg, https://vdxl.im/8721102855535_g_en_hd_9.jpg</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Antracitgrå</t>
+          <t>Sort</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>98 x 58 x (42-43) cm</t>
+          <t>160 x 200 cm</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr"/>
@@ -675,7 +675,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>sengeramme-med-sengegavl-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -685,25 +685,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4013111</t>
+          <t>3295599</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8721158317711</t>
+          <t>8721102856037</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1119</v>
+        <v>1959</v>
       </c>
       <c r="F3" t="n">
-        <v>1499</v>
+        <v>2619</v>
       </c>
       <c r="G3" t="n">
-        <v>653</v>
+        <v>1141</v>
       </c>
       <c r="H3" t="n">
-        <v>13050</v>
+        <v>51500</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317711_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102856037_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4013111</t>
+          <t>3295599</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -755,17 +755,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>4013111</t>
+          <t>3295599</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette sofabordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit sofabord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 98 x 58 x (42-43) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 580 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Anbefalet brug: sofabord&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Samling påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sofabordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne sengeramme! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Sengerammen er fremstillet af konstrueret træ. Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengerammen er forsynet med en lamelbund for at give din madras støtte, og så den kan ånde.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion: Denne sengeramme tilbyder skuffer til at holde dine magasiner, bøger, legetøj og andre småting pænt organiserede.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Sengerammens sengegavl giver fremragende rygstøtte, når du sidder op i sengen for at læse eller se fjernsyn.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;En madras medfølger ikke. Vi tilbyder dog et bredt udvalg af madrasser. Du kan finde en matchende madras i vores webshop.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale, sengeramme: Konstrueret træ&lt;/li&gt;&lt;li&gt;Materiale, lameller: Krydsfiner&lt;/li&gt;&lt;li&gt;Produktmål: 193 x 138 x 69 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Mål, hver skuffe: 82 x 28,5 x 19 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 135 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317711_a_en_hd_1.jpg, https://vdxl.im/8721158317711_g_en_hd_1.jpg, https://vdxl.im/8721158317711_g_en_hd_2.jpg, https://vdxl.im/8721158317711_g_en_hd_3.jpg, https://vdxl.im/8721158317711_g_en_hd_4.jpg, https://vdxl.im/8721158317711_g_en_hd_5.jpg, https://vdxl.im/8721158317711_g_en_hd_6.jpg, https://vdxl.im/8721158317711_g_en_hd_7.jpg, https://vdxl.im/8721158317711_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721102856037_m_en_hd_1.jpg, https://vdxl.im/8721102856037_a_en_hd_1.jpg, https://vdxl.im/8721102856037_g_en_hd_1.jpg, https://vdxl.im/8721102856037_g_en_hd_2.jpg, https://vdxl.im/8721102856037_g_en_hd_3.jpg, https://vdxl.im/8721102856037_g_en_hd_4.jpg, https://vdxl.im/8721102856037_g_en_hd_5.jpg, https://vdxl.im/8721102856037_g_en_hd_6.jpg, https://vdxl.im/8721102856037_g_en_hd_7.jpg, https://vdxl.im/8721102856037_g_en_hd_8.jpg, https://vdxl.im/8721102856037_g_en_hd_9.jpg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Naturfarvet</t>
+          <t>Sonoma-eg</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>98 x 58 x (42-43) cm</t>
+          <t>135 x 190 cm</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -794,7 +794,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>sengeramme-med-sengegavl-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -804,25 +804,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4013116</t>
+          <t>3295604</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8721158317766</t>
+          <t>8721102856082</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1379</v>
+        <v>1879</v>
       </c>
       <c r="F4" t="n">
-        <v>1839</v>
+        <v>2509</v>
       </c>
       <c r="G4" t="n">
-        <v>802</v>
+        <v>1098</v>
       </c>
       <c r="H4" t="n">
-        <v>17800</v>
+        <v>48900</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -859,12 +859,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317766_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721102856082_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>4013116</t>
+          <t>3295604</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>4013116</t>
+          <t>3295604</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Få en bedre og bedre nats søvn med denne sengeramme! Den er en indbydende tilføjelse til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Sengestellet er lavet af lamelbund. Det lamelbundede træ er af exceptionel kvalitet med en glat overflade og har også styrke, stabilitet og modstandsdygtighed over for fugt.&lt;/li&gt;&lt;li&gt;Lamelbund for optimal støtte: Sengestellet er udstyret med en lamelbund for støtte og åndbarhed til din madras.&lt;/li&gt;&lt;li&gt;Opbevaringsfunktion: Dette sengestel tilbyder skuffer til at holde dine blade, bøger, legetøj og andre småting velorganiserede.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Sengebundens hovedgærde giver dig fremragende rygstøtte, når du sætter dig op i sengen for at læse eller se tv.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Denne sengeramme har et lamelbundsdesign og inkluderer lameller.&lt;/li&gt;&lt;li&gt;Der medfølger ikke en madras til denne seng. Vi tilbyder et varieret udvalg af madrasser. Du kan tjekke vores butik for en matchende madras. &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, sengeramme: Konstrueret træ&lt;/li&gt;&lt;li&gt;Materiale, lameller: Krydsfiner&lt;/li&gt;&lt;li&gt;Produktmål: 193 x 123 x 69 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Mål, hver skuffe: 82 x 28,5 x 19 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Passer til madrasstørrelse: 120 x 190 cm (B x L) (madras medfølger ikke)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317766_a_en_hd_1.jpg, https://vdxl.im/8721158317766_g_en_hd_1.jpg, https://vdxl.im/8721158317766_g_en_hd_2.jpg, https://vdxl.im/8721158317766_g_en_hd_3.jpg, https://vdxl.im/8721158317766_g_en_hd_4.jpg, https://vdxl.im/8721158317766_g_en_hd_5.jpg, https://vdxl.im/8721158317766_g_en_hd_6.jpg, https://vdxl.im/8721158317766_g_en_hd_7.jpg, https://vdxl.im/8721158317766_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8721102856082_m_en_hd_1.jpg, https://vdxl.im/8721102856082_a_en_hd_1.jpg, https://vdxl.im/8721102856082_g_en_hd_1.jpg, https://vdxl.im/8721102856082_g_en_hd_2.jpg, https://vdxl.im/8721102856082_g_en_hd_3.jpg, https://vdxl.im/8721102856082_g_en_hd_4.jpg, https://vdxl.im/8721102856082_g_en_hd_5.jpg, https://vdxl.im/8721102856082_g_en_hd_6.jpg, https://vdxl.im/8721102856082_g_en_hd_7.jpg, https://vdxl.im/8721102856082_g_en_hd_8.jpg, https://vdxl.im/8721102856082_g_en_hd_9.jpg</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Hvid</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>150 x 78 x (72-73) cm</t>
+          <t>120 x 190 cm</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -913,7 +913,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>havebaenk-110-cm-stal-og-wpc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -923,25 +923,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4013117</t>
+          <t>317142</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8721158317773</t>
+          <t>8720286662199</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>999</v>
+        <v>759</v>
       </c>
       <c r="F5" t="n">
-        <v>1339</v>
+        <v>1019</v>
       </c>
       <c r="G5" t="n">
-        <v>585</v>
+        <v>442</v>
       </c>
       <c r="H5" t="n">
-        <v>20560</v>
+        <v>8800</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -978,12 +978,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317773_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720286662199_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4013117</t>
+          <t>317142</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>4013117</t>
+          <t>317142</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne havebænk er både slidstærk og vejrbestandig, og den giver en komfortabel siddeplads.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Terrassebænken er fremstillet af stål og WPC (træplastkomposit), hvilket er en kombination af træ og plast. Den er derfor sikker og langtidsholdbar til udendørs brug. Den er et glimrende valg til enhver have eller andre uderum.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;&lt;strong&gt;Bemærk:&lt;/strong&gt; Vi anbefaler, at du beskytter dine udendørsmøbler med et vandtæt overtræk for at forlænge deres levetid.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Brun og sort&lt;/li&gt;&lt;li&gt;Materiale: Stål og WPC (træplastkomposit)&lt;/li&gt;&lt;li&gt;Mål: 110 x 39 x 45 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Vejrbestandigt&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;Hynde medfølger: Nej&lt;/li&gt;&lt;/ul&gt; Maks. 110 kg per sæde.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317773_a_en_hd_1.jpg, https://vdxl.im/8721158317773_g_en_hd_1.jpg, https://vdxl.im/8721158317773_g_en_hd_2.jpg, https://vdxl.im/8721158317773_g_en_hd_3.jpg, https://vdxl.im/8721158317773_g_en_hd_4.jpg, https://vdxl.im/8721158317773_g_en_hd_5.jpg, https://vdxl.im/8721158317773_g_en_hd_6.jpg, https://vdxl.im/8721158317773_g_en_hd_7.jpg, https://vdxl.im/8721158317773_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720286662199_m_en_hd_1.jpg, https://vdxl.im/8720286662199_a_en_hd_1.jpg, https://vdxl.im/8720286662199_g_en_hd_1.jpg, https://vdxl.im/8720286662199_g_en_hd_2.jpg, https://vdxl.im/8720286662199_g_en_hd_3.jpg, https://vdxl.im/8720286662199_g_en_hd_4.jpg</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1013,26 +1013,18 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Hvid</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>150 x 78 x (72-73) cm</t>
-        </is>
-      </c>
+          <t>Brun og sort</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>havebaenk-110-cm-stal-og-wpc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1042,25 +1034,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4013118</t>
+          <t>317141</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8721158317780</t>
+          <t>8720286662182</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>749</v>
       </c>
       <c r="F6" t="n">
-        <v>1619</v>
+        <v>999</v>
       </c>
       <c r="G6" t="n">
-        <v>704</v>
+        <v>434</v>
       </c>
       <c r="H6" t="n">
-        <v>17800</v>
+        <v>8800</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1078,7 +1070,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1097,12 +1089,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317780_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720286662182_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4013118</t>
+          <t>317141</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1112,17 +1104,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>4013118</t>
+          <t>317141</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracit&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne havebænk er både slidstærk og vejrbestandig, og den giver en komfortabel siddeplads.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Terrassebænken er fremstillet af stål og WPC (træplastkomposit), hvilket er en kombination af træ og plast. Den er derfor sikker og langtidsholdbar til udendørs brug. Den er et glimrende valg til enhver have eller andre uderum.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;&lt;strong&gt;Bemærk:&lt;/strong&gt; Vi anbefaler, at du beskytter dine udendørsmøbler med et vandtæt overtræk for at forlænge deres levetid.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stål og WPC (træplastkomposit)&lt;/li&gt;&lt;li&gt;Mål: 110 x 39 x 45 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Vejrbestandigt&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;Hynde medfølger: Nej&lt;/li&gt;&lt;/ul&gt; Maks. 110 kg per sæde.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317780_a_en_hd_1.jpg, https://vdxl.im/8721158317780_g_en_hd_1.jpg, https://vdxl.im/8721158317780_g_en_hd_2.jpg, https://vdxl.im/8721158317780_g_en_hd_3.jpg, https://vdxl.im/8721158317780_g_en_hd_4.jpg, https://vdxl.im/8721158317780_g_en_hd_5.jpg, https://vdxl.im/8721158317780_g_en_hd_6.jpg, https://vdxl.im/8721158317780_g_en_hd_7.jpg, https://vdxl.im/8721158317780_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720286662182_m_en_hd_1.jpg, https://vdxl.im/8720286662182_a_en_hd_1.jpg, https://vdxl.im/8720286662182_g_en_hd_1.jpg, https://vdxl.im/8720286662182_g_en_hd_2.jpg, https://vdxl.im/8720286662182_g_en_hd_3.jpg, https://vdxl.im/8720286662182_g_en_hd_4.jpg</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1132,26 +1124,18 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Antracitgrå</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>150 x 78 x (72-73) cm</t>
-        </is>
-      </c>
+          <t>Sort</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1161,25 +1145,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4013119</t>
+          <t>827341</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8721158317797</t>
+          <t>8720845909208</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1219</v>
+        <v>799</v>
       </c>
       <c r="F7" t="n">
-        <v>1629</v>
+        <v>1069</v>
       </c>
       <c r="G7" t="n">
-        <v>708</v>
+        <v>463</v>
       </c>
       <c r="H7" t="n">
-        <v>20560</v>
+        <v>23000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1197,7 +1181,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1216,12 +1200,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317797_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909208_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4013119</t>
+          <t>827341</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1231,17 +1215,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>4013119</t>
+          <t>827341</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 150 x 78 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 780 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Giv din indretning et strejf af moderne charme med dette sengebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. &lt;/li&gt;&lt;li&gt;God opbevaringsplads: Natbordet har skuffer med god plads til at holde dine bøger, multimedieapparater og andre ting inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sideskabet for at gøre din indretning smuk og personlig. &lt;/li&gt;&lt;li&gt;Metalfødder: Metalfødderne føjer en rolig stil til dit interiør, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, jern, aluminium&lt;/li&gt;&lt;li&gt;Mål: 40 x 35 x 47,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x sengeborde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317797_a_en_hd_1.jpg, https://vdxl.im/8721158317797_g_en_hd_1.jpg, https://vdxl.im/8721158317797_g_en_hd_2.jpg, https://vdxl.im/8721158317797_g_en_hd_3.jpg, https://vdxl.im/8721158317797_g_en_hd_4.jpg, https://vdxl.im/8721158317797_g_en_hd_5.jpg, https://vdxl.im/8721158317797_g_en_hd_6.jpg, https://vdxl.im/8721158317797_g_en_hd_7.jpg, https://vdxl.im/8721158317797_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845909208_m_en_hd_1.jpg, https://vdxl.im/8720845909208_a_en_hd_1.jpg, https://vdxl.im/8720845909208_g_en_hd_1.jpg, https://vdxl.im/8720845909208_g_en_hd_2.jpg, https://vdxl.im/8720845909208_g_en_hd_3.jpg, https://vdxl.im/8720845909208_g_en_hd_4.jpg, https://vdxl.im/8720845909208_g_en_hd_5.jpg, https://vdxl.im/8720845909208_g_en_hd_6.jpg, https://vdxl.im/8720845909208_g_en_hd_7.jpg, https://vdxl.im/8720845909208_g_en_hd_8.jpg, https://vdxl.im/8720845909208_g_en_hd_9.jpg, https://vdxl.im/8720845909208_g_en_hd_10.jpg, https://vdxl.im/8720845909208_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1251,17 +1235,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Naturfarvet</t>
+          <t>Hvid</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>150 x 78 x (72-73) cm</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr"/>
@@ -1270,7 +1254,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1280,25 +1264,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4013120</t>
+          <t>827345</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8721158317803</t>
+          <t>8720845909246</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1129</v>
+        <v>919</v>
       </c>
       <c r="F8" t="n">
-        <v>1509</v>
+        <v>1229</v>
       </c>
       <c r="G8" t="n">
-        <v>657</v>
+        <v>533</v>
       </c>
       <c r="H8" t="n">
-        <v>16200</v>
+        <v>23000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1316,7 +1300,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1335,12 +1319,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317803_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909246_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4013120</t>
+          <t>827345</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1350,17 +1334,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>4013120</t>
+          <t>827345</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 85 x 85 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 850 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Giv din indretning et strejf af moderne charme med dette sengebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. &lt;/li&gt;&lt;li&gt;God opbevaringsplads: Natbordet har skuffer med god plads til at holde dine bøger, multimedieapparater og andre ting inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sideskabet for at gøre din indretning smuk og personlig. &lt;/li&gt;&lt;li&gt;Metalfødder: Metalfødderne føjer en rolig stil til dit interiør, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid højglans&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, jern, aluminium&lt;/li&gt;&lt;li&gt;Mål: 40 x 35 x 47,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x sengeborde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317803_a_en_hd_1.jpg, https://vdxl.im/8721158317803_g_en_hd_1.jpg, https://vdxl.im/8721158317803_g_en_hd_2.jpg, https://vdxl.im/8721158317803_g_en_hd_3.jpg, https://vdxl.im/8721158317803_g_en_hd_4.jpg, https://vdxl.im/8721158317803_g_en_hd_5.jpg, https://vdxl.im/8721158317803_g_en_hd_6.jpg, https://vdxl.im/8721158317803_g_en_hd_7.jpg, https://vdxl.im/8721158317803_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845909246_m_en_hd_1.jpg, https://vdxl.im/8720845909246_a_en_hd_1.jpg, https://vdxl.im/8720845909246_g_en_hd_1.jpg, https://vdxl.im/8720845909246_g_en_hd_2.jpg, https://vdxl.im/8720845909246_g_en_hd_3.jpg, https://vdxl.im/8720845909246_g_en_hd_4.jpg, https://vdxl.im/8720845909246_g_en_hd_5.jpg, https://vdxl.im/8720845909246_g_en_hd_6.jpg, https://vdxl.im/8720845909246_g_en_hd_7.jpg, https://vdxl.im/8720845909246_g_en_hd_8.jpg, https://vdxl.im/8720845909246_g_en_hd_9.jpg, https://vdxl.im/8720845909246_g_en_hd_10.jpg, https://vdxl.im/8720845909246_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1370,17 +1354,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Hvid højglans</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>85 x 85 x (72-73) cm</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr"/>
@@ -1389,7 +1373,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sofabordben-edderkopform-stal</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1399,25 +1383,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4013123</t>
+          <t>827351</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8721158317834</t>
+          <t>8720845909307</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1169</v>
+        <v>609</v>
       </c>
       <c r="F9" t="n">
-        <v>1559</v>
+        <v>819</v>
       </c>
       <c r="G9" t="n">
-        <v>683</v>
+        <v>356</v>
       </c>
       <c r="H9" t="n">
-        <v>16100</v>
+        <v>23000</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1435,7 +1419,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1454,12 +1438,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317834_a_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909307_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4013123</t>
+          <t>827351</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1469,17 +1453,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4013123</t>
+          <t>827351</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette spisebordsben kombinerer form og funktion. Det er et ideelt valg til at personliggøre dit spisebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbart materiale: Dette metalbordben er lavet af pulverlakeret stål, hvilket gør det robust og holdbart.&lt;/li&gt;&lt;li&gt;Robust struktur: Møbelbordbenets edderkopformede design sikrer, at det kan bære en tung bordplade.&lt;/li&gt;&lt;li&gt;Praktisk design: Dette skrivebordsbordben har justerbare fodjusteringer, der sikrer stabilitet selv på ujævne gulve og minimerer ridser i gulvet. Derudover har beslaget forborede huller og medfølgende skruer, som kan bruges til at fastgøre benet til bordpladen (medfølger ikke), hvilket gør det nemt at samle.&lt;/li&gt;&lt;li&gt;Moderne æstetik: Bordbenet har rene linjer og et geometrisk design, der forbedrer møblets overordnede udseende. Og det passer godt til enhver bordplade i en passende størrelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Leveringen indeholder kun bordben, bordpladen er ikke inkluderet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Pulverlakeret stål&lt;/li&gt;&lt;li&gt;Samlede mål: 85 x 85 x (72-73) cm (B x D x H)&lt;/li&gt;&lt;li&gt;Rørmål: 80 x 40 x 1,2 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (1): 80 x 850 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Beslagmål (2): 80 x 250 x 4 mm (L x B x T)&lt;/li&gt;&lt;li&gt;Edderkopform&lt;/li&gt;&lt;li&gt;Med justerbare plastikniveauer&lt;/li&gt;&lt;li&gt;Anbefalet brug: spisebord&lt;/li&gt;&lt;li&gt;Skal samles: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leveringen indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x Spisebordben&lt;/li&gt;&lt;li&gt;Skruer (M5x18mm) til fastgørelse af ben med bordplade&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Giv din indretning et strejf af moderne charme med dette sengebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. &lt;/li&gt;&lt;li&gt;God opbevaringsplads: Natbordet har skuffer med god plads til at holde dine bøger, multimedieapparater og andre ting inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sideskabet for at gøre din indretning smuk og personlig. &lt;/li&gt;&lt;li&gt;Metalfødder: Metalfødderne føjer en rolig stil til dit interiør, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, jern, aluminium&lt;/li&gt;&lt;li&gt;Mål: 40 x 35 x 47,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x sengeborde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158317834_a_en_hd_1.jpg, https://vdxl.im/8721158317834_g_en_hd_1.jpg, https://vdxl.im/8721158317834_g_en_hd_2.jpg, https://vdxl.im/8721158317834_g_en_hd_3.jpg, https://vdxl.im/8721158317834_g_en_hd_4.jpg, https://vdxl.im/8721158317834_g_en_hd_5.jpg, https://vdxl.im/8721158317834_g_en_hd_6.jpg, https://vdxl.im/8721158317834_g_en_hd_7.jpg, https://vdxl.im/8721158317834_g_en_hd_8.jpg</t>
+          <t>https://vdxl.im/8720845909307_m_en_hd_1.jpg, https://vdxl.im/8720845909307_a_en_hd_1.jpg, https://vdxl.im/8720845909307_g_en_hd_1.jpg, https://vdxl.im/8720845909307_g_en_hd_2.jpg, https://vdxl.im/8720845909307_g_en_hd_3.jpg, https://vdxl.im/8720845909307_g_en_hd_4.jpg, https://vdxl.im/8720845909307_g_en_hd_5.jpg, https://vdxl.im/8720845909307_g_en_hd_6.jpg, https://vdxl.im/8720845909307_g_en_hd_7.jpg, https://vdxl.im/8720845909307_g_en_hd_8.jpg, https://vdxl.im/8720845909307_g_en_hd_9.jpg, https://vdxl.im/8720845909307_g_en_hd_10.jpg, https://vdxl.im/8720845909307_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1489,17 +1473,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Naturfarvet</t>
+          <t>Røget eg</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>85 x 85 x (72-73) cm</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr"/>
@@ -1508,7 +1492,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>makeupbord-med-led-lys-80x41x134-5-cm</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1518,25 +1502,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>871537</t>
+          <t>827353</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8721288519887</t>
+          <t>8720845909321</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>959</v>
+        <v>629</v>
       </c>
       <c r="F10" t="n">
-        <v>1279</v>
+        <v>839</v>
       </c>
       <c r="G10" t="n">
-        <v>557</v>
+        <v>368</v>
       </c>
       <c r="H10" t="n">
-        <v>29800</v>
+        <v>23000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1554,7 +1538,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1573,12 +1557,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721288519887_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909321_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>871537</t>
+          <t>827353</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1588,17 +1572,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>871537</t>
+          <t>827353</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette moderne sminkebord fungerer som et midtpunkt i dit soveværelse med sit smukke design og gode opbevaringsplads. Den slanke, rektangulære form giver et moderne look og kombinerer funktionalitet med stil til dit klædeområde. De indbyggede LED-spejllamper sikrer godt lys, hvilket gør det super nemt at pleje og style.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ:&lt;/b&gt; Dette sminkebord er lavet af konstrueret træ og er både stærkt og holdbart, perfekt til dit soveværelse. Den glatte overflade gør det nemt at placere i moderne rum. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Integrerede komponenter:&lt;/b&gt; Bordet har et fladt spejl til personlig pleje og LED-lamper, der sørger for godt lys. Den smarte knap gør det let at styre lyset. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle funktioner:&lt;/b&gt; Flere skuffer og en stor hylde giver dig mulighed for at opbevare dine ting ordentligt, mens det holder rummet ryddeligt. Det gennemtænkte design gør det nemt at bruge dagligt. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Alsidig brug:&lt;/b&gt; Perfekt til soveværelser eller klædeskabe, dette bord kan rumme mange genstande som kosmetik, tilbehør og plejeprodukter. Den slanke stil gør det til en god pasform i alle moderne rum og komplementerer indretningen i dit soveværelse. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Pleje &amp; vedligeholdelse:&lt;/b&gt; Tør det let af med en tør klud for at holde det pænt. Husk at tjekke spejllamperne og USB-opkoblingen med jævne mellemrum for at sikre, at bordet holder sig i topform.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 41 x 134,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 28,3 kg&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Strømkilde: USB&lt;/li&gt;&lt;li&gt;Lystype: Spejllamper&lt;/li&gt;&lt;li&gt;Med 2 skuffer&lt;/li&gt;&lt;li&gt;Planspejl&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Sminkebord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Der må kun bruges et certificeret DC 5V-input. Højere spænding kan forårsage overophedning og kan resultere i skader på enheden og potentiel risiko for brand. Tilslut ikke dette produkt til nogen form for strømforsyning, andet en den der er beskrevet i manualen, på typeskiltet, eller som er specifikt anbefalet af . Dette apparat må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring angående brugen af elektroniske apparater. Elektricitet er farlig. Skader og forkert installation, brug eller ændring (udskiftning af individuelle dele) kan medføre skader på enheden, hvilket kan resultere i elektrisk stød og personskader. Dette produkt må ikke betjenes i eksplosive omgivelser, såsom i nærheden af brandbare væsker, gasser og støv, eller over 50 grader celsius. Tænd ikke for produktet, hvis tilslutningskablet eller strømforsyningen er synligt beskadiget. Hvis armaturets eksterne fleksible kabel er beskadiget, må det kun udskiftes af producenten eller dennes serviceagent eller en lignende kvalificeret person for at undgå skader. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er nedkølede. Armaturets lyskilde kan ikke udskiftes; når lyskilden ikke længere virker, skal hele armaturet udskiftes. Kun til indendørs brug. Brug ikke dette produkt udenfor.</t>
+          <t>&lt;p&gt;Giv din indretning et strejf af moderne charme med dette sengebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. &lt;/li&gt;&lt;li&gt;God opbevaringsplads: Natbordet har skuffer med god plads til at holde dine bøger, multimedieapparater og andre ting inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sideskabet for at gøre din indretning smuk og personlig. &lt;/li&gt;&lt;li&gt;Metalfødder: Metalfødderne føjer en rolig stil til dit interiør, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, jern, aluminium&lt;/li&gt;&lt;li&gt;Mål: 40 x 35 x 47,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x sengeborde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721288519887_mo-im_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288519887_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288519887_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288519887_detail_en_hd_1.jpg, https://vdxl.im/8721288519887_detail_en_hd_2.jpg, https://vdxl.im/8721288519887_detail_en_hd_3.jpg, https://vdxl.im/8721288519887_detail_en_hd_4.jpg, https://vdxl.im/8721288519887_detail_en_hd_5.jpg, https://vdxl.im/8721288519887_detail_en_hd_6.jpg, https://vdxl.im/8721288519887_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288519887_wbg-com_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909321_m_en_hd_1.jpg, https://vdxl.im/8720845909321_a_en_hd_1.jpg, https://vdxl.im/8720845909321_g_en_hd_1.jpg, https://vdxl.im/8720845909321_g_en_hd_2.jpg, https://vdxl.im/8720845909321_g_en_hd_3.jpg, https://vdxl.im/8720845909321_g_en_hd_4.jpg, https://vdxl.im/8720845909321_g_en_hd_5.jpg, https://vdxl.im/8720845909321_g_en_hd_6.jpg, https://vdxl.im/8720845909321_g_en_hd_7.jpg, https://vdxl.im/8720845909321_g_en_hd_8.jpg, https://vdxl.im/8720845909321_g_en_hd_9.jpg, https://vdxl.im/8720845909321_g_en_hd_10.jpg, https://vdxl.im/8720845909321_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1608,18 +1592,26 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Gammelt træ</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>makeupbord-med-led-lys-80x41x134-5-cm</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1629,25 +1621,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>871538</t>
+          <t>827347</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8721288519894</t>
+          <t>8720845909260</t>
         </is>
       </c>
       <c r="E11" t="n">
+        <v>769</v>
+      </c>
+      <c r="F11" t="n">
         <v>1029</v>
       </c>
-      <c r="F11" t="n">
-        <v>1379</v>
-      </c>
       <c r="G11" t="n">
-        <v>602</v>
+        <v>447</v>
       </c>
       <c r="H11" t="n">
-        <v>29800</v>
+        <v>23000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1665,7 +1657,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1684,12 +1676,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721288519894_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909260_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>871538</t>
+          <t>827347</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1699,17 +1691,17 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>871538</t>
+          <t>827347</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette moderne sminkebord fungerer som et midtpunkt i dit soveværelse med sit smukke design og gode opbevaringsplads. Den slanke, rektangulære form giver et moderne look og kombinerer funktionalitet med stil til dit klædeområde. De indbyggede LED-spejllamper sikrer godt lys, hvilket gør det super nemt at pleje og style.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ:&lt;/b&gt; Dette sminkebord er lavet af konstrueret træ og er både stærkt og holdbart, perfekt til dit soveværelse. Den glatte overflade gør det nemt at placere i moderne rum. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Integrerede komponenter:&lt;/b&gt; Bordet har et fladt spejl til personlig pleje og LED-lamper, der sørger for godt lys. Den smarte knap gør det let at styre lyset. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle funktioner:&lt;/b&gt; Flere skuffer og en stor hylde giver dig mulighed for at opbevare dine ting ordentligt, mens det holder rummet ryddeligt. Det gennemtænkte design gør det nemt at bruge dagligt. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Alsidig brug:&lt;/b&gt; Perfekt til soveværelser eller klædeskabe, dette bord kan rumme mange genstande som kosmetik, tilbehør og plejeprodukter. Den slanke stil gør det til en god pasform i alle moderne rum og komplementerer indretningen i dit soveværelse. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Pleje &amp; vedligeholdelse:&lt;/b&gt; Tør det let af med en tør klud for at holde det pænt. Husk at tjekke spejllamperne og USB-opkoblingen med jævne mellemrum for at sikre, at bordet holder sig i topform.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 41 x 134,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 28,3 kg&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Strømkilde: USB&lt;/li&gt;&lt;li&gt;Lystype: Spejllamper&lt;/li&gt;&lt;li&gt;Med 2 skuffer&lt;/li&gt;&lt;li&gt;Planspejl&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Sminkebord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Der må kun bruges et certificeret DC 5V-input. Højere spænding kan forårsage overophedning og kan resultere i skader på enheden og potentiel risiko for brand. Tilslut ikke dette produkt til nogen form for strømforsyning, andet en den der er beskrevet i manualen, på typeskiltet, eller som er specifikt anbefalet af . Dette apparat må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring angående brugen af elektroniske apparater. Elektricitet er farlig. Skader og forkert installation, brug eller ændring (udskiftning af individuelle dele) kan medføre skader på enheden, hvilket kan resultere i elektrisk stød og personskader. Dette produkt må ikke betjenes i eksplosive omgivelser, såsom i nærheden af brandbare væsker, gasser og støv, eller over 50 grader celsius. Tænd ikke for produktet, hvis tilslutningskablet eller strømforsyningen er synligt beskadiget. Hvis armaturets eksterne fleksible kabel er beskadiget, må det kun udskiftes af producenten eller dennes serviceagent eller en lignende kvalificeret person for at undgå skader. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er nedkølede. Armaturets lyskilde kan ikke udskiftes; når lyskilden ikke længere virker, skal hele armaturet udskiftes. Kun til indendørs brug. Brug ikke dette produkt udenfor.</t>
+          <t>&lt;p&gt;Giv din indretning et strejf af moderne charme med dette sengebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. &lt;/li&gt;&lt;li&gt;God opbevaringsplads: Natbordet har skuffer med god plads til at holde dine bøger, multimedieapparater og andre ting inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sideskabet for at gøre din indretning smuk og personlig. &lt;/li&gt;&lt;li&gt;Metalfødder: Metalfødderne føjer en rolig stil til dit interiør, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, jern, aluminium&lt;/li&gt;&lt;li&gt;Mål: 40 x 35 x 47,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x sengeborde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721288519894_mo-im_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288519894_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288519894_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288519894_detail_en_hd_1.jpg, https://vdxl.im/8721288519894_detail_en_hd_2.jpg, https://vdxl.im/8721288519894_detail_en_hd_3.jpg, https://vdxl.im/8721288519894_detail_en_hd_4.jpg, https://vdxl.im/8721288519894_detail_en_hd_5.jpg, https://vdxl.im/8721288519894_detail_en_hd_6.jpg, https://vdxl.im/8721288519894_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288519894_wbg-com_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909260_m_en_hd_1.jpg, https://vdxl.im/8720845909260_a_en_hd_1.jpg, https://vdxl.im/8720845909260_g_en_hd_1.jpg, https://vdxl.im/8720845909260_g_en_hd_2.jpg, https://vdxl.im/8720845909260_g_en_hd_3.jpg, https://vdxl.im/8720845909260_g_en_hd_4.jpg, https://vdxl.im/8720845909260_g_en_hd_5.jpg, https://vdxl.im/8720845909260_g_en_hd_6.jpg, https://vdxl.im/8720845909260_g_en_hd_7.jpg, https://vdxl.im/8720845909260_g_en_hd_8.jpg, https://vdxl.im/8720845909260_g_en_hd_9.jpg, https://vdxl.im/8720845909260_g_en_hd_10.jpg, https://vdxl.im/8720845909260_g_en_hd_11.jpg</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1719,18 +1711,26 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>artisan eg</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>makeupbord-med-led-lys-80x41x134-5-cm</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1740,25 +1740,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>871539</t>
+          <t>827349</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8721288519900</t>
+          <t>8720845909284</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>919</v>
+        <v>759</v>
       </c>
       <c r="F12" t="n">
-        <v>1229</v>
+        <v>1019</v>
       </c>
       <c r="G12" t="n">
-        <v>537</v>
+        <v>444</v>
       </c>
       <c r="H12" t="n">
-        <v>29800</v>
+        <v>23000</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>200</v>
+        <v>14</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721288519900_mo-im_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909284_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>871539</t>
+          <t>827349</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>871539</t>
+          <t>827349</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Dette moderne sminkebord fungerer som et midtpunkt i dit soveværelse med sit smukke design og gode opbevaringsplads. Den slanke, rektangulære form giver et moderne look og kombinerer funktionalitet med stil til dit klædeområde. De indbyggede LED-spejllamper sikrer godt lys, hvilket gør det super nemt at pleje og style.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ:&lt;/b&gt; Dette sminkebord er lavet af konstrueret træ og er både stærkt og holdbart, perfekt til dit soveværelse. Den glatte overflade gør det nemt at placere i moderne rum. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Integrerede komponenter:&lt;/b&gt; Bordet har et fladt spejl til personlig pleje og LED-lamper, der sørger for godt lys. Den smarte knap gør det let at styre lyset. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Funktionelle funktioner:&lt;/b&gt; Flere skuffer og en stor hylde giver dig mulighed for at opbevare dine ting ordentligt, mens det holder rummet ryddeligt. Det gennemtænkte design gør det nemt at bruge dagligt. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Alsidig brug:&lt;/b&gt; Perfekt til soveværelser eller klædeskabe, dette bord kan rumme mange genstande som kosmetik, tilbehør og plejeprodukter. Den slanke stil gør det til en god pasform i alle moderne rum og komplementerer indretningen i dit soveværelse. &lt;/li&gt; &lt;li&gt;&lt;b&gt;Pleje &amp; vedligeholdelse:&lt;/b&gt; Tør det let af med en tør klud for at holde det pænt. Husk at tjekke spejllamperne og USB-opkoblingen med jævne mellemrum for at sikre, at bordet holder sig i topform.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 41 x 134,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 28,3 kg&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Strømkilde: USB&lt;/li&gt;&lt;li&gt;Lystype: Spejllamper&lt;/li&gt;&lt;li&gt;Med 2 skuffer&lt;/li&gt;&lt;li&gt;Planspejl&lt;/li&gt;&lt;li&gt;Med 2 hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Sminkebord&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt; Der må kun bruges et certificeret DC 5V-input. Højere spænding kan forårsage overophedning og kan resultere i skader på enheden og potentiel risiko for brand. Tilslut ikke dette produkt til nogen form for strømforsyning, andet en den der er beskrevet i manualen, på typeskiltet, eller som er specifikt anbefalet af . Dette apparat må ikke bruges af børn under 14 år, eller af personer med nedsatte fysiske, sensoriske eller mentale evner eller manglende erfaring angående brugen af elektroniske apparater. Elektricitet er farlig. Skader og forkert installation, brug eller ændring (udskiftning af individuelle dele) kan medføre skader på enheden, hvilket kan resultere i elektrisk stød og personskader. Dette produkt må ikke betjenes i eksplosive omgivelser, såsom i nærheden af brandbare væsker, gasser og støv, eller over 50 grader celsius. Tænd ikke for produktet, hvis tilslutningskablet eller strømforsyningen er synligt beskadiget. Hvis armaturets eksterne fleksible kabel er beskadiget, må det kun udskiftes af producenten eller dennes serviceagent eller en lignende kvalificeret person for at undgå skader. Sluk for strømmen under installation og vedligeholdelse. Sørg for, at pærerne er nedkølede. Armaturets lyskilde kan ikke udskiftes; når lyskilden ikke længere virker, skal hele armaturet udskiftes. Kun til indendørs brug. Brug ikke dette produkt udenfor.</t>
+          <t>&lt;p&gt;Giv din indretning et strejf af moderne charme med dette sengebord.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. &lt;/li&gt;&lt;li&gt;God opbevaringsplads: Natbordet har skuffer med god plads til at holde dine bøger, multimedieapparater og andre ting inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Plads til dekorationer: Du kan også stille dine yndlingsbilleder, dekorationer eller blomster oven på sideskabet for at gøre din indretning smuk og personlig. &lt;/li&gt;&lt;li&gt;Metalfødder: Metalfødderne føjer en rolig stil til dit interiør, samtidig med at de giver stabilitet.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Betongrå&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, jern, aluminium&lt;/li&gt;&lt;li&gt;Mål: 40 x 35 x 47,5 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;2 x sengeborde&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721288519900_mo-im_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288519900_mo-im-da_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288519900_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288519900_detail_en_hd_1.jpg, https://vdxl.im/8721288519900_detail_en_hd_2.jpg, https://vdxl.im/8721288519900_detail_en_hd_3.jpg, https://vdxl.im/8721288519900_detail_en_hd_4.jpg, https://vdxl.im/8721288519900_detail_en_hd_5.jpg, https://vdxl.im/8721288519900_detail_en_hd_6.jpg, https://vdxl.im/8721288519900_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288519900_wbg-com_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845909284_m_en_hd_1.jpg, https://vdxl.im/8720845909284_a_en_hd_1.jpg, https://vdxl.im/8720845909284_g_en_hd_1.jpg, https://vdxl.im/8720845909284_g_en_hd_2.jpg, https://vdxl.im/8720845909284_g_en_hd_3.jpg, https://vdxl.im/8720845909284_g_en_hd_4.jpg, https://vdxl.im/8720845909284_g_en_hd_5.jpg, https://vdxl.im/8720845909284_g_en_hd_6.jpg, https://vdxl.im/8720845909284_g_en_hd_7.jpg, https://vdxl.im/8720845909284_g_en_hd_8.jpg, https://vdxl.im/8720845909284_g_en_hd_9.jpg, https://vdxl.im/8720845909284_g_en_hd_10.jpg, https://vdxl.im/8720845909284_g_en_hd_11.jpg, https://vdxl.im/8720845909284_g_en_hd_12.jpg</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1830,18 +1830,26 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Sort eg</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+          <t>Betongrå</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Antal i pakke</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1851,25 +1859,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3310494</t>
+          <t>882044</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8721158430922</t>
+          <t>8721288916419</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2589</v>
+        <v>879</v>
       </c>
       <c r="F13" t="n">
-        <v>3459</v>
+        <v>1179</v>
       </c>
       <c r="G13" t="n">
-        <v>1511</v>
+        <v>511</v>
       </c>
       <c r="H13" t="n">
-        <v>31950</v>
+        <v>22910</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1887,7 +1895,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1906,12 +1914,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430922_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288916419_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3310494</t>
+          <t>882044</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1921,17 +1929,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3310494</t>
+          <t>882044</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 85 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 80 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 80 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette moderne natbord, der måler 40 x 35 x 47,5 cm, er en vigtig tilføjelse til ethvert soveværelse. Det har en rustik stil, der blander funktionalitet og charme, og giver dig plads til at organisere lamper, vækkeure og personlige ting. Det er lavet af konstrueret træ med en mat finish, der gør, at det passer godt ind i forskellige indretningsstile.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ&lt;/b&gt; Natbordet er lavet i konstrueret træ, som er holdbart og nemt at vedligeholde. Det har en glat overflade, der ser godt ud i enhver indretning, samtidig med at det sikrer lang holdbarhed. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionel opbevaring&lt;/b&gt; Med traditionelt design tilbyder dette natbord skuffer, der er nemme at åbne med et håndtag. Her er der god plads til at holde alt i orden, så du har hvad du skal bruge indenfor rækkevidde. Det tilfører dit rum både stil og praktisk funktion.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Sleek taperede ben&lt;/b&gt; De taperede stålbene løfter natbordet op fra gulvet, så det ikke samler støv og tilfører et elegant look. Deres matte finish forstærker det samlede design og sikrer, at bordet står stabilt. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Velegnet til indendørs brug&lt;/b&gt; Specielt designet til soveværelser, passer dette natbord ind som en stilfuld tilføjelse. Dets mål og funktion gør, at det nemt passer ved siden af enhver seng eller sofa og hjælper med at skabe et ordenligt miljø. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Samling kræves&lt;/b&gt; Det kræver samling af to personer og en skruetrækker. Grundlæggende værktøjer sørger for, at du hurtigt kan samle det, så natbordet er klar til brug. De klare instruktioner sikrer, at det holder godt i længden.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 40 x 35 x 47,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Dimensioner af hver hylde: 40 x 30 x 18.5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;Med 4 skuffer&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430922_m_en_hd_1.jpg, https://vdxl.im/8721158430922_a_en_hd_1.jpg, https://vdxl.im/8721158430922_g_en_hd_1.jpg, https://vdxl.im/8721158430922_g_en_hd_2.jpg, https://vdxl.im/8721158430922_g_en_hd_3.jpg, https://vdxl.im/8721158430922_g_en_hd_4.jpg, https://vdxl.im/8721158430922_g_en_hd_5.jpg, https://vdxl.im/8721158430922_g_en_hd_6.jpg, https://vdxl.im/8721158430922_g_en_hd_7.jpg, https://vdxl.im/8721158430922_g_en_hd_8.jpg, https://vdxl.im/8721158430922_g_en_hd_9.jpg, https://vdxl.im/8721158430922_g_en_hd_10.jpg, https://vdxl.im/8721158430922_g_en_hd_11.jpg, https://vdxl.im/8721158430922_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288916419_mo-im_en_hd_1.jpg, https://vdxl.im/8721288916419_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721288916419_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288916419_mo-im_en_hd_2.jpg, https://vdxl.im/8721288916419_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288916419_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288916419_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721288916419_wbg-si_en_hd_6.jpg, https://vdxl.im/8721288916419_wbg-ba_en_hd_4.jpg, https://vdxl.im/8721288916419_detail_en_hd_1.jpg, https://vdxl.im/8721288916419_detail_en_hd_2.jpg, https://vdxl.im/8721288916419_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288916419_wbg-siz_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1941,17 +1949,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Creme</t>
+          <t>artisan eg</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>80 x 200 cm</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr"/>
@@ -1960,7 +1968,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1970,25 +1978,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3310499</t>
+          <t>882046</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8721158430977</t>
+          <t>8721288916433</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2659</v>
+        <v>899</v>
       </c>
       <c r="F14" t="n">
-        <v>3549</v>
+        <v>1199</v>
       </c>
       <c r="G14" t="n">
-        <v>1552</v>
+        <v>522</v>
       </c>
       <c r="H14" t="n">
-        <v>32750</v>
+        <v>22910</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -2006,7 +2014,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2025,12 +2033,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430977_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288916433_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3310499</t>
+          <t>882046</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2040,17 +2048,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>3310499</t>
+          <t>882046</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkebrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkebrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette moderne natbord, der måler 40 x 35 x 47,5 cm, er en vigtig tilføjelse til ethvert soveværelse. Det har en rustik stil, der blander funktionalitet og charme, og giver dig plads til at organisere lamper, vækkeure og personlige ting. Det er lavet af konstrueret træ med en mat finish, der gør, at det passer godt ind i forskellige indretningsstile.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ&lt;/b&gt; Natbordet er lavet i konstrueret træ, som er holdbart og nemt at vedligeholde. Det har en glat overflade, der ser godt ud i enhver indretning, samtidig med at det sikrer lang holdbarhed. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionel opbevaring&lt;/b&gt; Med traditionelt design tilbyder dette natbord skuffer, der er nemme at åbne med et håndtag. Her er der god plads til at holde alt i orden, så du har hvad du skal bruge indenfor rækkevidde. Det tilfører dit rum både stil og praktisk funktion.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Sleek taperede ben&lt;/b&gt; De taperede stålbene løfter natbordet op fra gulvet, så det ikke samler støv og tilfører et elegant look. Deres matte finish forstærker det samlede design og sikrer, at bordet står stabilt. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Velegnet til indendørs brug&lt;/b&gt; Specielt designet til soveværelser, passer dette natbord ind som en stilfuld tilføjelse. Dets mål og funktion gør, at det nemt passer ved siden af enhver seng eller sofa og hjælper med at skabe et ordenligt miljø. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Samling kræves&lt;/b&gt; Det kræver samling af to personer og en skruetrækker. Grundlæggende værktøjer sørger for, at du hurtigt kan samle det, så natbordet er klar til brug. De klare instruktioner sikrer, at det holder godt i længden.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 40 x 35 x 47,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Dimensioner af hver hylde: 40 x 30 x 18.5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;Med 4 skuffer&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430977_m_en_hd_1.jpg, https://vdxl.im/8721158430977_a_en_hd_1.jpg, https://vdxl.im/8721158430977_g_en_hd_1.jpg, https://vdxl.im/8721158430977_g_en_hd_2.jpg, https://vdxl.im/8721158430977_g_en_hd_3.jpg, https://vdxl.im/8721158430977_g_en_hd_4.jpg, https://vdxl.im/8721158430977_g_en_hd_5.jpg, https://vdxl.im/8721158430977_g_en_hd_6.jpg, https://vdxl.im/8721158430977_g_en_hd_7.jpg, https://vdxl.im/8721158430977_g_en_hd_8.jpg, https://vdxl.im/8721158430977_g_en_hd_9.jpg, https://vdxl.im/8721158430977_g_en_hd_10.jpg, https://vdxl.im/8721158430977_g_en_hd_11.jpg, https://vdxl.im/8721158430977_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288916433_mo-im_en_hd_1.jpg, https://vdxl.im/8721288916433_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721288916433_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288916433_mo-im_en_hd_2.jpg, https://vdxl.im/8721288916433_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288916433_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288916433_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721288916433_wbg-si_en_hd_6.jpg, https://vdxl.im/8721288916433_wbg-ba_en_hd_4.jpg, https://vdxl.im/8721288916433_detail_en_hd_1.jpg, https://vdxl.im/8721288916433_detail_en_hd_2.jpg, https://vdxl.im/8721288916433_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288916433_wbg-siz_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2060,17 +2068,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Mørkebrun</t>
+          <t>Sort eg</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>90 x 190 cm</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr"/>
@@ -2079,7 +2087,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sengeborde-2-stk-40x35x47-5-cm-konstrueret-trae-6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2089,25 +2097,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3310500</t>
+          <t>884066</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8721158430984</t>
+          <t>8721288961853</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2699</v>
+        <v>1089</v>
       </c>
       <c r="F15" t="n">
-        <v>3599</v>
+        <v>1459</v>
       </c>
       <c r="G15" t="n">
-        <v>1574</v>
+        <v>637</v>
       </c>
       <c r="H15" t="n">
-        <v>32750</v>
+        <v>23250</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -2125,7 +2133,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2144,12 +2152,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430984_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288961853_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>3310500</t>
+          <t>884066</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2159,17 +2167,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>3310500</t>
+          <t>884066</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette moderne natbord, der måler 40 x 35 x 47,5 cm, er en vigtig tilføjelse til ethvert soveværelse. Det har en rustik stil, der blander funktionalitet og charme, og giver dig plads til at organisere lamper, vækkeure og personlige ting. Det er lavet af konstrueret træ med en mat finish, der gør, at det passer godt ind i forskellige indretningsstile.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ&lt;/b&gt; Natbordet er lavet i konstrueret træ, som er holdbart og nemt at vedligeholde. Det har en glat overflade, der ser godt ud i enhver indretning, samtidig med at det sikrer lang holdbarhed. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionel opbevaring&lt;/b&gt; Med traditionelt design tilbyder dette natbord skuffer, der er nemme at åbne med et håndtag. Her er der god plads til at holde alt i orden, så du har hvad du skal bruge indenfor rækkevidde. Det tilfører dit rum både stil og praktisk funktion.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Sleek taperede ben&lt;/b&gt; De taperede stålbene løfter natbordet op fra gulvet, så det ikke samler støv og tilfører et elegant look. Deres matte finish forstærker det samlede design og sikrer, at bordet står stabilt. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Velegnet til indendørs brug&lt;/b&gt; Specielt designet til soveværelser, passer dette natbord ind som en stilfuld tilføjelse. Dets mål og funktion gør, at det nemt passer ved siden af enhver seng eller sofa og hjælper med at skabe et ordenligt miljø. &lt;/li&gt;&lt;li&gt;&lt;b&gt;Samling kræves&lt;/b&gt; Det kræver samling af to personer og en skruetrækker. Grundlæggende værktøjer sørger for, at du hurtigt kan samle det, så natbordet er klar til brug. De klare instruktioner sikrer, at det holder godt i længden.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 40 x 35 x 47,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Dimensioner af hver hylde: 40 x 30 x 18.5 cm (B x L x H)&lt;/li&gt;&lt;li&gt;Med 4 skuffer&lt;/li&gt;&lt;li&gt;Opbevaring&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430984_m_en_hd_1.jpg, https://vdxl.im/8721158430984_a_en_hd_1.jpg, https://vdxl.im/8721158430984_g_en_hd_1.jpg, https://vdxl.im/8721158430984_g_en_hd_2.jpg, https://vdxl.im/8721158430984_g_en_hd_3.jpg, https://vdxl.im/8721158430984_g_en_hd_4.jpg, https://vdxl.im/8721158430984_g_en_hd_5.jpg, https://vdxl.im/8721158430984_g_en_hd_6.jpg, https://vdxl.im/8721158430984_g_en_hd_7.jpg, https://vdxl.im/8721158430984_g_en_hd_8.jpg, https://vdxl.im/8721158430984_g_en_hd_9.jpg, https://vdxl.im/8721158430984_g_en_hd_10.jpg, https://vdxl.im/8721158430984_g_en_hd_11.jpg, https://vdxl.im/8721158430984_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288961853_mo-im_en_hd_1.jpg, https://vdxl.im/8721288961853_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721288961853_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288961853_mo-im-zo_en_hd_1.jpg, https://vdxl.im/8721288961853_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288961853_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288961853_wbg-fr_en_hd_5.jpg, https://vdxl.im/8721288961853_wbg-si_en_hd_6.jpg, https://vdxl.im/8721288961853_wbg-ba_en_hd_4.jpg, https://vdxl.im/8721288961853_detail_en_hd_1.jpg, https://vdxl.im/8721288961853_detail_en_hd_2.jpg, https://vdxl.im/8721288961853_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288961853_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288961853_wbg-com_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2179,17 +2187,17 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Gråbrun</t>
+          <t>Gammelt træ</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Størrelse</t>
+          <t>Antal i pakke</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>90 x 190 cm</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr"/>
@@ -2198,7 +2206,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>skab-90x34x80-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2208,25 +2216,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3310501</t>
+          <t>817463</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8721158430991</t>
+          <t>8720286973714</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2479</v>
+        <v>799</v>
       </c>
       <c r="F16" t="n">
-        <v>3309</v>
+        <v>1069</v>
       </c>
       <c r="G16" t="n">
-        <v>1445</v>
+        <v>467</v>
       </c>
       <c r="H16" t="n">
-        <v>32750</v>
+        <v>30000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2244,7 +2252,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2263,12 +2271,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430991_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720286973714_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3310501</t>
+          <t>817463</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2278,17 +2286,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>3310501</t>
+          <t>817463</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få en bedre og afslappende nats søvn med denne seng med madras! Den er en indbydende tilføjelse til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og slidstærkt materiale: Polyesterstof tilbyder en kombination af blødhed, åndbarhed og holdbarhed, hvilket sikrer, at du oplever ultimativ komfort og hygge.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har lag af skum, der former sig efter din krop og aflaster trykket på følsomme søvnområder som nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelse om natten.&lt;/li&gt;&lt;li&gt;Ingen boxmadras nødvendig: Sengestellet har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boxmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Hovedgærdepuden er fyldt med PP-fiber for ultrablød og optimal komfort, hvilket giver dig fremragende rygstøtte, mens du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Stabile og holdbare ben: Denne seng understøttes af robuste ben, der sikrer stabilitet, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Denne sengestel har et lamelbundsdesign og inkluderer lamellerne.&lt;/li&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen fjernes eller åbnes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk er en dekorativ og praktisk tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt; Materiale i høj kvalitet: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Sideskabet har 6 rum, der giver rigelig opbevaringsplads til at holde dine forskellige ting pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Toppen af dette skab er glimrende til fremvisning af dine pyntegenstande. &lt;/li&gt;&lt;li&gt;Industriel stil: Denne opbevaringsskænk har en industriel stil, så den føjer en unik charme til din boligindretning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel :&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det medfølgende vægmonteringsudstyr anvendes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Grå sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 90 x 34 x 80 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158430991_m_en_hd_1.jpg, https://vdxl.im/8721158430991_a_en_hd_1.jpg, https://vdxl.im/8721158430991_g_en_hd_1.jpg, https://vdxl.im/8721158430991_g_en_hd_2.jpg, https://vdxl.im/8721158430991_g_en_hd_3.jpg, https://vdxl.im/8721158430991_g_en_hd_4.jpg, https://vdxl.im/8721158430991_g_en_hd_5.jpg, https://vdxl.im/8721158430991_g_en_hd_6.jpg, https://vdxl.im/8721158430991_g_en_hd_7.jpg, https://vdxl.im/8721158430991_g_en_hd_8.jpg, https://vdxl.im/8721158430991_g_en_hd_9.jpg, https://vdxl.im/8721158430991_g_en_hd_10.jpg, https://vdxl.im/8721158430991_g_en_hd_11.jpg, https://vdxl.im/8721158430991_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8720286973714_m_en_hd_1.jpg, https://vdxl.im/8720286973714_a_en_hd_1.jpg, https://vdxl.im/8720286973714_g_en_hd_1.jpg, https://vdxl.im/8720286973714_g_en_hd_2.jpg, https://vdxl.im/8720286973714_g_en_hd_3.jpg, https://vdxl.im/8720286973714_g_en_hd_4.jpg, https://vdxl.im/8720286973714_g_en_hd_5.jpg, https://vdxl.im/8720286973714_g_en_hd_6.jpg, https://vdxl.im/8720286973714_g_en_hd_7.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1666594503/test/Image%20with%20Text/8888%20Wood%20Legs/Renamed/GSmetallegdk.png</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2298,26 +2306,18 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Creme</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>90 x 190 cm</t>
-        </is>
-      </c>
+          <t>Grå sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>skab-90x34x80-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2327,25 +2327,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3310502</t>
+          <t>856892</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8721158431004</t>
+          <t>8721158442314</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2659</v>
+        <v>919</v>
       </c>
       <c r="F17" t="n">
-        <v>3549</v>
+        <v>1229</v>
       </c>
       <c r="G17" t="n">
-        <v>1552</v>
+        <v>536</v>
       </c>
       <c r="H17" t="n">
-        <v>32750</v>
+        <v>28200</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431004_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158442314_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3310502</t>
+          <t>856892</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2397,17 +2397,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3310502</t>
+          <t>856892</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk er en dekorativ og praktisk tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Materiale i høj kvalitet: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Sideskabet har 6 rum, der giver rigelig opbevaringsplads til at holde dine forskellige ting pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Toppen af dette skab er glimrende til fremvisning af dine pyntegenstande.&lt;/li&gt;&lt;li&gt;Industriel stil: Denne opbevaringsskænk har en industriel stil, så den føjer en unik charme til din boligindretning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det medfølgende vægmonteringsudstyr anvendes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: antikt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 90 x 34 x 80 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431004_m_en_hd_1.jpg, https://vdxl.im/8721158431004_a_en_hd_1.jpg, https://vdxl.im/8721158431004_g_en_hd_1.jpg, https://vdxl.im/8721158431004_g_en_hd_2.jpg, https://vdxl.im/8721158431004_g_en_hd_3.jpg, https://vdxl.im/8721158431004_g_en_hd_4.jpg, https://vdxl.im/8721158431004_g_en_hd_5.jpg, https://vdxl.im/8721158431004_g_en_hd_6.jpg, https://vdxl.im/8721158431004_g_en_hd_7.jpg, https://vdxl.im/8721158431004_g_en_hd_8.jpg, https://vdxl.im/8721158431004_g_en_hd_9.jpg, https://vdxl.im/8721158431004_g_en_hd_10.jpg, https://vdxl.im/8721158431004_g_en_hd_11.jpg, https://vdxl.im/8721158431004_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721158442314_m_en_hd_1.jpg, https://vdxl.im/8721158442314_a_en_hd_1.jpg, https://vdxl.im/8721158442314_g_en_hd_1.jpg, https://vdxl.im/8721158442314_g_en_hd_2.jpg, https://vdxl.im/8721158442314_g_en_hd_3.jpg, https://vdxl.im/8721158442314_g_en_hd_4.jpg, https://vdxl.im/8721158442314_g_en_hd_5.jpg, https://vdxl.im/8721158442314_g_en_hd_6.jpg, https://vdxl.im/8721158442314_g_en_hd_7.jpg, https://vdxl.im/8721158442314_g_en_hd_8.jpg, https://vdxl.im/8721158442314_g_en_hd_9.jpg, https://vdxl.im/8721158442314_g_en_hd_10.jpg</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2417,26 +2417,18 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Blå</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>90 x 190 cm</t>
-        </is>
-      </c>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>skab-90x34x80-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2446,25 +2438,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3310507</t>
+          <t>856893</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8721158431059</t>
+          <t>8721158442321</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2679</v>
+        <v>909</v>
       </c>
       <c r="F18" t="n">
-        <v>3579</v>
+        <v>1219</v>
       </c>
       <c r="G18" t="n">
-        <v>1566</v>
+        <v>529</v>
       </c>
       <c r="H18" t="n">
-        <v>33450</v>
+        <v>27900</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2482,7 +2474,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -2501,12 +2493,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431059_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158442321_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3310507</t>
+          <t>856893</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2516,17 +2508,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>3310507</t>
+          <t>856893</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Denne klassiske skænk er en dekorativ og praktisk tilføjelse til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Materiale i høj kvalitet: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Sideskabet har 6 rum, der giver rigelig opbevaringsplads til at holde dine forskellige ting pænt organiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Displayfunktion: Toppen af dette skab er glimrende til fremvisning af dine pyntegenstande.&lt;/li&gt;&lt;li&gt;Industriel stil: Denne opbevaringsskænk har en industriel stil, så den føjer en unik charme til din boligindretning.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det medfølgende vægmonteringsudstyr anvendes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: egetræsfarve&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ, metal&lt;/li&gt;&lt;li&gt;Mål: 90 x 34 x 80 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431059_m_en_hd_1.jpg, https://vdxl.im/8721158431059_a_en_hd_1.jpg, https://vdxl.im/8721158431059_g_en_hd_1.jpg, https://vdxl.im/8721158431059_g_en_hd_2.jpg, https://vdxl.im/8721158431059_g_en_hd_3.jpg, https://vdxl.im/8721158431059_g_en_hd_4.jpg, https://vdxl.im/8721158431059_g_en_hd_5.jpg, https://vdxl.im/8721158431059_g_en_hd_6.jpg, https://vdxl.im/8721158431059_g_en_hd_7.jpg, https://vdxl.im/8721158431059_g_en_hd_8.jpg, https://vdxl.im/8721158431059_g_en_hd_9.jpg, https://vdxl.im/8721158431059_g_en_hd_10.jpg, https://vdxl.im/8721158431059_g_en_hd_11.jpg, https://vdxl.im/8721158431059_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721158442321_m_en_hd_1.jpg, https://vdxl.im/8721158442321_a_en_hd_1.jpg, https://vdxl.im/8721158442321_g_en_hd_1.jpg, https://vdxl.im/8721158442321_g_en_hd_2.jpg, https://vdxl.im/8721158442321_g_en_hd_3.jpg, https://vdxl.im/8721158442321_g_en_hd_4.jpg, https://vdxl.im/8721158442321_g_en_hd_5.jpg, https://vdxl.im/8721158442321_g_en_hd_6.jpg, https://vdxl.im/8721158442321_g_en_hd_7.jpg, https://vdxl.im/8721158442321_g_en_hd_8.jpg, https://vdxl.im/8721158442321_g_en_hd_9.jpg</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2536,26 +2528,18 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Gråbrun</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>90 x 200 cm</t>
-        </is>
-      </c>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>skab-90x34x80-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2565,25 +2549,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3310508</t>
+          <t>880682</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8721158431066</t>
+          <t>8721288904966</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>699</v>
       </c>
       <c r="F19" t="n">
-        <v>3829</v>
+        <v>939</v>
       </c>
       <c r="G19" t="n">
-        <v>1677</v>
+        <v>408</v>
       </c>
       <c r="H19" t="n">
-        <v>33450</v>
+        <v>28240</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2601,7 +2585,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2620,12 +2604,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431066_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288904966_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3310508</t>
+          <t>880682</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2635,17 +2619,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>3310508</t>
+          <t>880682</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få en bedre og afslappende nats søvn med denne seng med madras! Den er en indbydende tilføjelse til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og slidstærkt materiale: Polyesterstof tilbyder en kombination af blødhed, åndbarhed og holdbarhed, hvilket sikrer, at du oplever ultimativ komfort og hygge.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har lag af skum, der former sig efter din krop og aflaster trykket på følsomme søvnområder som nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelse om natten.&lt;/li&gt;&lt;li&gt;Ingen boxmadras nødvendig: Sengestellet har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boxmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Hovedgærdepuden er fyldt med PP-fiber for ultrablød og optimal komfort, hvilket giver dig fremragende rygstøtte, mens du sidder op i sengen for at læse eller se tv.&lt;/li&gt;&lt;li&gt;Stabile og holdbare ben: Denne seng understøttes af robuste ben, der sikrer stabilitet, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Denne sengestel har et lamelbundsdesign og inkluderer lamellerne.&lt;/li&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen fjernes eller åbnes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Lavt til moderne hjem, blander træskabet enkelhed og praktisk brug i et slankt, minimalistisk design. Det er en smart opbevaringsmulighed, der passer perfekt ind i stuer og supplerer enhver moderne indretning. Dets smarte design er for dem, der værdsætter både orden og et godt udseende. Den rektangulære form kan rumme mange forskellige ting, mens den glatte overflade er både praktisk og stilfuld.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstruktion af konstrueret træ&lt;/b&gt; Dette skab er lavet af konstrueret træ, som giver det en solid fornemmelse. Det er stærkt nok til daglig brug og ser fantastisk ud i ethvert rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne håndtag&lt;/b&gt; Hold stilen med sorte stanghåndtag, der både ser godt ud og er behagelige at bruge. Deres særprægede farve mod træet giver et flot udtryk.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle døre&lt;/b&gt; De flush døre er lette at rengøre og åbne. De skjuler dine ting, så du kan have et ryddeligt rum.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Rummelig opbevaring&lt;/b&gt; Indeni er der masser af plads, perfekt til alt fra stel til bøger, og hjælper med at holde orden.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Samling kræves&lt;/b&gt; Det skal samles, men det er let med blot to personer og en skruetrækker. Når det er samlet, får du et robust skab, og instruktionerne hjælper dig med at passe på det over tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 34 x 90 x 80 CM (B x L x H)&lt;/li&gt;&lt;li&gt;Med 3 døre&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Skab&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431066_m_en_hd_1.jpg, https://vdxl.im/8721158431066_a_en_hd_1.jpg, https://vdxl.im/8721158431066_g_en_hd_1.jpg, https://vdxl.im/8721158431066_g_en_hd_2.jpg, https://vdxl.im/8721158431066_g_en_hd_3.jpg, https://vdxl.im/8721158431066_g_en_hd_4.jpg, https://vdxl.im/8721158431066_g_en_hd_5.jpg, https://vdxl.im/8721158431066_g_en_hd_6.jpg, https://vdxl.im/8721158431066_g_en_hd_7.jpg, https://vdxl.im/8721158431066_g_en_hd_8.jpg, https://vdxl.im/8721158431066_g_en_hd_9.jpg, https://vdxl.im/8721158431066_g_en_hd_10.jpg, https://vdxl.im/8721158431066_g_en_hd_11.jpg, https://vdxl.im/8721158431066_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288904966_mo-im_en_hd_1.jpg, https://vdxl.im/8721288904966_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288904966_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288904966_mo-im_en_hd_2.jpg, https://vdxl.im/8721288904966_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288904966_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721288904966_wbg-si_en_hd_5.jpg, https://vdxl.im/8721288904966_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721288904966_detail_en_hd_1.jpg, https://vdxl.im/8721288904966_detail_en_hd_2.jpg, https://vdxl.im/8721288904966_detail_en_hd_3.jpg, https://vdxl.im/8721288904966_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288904966_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288904966_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288904966_wbg-com_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2655,26 +2639,18 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Creme</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>90 x 200 cm</t>
-        </is>
-      </c>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sofabord-80x50x40-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2684,25 +2660,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3310509</t>
+          <t>816531</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8721158431073</t>
+          <t>8720845666965</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2879</v>
+        <v>699</v>
       </c>
       <c r="F20" t="n">
-        <v>3839</v>
+        <v>939</v>
       </c>
       <c r="G20" t="n">
-        <v>1682</v>
+        <v>407</v>
       </c>
       <c r="H20" t="n">
-        <v>33450</v>
+        <v>24260</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2720,7 +2696,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -2739,12 +2715,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431073_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845666965_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3310509</t>
+          <t>816531</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2754,17 +2730,17 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>3310509</t>
+          <t>816531</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 95 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 90 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 90 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Leder du efter et sofabord til dit hjem? Så skal du vælge dette funktionelle sofabord, som giver dit rum et unikt look.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Slidstærkt materiale: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende. Sidebordet er fremstillet af konstrueret træ, så det er let at rengøre.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Dette sofabord har 2 skuffer, så det giver god plads til opbevaring af dine ting og sager.&lt;/li&gt;&lt;li&gt;Robust bordplade: Stuebordets bordplade giver en sikker overflade, som du kan stille snacks, drikkevarer, vaser, frugtskåle og andre pyntegenstande på.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 80 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431073_m_en_hd_1.jpg, https://vdxl.im/8721158431073_a_en_hd_1.jpg, https://vdxl.im/8721158431073_g_en_hd_1.jpg, https://vdxl.im/8721158431073_g_en_hd_2.jpg, https://vdxl.im/8721158431073_g_en_hd_3.jpg, https://vdxl.im/8721158431073_g_en_hd_4.jpg, https://vdxl.im/8721158431073_g_en_hd_5.jpg, https://vdxl.im/8721158431073_g_en_hd_6.jpg, https://vdxl.im/8721158431073_g_en_hd_7.jpg, https://vdxl.im/8721158431073_g_en_hd_8.jpg, https://vdxl.im/8721158431073_g_en_hd_9.jpg, https://vdxl.im/8721158431073_g_en_hd_10.jpg, https://vdxl.im/8721158431073_g_en_hd_11.jpg, https://vdxl.im/8721158431073_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8720845666965_m_en_hd_1.jpg, https://vdxl.im/8720845666965_a_en_hd_1.jpg, https://vdxl.im/8720845666965_g_en_hd_1.jpg, https://vdxl.im/8720845666965_g_en_hd_2.jpg, https://vdxl.im/8720845666965_g_en_hd_3.jpg, https://vdxl.im/8720845666965_g_en_hd_4.jpg, https://vdxl.im/8720845666965_g_en_hd_5.jpg, https://vdxl.im/8720845666965_g_en_hd_6.jpg, https://vdxl.im/8720845666965_g_en_hd_7.jpg</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2774,26 +2750,18 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Blå</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>90 x 200 cm</t>
-        </is>
-      </c>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sofabord-80x50x40-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2803,25 +2771,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3310515</t>
+          <t>881129</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8721158431134</t>
+          <t>8721288908476</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3119</v>
+        <v>619</v>
       </c>
       <c r="F21" t="n">
-        <v>4159</v>
+        <v>829</v>
       </c>
       <c r="G21" t="n">
-        <v>1822</v>
+        <v>360</v>
       </c>
       <c r="H21" t="n">
-        <v>34600</v>
+        <v>23560</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2839,7 +2807,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -2858,12 +2826,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431134_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288908476_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3310515</t>
+          <t>881129</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2873,17 +2841,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>3310515</t>
+          <t>881129</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 105 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 100 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Cremefarvet&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 100 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette store rektangulære sofabord er lavet til at være både funktionelt og stilfuldt, og det tilfører et rustikt præg til din stue. Den teksturerede overflade viser en naturlig skønhed, som skaber en hyggelig atmosfære. Sofabordet er perfekt til opbevaring af drikkevarer, bøger og dekorative genstande. Det er både pænt at se på og praktisk, og det passer ind i næsten enhver indretning.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træmateriale&lt;/b&gt; Høj kvalitet konstrueret træ, der gør bordet slidstærkt, samtidig med at det ser smart ud. Træet holder bordet stabilt og giver et varmt udseende, der passer perfekt ind i den rustikke stil.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Integrerede opbevaringsløsninger&lt;/b&gt; Dette bord har masser af opbevaring med smarte skuffer og metalhåndtag. De rummelige rum gør det nemt at holde styr på magasiner, fjernbetjeninger og andre ting, så det ser godt og ryddeligt ud.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle designfunktioner&lt;/b&gt; Bordet har en lav skuffe og konstrueret træ, der kombinerer stil og funktionalitet, så det opfylder dine behov uden at gå på kompromis med udseendet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige brugsoptions&lt;/b&gt; Perfekt til stuen, dette bord er slidstærkt og passer ind i både moderne og traditionelle stilarter. Det er ideelt til sociale sammenkomster eller stille stunder og fungerer godt som støtte til dekorative genstande.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Praktisk pleje og vedligeholdelse&lt;/b&gt; For at holde bordet flot, tør det af med en blød klud jævnligt. Undgå skrappe kemikalier for at bevare overfladen, så det holder sig pænt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;With drawer&lt;/li&gt;&lt;li&gt;Med 1  hylde&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431134_m_en_hd_1.jpg, https://vdxl.im/8721158431134_a_en_hd_1.jpg, https://vdxl.im/8721158431134_g_en_hd_1.jpg, https://vdxl.im/8721158431134_g_en_hd_2.jpg, https://vdxl.im/8721158431134_g_en_hd_3.jpg, https://vdxl.im/8721158431134_g_en_hd_4.jpg, https://vdxl.im/8721158431134_g_en_hd_5.jpg, https://vdxl.im/8721158431134_g_en_hd_6.jpg, https://vdxl.im/8721158431134_g_en_hd_7.jpg, https://vdxl.im/8721158431134_g_en_hd_8.jpg, https://vdxl.im/8721158431134_g_en_hd_9.jpg, https://vdxl.im/8721158431134_g_en_hd_10.jpg, https://vdxl.im/8721158431134_g_en_hd_11.jpg, https://vdxl.im/8721158431134_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288908476_mo-im_en_hd_1.jpg, https://vdxl.im/8721288908476_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288908476_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288908476_mo-im_en_hd_2.jpg, https://vdxl.im/8721288908476_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288908476_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288908476_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288908476_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288908476_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288908476_wbg-siz_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2893,26 +2861,18 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Creme</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>100 x 200 cm</t>
-        </is>
-      </c>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sofabord-80x50x40-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2922,25 +2882,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3310516</t>
+          <t>881130</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8721158431141</t>
+          <t>8721288908483</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2969</v>
+        <v>669</v>
       </c>
       <c r="F22" t="n">
-        <v>3959</v>
+        <v>899</v>
       </c>
       <c r="G22" t="n">
-        <v>1737</v>
+        <v>392</v>
       </c>
       <c r="H22" t="n">
-        <v>34600</v>
+        <v>23560</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2958,7 +2918,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -2977,12 +2937,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431141_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288908483_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>3310516</t>
+          <t>881130</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2992,17 +2952,17 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>3310516</t>
+          <t>881130</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 105 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 100 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 100 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette store rektangulære sofabord er lavet til at være både funktionelt og stilfuldt, og det tilfører et rustikt præg til din stue. Den teksturerede overflade viser en naturlig skønhed, som skaber en hyggelig atmosfære. Sofabordet er perfekt til opbevaring af drikkevarer, bøger og dekorative genstande. Det er både pænt at se på og praktisk, og det passer ind i næsten enhver indretning.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træmateriale&lt;/b&gt; Høj kvalitet konstrueret træ, der gør bordet slidstærkt, samtidig med at det ser smart ud. Træet holder bordet stabilt og giver et varmt udseende, der passer perfekt ind i den rustikke stil.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Integrerede opbevaringsløsninger&lt;/b&gt; Dette bord har masser af opbevaring med smarte skuffer og metalhåndtag. De rummelige rum gør det nemt at holde styr på magasiner, fjernbetjeninger og andre ting, så det ser godt og ryddeligt ud.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle designfunktioner&lt;/b&gt; Bordet har en lav skuffe og konstrueret træ, der kombinerer stil og funktionalitet, så det opfylder dine behov uden at gå på kompromis med udseendet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige brugsoptions&lt;/b&gt; Perfekt til stuen, dette bord er slidstærkt og passer ind i både moderne og traditionelle stilarter. Det er ideelt til sociale sammenkomster eller stille stunder og fungerer godt som støtte til dekorative genstande.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Praktisk pleje og vedligeholdelse&lt;/b&gt; For at holde bordet flot, tør det af med en blød klud jævnligt. Undgå skrappe kemikalier for at bevare overfladen, så det holder sig pænt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;With drawer&lt;/li&gt;&lt;li&gt;Med 1  hylde&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431141_m_en_hd_1.jpg, https://vdxl.im/8721158431141_a_en_hd_1.jpg, https://vdxl.im/8721158431141_g_en_hd_1.jpg, https://vdxl.im/8721158431141_g_en_hd_2.jpg, https://vdxl.im/8721158431141_g_en_hd_3.jpg, https://vdxl.im/8721158431141_g_en_hd_4.jpg, https://vdxl.im/8721158431141_g_en_hd_5.jpg, https://vdxl.im/8721158431141_g_en_hd_6.jpg, https://vdxl.im/8721158431141_g_en_hd_7.jpg, https://vdxl.im/8721158431141_g_en_hd_8.jpg, https://vdxl.im/8721158431141_g_en_hd_9.jpg, https://vdxl.im/8721158431141_g_en_hd_10.jpg, https://vdxl.im/8721158431141_g_en_hd_11.jpg, https://vdxl.im/8721158431141_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288908483_mo-im_en_hd_1.jpg, https://vdxl.im/8721288908483_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288908483_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288908483_mo-im_en_hd_2.jpg, https://vdxl.im/8721288908483_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288908483_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288908483_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288908483_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288908483_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288908483_wbg-siz_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3012,26 +2972,18 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Blå</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>100 x 200 cm</t>
-        </is>
-      </c>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sofabord-80x50x40-cm-konstrueret-trae-1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3041,25 +2993,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3310517</t>
+          <t>881131</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8721158431158</t>
+          <t>8721288908490</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3449</v>
+        <v>649</v>
       </c>
       <c r="F23" t="n">
-        <v>4599</v>
+        <v>869</v>
       </c>
       <c r="G23" t="n">
-        <v>2016</v>
+        <v>380</v>
       </c>
       <c r="H23" t="n">
-        <v>36650</v>
+        <v>23560</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -3077,7 +3029,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -3096,12 +3048,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431158_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288908490_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3310517</t>
+          <t>881131</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3111,17 +3063,17 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>3310517</t>
+          <t>881131</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 125 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 120 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 120 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette store rektangulære sofabord er lavet til at være både funktionelt og stilfuldt, og det tilfører et rustikt præg til din stue. Den teksturerede overflade viser en naturlig skønhed, som skaber en hyggelig atmosfære. Sofabordet er perfekt til opbevaring af drikkevarer, bøger og dekorative genstande. Det er både pænt at se på og praktisk, og det passer ind i næsten enhver indretning.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstrueret træmateriale&lt;/b&gt; Høj kvalitet konstrueret træ, der gør bordet slidstærkt, samtidig med at det ser smart ud. Træet holder bordet stabilt og giver et varmt udseende, der passer perfekt ind i den rustikke stil.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Integrerede opbevaringsløsninger&lt;/b&gt; Dette bord har masser af opbevaring med smarte skuffer og metalhåndtag. De rummelige rum gør det nemt at holde styr på magasiner, fjernbetjeninger og andre ting, så det ser godt og ryddeligt ud.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Funktionelle designfunktioner&lt;/b&gt; Bordet har en lav skuffe og konstrueret træ, der kombinerer stil og funktionalitet, så det opfylder dine behov uden at gå på kompromis med udseendet.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Alsidige brugsoptions&lt;/b&gt; Perfekt til stuen, dette bord er slidstærkt og passer ind i både moderne og traditionelle stilarter. Det er ideelt til sociale sammenkomster eller stille stunder og fungerer godt som støtte til dekorative genstande.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Praktisk pleje og vedligeholdelse&lt;/b&gt; For at holde bordet flot, tør det af med en blød klud jævnligt. Undgå skrappe kemikalier for at bevare overfladen, så det holder sig pænt i lang tid.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 80 x 50 x 40 cm (L x B x H)&lt;/li&gt;&lt;li&gt;With drawer&lt;/li&gt;&lt;li&gt;Med 1  hylde&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Slidstærk&lt;/li&gt;&lt;li&gt;Maks. vægt: 60 kg&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431158_m_en_hd_1.jpg, https://vdxl.im/8721158431158_a_en_hd_1.jpg, https://vdxl.im/8721158431158_g_en_hd_1.jpg, https://vdxl.im/8721158431158_g_en_hd_2.jpg, https://vdxl.im/8721158431158_g_en_hd_3.jpg, https://vdxl.im/8721158431158_g_en_hd_4.jpg, https://vdxl.im/8721158431158_g_en_hd_5.jpg, https://vdxl.im/8721158431158_g_en_hd_6.jpg, https://vdxl.im/8721158431158_g_en_hd_7.jpg, https://vdxl.im/8721158431158_g_en_hd_8.jpg, https://vdxl.im/8721158431158_g_en_hd_9.jpg, https://vdxl.im/8721158431158_g_en_hd_10.jpg, https://vdxl.im/8721158431158_g_en_hd_11.jpg, https://vdxl.im/8721158431158_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288908490_mo-im_en_hd_1.jpg, https://vdxl.im/8721288908490_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721288908490_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288908490_mo-im_en_hd_2.jpg, https://vdxl.im/8721288908490_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288908490_wbg-fr_en_hd_1.jpg, https://vdxl.im/8721288908490_wbg-si_en_hd_1.jpg, https://vdxl.im/8721288908490_wbg-ba_en_hd_1.jpg, https://vdxl.im/8721288908490_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288908490_wbg-siz_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3131,26 +3083,18 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Lysegrå</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>120 x 200 cm</t>
-        </is>
-      </c>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>tv-skabssaet-3-dele-konstrueret-trae-2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3160,25 +3104,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3310518</t>
+          <t>3079631</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8721158431165</t>
+          <t>8720286590331</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3249</v>
+        <v>1309</v>
       </c>
       <c r="F24" t="n">
-        <v>4339</v>
+        <v>1749</v>
       </c>
       <c r="G24" t="n">
-        <v>1898</v>
+        <v>762</v>
       </c>
       <c r="H24" t="n">
-        <v>36650</v>
+        <v>52490</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -3196,7 +3140,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -3215,12 +3159,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431165_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720286590331_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3310518</t>
+          <t>3079631</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3230,17 +3174,17 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3310518</t>
+          <t>3079631</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 125 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 120 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 120 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Det væghængte tv-skab har rigelig med plads til opbevaring af forskellige ting og sager, og det er med sikkerhed et praktisk og flot supplement til dit hjem.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Tv-møblet hænges på væggen og vil være en tidløs tilføjelse til dit hjem. HiFi-skabet er ideelt til at fremvise eller opbevare dine ting pænt organiseret og inden for rækkevidde. Derudover er stereoskabet let at rengøre med en fugtig klud.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;Farve: Sonoma-eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x tv-skab: 37 x 37 x 72 cm (B x D x H)&lt;/li&gt;&lt;li&gt;2 x tv-skab: 37 x 37 x 107 cm (B x D x H)&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431165_m_en_hd_1.jpg, https://vdxl.im/8721158431165_a_en_hd_1.jpg, https://vdxl.im/8721158431165_g_en_hd_1.jpg, https://vdxl.im/8721158431165_g_en_hd_2.jpg, https://vdxl.im/8721158431165_g_en_hd_3.jpg, https://vdxl.im/8721158431165_g_en_hd_4.jpg, https://vdxl.im/8721158431165_g_en_hd_5.jpg, https://vdxl.im/8721158431165_g_en_hd_6.jpg, https://vdxl.im/8721158431165_g_en_hd_7.jpg, https://vdxl.im/8721158431165_g_en_hd_8.jpg, https://vdxl.im/8721158431165_g_en_hd_9.jpg, https://vdxl.im/8721158431165_g_en_hd_10.jpg, https://vdxl.im/8721158431165_g_en_hd_11.jpg, https://vdxl.im/8721158431165_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8720286590331_m_en_hd_1.jpg, https://vdxl.im/8720286590331_a_en_hd_1.jpg, https://vdxl.im/8720286590331_g_en_hd_1.jpg, https://vdxl.im/8720286590331_g_en_hd_2.jpg, https://vdxl.im/8720286590331_g_en_hd_3.jpg, https://vdxl.im/8720286590331_g_en_hd_4.jpg, https://vdxl.im/8720286590331_g_en_hd_5.jpg</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3250,26 +3194,18 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Mørkegrå</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>120 x 200 cm</t>
-        </is>
-      </c>
+          <t>Sonoma-eg</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>tv-skabssaet-3-dele-konstrueret-trae-2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3279,25 +3215,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3310519</t>
+          <t>3393363</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8721158431172</t>
+          <t>8721288873408</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3789</v>
+        <v>1439</v>
       </c>
       <c r="F25" t="n">
-        <v>5059</v>
+        <v>1919</v>
       </c>
       <c r="G25" t="n">
-        <v>2214</v>
+        <v>841</v>
       </c>
       <c r="H25" t="n">
-        <v>36650</v>
+        <v>50700</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -3315,7 +3251,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -3334,12 +3270,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431172_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288873408_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>3310519</t>
+          <t>3393363</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3349,17 +3285,17 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>3310519</t>
+          <t>3393363</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 125 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 120 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 120 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette væghængte tv-standsæt blander stil og funktionalitet og giver en smart opbevaringsløsning til moderne stuer. Det væghængte design sparer ikke kun gulvplads, men giver også et rart og strømlinet look.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ-konstruktion&lt;/b&gt; Skabet er lavet af konstrueret træ, som er kendt for sin stabilitet og langtidsholdbarhed. Materialet sørger for, at det holder formen og fungerer godt over tid, så du får en pålidelig løsning til dit opbevaringsbehov.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Minimalistisk moderne design&lt;/b&gt; Dette skab er et perfekt eksempel på moderne stil med sine rene linjer og enkelhed. Det glider let ind i nutidige indretninger, mens det giver funktionel opbevaring uden at ofre æstetikken.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Pladsbesparende montering&lt;/b&gt; Det væghængte design er ideelt til små rum, fordi det frigiver gulvplads og giver god opbevaring til de vigtigste ting som fjernbetjeninger, kabler og pyntegenstande.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Funktionelle opbevaringsløsninger&lt;/b&gt; Det har fleksible hylder, der gør det nemt at holde orden og opbevare ting på en smart måde. Hver afdeling er rummelig og kan rumme alt fra dvd'er til dekorative ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Konstruerede komponenter&lt;/b&gt; Skabet kommer med holdbare bagsider og hylder lavet af konstrueret træ. Disse komponenter giver skabet et helhedsorienteret udtryk og en robust følelse, som gør det brugbart til enhver opgave.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Gammelt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 37 x 37 x 107 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 7 pladehylder&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Væghængt TV-skab (S): 37 x 37 x 72 cm (L x B x H)&lt;/li&gt;&lt;li&gt;2 x Væghængt TV Skab (L): 37 x 37 x 107 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431172_m_en_hd_1.jpg, https://vdxl.im/8721158431172_a_en_hd_1.jpg, https://vdxl.im/8721158431172_g_en_hd_1.jpg, https://vdxl.im/8721158431172_g_en_hd_2.jpg, https://vdxl.im/8721158431172_g_en_hd_3.jpg, https://vdxl.im/8721158431172_g_en_hd_4.jpg, https://vdxl.im/8721158431172_g_en_hd_5.jpg, https://vdxl.im/8721158431172_g_en_hd_6.jpg, https://vdxl.im/8721158431172_g_en_hd_7.jpg, https://vdxl.im/8721158431172_g_en_hd_8.jpg, https://vdxl.im/8721158431172_g_en_hd_9.jpg, https://vdxl.im/8721158431172_g_en_hd_10.jpg, https://vdxl.im/8721158431172_g_en_hd_11.jpg, https://vdxl.im/8721158431172_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288873408_mo-im_en_hd_1.jpg, https://vdxl.im/8721288873408_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721288873408_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288873408_mo-im_en_hd_2.jpg, https://vdxl.im/8721288873408_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288873408_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288873408_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288873408_wbg-fu_en_hd_2.jpg, https://vdxl.im/8721288873408_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288873408_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288873408_wbg-siz_en_hd_2.jpg</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3369,26 +3305,18 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>120 x 200 cm</t>
-        </is>
-      </c>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>tv-skabssaet-3-dele-konstrueret-trae-2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3398,25 +3326,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3310524</t>
+          <t>3393364</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8721158431226</t>
+          <t>8721288873415</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3139</v>
+        <v>1489</v>
       </c>
       <c r="F26" t="n">
-        <v>4189</v>
+        <v>1989</v>
       </c>
       <c r="G26" t="n">
-        <v>1834</v>
+        <v>869</v>
       </c>
       <c r="H26" t="n">
-        <v>40250</v>
+        <v>50700</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -3434,7 +3362,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -3453,12 +3381,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431226_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288873415_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>3310524</t>
+          <t>3393364</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3468,17 +3396,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>3310524</t>
+          <t>3393364</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette væghængte tv-standsæt blander stil og funktionalitet og giver en smart opbevaringsløsning til moderne stuer. Det væghængte design sparer ikke kun gulvplads, men giver også et rart og strømlinet look.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ-konstruktion&lt;/b&gt; Skabet er lavet af konstrueret træ, som er kendt for sin stabilitet og langtidsholdbarhed. Materialet sørger for, at det holder formen og fungerer godt over tid, så du får en pålidelig løsning til dit opbevaringsbehov.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Minimalistisk moderne design&lt;/b&gt; Dette skab er et perfekt eksempel på moderne stil med sine rene linjer og enkelhed. Det glider let ind i nutidige indretninger, mens det giver funktionel opbevaring uden at ofre æstetikken.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Pladsbesparende montering&lt;/b&gt; Det væghængte design er ideelt til små rum, fordi det frigiver gulvplads og giver god opbevaring til de vigtigste ting som fjernbetjeninger, kabler og pyntegenstande.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Funktionelle opbevaringsløsninger&lt;/b&gt; Det har fleksible hylder, der gør det nemt at holde orden og opbevare ting på en smart måde. Hver afdeling er rummelig og kan rumme alt fra dvd'er til dekorative ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Konstruerede komponenter&lt;/b&gt; Skabet kommer med holdbare bagsider og hylder lavet af konstrueret træ. Disse komponenter giver skabet et helhedsorienteret udtryk og en robust følelse, som gør det brugbart til enhver opgave.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 37 x 37 x 107 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 7 pladehylder&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Væghængt TV-skab (S): 37 x 37 x 72 cm (L x B x H)&lt;/li&gt;&lt;li&gt;2 x Væghængt TV Skab (L): 37 x 37 x 107 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431226_m_en_hd_1.jpg, https://vdxl.im/8721158431226_a_en_hd_1.jpg, https://vdxl.im/8721158431226_g_en_hd_1.jpg, https://vdxl.im/8721158431226_g_en_hd_2.jpg, https://vdxl.im/8721158431226_g_en_hd_3.jpg, https://vdxl.im/8721158431226_g_en_hd_4.jpg, https://vdxl.im/8721158431226_g_en_hd_5.jpg, https://vdxl.im/8721158431226_g_en_hd_6.jpg, https://vdxl.im/8721158431226_g_en_hd_7.jpg, https://vdxl.im/8721158431226_g_en_hd_8.jpg, https://vdxl.im/8721158431226_g_en_hd_9.jpg, https://vdxl.im/8721158431226_g_en_hd_10.jpg, https://vdxl.im/8721158431226_g_en_hd_11.jpg, https://vdxl.im/8721158431226_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288873415_mo-im_en_hd_1.jpg, https://vdxl.im/8721288873415_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721288873415_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288873415_mo-im_en_hd_2.jpg, https://vdxl.im/8721288873415_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288873415_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288873415_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288873415_wbg-fu_en_hd_2.jpg, https://vdxl.im/8721288873415_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288873415_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288873415_wbg-siz_en_hd_2.jpg</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3488,26 +3416,18 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Lysegrå</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>tv-skabssaet-3-dele-konstrueret-trae-2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3517,25 +3437,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3310525</t>
+          <t>3393365</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8721158431233</t>
+          <t>8721288873422</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3149</v>
+        <v>1409</v>
       </c>
       <c r="F27" t="n">
-        <v>4199</v>
+        <v>1879</v>
       </c>
       <c r="G27" t="n">
-        <v>1841</v>
+        <v>820</v>
       </c>
       <c r="H27" t="n">
-        <v>40250</v>
+        <v>50700</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -3553,7 +3473,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -3572,12 +3492,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431233_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721288873422_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3310525</t>
+          <t>3393365</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3587,17 +3507,17 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>3310525</t>
+          <t>3393365</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette væghængte tv-standsæt blander stil og funktionalitet og giver en smart opbevaringsløsning til moderne stuer. Det væghængte design sparer ikke kun gulvplads, men giver også et rart og strømlinet look.&lt;/p&gt; &lt;ul&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Konstrueret træ-konstruktion&lt;/b&gt; Skabet er lavet af konstrueret træ, som er kendt for sin stabilitet og langtidsholdbarhed. Materialet sørger for, at det holder formen og fungerer godt over tid, så du får en pålidelig løsning til dit opbevaringsbehov.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Minimalistisk moderne design&lt;/b&gt; Dette skab er et perfekt eksempel på moderne stil med sine rene linjer og enkelhed. Det glider let ind i nutidige indretninger, mens det giver funktionel opbevaring uden at ofre æstetikken.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Pladsbesparende montering&lt;/b&gt; Det væghængte design er ideelt til små rum, fordi det frigiver gulvplads og giver god opbevaring til de vigtigste ting som fjernbetjeninger, kabler og pyntegenstande.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Funktionelle opbevaringsløsninger&lt;/b&gt; Det har fleksible hylder, der gør det nemt at holde orden og opbevare ting på en smart måde. Hver afdeling er rummelig og kan rumme alt fra dvd'er til dekorative ting.&lt;/li&gt;&lt;/br&gt;&lt;li&gt;&lt;b&gt;Konstruerede komponenter&lt;/b&gt; Skabet kommer med holdbare bagsider og hylder lavet af konstrueret træ. Disse komponenter giver skabet et helhedsorienteret udtryk og en robust følelse, som gør det brugbart til enhver opgave.&lt;/li&gt;&lt;/br&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Artisan egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 37 x 37 x 107 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Med 7 pladehylder&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Væghængt TV-skab (S): 37 x 37 x 72 cm (L x B x H)&lt;/li&gt;&lt;li&gt;2 x Væghængt TV Skab (L): 37 x 37 x 107 cm (L x B x H)&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431233_m_en_hd_1.jpg, https://vdxl.im/8721158431233_a_en_hd_1.jpg, https://vdxl.im/8721158431233_g_en_hd_1.jpg, https://vdxl.im/8721158431233_g_en_hd_2.jpg, https://vdxl.im/8721158431233_g_en_hd_3.jpg, https://vdxl.im/8721158431233_g_en_hd_4.jpg, https://vdxl.im/8721158431233_g_en_hd_5.jpg, https://vdxl.im/8721158431233_g_en_hd_6.jpg, https://vdxl.im/8721158431233_g_en_hd_7.jpg, https://vdxl.im/8721158431233_g_en_hd_8.jpg, https://vdxl.im/8721158431233_g_en_hd_9.jpg, https://vdxl.im/8721158431233_g_en_hd_10.jpg, https://vdxl.im/8721158431233_g_en_hd_11.jpg, https://vdxl.im/8721158431233_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721288873422_mo-im_en_hd_1.jpg, https://vdxl.im/8721288873422_wbg-an-m_en_hd_3.jpg, https://vdxl.im/8721288873422_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721288873422_mo-im_en_hd_2.jpg, https://vdxl.im/8721288873422_wbg-an_en_hd_1.jpg, https://vdxl.im/8721288873422_wbg-an_en_hd_2.jpg, https://vdxl.im/8721288873422_wbg-fu_en_hd_1.jpg, https://vdxl.im/8721288873422_wbg-fu_en_hd_2.jpg, https://vdxl.im/8721288873422_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721288873422_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721288873422_wbg-siz_en_hd_2.jpg</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3607,26 +3527,18 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Mørkegrå</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>badevaerelsesskab-25x26-5x170-cm-konstrueret-trae</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3636,25 +3548,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3310526</t>
+          <t>815960</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>8721158431240</t>
+          <t>8720286956373</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3539</v>
+        <v>619</v>
       </c>
       <c r="F28" t="n">
-        <v>4719</v>
+        <v>829</v>
       </c>
       <c r="G28" t="n">
-        <v>2065</v>
+        <v>360</v>
       </c>
       <c r="H28" t="n">
-        <v>40250</v>
+        <v>19220</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3672,7 +3584,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -3691,12 +3603,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431240_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720286956373_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>3310526</t>
+          <t>815960</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3706,17 +3618,17 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>3310526</t>
+          <t>815960</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette flotte badeværelsesskab har rigelig med opbevaringsplads,og det imponerer med sit enkle og tidløse design.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Materiale i høj kvalitet: Konstrueret træ har en enestående kvalitet med en glat overflade, og det er både stærkt, stabilt og fugtafvisende.&lt;/li&gt;&lt;li&gt;Ekstra opbevaringsplads: Dette badeværelsesskab tilbyder god plads til at holde dine vaskemidler, toiletartikler samt andre ting og sager pænt organiseret og inden for rækkevidde. Du kan skabe mere opbevaringsplads på dit badeværelse ved hjælp af dette skab.&lt;/li&gt;&lt;li&gt;Stilfuldt design: De rene linjer og det elegante design får dette opbevaringsskab til at passe perfekt ind i dit badeværelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til brug i væggen er ikke inkluderet. Brug kun skruer og rawlplugs, der passer til dine vægge. Hvis du er usikker, så søg professionel rådgivning. Læs og følg hvert trin i instruktionen omhyggeligt.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel :&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det medfølgende vægmonteringsudstyr anvendes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Røget egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 25 x 26,5 x 170 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li class="legalDocument"&gt;Legal Documents:&lt;br/&gt;&lt;p&gt;&lt;span&gt;Flere detaljer om, hvordan du forhindrer, at dine m&amp;oslash;bler tipper, kan findes &lt;strong&gt;&lt;span style="text-decoration: underline;"&gt;&lt;a title="https://bit.ly/3yHcZMv" href="https://bit.ly/3yHcZMv" target="_blank"&gt;her&lt;/a&gt;&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431240_m_en_hd_1.jpg, https://vdxl.im/8721158431240_a_en_hd_1.jpg, https://vdxl.im/8721158431240_g_en_hd_1.jpg, https://vdxl.im/8721158431240_g_en_hd_2.jpg, https://vdxl.im/8721158431240_g_en_hd_3.jpg, https://vdxl.im/8721158431240_g_en_hd_4.jpg, https://vdxl.im/8721158431240_g_en_hd_5.jpg, https://vdxl.im/8721158431240_g_en_hd_6.jpg, https://vdxl.im/8721158431240_g_en_hd_7.jpg, https://vdxl.im/8721158431240_g_en_hd_8.jpg, https://vdxl.im/8721158431240_g_en_hd_9.jpg, https://vdxl.im/8721158431240_g_en_hd_10.jpg, https://vdxl.im/8721158431240_g_en_hd_11.jpg, https://vdxl.im/8721158431240_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8720286956373_m_en_hd_1.jpg, https://vdxl.im/8720286956373_a_en_hd_1.jpg, https://vdxl.im/8720286956373_g_en_hd_1.jpg, https://vdxl.im/8720286956373_g_en_hd_2.jpg, https://vdxl.im/8720286956373_g_en_hd_3.jpg, https://vdxl.im/8720286956373_g_en_hd_4.jpg, https://vdxl.im/8720286956373_g_en_hd_5.jpg, https://vdxl.im/8720286956373_g_en_hd_6.jpg, https://vdxl.im/8720286956373_g_en_hd_7.jpg, https://res.cloudinary.com/vdxl-test/image/upload/v1663923940/test/Image%20with%20Text/8888%20engineered%20wood/DKengineeredwood.png</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3726,26 +3638,18 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Sort</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
+          <t>Røget eg</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>badevaerelsesskab-25x26-5x170-cm-konstrueret-trae</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3755,25 +3659,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3310528</t>
+          <t>856652</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8721158431264</t>
+          <t>8721158440051</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3149</v>
+        <v>619</v>
       </c>
       <c r="F29" t="n">
-        <v>4199</v>
+        <v>829</v>
       </c>
       <c r="G29" t="n">
-        <v>1838</v>
+        <v>358</v>
       </c>
       <c r="H29" t="n">
-        <v>40250</v>
+        <v>18950</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3791,7 +3695,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -3810,12 +3714,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431264_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158440051_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3310528</t>
+          <t>856652</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3825,17 +3729,17 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3310528</t>
+          <t>856652</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Gråbrun&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette badeværelsesskab er et glimrende valg til dit badeværelse, da det gør det ryddeligt og organiseret!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;Rigelig opbevaringsplads: Dette badeværelsesopbevaringsskab tilbyder rigelig opbevaringsplads til at holde dine væsentlige ting velorganiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Praktiske håndtag: Badeskabet kommer med håndtag, der giver et behageligt greb, der hjælper dig med at åbne og lukke badeskabet nemt og samtidig tilføje ekstra skønhed.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Badeværelsesskabet er nemt at rengøre med en fugtig klud takket være den glatte overflade, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: antikt træ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 25 x 25 x 170 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maks. bæreevne (i alt): 60 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431264_m_en_hd_1.jpg, https://vdxl.im/8721158431264_a_en_hd_1.jpg, https://vdxl.im/8721158431264_g_en_hd_1.jpg, https://vdxl.im/8721158431264_g_en_hd_2.jpg, https://vdxl.im/8721158431264_g_en_hd_3.jpg, https://vdxl.im/8721158431264_g_en_hd_4.jpg, https://vdxl.im/8721158431264_g_en_hd_5.jpg, https://vdxl.im/8721158431264_g_en_hd_6.jpg, https://vdxl.im/8721158431264_g_en_hd_7.jpg, https://vdxl.im/8721158431264_g_en_hd_8.jpg, https://vdxl.im/8721158431264_g_en_hd_9.jpg, https://vdxl.im/8721158431264_g_en_hd_10.jpg, https://vdxl.im/8721158431264_g_en_hd_11.jpg, https://vdxl.im/8721158431264_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721158440051_m_en_hd_1.jpg, https://vdxl.im/8721158440051_a_en_hd_1.jpg, https://vdxl.im/8721158440051_g_en_hd_1.jpg, https://vdxl.im/8721158440051_g_en_hd_2.jpg, https://vdxl.im/8721158440051_g_en_hd_3.jpg, https://vdxl.im/8721158440051_g_en_hd_4.jpg, https://vdxl.im/8721158440051_g_en_hd_5.jpg, https://vdxl.im/8721158440051_g_en_hd_6.jpg, https://vdxl.im/8721158440051_g_en_hd_7.jpg, https://vdxl.im/8721158440051_g_en_hd_8.jpg, https://vdxl.im/8721158440051_g_en_hd_9.jpg</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3845,26 +3749,18 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Gråbrun</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
+          <t>Gammelt træ</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>badevaerelsesskab-25x26-5x170-cm-konstrueret-trae</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3874,25 +3770,25 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3310530</t>
+          <t>856653</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8721158431288</t>
+          <t>8721158440068</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3119</v>
+        <v>609</v>
       </c>
       <c r="F30" t="n">
-        <v>4159</v>
+        <v>819</v>
       </c>
       <c r="G30" t="n">
-        <v>1822</v>
+        <v>357</v>
       </c>
       <c r="H30" t="n">
-        <v>40250</v>
+        <v>18950</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3910,7 +3806,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -3929,12 +3825,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431288_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158440068_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3310530</t>
+          <t>856653</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3944,17 +3840,17 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>3310530</t>
+          <t>856653</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 208 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 190 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Blå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette badeværelsesskab er et glimrende valg til dit badeværelse, da det gør det ryddeligt og organiseret!&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Stabilt og slidstærkt materiale: Konstrueret træ er et slidstærkt og stabilt materiale med en glat overflade. Det er fugtafvisende, og det vrider eller splintrer ikke, så det er et pålideligt valg til forskellige projekter.&lt;/li&gt;&lt;li&gt;Rigelig opbevaringsplads: Dette badeværelsesopbevaringsskab tilbyder rigelig opbevaringsplads til at holde dine væsentlige ting velorganiseret og inden for rækkevidde.&lt;/li&gt;&lt;li&gt;Praktiske håndtag: Badeskabet kommer med håndtag, der giver et behageligt greb, der hjælper dig med at åbne og lukke badeskabet nemt og samtidig tilføje ekstra skønhed.&lt;/li&gt;&lt;li&gt;Nem vedligeholdelse: Badeværelsesskabet er nemt at rengøre med en fugtig klud takket være den glatte overflade, og det kræver ikke meget vedligeholdelse.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;For at undgå, at produktet vælter, skal det anvendes med det medfølgende vægmonteringsudstyr.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Skruer og rawlplugs til væggen medfølger ikke. Vi anbefaler, at du anvender skruer og rawlplugs, der passer til dine vægge. Hvis du er i tvivl, skal du søge professionel rådgivning. Læs og følg hvert trin i instruktionerne.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Egetræ&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 25 x 25 x 170 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Maks. bæreevne (i alt): 60 kg&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431288_m_en_hd_1.jpg, https://vdxl.im/8721158431288_a_en_hd_1.jpg, https://vdxl.im/8721158431288_g_en_hd_1.jpg, https://vdxl.im/8721158431288_g_en_hd_2.jpg, https://vdxl.im/8721158431288_g_en_hd_3.jpg, https://vdxl.im/8721158431288_g_en_hd_4.jpg, https://vdxl.im/8721158431288_g_en_hd_5.jpg, https://vdxl.im/8721158431288_g_en_hd_6.jpg, https://vdxl.im/8721158431288_g_en_hd_7.jpg, https://vdxl.im/8721158431288_g_en_hd_8.jpg, https://vdxl.im/8721158431288_g_en_hd_9.jpg, https://vdxl.im/8721158431288_g_en_hd_10.jpg, https://vdxl.im/8721158431288_g_en_hd_11.jpg, https://vdxl.im/8721158431288_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721158440068_m_en_hd_1.jpg, https://vdxl.im/8721158440068_a_en_hd_1.jpg, https://vdxl.im/8721158440068_g_en_hd_1.jpg, https://vdxl.im/8721158440068_g_en_hd_2.jpg, https://vdxl.im/8721158440068_g_en_hd_3.jpg, https://vdxl.im/8721158440068_g_en_hd_4.jpg, https://vdxl.im/8721158440068_g_en_hd_5.jpg, https://vdxl.im/8721158440068_g_en_hd_6.jpg, https://vdxl.im/8721158440068_g_en_hd_7.jpg, https://vdxl.im/8721158440068_g_en_hd_8.jpg, https://vdxl.im/8721158440068_g_en_hd_9.jpg</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3964,26 +3860,18 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Blå</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>140 x 190 cm</t>
-        </is>
-      </c>
+          <t>artisan eg</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>badevaerelsesskab-25x26-5x170-cm-konstrueret-trae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3993,25 +3881,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3310531</t>
+          <t>862669</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8721158431295</t>
+          <t>8721158770684</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3429</v>
+        <v>549</v>
       </c>
       <c r="F31" t="n">
-        <v>4579</v>
+        <v>739</v>
       </c>
       <c r="G31" t="n">
-        <v>2002</v>
+        <v>320</v>
       </c>
       <c r="H31" t="n">
-        <v>41150</v>
+        <v>17600</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -4029,7 +3917,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4048,12 +3936,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431295_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721158770684_mo-im_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3310531</t>
+          <t>862669</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4063,17 +3951,17 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3310531</t>
+          <t>862669</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Det her moderne badevægskab er en fantastisk blanding af stil og funktion, der kan pifte ethvert badeværelse op. Med sine slanke, rektangulære former og en højde på 170 cm fungerer det som et centralt element, der kombinerer stil med praktisk brug. Det minimalistiske design med rene linjer gør det perfekt til moderne rum. Dets fritstående konstruktion giver dig mulighed for at placere det, hvor det passer bedst, og det holdbare træ sikrer, at det ser godt ud i lang tid.&lt;/p&gt; &lt;ul&gt;&lt;li&gt;&lt;b&gt;Konstruktion i konstrueret træ:&lt;/b&gt; Skabet er lavet af konstrueret træ, som er valgt for sin styrke og evne til at klare fugtigheden på badeværelset. Det har en glat overflade, der passer perfekt til det moderne look og sikrer, at det holder sig flot i lang tid.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Godt med opbevaringsplads:&lt;/b&gt; Skabet har masser af plads med hylder, skuffer og hængseldøre, så du kan holde styr på alle dine badeværelsesting. Uanset om det er toiletartikler eller håndklæder, hjælper det med at holde alt pænt og ryddeligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Moderne designelementer:&lt;/b&gt; Med stilfulde stålknopper og hængseldøre har skabet et moderne udtryk. De sølvfarvede håndtag giver et luksuriøst touch, samtidig med at de er praktiske. Det fokus på detaljerne gør, at det er både smukt og brugervenligt.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Praktisk og fleksible:&lt;/b&gt; Skabet er super alsidigt, lige meget om det er til familie- eller gæstebadeværelset. Det tilpasser sig nemt til forskellige rum og kan ændres alt efter behov. Den rektangulære form gør det let at finde plads til det.&lt;/li&gt;&lt;li&gt;&lt;b&gt;Nem at vedligeholde:&lt;/b&gt; Det er let at holde skabet flot. Tør det bare af med en fugtig klud, så holder det sig som nyt. Med lidt pleje kan det holde sig pænt i lang tid og bidrage til et velholdt badeværelse.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Sort eg&lt;/li&gt;&lt;li&gt;Materiale: Konstrueret træ&lt;/li&gt;&lt;li&gt;Samlede dimensioner: 25 x 25 x 170 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Vægt: 16,1 kg&lt;/li&gt;&lt;li&gt;Rigelig opbevaring&lt;/li&gt;&lt;li&gt;Med skuffe&lt;/li&gt;&lt;li&gt;Med 2  hylder&lt;/li&gt;&lt;li&gt;Rammemateriale: Træ&lt;/li&gt;&lt;li&gt;Med 2 døre&lt;/li&gt;&lt;li&gt;Indendørs / udendørs: Kun til indendørs brug&lt;/li&gt;&lt;li&gt;Leveringsindhold:&lt;/li&gt;&lt;li&gt;1 x Badeværelsesskab&lt;/li&gt;&lt;li&gt;Forsamling krævet: Ja&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431295_m_en_hd_1.jpg, https://vdxl.im/8721158431295_a_en_hd_1.jpg, https://vdxl.im/8721158431295_g_en_hd_1.jpg, https://vdxl.im/8721158431295_g_en_hd_2.jpg, https://vdxl.im/8721158431295_g_en_hd_3.jpg, https://vdxl.im/8721158431295_g_en_hd_4.jpg, https://vdxl.im/8721158431295_g_en_hd_5.jpg, https://vdxl.im/8721158431295_g_en_hd_6.jpg, https://vdxl.im/8721158431295_g_en_hd_7.jpg, https://vdxl.im/8721158431295_g_en_hd_8.jpg, https://vdxl.im/8721158431295_g_en_hd_9.jpg, https://vdxl.im/8721158431295_g_en_hd_10.jpg, https://vdxl.im/8721158431295_g_en_hd_11.jpg, https://vdxl.im/8721158431295_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721158770684_mo-im_en_hd_1.jpg, https://vdxl.im/8721158770684_wbg-an-m_en_hd_1.jpg, https://vdxl.im/8721158770684_wbg-mo_en_hd_1.jpg, https://vdxl.im/8721158770684_mo-im_en_hd_2.jpg, https://vdxl.im/8721158770684_wbg-an_en_hd_2.jpg, https://vdxl.im/8721158770684_wbg-ba_en_hd_3.jpg, https://vdxl.im/8721158770684_wbg-fr_en_hd_4.jpg, https://vdxl.im/8721158770684_wbg-si_en_hd_5.jpg, https://vdxl.im/8721158770684_detail_en_hd_1.jpg, https://vdxl.im/8721158770684_wbg-ma_en_hd_1.jpg, https://vdxl.im/8721158770684_wbg-siz_en_hd_1.jpg, https://vdxl.im/8721158770684_wbg-com_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4083,26 +3971,18 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Lysegrå</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>140 x 200 cm</t>
-        </is>
-      </c>
+          <t>Sort eg</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>sengebord-molde-40x35x48-cm-massivt-fyrretrae</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4112,25 +3992,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3310532</t>
+          <t>350496</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8721158431301</t>
+          <t>8720845541835</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3469</v>
+        <v>799</v>
       </c>
       <c r="F32" t="n">
-        <v>4629</v>
+        <v>1069</v>
       </c>
       <c r="G32" t="n">
-        <v>2025</v>
+        <v>464</v>
       </c>
       <c r="H32" t="n">
-        <v>41150</v>
+        <v>7800</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -4148,7 +4028,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4167,12 +4047,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431301_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8720845541835_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3310532</t>
+          <t>350496</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -4182,17 +4062,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>3310532</t>
+          <t>350496</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Dette trendy sengebord i træ har en skandinavisk charme, og det er designet til at forskønne dit interiør.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Massivt fyrretræ: Massivt fyrretræ er et smukt og naturligt materiale. Fyrretræ har lige åremønstre, og knuderne giver materialet sit karakteristiske, rustikke udseende.&lt;/li&gt;&lt;li&gt;UV-lakering: UV-lakering er en speciel type lakering, der afsluttes med en ultraviolet tørremaskine. Det skaber en mere levende, luksuriøs og taktil finish sammenlignet med lakeringer uden UV.&lt;/li&gt;&lt;li&gt;Stabil ramme: Trærammen sikrer robusthed og stabilitet.&lt;/li&gt;&lt;li&gt;God opbevaringsplads: Natbordet har 2 skuffer. De rummelige skuffer giver dig mulighed for at holde orden i tingene.&lt;/li&gt;&lt;li&gt;Robust top: Den robuste top er ideel til fremvisning af pyntegenstande, billedrammer eller potteplanter.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Bemærk:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Hvert produkt kommer med en brugermanual for nem montering.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale: Massivt fyrretræ med UV-lakering, konstrueret træ&lt;/li&gt;&lt;li&gt;Mål: 40 x 35 x 48 cm (B x D x H)&lt;/li&gt;&lt;li&gt;Møbelserie: MOLDE&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431301_m_en_hd_1.jpg, https://vdxl.im/8721158431301_a_en_hd_1.jpg, https://vdxl.im/8721158431301_g_en_hd_1.jpg, https://vdxl.im/8721158431301_g_en_hd_2.jpg, https://vdxl.im/8721158431301_g_en_hd_3.jpg, https://vdxl.im/8721158431301_g_en_hd_4.jpg, https://vdxl.im/8721158431301_g_en_hd_5.jpg, https://vdxl.im/8721158431301_g_en_hd_6.jpg, https://vdxl.im/8721158431301_g_en_hd_7.jpg, https://vdxl.im/8721158431301_g_en_hd_8.jpg, https://vdxl.im/8721158431301_g_en_hd_9.jpg, https://vdxl.im/8721158431301_g_en_hd_10.jpg, https://vdxl.im/8721158431301_g_en_hd_11.jpg, https://vdxl.im/8721158431301_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8720845541835_m_en_hd_1.jpg, https://vdxl.im/8720845541835_a_en_hd_1.jpg, https://vdxl.im/8720845541835_g_en_hd_1.jpg, https://vdxl.im/8720845541835_g_en_hd_2.jpg, https://vdxl.im/8720845541835_g_en_hd_3.jpg, https://vdxl.im/8720845541835_g_en_hd_4.jpg, https://vdxl.im/8720845541835_g_en_hd_5.jpg, https://vdxl.im/8720845541835_g_en_hd_6.jpg</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -4202,26 +4082,18 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Mørkegrå</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Størrelse</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>140 x 200 cm</t>
-        </is>
-      </c>
+          <t>Hvid</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>gulvtaeppe-oviedo-kort-luv</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4231,25 +4103,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3310533</t>
+          <t>375467</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8721158431318</t>
+          <t>8721012230682</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3639</v>
+        <v>389</v>
       </c>
       <c r="F33" t="n">
-        <v>4859</v>
+        <v>559</v>
       </c>
       <c r="G33" t="n">
-        <v>2125</v>
+        <v>229</v>
       </c>
       <c r="H33" t="n">
-        <v>41150</v>
+        <v>3180</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -4267,7 +4139,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -4286,12 +4158,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431318_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721012230682_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3310533</t>
+          <t>375467</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4301,17 +4173,17 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>3310533</t>
+          <t>375467</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 145 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 140 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Sort&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 140 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Tilføj komfort og stil til din boligindretning med dette bløde tæppe.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbar og sikker: Dette tæppe er lavet af 100% polyester og er testet for skadelige stoffer i henhold til STANDARD 100 by OEKO-TEX.&lt;/li&gt;&lt;li&gt;Superblød tekstur: Dette gulvtæppe har bløde, tætte og flade luv, der giver det et Teddy-look og en hyggelig, varm fornemmelse.&lt;/li&gt;&lt;li&gt;Nem at opbevare: Det luftige tæppe er foldbart og kan rulles sammen for nem opbevaring og transport.&lt;/li&gt;&lt;li&gt;Bred anvendelsesmuligheder: Dette moderne tæppe er velegnet til forskellige indendørs rum med gulvvarme, herunder stuer, soveværelser, gange og kontorer.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Tæppet er foldet i en kasse for nem transport. Giv produktet lidt tid til at glatte og flade ud.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Må ikke vaskes, bleges, tørretumbles eller stryges.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Materiale: 100 % polyester&lt;/li&gt;&lt;li&gt;Mål: 120 x 120 cm (B x L)&lt;/li&gt;&lt;li&gt;Luvhøjde: 12,5 mm&lt;/li&gt;&lt;li&gt;Samlet vægt: 1800 g/m²&lt;/li&gt;&lt;li&gt;Velegnet til gulve med gulvvarme&lt;/li&gt;&lt;li&gt;Testet mod skadelige stoffer i henhold til STANDARD 100 af OEKO-TEX&lt;/li&gt;&lt;li&gt;Kollektion: OVIEDO&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431318_m_en_hd_1.jpg, https://vdxl.im/8721158431318_a_en_hd_1.jpg, https://vdxl.im/8721158431318_g_en_hd_1.jpg, https://vdxl.im/8721158431318_g_en_hd_2.jpg, https://vdxl.im/8721158431318_g_en_hd_3.jpg, https://vdxl.im/8721158431318_g_en_hd_4.jpg, https://vdxl.im/8721158431318_g_en_hd_5.jpg, https://vdxl.im/8721158431318_g_en_hd_6.jpg, https://vdxl.im/8721158431318_g_en_hd_7.jpg, https://vdxl.im/8721158431318_g_en_hd_8.jpg, https://vdxl.im/8721158431318_g_en_hd_9.jpg, https://vdxl.im/8721158431318_g_en_hd_10.jpg, https://vdxl.im/8721158431318_g_en_hd_11.jpg, https://vdxl.im/8721158431318_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721012230682_m_en_hd_1.jpg, https://vdxl.im/8721012230682_a_en_hd_1.jpg, https://vdxl.im/8721012230682_g_en_hd_1.jpg, https://vdxl.im/8721012230682_g_en_hd_2.jpg, https://vdxl.im/8721012230682_g_en_hd_3.jpg, https://vdxl.im/8721012230682_g_en_hd_4.jpg, https://vdxl.im/8721012230682_g_en_hd_5.jpg, https://vdxl.im/8721012230682_g_en_hd_6.jpg, https://vdxl.im/8721012230682_g_en_hd_7.jpg, https://vdxl.im/8721012230682_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4321,7 +4193,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Sort</t>
+          <t>Antracitgrå</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4331,7 +4203,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>140 x 200 cm</t>
+          <t>120 x 120 cm</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr"/>
@@ -4340,7 +4212,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>gulvtaeppe-oviedo-kort-luv</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4350,25 +4222,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3310545</t>
+          <t>375472</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8721158431431</t>
+          <t>8721012230736</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4259</v>
+        <v>829</v>
       </c>
       <c r="F34" t="n">
-        <v>5679</v>
+        <v>1189</v>
       </c>
       <c r="G34" t="n">
-        <v>2491</v>
+        <v>486</v>
       </c>
       <c r="H34" t="n">
-        <v>47750</v>
+        <v>8530</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -4386,7 +4258,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -4405,12 +4277,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431431_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721012230736_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>3310545</t>
+          <t>375472</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4420,17 +4292,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>3310545</t>
+          <t>375472</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 185 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Lysegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 180 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Tilføj komfort og stil til din boligindretning med dette bløde tæppe.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbar og sikker: Dette tæppe er lavet af 100% polyester og er testet for skadelige stoffer i henhold til STANDARD 100 by OEKO-TEX.&lt;/li&gt;&lt;li&gt;Superblød tekstur: Dette gulvtæppe har bløde, tætte og flade luv, der giver det et Teddy-look og en hyggelig, varm fornemmelse.&lt;/li&gt;&lt;li&gt;Nem at opbevare: Det luftige tæppe er foldbart og kan rulles sammen for nem opbevaring og transport.&lt;/li&gt;&lt;li&gt;Bred anvendelsesmuligheder: Dette moderne tæppe er velegnet til forskellige indendørs rum med gulvvarme, herunder stuer, soveværelser, gange og kontorer.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Tæppet er foldet i en kasse for nem transport. Giv produktet lidt tid til at glatte og flade ud.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Må ikke vaskes, bleges, tørretumbles eller stryges.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Materiale: 100 % polyester&lt;/li&gt;&lt;li&gt;Mål: 200 x 200 cm (B x L)&lt;/li&gt;&lt;li&gt;Luvhøjde: 12,5 mm&lt;/li&gt;&lt;li&gt;Samlet vægt: 1800 g/m²&lt;/li&gt;&lt;li&gt;Velegnet til gulve med gulvvarme&lt;/li&gt;&lt;li&gt;Testet mod skadelige stoffer i henhold til STANDARD 100 af OEKO-TEX&lt;/li&gt;&lt;li&gt;Kollektion: OVIEDO&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431431_m_en_hd_1.jpg, https://vdxl.im/8721158431431_a_en_hd_1.jpg, https://vdxl.im/8721158431431_g_en_hd_1.jpg, https://vdxl.im/8721158431431_g_en_hd_2.jpg, https://vdxl.im/8721158431431_g_en_hd_3.jpg, https://vdxl.im/8721158431431_g_en_hd_4.jpg, https://vdxl.im/8721158431431_g_en_hd_5.jpg, https://vdxl.im/8721158431431_g_en_hd_6.jpg, https://vdxl.im/8721158431431_g_en_hd_7.jpg, https://vdxl.im/8721158431431_g_en_hd_8.jpg, https://vdxl.im/8721158431431_g_en_hd_9.jpg, https://vdxl.im/8721158431431_g_en_hd_10.jpg, https://vdxl.im/8721158431431_g_en_hd_11.jpg, https://vdxl.im/8721158431431_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721012230736_m_en_hd_1.jpg, https://vdxl.im/8721012230736_a_en_hd_1.jpg, https://vdxl.im/8721012230736_g_en_hd_1.jpg, https://vdxl.im/8721012230736_g_en_hd_2.jpg, https://vdxl.im/8721012230736_g_en_hd_3.jpg, https://vdxl.im/8721012230736_g_en_hd_4.jpg, https://vdxl.im/8721012230736_g_en_hd_5.jpg, https://vdxl.im/8721012230736_g_en_hd_6.jpg, https://vdxl.im/8721012230736_g_en_hd_7.jpg, https://vdxl.im/8721012230736_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4440,7 +4312,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Lysegrå</t>
+          <t>Antracitgrå</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4450,7 +4322,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>180 x 200 cm</t>
+          <t>200 x 200 cm</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr"/>
@@ -4459,7 +4331,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>gulvtaeppe-oviedo-kort-luv</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4469,25 +4341,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3310546</t>
+          <t>375474</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8721158431448</t>
+          <t>8721012230750</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3839</v>
+        <v>1319</v>
       </c>
       <c r="F35" t="n">
-        <v>5119</v>
+        <v>1889</v>
       </c>
       <c r="G35" t="n">
-        <v>2245</v>
+        <v>775</v>
       </c>
       <c r="H35" t="n">
-        <v>47750</v>
+        <v>11640</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -4505,7 +4377,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -4524,12 +4396,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431448_m_en_hd_1.jpg</t>
+          <t>https://vdxl.im/8721012230750_m_en_hd_1.jpg</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3310546</t>
+          <t>375474</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4539,17 +4411,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>3310546</t>
+          <t>375474</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Få bedre søvn ved hjælp af denne seng med madras! Den er et glimrende supplement til ethvert soveværelse.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Blødt og holdbart materiale: Polyesterstof er både blødt, åndbart og slidstærkt, så det giver ultimativ komfort.&lt;/li&gt;&lt;li&gt;Skummadras: Denne madras har et skumlag, der former sig efter din krop, aflaster trykket på følsomme områder såsom nakke, skuldre, ryg og hofter. Den absorberer også stød og reducerer støj fra bevægelser om natten.&lt;/li&gt;&lt;li&gt;Der kræves ingen springmadras: Sengerammen har en lamelbund, der giver fremragende støtte og åndbarhed til din madras, hvilket eliminerer behovet for en boksmadras.&lt;/li&gt;&lt;li&gt;Fremragende støtte: Gavlpuden er fyldt med PP-fibre for ultrablød og optimal komfort. Den tilbyder fremragende rygstøtte, mens du sidder i sengen og læser eller ser fjernsyn&lt;/li&gt;&lt;li&gt;Stabile og slidstærke ben: Denne sengeramme understøttes af robuste ben, hvilket giver stabilitet,, sikkerhed og fasthed.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Af hygiejniske årsager kan madrassen ikke returneres, hvis emballagen åbnes eller fjernes.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sengestel:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester), metal, krydsfiner, konstrueret træ&lt;/li&gt;&lt;li&gt;Produktmål: 218 x 185 x 74,5 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Madras:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Hvid&lt;/li&gt;&lt;li&gt;Materiale, betræk: Strikket stof&lt;/li&gt;&lt;li&gt;Materiale, fyld: 22D PU-skum&lt;/li&gt;&lt;li&gt;Hårdhed: H2 og H3&lt;/li&gt;&lt;li&gt;Mål: 180 x 200 x 17 cm (B x L x H)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Gavlpude:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Farve: Mørkegrå&lt;/li&gt;&lt;li&gt;Materiale: Stof (100 % polyester)&lt;/li&gt;&lt;li&gt;Materiale, fyld: PP-fibre&lt;/li&gt;&lt;li&gt;Mål: 180 x 3 x 45 cm (L x B x H)&lt;/li&gt;&lt;li&gt;Rangenavn: Hanko&lt;/li&gt;&lt;li&gt;Montering påkrævet: Ja&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pakken indeholder:&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;1 x sengeramme&lt;/li&gt;&lt;li&gt;1 x madras&lt;/li&gt;&lt;li&gt;1 x gavlpude&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;Tilføj komfort og stil til din boligindretning med dette bløde tæppe.&lt;/p&gt;&lt;p&gt; &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Holdbar og sikker: Dette tæppe er lavet af 100% polyester og er testet for skadelige stoffer i henhold til STANDARD 100 by OEKO-TEX.&lt;/li&gt;&lt;li&gt;Superblød tekstur: Dette gulvtæppe har bløde, tætte og flade luv, der giver det et Teddy-look og en hyggelig, varm fornemmelse.&lt;/li&gt;&lt;li&gt;Nem at opbevare: Det luftige tæppe er foldbart og kan rulles sammen for nem opbevaring og transport.&lt;/li&gt;&lt;li&gt;Bred anvendelsesmuligheder: Dette moderne tæppe er velegnet til forskellige indendørs rum med gulvvarme, herunder stuer, soveværelser, gange og kontorer.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt; &lt;/p&gt;&lt;p&gt;Godt at vide:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Tæppet er foldet i en kasse for nem transport. Giv produktet lidt tid til at glatte og flade ud.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Advarsel:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Må ikke vaskes, bleges, tørretumbles eller stryges.&lt;/li&gt;&lt;/ul&gt; &lt;ul&gt;&lt;li&gt;Farve: Antracitgrå&lt;/li&gt;&lt;li&gt;Materiale: 100 % polyester&lt;/li&gt;&lt;li&gt;Mål: 240 x 240 cm (B x L)&lt;/li&gt;&lt;li&gt;Luvhøjde: 12,5 mm&lt;/li&gt;&lt;li&gt;Samlet vægt: 1800 g/m²&lt;/li&gt;&lt;li&gt;Velegnet til gulve med gulvvarme&lt;/li&gt;&lt;li&gt;Testet mod skadelige stoffer i henhold til STANDARD 100 af OEKO-TEX&lt;/li&gt;&lt;li&gt;Kollektion: OVIEDO&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://vdxl.im/8721158431448_m_en_hd_1.jpg, https://vdxl.im/8721158431448_a_en_hd_1.jpg, https://vdxl.im/8721158431448_g_en_hd_1.jpg, https://vdxl.im/8721158431448_g_en_hd_2.jpg, https://vdxl.im/8721158431448_g_en_hd_3.jpg, https://vdxl.im/8721158431448_g_en_hd_4.jpg, https://vdxl.im/8721158431448_g_en_hd_5.jpg, https://vdxl.im/8721158431448_g_en_hd_6.jpg, https://vdxl.im/8721158431448_g_en_hd_7.jpg, https://vdxl.im/8721158431448_g_en_hd_8.jpg, https://vdxl.im/8721158431448_g_en_hd_9.jpg, https://vdxl.im/8721158431448_g_en_hd_10.jpg, https://vdxl.im/8721158431448_g_en_hd_11.jpg, https://vdxl.im/8721158431448_g_en_hd_12.jpg</t>
+          <t>https://vdxl.im/8721012230750_m_en_hd_1.jpg, https://vdxl.im/8721012230750_a_en_hd_1.jpg, https://vdxl.im/8721012230750_g_en_hd_1.jpg, https://vdxl.im/8721012230750_g_en_hd_2.jpg, https://vdxl.im/8721012230750_g_en_hd_3.jpg, https://vdxl.im/8721012230750_g_en_hd_4.jpg, https://vdxl.im/8721012230750_g_en_hd_5.jpg, https://vdxl.im/8721012230750_g_en_hd_6.jpg, https://vdxl.im/8721012230750_g_en_hd_7.jpg, https://vdxl.im/8721012230750_g_en_hd_8.jpg</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4559,7 +4431,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Mørkegrå</t>
+          <t>Antracitgrå</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4569,7 +4441,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>180 x 200 cm</t>
+          <t>240 x 240 cm</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr"/>
@@ -4578,7 +4450,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>seng-med-madras-stof-2</t>
+          <t>gulvtaeppe-oviedo-kort-luv</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4588,25 +4460,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3310552</t>
+          <t>375475</t>
         </is>
       </c>
       <c r="D36" t="inlineSt